--- a/data/ANET_data.xlsx
+++ b/data/ANET_data.xlsx
@@ -10653,7 +10653,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-07 03:09:15</t>
+          <t>2026-09-08 08:53:08</t>
         </is>
       </c>
     </row>

--- a/data/ANET_data.xlsx
+++ b/data/ANET_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45905</v>
+        <v>45909</v>
       </c>
       <c r="B2" t="n">
-        <v>144.1300048828125</v>
+        <v>140.9700012207031</v>
       </c>
       <c r="C2" t="n">
-        <v>145.4600067138672</v>
+        <v>142.8809967041016</v>
       </c>
       <c r="D2" t="n">
-        <v>140.25</v>
+        <v>139.5099945068359</v>
       </c>
       <c r="E2" t="n">
-        <v>142.8500061035156</v>
+        <v>141.9100036621094</v>
       </c>
       <c r="F2" t="n">
-        <v>9567500</v>
+        <v>6158500</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45908</v>
+        <v>45910</v>
       </c>
       <c r="B3" t="n">
-        <v>143.8000030517578</v>
+        <v>145.5599975585938</v>
       </c>
       <c r="C3" t="n">
-        <v>144.1000061035156</v>
+        <v>151.7100067138672</v>
       </c>
       <c r="D3" t="n">
-        <v>139.8399963378906</v>
+        <v>144.8999938964844</v>
       </c>
       <c r="E3" t="n">
-        <v>140.0099945068359</v>
+        <v>150.7200012207031</v>
       </c>
       <c r="F3" t="n">
-        <v>7925500</v>
+        <v>19772500</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="B4" t="n">
-        <v>140.9700012207031</v>
+        <v>151.9900054931641</v>
       </c>
       <c r="C4" t="n">
-        <v>142.8809967041016</v>
+        <v>156.3200073242188</v>
       </c>
       <c r="D4" t="n">
-        <v>139.5099945068359</v>
+        <v>150.3600006103516</v>
       </c>
       <c r="E4" t="n">
-        <v>141.9100036621094</v>
+        <v>153.0399932861328</v>
       </c>
       <c r="F4" t="n">
-        <v>6158500</v>
+        <v>13666200</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45910</v>
+        <v>45912</v>
       </c>
       <c r="B5" t="n">
-        <v>145.5599975585938</v>
+        <v>149.1799926757812</v>
       </c>
       <c r="C5" t="n">
-        <v>151.7100067138672</v>
+        <v>149.4700012207031</v>
       </c>
       <c r="D5" t="n">
-        <v>144.8999938964844</v>
+        <v>139.0200042724609</v>
       </c>
       <c r="E5" t="n">
-        <v>150.7200012207031</v>
+        <v>139.3899993896484</v>
       </c>
       <c r="F5" t="n">
-        <v>19772500</v>
+        <v>17920400</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45911</v>
+        <v>45915</v>
       </c>
       <c r="B6" t="n">
-        <v>151.9900054931641</v>
+        <v>139.6000061035156</v>
       </c>
       <c r="C6" t="n">
-        <v>156.3200073242188</v>
+        <v>146.8999938964844</v>
       </c>
       <c r="D6" t="n">
-        <v>150.3600006103516</v>
+        <v>139.1699981689453</v>
       </c>
       <c r="E6" t="n">
-        <v>153.0399932861328</v>
+        <v>145.4299926757812</v>
       </c>
       <c r="F6" t="n">
-        <v>13666200</v>
+        <v>12140800</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45912</v>
+        <v>45916</v>
       </c>
       <c r="B7" t="n">
-        <v>149.1799926757812</v>
+        <v>145.2599945068359</v>
       </c>
       <c r="C7" t="n">
-        <v>149.4700012207031</v>
+        <v>147.3699951171875</v>
       </c>
       <c r="D7" t="n">
-        <v>139.0200042724609</v>
+        <v>141</v>
       </c>
       <c r="E7" t="n">
-        <v>139.3899993896484</v>
+        <v>142.1600036621094</v>
       </c>
       <c r="F7" t="n">
-        <v>17920400</v>
+        <v>9382400</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B8" t="n">
-        <v>139.6000061035156</v>
+        <v>142.6349945068359</v>
       </c>
       <c r="C8" t="n">
-        <v>146.8999938964844</v>
+        <v>143.4250030517578</v>
       </c>
       <c r="D8" t="n">
-        <v>139.1699981689453</v>
+        <v>138.5</v>
       </c>
       <c r="E8" t="n">
-        <v>145.4299926757812</v>
+        <v>142.8399963378906</v>
       </c>
       <c r="F8" t="n">
-        <v>12140800</v>
+        <v>8295400</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B9" t="n">
-        <v>145.2599945068359</v>
+        <v>144</v>
       </c>
       <c r="C9" t="n">
-        <v>147.3699951171875</v>
+        <v>146.7200012207031</v>
       </c>
       <c r="D9" t="n">
-        <v>141</v>
+        <v>143.4250030517578</v>
       </c>
       <c r="E9" t="n">
-        <v>142.1600036621094</v>
+        <v>146.6600036621094</v>
       </c>
       <c r="F9" t="n">
-        <v>9382400</v>
+        <v>6939000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B10" t="n">
-        <v>142.6349945068359</v>
+        <v>148.8999938964844</v>
       </c>
       <c r="C10" t="n">
-        <v>143.4250030517578</v>
+        <v>150.25</v>
       </c>
       <c r="D10" t="n">
-        <v>138.5</v>
+        <v>146.6699981689453</v>
       </c>
       <c r="E10" t="n">
-        <v>142.8399963378906</v>
+        <v>149.6100006103516</v>
       </c>
       <c r="F10" t="n">
-        <v>8295400</v>
+        <v>17810900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B11" t="n">
-        <v>144</v>
+        <v>148.7799987792969</v>
       </c>
       <c r="C11" t="n">
-        <v>146.7200012207031</v>
+        <v>149.7100067138672</v>
       </c>
       <c r="D11" t="n">
-        <v>143.4250030517578</v>
+        <v>145.0549926757812</v>
       </c>
       <c r="E11" t="n">
-        <v>146.6600036621094</v>
+        <v>145.3999938964844</v>
       </c>
       <c r="F11" t="n">
-        <v>6939000</v>
+        <v>8675200</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B12" t="n">
-        <v>148.8999938964844</v>
+        <v>144.8600006103516</v>
       </c>
       <c r="C12" t="n">
-        <v>150.25</v>
+        <v>147.4600067138672</v>
       </c>
       <c r="D12" t="n">
-        <v>146.6699981689453</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="E12" t="n">
-        <v>149.6100006103516</v>
+        <v>144.0899963378906</v>
       </c>
       <c r="F12" t="n">
-        <v>17810900</v>
+        <v>8215500</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B13" t="n">
-        <v>148.7799987792969</v>
+        <v>144.6799926757812</v>
       </c>
       <c r="C13" t="n">
-        <v>149.7100067138672</v>
+        <v>144.6799926757812</v>
       </c>
       <c r="D13" t="n">
-        <v>145.0549926757812</v>
+        <v>141.2899932861328</v>
       </c>
       <c r="E13" t="n">
-        <v>145.3999938964844</v>
+        <v>142.6399993896484</v>
       </c>
       <c r="F13" t="n">
-        <v>8675200</v>
+        <v>7035700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B14" t="n">
-        <v>144.8600006103516</v>
+        <v>141.6900024414062</v>
       </c>
       <c r="C14" t="n">
-        <v>147.4600067138672</v>
+        <v>143.2400054931641</v>
       </c>
       <c r="D14" t="n">
-        <v>143.0200042724609</v>
+        <v>139.2299957275391</v>
       </c>
       <c r="E14" t="n">
-        <v>144.0899963378906</v>
+        <v>143.0599975585938</v>
       </c>
       <c r="F14" t="n">
-        <v>8215500</v>
+        <v>6325300</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B15" t="n">
-        <v>144.6799926757812</v>
+        <v>144.0899963378906</v>
       </c>
       <c r="C15" t="n">
-        <v>144.6799926757812</v>
+        <v>144.3999938964844</v>
       </c>
       <c r="D15" t="n">
-        <v>141.2899932861328</v>
+        <v>140.7599945068359</v>
       </c>
       <c r="E15" t="n">
-        <v>142.6399993896484</v>
+        <v>142.5</v>
       </c>
       <c r="F15" t="n">
-        <v>7035700</v>
+        <v>4867700</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B16" t="n">
-        <v>141.6900024414062</v>
+        <v>144.9199981689453</v>
       </c>
       <c r="C16" t="n">
-        <v>143.2400054931641</v>
+        <v>147.8000030517578</v>
       </c>
       <c r="D16" t="n">
-        <v>139.2299957275391</v>
+        <v>142.6199951171875</v>
       </c>
       <c r="E16" t="n">
-        <v>143.0599975585938</v>
+        <v>143.3699951171875</v>
       </c>
       <c r="F16" t="n">
-        <v>6325300</v>
+        <v>6183600</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B17" t="n">
-        <v>144.0899963378906</v>
+        <v>143.4299926757812</v>
       </c>
       <c r="C17" t="n">
-        <v>144.3999938964844</v>
+        <v>145.8399963378906</v>
       </c>
       <c r="D17" t="n">
-        <v>140.7599945068359</v>
+        <v>143.1600036621094</v>
       </c>
       <c r="E17" t="n">
-        <v>142.5</v>
+        <v>145.7100067138672</v>
       </c>
       <c r="F17" t="n">
-        <v>4867700</v>
+        <v>5828900</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B18" t="n">
-        <v>144.9199981689453</v>
+        <v>144.6499938964844</v>
       </c>
       <c r="C18" t="n">
-        <v>147.8000030517578</v>
+        <v>149.9499969482422</v>
       </c>
       <c r="D18" t="n">
-        <v>142.6199951171875</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="E18" t="n">
-        <v>143.3699951171875</v>
+        <v>149.2700042724609</v>
       </c>
       <c r="F18" t="n">
-        <v>6183600</v>
+        <v>7820700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B19" t="n">
-        <v>143.4299926757812</v>
+        <v>150</v>
       </c>
       <c r="C19" t="n">
-        <v>145.8399963378906</v>
+        <v>150.5399932861328</v>
       </c>
       <c r="D19" t="n">
-        <v>143.1600036621094</v>
+        <v>141.25</v>
       </c>
       <c r="E19" t="n">
-        <v>145.7100067138672</v>
+        <v>144.4600067138672</v>
       </c>
       <c r="F19" t="n">
-        <v>5828900</v>
+        <v>9473800</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B20" t="n">
-        <v>144.6499938964844</v>
+        <v>146.0099945068359</v>
       </c>
       <c r="C20" t="n">
-        <v>149.9499969482422</v>
+        <v>149.0899963378906</v>
       </c>
       <c r="D20" t="n">
-        <v>143.0200042724609</v>
+        <v>144.1000061035156</v>
       </c>
       <c r="E20" t="n">
-        <v>149.2700042724609</v>
+        <v>145.5</v>
       </c>
       <c r="F20" t="n">
-        <v>7820700</v>
+        <v>7178600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B21" t="n">
-        <v>150</v>
+        <v>151.6000061035156</v>
       </c>
       <c r="C21" t="n">
-        <v>150.5399932861328</v>
+        <v>153.7299957275391</v>
       </c>
       <c r="D21" t="n">
-        <v>141.25</v>
+        <v>149.5</v>
       </c>
       <c r="E21" t="n">
-        <v>144.4600067138672</v>
+        <v>149.5</v>
       </c>
       <c r="F21" t="n">
-        <v>9473800</v>
+        <v>7277600</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B22" t="n">
-        <v>146.0099945068359</v>
+        <v>150.4799957275391</v>
       </c>
       <c r="C22" t="n">
-        <v>149.0899963378906</v>
+        <v>151.5500030517578</v>
       </c>
       <c r="D22" t="n">
-        <v>144.1000061035156</v>
+        <v>143.2799987792969</v>
       </c>
       <c r="E22" t="n">
-        <v>145.5</v>
+        <v>145.2899932861328</v>
       </c>
       <c r="F22" t="n">
-        <v>7178600</v>
+        <v>7348700</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B23" t="n">
-        <v>151.6000061035156</v>
+        <v>147.9900054931641</v>
       </c>
       <c r="C23" t="n">
-        <v>153.7299957275391</v>
+        <v>158.5099945068359</v>
       </c>
       <c r="D23" t="n">
-        <v>149.5</v>
+        <v>147.4049987792969</v>
       </c>
       <c r="E23" t="n">
-        <v>149.5</v>
+        <v>157.3600006103516</v>
       </c>
       <c r="F23" t="n">
-        <v>7277600</v>
+        <v>11283400</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B24" t="n">
-        <v>150.4799957275391</v>
+        <v>157</v>
       </c>
       <c r="C24" t="n">
-        <v>151.5500030517578</v>
+        <v>159.8000030517578</v>
       </c>
       <c r="D24" t="n">
-        <v>143.2799987792969</v>
+        <v>154.6009979248047</v>
       </c>
       <c r="E24" t="n">
-        <v>145.2899932861328</v>
+        <v>158.2299957275391</v>
       </c>
       <c r="F24" t="n">
-        <v>7348700</v>
+        <v>8459900</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B25" t="n">
-        <v>147.9900054931641</v>
+        <v>159.8600006103516</v>
       </c>
       <c r="C25" t="n">
-        <v>158.5099945068359</v>
+        <v>162.6799926757812</v>
       </c>
       <c r="D25" t="n">
-        <v>147.4049987792969</v>
+        <v>153.7400054931641</v>
       </c>
       <c r="E25" t="n">
-        <v>157.3600006103516</v>
+        <v>154.1000061035156</v>
       </c>
       <c r="F25" t="n">
-        <v>11283400</v>
+        <v>10459300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B26" t="n">
-        <v>157</v>
+        <v>160.7599945068359</v>
       </c>
       <c r="C26" t="n">
-        <v>159.8000030517578</v>
+        <v>162</v>
       </c>
       <c r="D26" t="n">
-        <v>154.6009979248047</v>
+        <v>145.0899963378906</v>
       </c>
       <c r="E26" t="n">
-        <v>158.2299957275391</v>
+        <v>147.4499969482422</v>
       </c>
       <c r="F26" t="n">
-        <v>8459900</v>
+        <v>14233900</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B27" t="n">
-        <v>159.8600006103516</v>
+        <v>142.9850006103516</v>
       </c>
       <c r="C27" t="n">
-        <v>162.6799926757812</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="D27" t="n">
-        <v>153.7400054931641</v>
+        <v>136.7899932861328</v>
       </c>
       <c r="E27" t="n">
-        <v>154.1000061035156</v>
+        <v>138.7899932861328</v>
       </c>
       <c r="F27" t="n">
-        <v>10459300</v>
+        <v>13672400</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B28" t="n">
-        <v>160.7599945068359</v>
+        <v>140.4199981689453</v>
       </c>
       <c r="C28" t="n">
-        <v>162</v>
+        <v>145.3899993896484</v>
       </c>
       <c r="D28" t="n">
-        <v>145.0899963378906</v>
+        <v>140.1100006103516</v>
       </c>
       <c r="E28" t="n">
-        <v>147.4499969482422</v>
+        <v>143.3800048828125</v>
       </c>
       <c r="F28" t="n">
-        <v>14233900</v>
+        <v>8687000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B29" t="n">
-        <v>142.9850006103516</v>
+        <v>144.8999938964844</v>
       </c>
       <c r="C29" t="n">
-        <v>143.0200042724609</v>
+        <v>147.6499938964844</v>
       </c>
       <c r="D29" t="n">
-        <v>136.7899932861328</v>
+        <v>143.8600006103516</v>
       </c>
       <c r="E29" t="n">
-        <v>138.7899932861328</v>
+        <v>146.0099945068359</v>
       </c>
       <c r="F29" t="n">
-        <v>13672400</v>
+        <v>6909500</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B30" t="n">
-        <v>140.4199981689453</v>
+        <v>143.0099945068359</v>
       </c>
       <c r="C30" t="n">
-        <v>145.3899993896484</v>
+        <v>144.5</v>
       </c>
       <c r="D30" t="n">
-        <v>140.1100006103516</v>
+        <v>139.2400054931641</v>
       </c>
       <c r="E30" t="n">
-        <v>143.3800048828125</v>
+        <v>143.1000061035156</v>
       </c>
       <c r="F30" t="n">
-        <v>8687000</v>
+        <v>6533900</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B31" t="n">
-        <v>144.8999938964844</v>
+        <v>146.3249969482422</v>
       </c>
       <c r="C31" t="n">
-        <v>147.6499938964844</v>
+        <v>149.8800048828125</v>
       </c>
       <c r="D31" t="n">
-        <v>143.8600006103516</v>
+        <v>146.1900024414062</v>
       </c>
       <c r="E31" t="n">
-        <v>146.0099945068359</v>
+        <v>146.4799957275391</v>
       </c>
       <c r="F31" t="n">
-        <v>6909500</v>
+        <v>6120700</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B32" t="n">
-        <v>143.0099945068359</v>
+        <v>145.4499969482422</v>
       </c>
       <c r="C32" t="n">
-        <v>144.5</v>
+        <v>147.6100006103516</v>
       </c>
       <c r="D32" t="n">
-        <v>139.2400054931641</v>
+        <v>144.1399993896484</v>
       </c>
       <c r="E32" t="n">
-        <v>143.1000061035156</v>
+        <v>145.9400024414062</v>
       </c>
       <c r="F32" t="n">
-        <v>6533900</v>
+        <v>3648900</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B33" t="n">
-        <v>146.3249969482422</v>
+        <v>145.8650054931641</v>
       </c>
       <c r="C33" t="n">
-        <v>149.8800048828125</v>
+        <v>147.4900054931641</v>
       </c>
       <c r="D33" t="n">
-        <v>146.1900024414062</v>
+        <v>141.6799926757812</v>
       </c>
       <c r="E33" t="n">
-        <v>146.4799957275391</v>
+        <v>146.5899963378906</v>
       </c>
       <c r="F33" t="n">
-        <v>6120700</v>
+        <v>7349200</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B34" t="n">
-        <v>145.4499969482422</v>
+        <v>146.7799987792969</v>
       </c>
       <c r="C34" t="n">
-        <v>147.6100006103516</v>
+        <v>153.9499969482422</v>
       </c>
       <c r="D34" t="n">
-        <v>144.1399993896484</v>
+        <v>146.6399993896484</v>
       </c>
       <c r="E34" t="n">
-        <v>145.9400024414062</v>
+        <v>152.7599945068359</v>
       </c>
       <c r="F34" t="n">
-        <v>3648900</v>
+        <v>7327400</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B35" t="n">
-        <v>145.8650054931641</v>
+        <v>155</v>
       </c>
       <c r="C35" t="n">
-        <v>147.4900054931641</v>
+        <v>155.8300018310547</v>
       </c>
       <c r="D35" t="n">
-        <v>141.6799926757812</v>
+        <v>152.2969970703125</v>
       </c>
       <c r="E35" t="n">
-        <v>146.5899963378906</v>
+        <v>153.8200073242188</v>
       </c>
       <c r="F35" t="n">
-        <v>7349200</v>
+        <v>5170800</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B36" t="n">
-        <v>146.7799987792969</v>
+        <v>157.4100036621094</v>
       </c>
       <c r="C36" t="n">
-        <v>153.9499969482422</v>
+        <v>157.6999969482422</v>
       </c>
       <c r="D36" t="n">
-        <v>146.6399993896484</v>
+        <v>155.0099945068359</v>
       </c>
       <c r="E36" t="n">
-        <v>152.7599945068359</v>
+        <v>156.8099975585938</v>
       </c>
       <c r="F36" t="n">
-        <v>7327400</v>
+        <v>5509100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B37" t="n">
-        <v>155</v>
+        <v>156.6199951171875</v>
       </c>
       <c r="C37" t="n">
-        <v>155.8300018310547</v>
+        <v>158.6600036621094</v>
       </c>
       <c r="D37" t="n">
-        <v>152.2969970703125</v>
+        <v>152.3300018310547</v>
       </c>
       <c r="E37" t="n">
-        <v>153.8200073242188</v>
+        <v>156.7700042724609</v>
       </c>
       <c r="F37" t="n">
-        <v>5170800</v>
+        <v>5037400</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B38" t="n">
-        <v>157.4100036621094</v>
+        <v>157.2100067138672</v>
       </c>
       <c r="C38" t="n">
-        <v>157.6999969482422</v>
+        <v>162.3999938964844</v>
       </c>
       <c r="D38" t="n">
-        <v>155.0099945068359</v>
+        <v>156.7799987792969</v>
       </c>
       <c r="E38" t="n">
-        <v>156.8099975585938</v>
+        <v>162.0299987792969</v>
       </c>
       <c r="F38" t="n">
-        <v>5509100</v>
+        <v>6901400</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B39" t="n">
-        <v>156.6199951171875</v>
+        <v>162.4700012207031</v>
       </c>
       <c r="C39" t="n">
-        <v>158.6600036621094</v>
+        <v>164.9400024414062</v>
       </c>
       <c r="D39" t="n">
-        <v>152.3300018310547</v>
+        <v>158.3999938964844</v>
       </c>
       <c r="E39" t="n">
-        <v>156.7700042724609</v>
+        <v>158.4400024414062</v>
       </c>
       <c r="F39" t="n">
-        <v>5037400</v>
+        <v>6911300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B40" t="n">
-        <v>157.2100067138672</v>
+        <v>161.0899963378906</v>
       </c>
       <c r="C40" t="n">
-        <v>162.3999938964844</v>
+        <v>162.1150054931641</v>
       </c>
       <c r="D40" t="n">
-        <v>156.7799987792969</v>
+        <v>155.7400054931641</v>
       </c>
       <c r="E40" t="n">
-        <v>162.0299987792969</v>
+        <v>157.6900024414062</v>
       </c>
       <c r="F40" t="n">
-        <v>6901400</v>
+        <v>6209300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B41" t="n">
-        <v>162.4700012207031</v>
+        <v>160.5</v>
       </c>
       <c r="C41" t="n">
-        <v>164.9400024414062</v>
+        <v>160.8999938964844</v>
       </c>
       <c r="D41" t="n">
-        <v>158.3999938964844</v>
+        <v>155.4199981689453</v>
       </c>
       <c r="E41" t="n">
-        <v>158.4400024414062</v>
+        <v>157.5899963378906</v>
       </c>
       <c r="F41" t="n">
-        <v>6911300</v>
+        <v>6422600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B42" t="n">
-        <v>161.0899963378906</v>
+        <v>152.8600006103516</v>
       </c>
       <c r="C42" t="n">
-        <v>162.1150054931641</v>
+        <v>157.0249938964844</v>
       </c>
       <c r="D42" t="n">
-        <v>155.7400054931641</v>
+        <v>150.9900054931641</v>
       </c>
       <c r="E42" t="n">
-        <v>157.6900024414062</v>
+        <v>153.5500030517578</v>
       </c>
       <c r="F42" t="n">
-        <v>6209300</v>
+        <v>9026400</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B43" t="n">
-        <v>160.5</v>
+        <v>142.6699981689453</v>
       </c>
       <c r="C43" t="n">
-        <v>160.8999938964844</v>
+        <v>148</v>
       </c>
       <c r="D43" t="n">
-        <v>155.4199981689453</v>
+        <v>140.0200042724609</v>
       </c>
       <c r="E43" t="n">
-        <v>157.5899963378906</v>
+        <v>140.4199981689453</v>
       </c>
       <c r="F43" t="n">
-        <v>6422600</v>
+        <v>15901000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B44" t="n">
-        <v>152.8600006103516</v>
+        <v>140.6499938964844</v>
       </c>
       <c r="C44" t="n">
-        <v>157.0249938964844</v>
+        <v>141.9900054931641</v>
       </c>
       <c r="D44" t="n">
-        <v>150.9900054931641</v>
+        <v>132.5899963378906</v>
       </c>
       <c r="E44" t="n">
-        <v>153.5500030517578</v>
+        <v>134.0200042724609</v>
       </c>
       <c r="F44" t="n">
-        <v>9026400</v>
+        <v>13296100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B45" t="n">
-        <v>142.6699981689453</v>
+        <v>134.4100036621094</v>
       </c>
       <c r="C45" t="n">
-        <v>148</v>
+        <v>136.6100006103516</v>
       </c>
       <c r="D45" t="n">
-        <v>140.0200042724609</v>
+        <v>132.4499969482422</v>
       </c>
       <c r="E45" t="n">
-        <v>140.4199981689453</v>
+        <v>134.6499938964844</v>
       </c>
       <c r="F45" t="n">
-        <v>15901000</v>
+        <v>11341600</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B46" t="n">
-        <v>140.6499938964844</v>
+        <v>137.5</v>
       </c>
       <c r="C46" t="n">
-        <v>141.9900054931641</v>
+        <v>138.9799957275391</v>
       </c>
       <c r="D46" t="n">
-        <v>132.5899963378906</v>
+        <v>134.5870056152344</v>
       </c>
       <c r="E46" t="n">
-        <v>134.0200042724609</v>
+        <v>137.2599945068359</v>
       </c>
       <c r="F46" t="n">
-        <v>13296100</v>
+        <v>6974300</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B47" t="n">
-        <v>134.4100036621094</v>
+        <v>134.8699951171875</v>
       </c>
       <c r="C47" t="n">
-        <v>136.6100006103516</v>
+        <v>136.375</v>
       </c>
       <c r="D47" t="n">
-        <v>132.4499969482422</v>
+        <v>132.4100036621094</v>
       </c>
       <c r="E47" t="n">
-        <v>134.6499938964844</v>
+        <v>134.9299926757812</v>
       </c>
       <c r="F47" t="n">
-        <v>11341600</v>
+        <v>7189300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B48" t="n">
-        <v>137.5</v>
+        <v>136.2200012207031</v>
       </c>
       <c r="C48" t="n">
-        <v>138.9799957275391</v>
+        <v>136.5980072021484</v>
       </c>
       <c r="D48" t="n">
-        <v>134.5870056152344</v>
+        <v>133.7779998779297</v>
       </c>
       <c r="E48" t="n">
-        <v>137.2599945068359</v>
+        <v>134.9799957275391</v>
       </c>
       <c r="F48" t="n">
-        <v>6974300</v>
+        <v>6471400</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B49" t="n">
-        <v>134.8699951171875</v>
+        <v>134.4299926757812</v>
       </c>
       <c r="C49" t="n">
-        <v>136.375</v>
+        <v>135.5800018310547</v>
       </c>
       <c r="D49" t="n">
-        <v>132.4100036621094</v>
+        <v>129.1699981689453</v>
       </c>
       <c r="E49" t="n">
-        <v>134.9299926757812</v>
+        <v>130.3000030517578</v>
       </c>
       <c r="F49" t="n">
-        <v>7189300</v>
+        <v>10471400</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B50" t="n">
-        <v>136.2200012207031</v>
+        <v>127.0599975585938</v>
       </c>
       <c r="C50" t="n">
-        <v>136.5980072021484</v>
+        <v>135.3699951171875</v>
       </c>
       <c r="D50" t="n">
-        <v>133.7779998779297</v>
+        <v>125.3600006103516</v>
       </c>
       <c r="E50" t="n">
-        <v>134.9799957275391</v>
+        <v>131.3699951171875</v>
       </c>
       <c r="F50" t="n">
-        <v>6471400</v>
+        <v>10672500</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B51" t="n">
-        <v>134.4299926757812</v>
+        <v>131.3500061035156</v>
       </c>
       <c r="C51" t="n">
-        <v>135.5800018310547</v>
+        <v>133.3200073242188</v>
       </c>
       <c r="D51" t="n">
-        <v>129.1699981689453</v>
+        <v>125.4000015258789</v>
       </c>
       <c r="E51" t="n">
-        <v>130.3000030517578</v>
+        <v>127.2600021362305</v>
       </c>
       <c r="F51" t="n">
-        <v>10471400</v>
+        <v>12455900</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B52" t="n">
-        <v>127.0599975585938</v>
+        <v>125.75</v>
       </c>
       <c r="C52" t="n">
-        <v>135.3699951171875</v>
+        <v>127.5500030517578</v>
       </c>
       <c r="D52" t="n">
-        <v>125.3600006103516</v>
+        <v>122.0800018310547</v>
       </c>
       <c r="E52" t="n">
-        <v>131.3699951171875</v>
+        <v>123.4499969482422</v>
       </c>
       <c r="F52" t="n">
-        <v>10672500</v>
+        <v>12561100</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B53" t="n">
-        <v>131.3500061035156</v>
+        <v>123.0500030517578</v>
       </c>
       <c r="C53" t="n">
-        <v>133.3200073242188</v>
+        <v>126.5699996948242</v>
       </c>
       <c r="D53" t="n">
-        <v>125.4000015258789</v>
+        <v>122.9000015258789</v>
       </c>
       <c r="E53" t="n">
-        <v>127.2600021362305</v>
+        <v>124.8099975585938</v>
       </c>
       <c r="F53" t="n">
-        <v>12455900</v>
+        <v>7703500</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B54" t="n">
-        <v>125.75</v>
+        <v>129.8899993896484</v>
       </c>
       <c r="C54" t="n">
-        <v>127.5500030517578</v>
+        <v>131.7899932861328</v>
       </c>
       <c r="D54" t="n">
-        <v>122.0800018310547</v>
+        <v>118.9000015258789</v>
       </c>
       <c r="E54" t="n">
-        <v>123.4499969482422</v>
+        <v>119.5899963378906</v>
       </c>
       <c r="F54" t="n">
-        <v>12561100</v>
+        <v>12642000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B55" t="n">
-        <v>123.0500030517578</v>
+        <v>118.4199981689453</v>
       </c>
       <c r="C55" t="n">
-        <v>126.5699996948242</v>
+        <v>120.004997253418</v>
       </c>
       <c r="D55" t="n">
-        <v>122.9000015258789</v>
+        <v>114.5199966430664</v>
       </c>
       <c r="E55" t="n">
-        <v>124.8099975585938</v>
+        <v>117.4300003051758</v>
       </c>
       <c r="F55" t="n">
-        <v>7703500</v>
+        <v>16704100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B56" t="n">
-        <v>129.8899993896484</v>
+        <v>118.9150009155273</v>
       </c>
       <c r="C56" t="n">
-        <v>131.7899932861328</v>
+        <v>122.4199981689453</v>
       </c>
       <c r="D56" t="n">
-        <v>118.9000015258789</v>
+        <v>118.1999969482422</v>
       </c>
       <c r="E56" t="n">
-        <v>119.5899963378906</v>
+        <v>122.1699981689453</v>
       </c>
       <c r="F56" t="n">
-        <v>12642000</v>
+        <v>12758600</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B57" t="n">
-        <v>118.4199981689453</v>
+        <v>122.4000015258789</v>
       </c>
       <c r="C57" t="n">
-        <v>120.004997253418</v>
+        <v>125.9100036621094</v>
       </c>
       <c r="D57" t="n">
-        <v>114.5199966430664</v>
+        <v>122.3199996948242</v>
       </c>
       <c r="E57" t="n">
-        <v>117.4300003051758</v>
+        <v>125.0400009155273</v>
       </c>
       <c r="F57" t="n">
-        <v>16704100</v>
+        <v>7143400</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B58" t="n">
-        <v>118.9150009155273</v>
+        <v>127.4749984741211</v>
       </c>
       <c r="C58" t="n">
-        <v>122.4199981689453</v>
+        <v>128.4750061035156</v>
       </c>
       <c r="D58" t="n">
-        <v>118.1999969482422</v>
+        <v>125.2460021972656</v>
       </c>
       <c r="E58" t="n">
-        <v>122.1699981689453</v>
+        <v>127.6500015258789</v>
       </c>
       <c r="F58" t="n">
-        <v>12758600</v>
+        <v>5995000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B59" t="n">
-        <v>122.4000015258789</v>
+        <v>130</v>
       </c>
       <c r="C59" t="n">
-        <v>125.9100036621094</v>
+        <v>131.4049987792969</v>
       </c>
       <c r="D59" t="n">
-        <v>122.3199996948242</v>
+        <v>128.1150054931641</v>
       </c>
       <c r="E59" t="n">
-        <v>125.0400009155273</v>
+        <v>130.6799926757812</v>
       </c>
       <c r="F59" t="n">
-        <v>7143400</v>
+        <v>3895000</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B60" t="n">
-        <v>127.4749984741211</v>
+        <v>128.9799957275391</v>
       </c>
       <c r="C60" t="n">
-        <v>128.4750061035156</v>
+        <v>129.5039978027344</v>
       </c>
       <c r="D60" t="n">
-        <v>125.2460021972656</v>
+        <v>126.1399993896484</v>
       </c>
       <c r="E60" t="n">
-        <v>127.6500015258789</v>
+        <v>128.1100006103516</v>
       </c>
       <c r="F60" t="n">
-        <v>5995000</v>
+        <v>4690600</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B61" t="n">
-        <v>130</v>
+        <v>129.75</v>
       </c>
       <c r="C61" t="n">
-        <v>131.4049987792969</v>
+        <v>131.0399932861328</v>
       </c>
       <c r="D61" t="n">
-        <v>128.1150054931641</v>
+        <v>126.2699966430664</v>
       </c>
       <c r="E61" t="n">
-        <v>130.6799926757812</v>
+        <v>127.2200012207031</v>
       </c>
       <c r="F61" t="n">
-        <v>3895000</v>
+        <v>5619000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B62" t="n">
-        <v>128.9799957275391</v>
+        <v>126.1600036621094</v>
       </c>
       <c r="C62" t="n">
-        <v>129.5039978027344</v>
+        <v>128.5</v>
       </c>
       <c r="D62" t="n">
-        <v>126.1399993896484</v>
+        <v>123.75</v>
       </c>
       <c r="E62" t="n">
-        <v>128.1100006103516</v>
+        <v>127.8000030517578</v>
       </c>
       <c r="F62" t="n">
-        <v>4690600</v>
+        <v>5286300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B63" t="n">
-        <v>129.75</v>
+        <v>127.0800018310547</v>
       </c>
       <c r="C63" t="n">
-        <v>131.0399932861328</v>
+        <v>130.7799987792969</v>
       </c>
       <c r="D63" t="n">
-        <v>126.2699966430664</v>
+        <v>126.7399978637695</v>
       </c>
       <c r="E63" t="n">
-        <v>127.2200012207031</v>
+        <v>128.5500030517578</v>
       </c>
       <c r="F63" t="n">
-        <v>5619000</v>
+        <v>4516400</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B64" t="n">
-        <v>126.1600036621094</v>
+        <v>128.5</v>
       </c>
       <c r="C64" t="n">
-        <v>128.5</v>
+        <v>129.6600036621094</v>
       </c>
       <c r="D64" t="n">
-        <v>123.75</v>
+        <v>126.8399963378906</v>
       </c>
       <c r="E64" t="n">
-        <v>127.8000030517578</v>
+        <v>128.5899963378906</v>
       </c>
       <c r="F64" t="n">
-        <v>5286300</v>
+        <v>5166300</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B65" t="n">
-        <v>127.0800018310547</v>
+        <v>129.7299957275391</v>
       </c>
       <c r="C65" t="n">
-        <v>130.7799987792969</v>
+        <v>133.5700073242188</v>
       </c>
       <c r="D65" t="n">
-        <v>126.7399978637695</v>
+        <v>128.2100067138672</v>
       </c>
       <c r="E65" t="n">
-        <v>128.5500030517578</v>
+        <v>129.1100006103516</v>
       </c>
       <c r="F65" t="n">
-        <v>4516400</v>
+        <v>7813800</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B66" t="n">
-        <v>128.5</v>
+        <v>128.6999969482422</v>
       </c>
       <c r="C66" t="n">
-        <v>129.6600036621094</v>
+        <v>130.8000030517578</v>
       </c>
       <c r="D66" t="n">
-        <v>126.8399963378906</v>
+        <v>127.3199996948242</v>
       </c>
       <c r="E66" t="n">
-        <v>128.5899963378906</v>
+        <v>130.0399932861328</v>
       </c>
       <c r="F66" t="n">
-        <v>5166300</v>
+        <v>5227900</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B67" t="n">
-        <v>129.7299957275391</v>
+        <v>131.0500030517578</v>
       </c>
       <c r="C67" t="n">
-        <v>133.5700073242188</v>
+        <v>134.4400024414062</v>
       </c>
       <c r="D67" t="n">
-        <v>128.2100067138672</v>
+        <v>130.25</v>
       </c>
       <c r="E67" t="n">
-        <v>129.1100006103516</v>
+        <v>132.3600006103516</v>
       </c>
       <c r="F67" t="n">
-        <v>7813800</v>
+        <v>5921300</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B68" t="n">
-        <v>128.6999969482422</v>
+        <v>135.5299987792969</v>
       </c>
       <c r="C68" t="n">
-        <v>130.8000030517578</v>
+        <v>136.3999938964844</v>
       </c>
       <c r="D68" t="n">
-        <v>127.3199996948242</v>
+        <v>128.9499969482422</v>
       </c>
       <c r="E68" t="n">
-        <v>130.0399932861328</v>
+        <v>134.3899993896484</v>
       </c>
       <c r="F68" t="n">
-        <v>5227900</v>
+        <v>6679500</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B69" t="n">
-        <v>131.0500030517578</v>
+        <v>132.4799957275391</v>
       </c>
       <c r="C69" t="n">
-        <v>134.4400024414062</v>
+        <v>134.0500030517578</v>
       </c>
       <c r="D69" t="n">
-        <v>130.25</v>
+        <v>124.3000030517578</v>
       </c>
       <c r="E69" t="n">
-        <v>132.3600006103516</v>
+        <v>124.7600021362305</v>
       </c>
       <c r="F69" t="n">
-        <v>5921300</v>
+        <v>8508700</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B70" t="n">
-        <v>135.5299987792969</v>
+        <v>125.5</v>
       </c>
       <c r="C70" t="n">
-        <v>136.3999938964844</v>
+        <v>127.3600006103516</v>
       </c>
       <c r="D70" t="n">
-        <v>128.9499969482422</v>
+        <v>123.6100006103516</v>
       </c>
       <c r="E70" t="n">
-        <v>134.3899993896484</v>
+        <v>125.8899993896484</v>
       </c>
       <c r="F70" t="n">
-        <v>6679500</v>
+        <v>6441900</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B71" t="n">
-        <v>132.4799957275391</v>
+        <v>126.1399993896484</v>
       </c>
       <c r="C71" t="n">
-        <v>134.0500030517578</v>
+        <v>127.8399963378906</v>
       </c>
       <c r="D71" t="n">
-        <v>124.3000030517578</v>
+        <v>124.1999969482422</v>
       </c>
       <c r="E71" t="n">
-        <v>124.7600021362305</v>
+        <v>126.129997253418</v>
       </c>
       <c r="F71" t="n">
-        <v>8508700</v>
+        <v>6656100</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B72" t="n">
-        <v>125.5</v>
+        <v>125.9400024414062</v>
       </c>
       <c r="C72" t="n">
-        <v>127.3600006103516</v>
+        <v>126.8300018310547</v>
       </c>
       <c r="D72" t="n">
-        <v>123.6100006103516</v>
+        <v>121.629997253418</v>
       </c>
       <c r="E72" t="n">
-        <v>125.8899993896484</v>
+        <v>122.3600006103516</v>
       </c>
       <c r="F72" t="n">
-        <v>6441900</v>
+        <v>8589200</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B73" t="n">
-        <v>126.1399993896484</v>
+        <v>125</v>
       </c>
       <c r="C73" t="n">
-        <v>127.8399963378906</v>
+        <v>127.1600036621094</v>
       </c>
       <c r="D73" t="n">
-        <v>124.1999969482422</v>
+        <v>123.879997253418</v>
       </c>
       <c r="E73" t="n">
-        <v>126.129997253418</v>
+        <v>124.620002746582</v>
       </c>
       <c r="F73" t="n">
-        <v>6656100</v>
+        <v>5515200</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B74" t="n">
-        <v>125.9400024414062</v>
+        <v>125.0100021362305</v>
       </c>
       <c r="C74" t="n">
-        <v>126.8300018310547</v>
+        <v>132.5200042724609</v>
       </c>
       <c r="D74" t="n">
-        <v>121.629997253418</v>
+        <v>125.0100021362305</v>
       </c>
       <c r="E74" t="n">
-        <v>122.3600006103516</v>
+        <v>131.1199951171875</v>
       </c>
       <c r="F74" t="n">
-        <v>8589200</v>
+        <v>12713100</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B75" t="n">
-        <v>125</v>
+        <v>133.4299926757812</v>
       </c>
       <c r="C75" t="n">
-        <v>127.1600036621094</v>
+        <v>134</v>
       </c>
       <c r="D75" t="n">
-        <v>123.879997253418</v>
+        <v>130.2200012207031</v>
       </c>
       <c r="E75" t="n">
-        <v>124.620002746582</v>
+        <v>130.7299957275391</v>
       </c>
       <c r="F75" t="n">
-        <v>5515200</v>
+        <v>5547300</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B76" t="n">
-        <v>125.0100021362305</v>
+        <v>129.3200073242188</v>
       </c>
       <c r="C76" t="n">
-        <v>132.5200042724609</v>
+        <v>131.7200012207031</v>
       </c>
       <c r="D76" t="n">
-        <v>125.0100021362305</v>
+        <v>129.25</v>
       </c>
       <c r="E76" t="n">
-        <v>131.1199951171875</v>
+        <v>131.3200073242188</v>
       </c>
       <c r="F76" t="n">
-        <v>12713100</v>
+        <v>2884300</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B77" t="n">
-        <v>133.4299926757812</v>
+        <v>131.1300048828125</v>
       </c>
       <c r="C77" t="n">
-        <v>134</v>
+        <v>131.5</v>
       </c>
       <c r="D77" t="n">
-        <v>130.2200012207031</v>
+        <v>130.1100006103516</v>
       </c>
       <c r="E77" t="n">
-        <v>130.7299957275391</v>
+        <v>130.7700042724609</v>
       </c>
       <c r="F77" t="n">
-        <v>5547300</v>
+        <v>1642400</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B78" t="n">
-        <v>129.3200073242188</v>
+        <v>131</v>
       </c>
       <c r="C78" t="n">
-        <v>131.7200012207031</v>
+        <v>132.125</v>
       </c>
       <c r="D78" t="n">
-        <v>129.25</v>
+        <v>130.4499969482422</v>
       </c>
       <c r="E78" t="n">
-        <v>131.3200073242188</v>
+        <v>131.8399963378906</v>
       </c>
       <c r="F78" t="n">
-        <v>2884300</v>
+        <v>2308400</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B79" t="n">
-        <v>131.1300048828125</v>
+        <v>131.1499938964844</v>
       </c>
       <c r="C79" t="n">
-        <v>131.5</v>
+        <v>135.2989959716797</v>
       </c>
       <c r="D79" t="n">
-        <v>130.1100006103516</v>
+        <v>131.0399932861328</v>
       </c>
       <c r="E79" t="n">
-        <v>130.7700042724609</v>
+        <v>134.1499938964844</v>
       </c>
       <c r="F79" t="n">
-        <v>1642400</v>
+        <v>6199700</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B80" t="n">
-        <v>131</v>
+        <v>134.25</v>
       </c>
       <c r="C80" t="n">
-        <v>132.125</v>
+        <v>134.4499969482422</v>
       </c>
       <c r="D80" t="n">
-        <v>130.4499969482422</v>
+        <v>132.3699951171875</v>
       </c>
       <c r="E80" t="n">
-        <v>131.8399963378906</v>
+        <v>132.4400024414062</v>
       </c>
       <c r="F80" t="n">
-        <v>2308400</v>
+        <v>4081100</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B81" t="n">
-        <v>131.1499938964844</v>
+        <v>132.5</v>
       </c>
       <c r="C81" t="n">
-        <v>135.2989959716797</v>
+        <v>132.8300018310547</v>
       </c>
       <c r="D81" t="n">
-        <v>131.0399932861328</v>
+        <v>130.8800048828125</v>
       </c>
       <c r="E81" t="n">
-        <v>134.1499938964844</v>
+        <v>131.0299987792969</v>
       </c>
       <c r="F81" t="n">
-        <v>6199700</v>
+        <v>3821600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B82" t="n">
-        <v>134.25</v>
+        <v>134.0500030517578</v>
       </c>
       <c r="C82" t="n">
-        <v>134.4499969482422</v>
+        <v>136.0899963378906</v>
       </c>
       <c r="D82" t="n">
-        <v>132.3699951171875</v>
+        <v>132.1849975585938</v>
       </c>
       <c r="E82" t="n">
-        <v>132.4400024414062</v>
+        <v>133.6000061035156</v>
       </c>
       <c r="F82" t="n">
-        <v>4081100</v>
+        <v>4707400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B83" t="n">
-        <v>132.5</v>
+        <v>138.3399963378906</v>
       </c>
       <c r="C83" t="n">
-        <v>132.8300018310547</v>
+        <v>141.4100036621094</v>
       </c>
       <c r="D83" t="n">
-        <v>130.8800048828125</v>
+        <v>134.5099945068359</v>
       </c>
       <c r="E83" t="n">
-        <v>131.0299987792969</v>
+        <v>137.1900024414062</v>
       </c>
       <c r="F83" t="n">
-        <v>3821600</v>
+        <v>9691900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B84" t="n">
-        <v>134.0500030517578</v>
+        <v>137.8999938964844</v>
       </c>
       <c r="C84" t="n">
-        <v>136.0899963378906</v>
+        <v>137.9299926757812</v>
       </c>
       <c r="D84" t="n">
-        <v>132.1849975585938</v>
+        <v>132.5</v>
       </c>
       <c r="E84" t="n">
-        <v>133.6000061035156</v>
+        <v>132.5800018310547</v>
       </c>
       <c r="F84" t="n">
-        <v>4707400</v>
+        <v>8004000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B85" t="n">
-        <v>138.3399963378906</v>
+        <v>130.0099945068359</v>
       </c>
       <c r="C85" t="n">
-        <v>141.4100036621094</v>
+        <v>131.6549987792969</v>
       </c>
       <c r="D85" t="n">
-        <v>134.5099945068359</v>
+        <v>128.6399993896484</v>
       </c>
       <c r="E85" t="n">
-        <v>137.1900024414062</v>
+        <v>130.0800018310547</v>
       </c>
       <c r="F85" t="n">
-        <v>9691900</v>
+        <v>7550700</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B86" t="n">
-        <v>137.8999938964844</v>
+        <v>129.3699951171875</v>
       </c>
       <c r="C86" t="n">
-        <v>137.9299926757812</v>
+        <v>129.6000061035156</v>
       </c>
       <c r="D86" t="n">
-        <v>132.5</v>
+        <v>122.8099975585938</v>
       </c>
       <c r="E86" t="n">
-        <v>132.5800018310547</v>
+        <v>123.7200012207031</v>
       </c>
       <c r="F86" t="n">
-        <v>8004000</v>
+        <v>8944200</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B87" t="n">
-        <v>130.0099945068359</v>
+        <v>124.5699996948242</v>
       </c>
       <c r="C87" t="n">
-        <v>131.6549987792969</v>
+        <v>124.8300018310547</v>
       </c>
       <c r="D87" t="n">
-        <v>128.6399993896484</v>
+        <v>121.9000015258789</v>
       </c>
       <c r="E87" t="n">
-        <v>130.0800018310547</v>
+        <v>122.8899993896484</v>
       </c>
       <c r="F87" t="n">
-        <v>7550700</v>
+        <v>8989700</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B88" t="n">
-        <v>129.3699951171875</v>
+        <v>121.5999984741211</v>
       </c>
       <c r="C88" t="n">
-        <v>129.6000061035156</v>
+        <v>124.4550018310547</v>
       </c>
       <c r="D88" t="n">
-        <v>122.8099975585938</v>
+        <v>120</v>
       </c>
       <c r="E88" t="n">
-        <v>123.7200012207031</v>
+        <v>123.4199981689453</v>
       </c>
       <c r="F88" t="n">
-        <v>8944200</v>
+        <v>8795900</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B89" t="n">
-        <v>124.5699996948242</v>
+        <v>123.6999969482422</v>
       </c>
       <c r="C89" t="n">
-        <v>124.8300018310547</v>
+        <v>130.6900024414062</v>
       </c>
       <c r="D89" t="n">
-        <v>121.9000015258789</v>
+        <v>123.0500030517578</v>
       </c>
       <c r="E89" t="n">
-        <v>122.8899993896484</v>
+        <v>129.9299926757812</v>
       </c>
       <c r="F89" t="n">
-        <v>8989700</v>
+        <v>8638900</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B90" t="n">
-        <v>121.5999984741211</v>
+        <v>128.7599945068359</v>
       </c>
       <c r="C90" t="n">
-        <v>124.4550018310547</v>
+        <v>129.7599945068359</v>
       </c>
       <c r="D90" t="n">
-        <v>120</v>
+        <v>123.3399963378906</v>
       </c>
       <c r="E90" t="n">
-        <v>123.4199981689453</v>
+        <v>125.0899963378906</v>
       </c>
       <c r="F90" t="n">
-        <v>8795900</v>
+        <v>7414600</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B91" t="n">
-        <v>123.6999969482422</v>
+        <v>127.5899963378906</v>
       </c>
       <c r="C91" t="n">
-        <v>130.6900024414062</v>
+        <v>133.3399963378906</v>
       </c>
       <c r="D91" t="n">
-        <v>123.0500030517578</v>
+        <v>127.370002746582</v>
       </c>
       <c r="E91" t="n">
-        <v>129.9299926757812</v>
+        <v>130.5899963378906</v>
       </c>
       <c r="F91" t="n">
-        <v>8638900</v>
+        <v>8562300</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B92" t="n">
-        <v>128.7599945068359</v>
+        <v>132.1799926757812</v>
       </c>
       <c r="C92" t="n">
-        <v>129.7599945068359</v>
+        <v>132.9400024414062</v>
       </c>
       <c r="D92" t="n">
-        <v>123.3399963378906</v>
+        <v>129.3300018310547</v>
       </c>
       <c r="E92" t="n">
-        <v>125.0899963378906</v>
+        <v>129.8300018310547</v>
       </c>
       <c r="F92" t="n">
-        <v>7414600</v>
+        <v>5987000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B93" t="n">
-        <v>127.5899963378906</v>
+        <v>126.4899978637695</v>
       </c>
       <c r="C93" t="n">
-        <v>133.3399963378906</v>
+        <v>130.3800048828125</v>
       </c>
       <c r="D93" t="n">
-        <v>127.370002746582</v>
+        <v>125.7799987792969</v>
       </c>
       <c r="E93" t="n">
-        <v>130.5899963378906</v>
+        <v>127.5199966430664</v>
       </c>
       <c r="F93" t="n">
-        <v>8562300</v>
+        <v>6371300</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B94" t="n">
-        <v>132.1799926757812</v>
+        <v>127.8600006103516</v>
       </c>
       <c r="C94" t="n">
-        <v>132.9400024414062</v>
+        <v>129.5500030517578</v>
       </c>
       <c r="D94" t="n">
-        <v>129.3300018310547</v>
+        <v>125.0400009155273</v>
       </c>
       <c r="E94" t="n">
-        <v>129.8300018310547</v>
+        <v>127.2900009155273</v>
       </c>
       <c r="F94" t="n">
-        <v>5987000</v>
+        <v>5931000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B95" t="n">
-        <v>126.4899978637695</v>
+        <v>139.8399963378906</v>
       </c>
       <c r="C95" t="n">
-        <v>130.3800048828125</v>
+        <v>146.3999938964844</v>
       </c>
       <c r="D95" t="n">
-        <v>125.7799987792969</v>
+        <v>137.4199981689453</v>
       </c>
       <c r="E95" t="n">
-        <v>127.5199966430664</v>
+        <v>138.4100036621094</v>
       </c>
       <c r="F95" t="n">
-        <v>6371300</v>
+        <v>14906700</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B96" t="n">
-        <v>127.8600006103516</v>
+        <v>138.3699951171875</v>
       </c>
       <c r="C96" t="n">
-        <v>129.5500030517578</v>
+        <v>138.8999938964844</v>
       </c>
       <c r="D96" t="n">
-        <v>125.0400009155273</v>
+        <v>134.8600006103516</v>
       </c>
       <c r="E96" t="n">
-        <v>127.2900009155273</v>
+        <v>136.3399963378906</v>
       </c>
       <c r="F96" t="n">
-        <v>5931000</v>
+        <v>8053900</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B97" t="n">
-        <v>139.8399963378906</v>
+        <v>139.3200073242188</v>
       </c>
       <c r="C97" t="n">
-        <v>146.3999938964844</v>
+        <v>146.4049987792969</v>
       </c>
       <c r="D97" t="n">
-        <v>137.4199981689453</v>
+        <v>139.2400054931641</v>
       </c>
       <c r="E97" t="n">
-        <v>138.4100036621094</v>
+        <v>143.7200012207031</v>
       </c>
       <c r="F97" t="n">
-        <v>14906700</v>
+        <v>10658200</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B98" t="n">
-        <v>138.3699951171875</v>
+        <v>144.8600006103516</v>
       </c>
       <c r="C98" t="n">
-        <v>138.8999938964844</v>
+        <v>149.2700042724609</v>
       </c>
       <c r="D98" t="n">
-        <v>134.8600006103516</v>
+        <v>143.8000030517578</v>
       </c>
       <c r="E98" t="n">
-        <v>136.3399963378906</v>
+        <v>146.6900024414062</v>
       </c>
       <c r="F98" t="n">
-        <v>8053900</v>
+        <v>8697000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B99" t="n">
-        <v>139.3200073242188</v>
+        <v>150.3500061035156</v>
       </c>
       <c r="C99" t="n">
-        <v>146.4049987792969</v>
+        <v>151.8000030517578</v>
       </c>
       <c r="D99" t="n">
-        <v>139.2400054931641</v>
+        <v>145.5700073242188</v>
       </c>
       <c r="E99" t="n">
-        <v>143.7200012207031</v>
+        <v>150.1499938964844</v>
       </c>
       <c r="F99" t="n">
-        <v>10658200</v>
+        <v>8568200</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B100" t="n">
-        <v>144.8600006103516</v>
+        <v>150.1499938964844</v>
       </c>
       <c r="C100" t="n">
-        <v>149.2700042724609</v>
+        <v>151.5500030517578</v>
       </c>
       <c r="D100" t="n">
-        <v>143.8000030517578</v>
+        <v>145.3300018310547</v>
       </c>
       <c r="E100" t="n">
-        <v>146.6900024414062</v>
+        <v>148.1499938964844</v>
       </c>
       <c r="F100" t="n">
-        <v>8697000</v>
+        <v>8915300</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B101" t="n">
-        <v>150.3500061035156</v>
+        <v>145.8500061035156</v>
       </c>
       <c r="C101" t="n">
-        <v>151.8000030517578</v>
+        <v>148.0599975585938</v>
       </c>
       <c r="D101" t="n">
-        <v>145.5700073242188</v>
+        <v>141.4400024414062</v>
       </c>
       <c r="E101" t="n">
-        <v>150.1499938964844</v>
+        <v>141.7400054931641</v>
       </c>
       <c r="F101" t="n">
-        <v>8568200</v>
+        <v>6364000</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B102" t="n">
-        <v>150.1499938964844</v>
+        <v>141.3200073242188</v>
       </c>
       <c r="C102" t="n">
-        <v>151.5500030517578</v>
+        <v>143.1100006103516</v>
       </c>
       <c r="D102" t="n">
-        <v>145.3300018310547</v>
+        <v>138.2200012207031</v>
       </c>
       <c r="E102" t="n">
-        <v>148.1499938964844</v>
+        <v>138.3699951171875</v>
       </c>
       <c r="F102" t="n">
-        <v>8915300</v>
+        <v>7719200</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B103" t="n">
-        <v>145.8500061035156</v>
+        <v>140.7149963378906</v>
       </c>
       <c r="C103" t="n">
-        <v>148.0599975585938</v>
+        <v>143.2720031738281</v>
       </c>
       <c r="D103" t="n">
-        <v>141.4400024414062</v>
+        <v>135.3300018310547</v>
       </c>
       <c r="E103" t="n">
-        <v>141.7400054931641</v>
+        <v>139.3899993896484</v>
       </c>
       <c r="F103" t="n">
-        <v>6364000</v>
+        <v>8202300</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B104" t="n">
-        <v>141.3200073242188</v>
+        <v>138</v>
       </c>
       <c r="C104" t="n">
-        <v>143.1100006103516</v>
+        <v>139.3699951171875</v>
       </c>
       <c r="D104" t="n">
-        <v>138.2200012207031</v>
+        <v>129.2400054931641</v>
       </c>
       <c r="E104" t="n">
-        <v>138.3699951171875</v>
+        <v>130.2799987792969</v>
       </c>
       <c r="F104" t="n">
-        <v>7719200</v>
+        <v>13313800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B105" t="n">
-        <v>140.7149963378906</v>
+        <v>127.7300033569336</v>
       </c>
       <c r="C105" t="n">
-        <v>143.2720031738281</v>
+        <v>130.3099975585938</v>
       </c>
       <c r="D105" t="n">
-        <v>135.3300018310547</v>
+        <v>125.3399963378906</v>
       </c>
       <c r="E105" t="n">
-        <v>139.3899993896484</v>
+        <v>128.6699981689453</v>
       </c>
       <c r="F105" t="n">
-        <v>8202300</v>
+        <v>9640500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B106" t="n">
-        <v>138</v>
+        <v>131.3999938964844</v>
       </c>
       <c r="C106" t="n">
-        <v>139.3699951171875</v>
+        <v>137.6100006103516</v>
       </c>
       <c r="D106" t="n">
-        <v>129.2400054931641</v>
+        <v>130.3200073242188</v>
       </c>
       <c r="E106" t="n">
-        <v>130.2799987792969</v>
+        <v>137.4900054931641</v>
       </c>
       <c r="F106" t="n">
-        <v>13313800</v>
+        <v>8986800</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B107" t="n">
-        <v>127.7300033569336</v>
+        <v>138.2799987792969</v>
       </c>
       <c r="C107" t="n">
-        <v>130.3099975585938</v>
+        <v>142.2700042724609</v>
       </c>
       <c r="D107" t="n">
-        <v>125.3399963378906</v>
+        <v>136.0549926757812</v>
       </c>
       <c r="E107" t="n">
-        <v>128.6699981689453</v>
+        <v>141.7400054931641</v>
       </c>
       <c r="F107" t="n">
-        <v>9640500</v>
+        <v>6801400</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B108" t="n">
-        <v>131.3999938964844</v>
+        <v>144.3249969482422</v>
       </c>
       <c r="C108" t="n">
-        <v>137.6100006103516</v>
+        <v>145.0350036621094</v>
       </c>
       <c r="D108" t="n">
-        <v>130.3200073242188</v>
+        <v>141.8000030517578</v>
       </c>
       <c r="E108" t="n">
-        <v>137.4900054931641</v>
+        <v>143.4499969482422</v>
       </c>
       <c r="F108" t="n">
-        <v>8986800</v>
+        <v>6138100</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B109" t="n">
-        <v>138.2799987792969</v>
+        <v>145.1100006103516</v>
       </c>
       <c r="C109" t="n">
-        <v>142.2700042724609</v>
+        <v>145.2400054931641</v>
       </c>
       <c r="D109" t="n">
-        <v>136.0549926757812</v>
+        <v>138.2200012207031</v>
       </c>
       <c r="E109" t="n">
-        <v>141.7400054931641</v>
+        <v>140.6600036621094</v>
       </c>
       <c r="F109" t="n">
-        <v>6801400</v>
+        <v>6942400</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B110" t="n">
-        <v>144.3249969482422</v>
+        <v>138</v>
       </c>
       <c r="C110" t="n">
-        <v>145.0350036621094</v>
+        <v>138.5</v>
       </c>
       <c r="D110" t="n">
-        <v>141.8000030517578</v>
+        <v>132.0099945068359</v>
       </c>
       <c r="E110" t="n">
-        <v>143.4499969482422</v>
+        <v>135.1199951171875</v>
       </c>
       <c r="F110" t="n">
-        <v>6138100</v>
+        <v>16322100</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B111" t="n">
-        <v>145.1100006103516</v>
+        <v>145.8200073242188</v>
       </c>
       <c r="C111" t="n">
-        <v>145.2400054931641</v>
+        <v>148.7700042724609</v>
       </c>
       <c r="D111" t="n">
-        <v>138.2200012207031</v>
+        <v>138</v>
       </c>
       <c r="E111" t="n">
-        <v>140.6600036621094</v>
+        <v>141.5899963378906</v>
       </c>
       <c r="F111" t="n">
-        <v>6942400</v>
+        <v>21823000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B112" t="n">
-        <v>138</v>
+        <v>140.6399993896484</v>
       </c>
       <c r="C112" t="n">
-        <v>138.5</v>
+        <v>145</v>
       </c>
       <c r="D112" t="n">
-        <v>132.0099945068359</v>
+        <v>140</v>
       </c>
       <c r="E112" t="n">
-        <v>135.1199951171875</v>
+        <v>142.5800018310547</v>
       </c>
       <c r="F112" t="n">
-        <v>16322100</v>
+        <v>8724200</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B113" t="n">
-        <v>145.8200073242188</v>
+        <v>140.4600067138672</v>
       </c>
       <c r="C113" t="n">
-        <v>148.7700042724609</v>
+        <v>142.5</v>
       </c>
       <c r="D113" t="n">
-        <v>138</v>
+        <v>136.6900024414062</v>
       </c>
       <c r="E113" t="n">
-        <v>141.5899963378906</v>
+        <v>139.5399932861328</v>
       </c>
       <c r="F113" t="n">
-        <v>21823000</v>
+        <v>9955700</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B114" t="n">
-        <v>140.6399993896484</v>
+        <v>138.6100006103516</v>
       </c>
       <c r="C114" t="n">
-        <v>145</v>
+        <v>140.3200073242188</v>
       </c>
       <c r="D114" t="n">
-        <v>140</v>
+        <v>135.3699951171875</v>
       </c>
       <c r="E114" t="n">
-        <v>142.5800018310547</v>
+        <v>137.2299957275391</v>
       </c>
       <c r="F114" t="n">
-        <v>8724200</v>
+        <v>5260600</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B115" t="n">
-        <v>140.4600067138672</v>
+        <v>136.0200042724609</v>
       </c>
       <c r="C115" t="n">
-        <v>142.5</v>
+        <v>138.3300018310547</v>
       </c>
       <c r="D115" t="n">
-        <v>136.6900024414062</v>
+        <v>132.1499938964844</v>
       </c>
       <c r="E115" t="n">
-        <v>139.5399932861328</v>
+        <v>132.7899932861328</v>
       </c>
       <c r="F115" t="n">
-        <v>9955700</v>
+        <v>8309000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B116" t="n">
-        <v>138.6100006103516</v>
+        <v>131.2250061035156</v>
       </c>
       <c r="C116" t="n">
-        <v>140.3200073242188</v>
+        <v>131.6349945068359</v>
       </c>
       <c r="D116" t="n">
-        <v>135.3699951171875</v>
+        <v>126.2600021362305</v>
       </c>
       <c r="E116" t="n">
-        <v>137.2299957275391</v>
+        <v>127.4300003051758</v>
       </c>
       <c r="F116" t="n">
-        <v>5260600</v>
+        <v>9706800</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B117" t="n">
-        <v>136.0200042724609</v>
+        <v>130.25</v>
       </c>
       <c r="C117" t="n">
-        <v>138.3300018310547</v>
+        <v>130.7299957275391</v>
       </c>
       <c r="D117" t="n">
-        <v>132.1499938964844</v>
+        <v>124.379997253418</v>
       </c>
       <c r="E117" t="n">
-        <v>132.7899932861328</v>
+        <v>128.7700042724609</v>
       </c>
       <c r="F117" t="n">
-        <v>8309000</v>
+        <v>8120000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B118" t="n">
-        <v>131.2250061035156</v>
+        <v>129.3699951171875</v>
       </c>
       <c r="C118" t="n">
-        <v>131.6349945068359</v>
+        <v>133.7799987792969</v>
       </c>
       <c r="D118" t="n">
-        <v>126.2600021362305</v>
+        <v>128.6399993896484</v>
       </c>
       <c r="E118" t="n">
-        <v>127.4300003051758</v>
+        <v>132.8899993896484</v>
       </c>
       <c r="F118" t="n">
-        <v>9706800</v>
+        <v>7611600</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B119" t="n">
+        <v>132</v>
+      </c>
+      <c r="C119" t="n">
+        <v>132.2200012207031</v>
+      </c>
+      <c r="D119" t="n">
+        <v>126.9199981689453</v>
+      </c>
+      <c r="E119" t="n">
         <v>130.25</v>
       </c>
-      <c r="C119" t="n">
-        <v>130.7299957275391</v>
-      </c>
-      <c r="D119" t="n">
-        <v>124.379997253418</v>
-      </c>
-      <c r="E119" t="n">
-        <v>128.7700042724609</v>
-      </c>
       <c r="F119" t="n">
-        <v>8120000</v>
+        <v>6360700</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B120" t="n">
-        <v>129.3699951171875</v>
+        <v>127.5199966430664</v>
       </c>
       <c r="C120" t="n">
-        <v>133.7799987792969</v>
+        <v>133.5800018310547</v>
       </c>
       <c r="D120" t="n">
-        <v>128.6399993896484</v>
+        <v>127.5</v>
       </c>
       <c r="E120" t="n">
-        <v>132.8899993896484</v>
+        <v>133.5</v>
       </c>
       <c r="F120" t="n">
-        <v>7611600</v>
+        <v>9043300</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B121" t="n">
-        <v>132</v>
+        <v>129.6499938964844</v>
       </c>
       <c r="C121" t="n">
-        <v>132.2200012207031</v>
+        <v>130.6900024414062</v>
       </c>
       <c r="D121" t="n">
-        <v>126.9199981689453</v>
+        <v>127.2600021362305</v>
       </c>
       <c r="E121" t="n">
-        <v>130.25</v>
+        <v>129.3000030517578</v>
       </c>
       <c r="F121" t="n">
-        <v>6360700</v>
+        <v>6875000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B122" t="n">
-        <v>127.5199966430664</v>
+        <v>125.3300018310547</v>
       </c>
       <c r="C122" t="n">
-        <v>133.5800018310547</v>
+        <v>126.8300018310547</v>
       </c>
       <c r="D122" t="n">
-        <v>127.5</v>
+        <v>122.370002746582</v>
       </c>
       <c r="E122" t="n">
-        <v>133.5</v>
+        <v>124.5999984741211</v>
       </c>
       <c r="F122" t="n">
-        <v>9043300</v>
+        <v>6119700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B123" t="n">
-        <v>129.6499938964844</v>
+        <v>127.870002746582</v>
       </c>
       <c r="C123" t="n">
-        <v>130.6900024414062</v>
+        <v>135.5599975585938</v>
       </c>
       <c r="D123" t="n">
-        <v>127.2600021362305</v>
+        <v>127.4000015258789</v>
       </c>
       <c r="E123" t="n">
-        <v>129.3000030517578</v>
+        <v>134.8300018310547</v>
       </c>
       <c r="F123" t="n">
-        <v>6875000</v>
+        <v>6897700</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B124" t="n">
-        <v>125.3300018310547</v>
+        <v>135.1150054931641</v>
       </c>
       <c r="C124" t="n">
-        <v>126.8300018310547</v>
+        <v>139.4799957275391</v>
       </c>
       <c r="D124" t="n">
-        <v>122.370002746582</v>
+        <v>134</v>
       </c>
       <c r="E124" t="n">
-        <v>124.5999984741211</v>
+        <v>139.3999938964844</v>
       </c>
       <c r="F124" t="n">
-        <v>6119700</v>
+        <v>8384600</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B125" t="n">
-        <v>127.870002746582</v>
+        <v>136.3899993896484</v>
       </c>
       <c r="C125" t="n">
-        <v>135.5599975585938</v>
+        <v>139.0579986572266</v>
       </c>
       <c r="D125" t="n">
-        <v>127.4000015258789</v>
+        <v>132.7299957275391</v>
       </c>
       <c r="E125" t="n">
-        <v>134.8300018310547</v>
+        <v>132.8899993896484</v>
       </c>
       <c r="F125" t="n">
-        <v>6897700</v>
+        <v>6282000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B126" t="n">
-        <v>135.1150054931641</v>
+        <v>130.4049987792969</v>
       </c>
       <c r="C126" t="n">
-        <v>139.4799957275391</v>
+        <v>137.6750030517578</v>
       </c>
       <c r="D126" t="n">
-        <v>134</v>
+        <v>129.7899932861328</v>
       </c>
       <c r="E126" t="n">
-        <v>139.3999938964844</v>
+        <v>137.1699981689453</v>
       </c>
       <c r="F126" t="n">
-        <v>8384600</v>
+        <v>6715200</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B127" t="n">
-        <v>136.3899993896484</v>
+        <v>138</v>
       </c>
       <c r="C127" t="n">
-        <v>139.0579986572266</v>
+        <v>141.7700042724609</v>
       </c>
       <c r="D127" t="n">
-        <v>132.7299957275391</v>
+        <v>137.8899993896484</v>
       </c>
       <c r="E127" t="n">
-        <v>132.8899993896484</v>
+        <v>139.6199951171875</v>
       </c>
       <c r="F127" t="n">
-        <v>6282000</v>
+        <v>5435800</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B128" t="n">
-        <v>130.4049987792969</v>
+        <v>139.1600036621094</v>
       </c>
       <c r="C128" t="n">
-        <v>137.6750030517578</v>
+        <v>141.1399993896484</v>
       </c>
       <c r="D128" t="n">
-        <v>129.7899932861328</v>
+        <v>137.6540069580078</v>
       </c>
       <c r="E128" t="n">
-        <v>137.1699981689453</v>
+        <v>138.2299957275391</v>
       </c>
       <c r="F128" t="n">
-        <v>6715200</v>
+        <v>4165100</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B129" t="n">
-        <v>138</v>
+        <v>137.7400054931641</v>
       </c>
       <c r="C129" t="n">
-        <v>141.7700042724609</v>
+        <v>137.7799987792969</v>
       </c>
       <c r="D129" t="n">
-        <v>137.8899993896484</v>
+        <v>133.6900024414062</v>
       </c>
       <c r="E129" t="n">
-        <v>139.6199951171875</v>
+        <v>134.0299987792969</v>
       </c>
       <c r="F129" t="n">
-        <v>5435800</v>
+        <v>5494200</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B130" t="n">
-        <v>139.1600036621094</v>
+        <v>134.8200073242188</v>
       </c>
       <c r="C130" t="n">
-        <v>141.1399993896484</v>
+        <v>137.5950012207031</v>
       </c>
       <c r="D130" t="n">
-        <v>137.6540069580078</v>
+        <v>130.5099945068359</v>
       </c>
       <c r="E130" t="n">
-        <v>138.2299957275391</v>
+        <v>133.5700073242188</v>
       </c>
       <c r="F130" t="n">
-        <v>4165100</v>
+        <v>5364800</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B131" t="n">
-        <v>137.7400054931641</v>
+        <v>133.8699951171875</v>
       </c>
       <c r="C131" t="n">
-        <v>137.7799987792969</v>
+        <v>136.2799987792969</v>
       </c>
       <c r="D131" t="n">
-        <v>133.6900024414062</v>
+        <v>131.9100036621094</v>
       </c>
       <c r="E131" t="n">
-        <v>134.0299987792969</v>
+        <v>135.3500061035156</v>
       </c>
       <c r="F131" t="n">
-        <v>5494200</v>
+        <v>7884200</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B132" t="n">
-        <v>134.8200073242188</v>
+        <v>135.0099945068359</v>
       </c>
       <c r="C132" t="n">
-        <v>137.5950012207031</v>
+        <v>136.6999969482422</v>
       </c>
       <c r="D132" t="n">
-        <v>130.5099945068359</v>
+        <v>132.3099975585938</v>
       </c>
       <c r="E132" t="n">
-        <v>133.5700073242188</v>
+        <v>133.0700073242188</v>
       </c>
       <c r="F132" t="n">
-        <v>5364800</v>
+        <v>5959000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B133" t="n">
-        <v>133.8699951171875</v>
+        <v>133.5</v>
       </c>
       <c r="C133" t="n">
-        <v>136.2799987792969</v>
+        <v>137.5599975585938</v>
       </c>
       <c r="D133" t="n">
-        <v>131.9100036621094</v>
+        <v>133.5</v>
       </c>
       <c r="E133" t="n">
-        <v>135.3500061035156</v>
+        <v>136.0700073242188</v>
       </c>
       <c r="F133" t="n">
-        <v>7884200</v>
+        <v>5264100</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B134" t="n">
-        <v>135.0099945068359</v>
+        <v>133.7400054931641</v>
       </c>
       <c r="C134" t="n">
-        <v>136.6999969482422</v>
+        <v>136.5700073242188</v>
       </c>
       <c r="D134" t="n">
-        <v>132.3099975585938</v>
+        <v>132.3500061035156</v>
       </c>
       <c r="E134" t="n">
-        <v>133.0700073242188</v>
+        <v>136.2599945068359</v>
       </c>
       <c r="F134" t="n">
-        <v>5959000</v>
+        <v>4418900</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B135" t="n">
-        <v>133.5</v>
+        <v>134</v>
       </c>
       <c r="C135" t="n">
-        <v>137.5599975585938</v>
+        <v>135.3000030517578</v>
       </c>
       <c r="D135" t="n">
-        <v>133.5</v>
+        <v>128.8999938964844</v>
       </c>
       <c r="E135" t="n">
-        <v>136.0700073242188</v>
+        <v>131.2200012207031</v>
       </c>
       <c r="F135" t="n">
-        <v>5264100</v>
+        <v>11351600</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B136" t="n">
-        <v>133.7400054931641</v>
+        <v>133.4799957275391</v>
       </c>
       <c r="C136" t="n">
-        <v>136.5700073242188</v>
+        <v>138.2100067138672</v>
       </c>
       <c r="D136" t="n">
-        <v>132.3500061035156</v>
+        <v>132.1999969482422</v>
       </c>
       <c r="E136" t="n">
-        <v>136.2599945068359</v>
+        <v>135.8800048828125</v>
       </c>
       <c r="F136" t="n">
-        <v>4418900</v>
+        <v>6402200</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B137" t="n">
-        <v>134</v>
+        <v>134.2100067138672</v>
       </c>
       <c r="C137" t="n">
-        <v>135.3000030517578</v>
+        <v>135.6999969482422</v>
       </c>
       <c r="D137" t="n">
-        <v>128.8999938964844</v>
+        <v>129.1900024414062</v>
       </c>
       <c r="E137" t="n">
-        <v>131.2200012207031</v>
+        <v>130.8000030517578</v>
       </c>
       <c r="F137" t="n">
-        <v>11351600</v>
+        <v>7858900</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B138" t="n">
-        <v>133.4799957275391</v>
+        <v>133.2100067138672</v>
       </c>
       <c r="C138" t="n">
-        <v>138.2100067138672</v>
+        <v>135.0800018310547</v>
       </c>
       <c r="D138" t="n">
-        <v>132.1999969482422</v>
+        <v>131.1499938964844</v>
       </c>
       <c r="E138" t="n">
-        <v>135.8800048828125</v>
+        <v>135.0099945068359</v>
       </c>
       <c r="F138" t="n">
-        <v>6402200</v>
+        <v>5353300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B139" t="n">
-        <v>134.2100067138672</v>
+        <v>131.7899932861328</v>
       </c>
       <c r="C139" t="n">
-        <v>135.6999969482422</v>
+        <v>132.5</v>
       </c>
       <c r="D139" t="n">
-        <v>129.1900024414062</v>
+        <v>122.5100021362305</v>
       </c>
       <c r="E139" t="n">
-        <v>130.8000030517578</v>
+        <v>122.5500030517578</v>
       </c>
       <c r="F139" t="n">
-        <v>7858900</v>
+        <v>7553500</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B140" t="n">
-        <v>133.2100067138672</v>
+        <v>121.3399963378906</v>
       </c>
       <c r="C140" t="n">
-        <v>135.0800018310547</v>
+        <v>123.7200012207031</v>
       </c>
       <c r="D140" t="n">
-        <v>131.1499938964844</v>
+        <v>120.3420028686523</v>
       </c>
       <c r="E140" t="n">
-        <v>135.0099945068359</v>
+        <v>120.7699966430664</v>
       </c>
       <c r="F140" t="n">
-        <v>5353300</v>
+        <v>5940200</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B141" t="n">
-        <v>131.7899932861328</v>
+        <v>122.0100021362305</v>
       </c>
       <c r="C141" t="n">
-        <v>132.5</v>
+        <v>123.3399963378906</v>
       </c>
       <c r="D141" t="n">
-        <v>122.5100021362305</v>
+        <v>115.4199981689453</v>
       </c>
       <c r="E141" t="n">
-        <v>122.5500030517578</v>
+        <v>116.129997253418</v>
       </c>
       <c r="F141" t="n">
-        <v>7553500</v>
+        <v>7540500</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B142" t="n">
-        <v>121.3399963378906</v>
+        <v>118.620002746582</v>
       </c>
       <c r="C142" t="n">
-        <v>123.7200012207031</v>
+        <v>123.4599990844727</v>
       </c>
       <c r="D142" t="n">
-        <v>120.3420028686523</v>
+        <v>117.4199981689453</v>
       </c>
       <c r="E142" t="n">
-        <v>120.7699966430664</v>
+        <v>122.7799987792969</v>
       </c>
       <c r="F142" t="n">
-        <v>5940200</v>
+        <v>7837700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B143" t="n">
-        <v>122.0100021362305</v>
+        <v>126.0599975585938</v>
       </c>
       <c r="C143" t="n">
-        <v>123.3399963378906</v>
+        <v>127.25</v>
       </c>
       <c r="D143" t="n">
-        <v>115.4199981689453</v>
+        <v>124.6600036621094</v>
       </c>
       <c r="E143" t="n">
-        <v>116.129997253418</v>
+        <v>124.8499984741211</v>
       </c>
       <c r="F143" t="n">
-        <v>7540500</v>
+        <v>5037700</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B144" t="n">
-        <v>118.620002746582</v>
+        <v>121.0999984741211</v>
       </c>
       <c r="C144" t="n">
-        <v>123.4599990844727</v>
+        <v>127.1999969482422</v>
       </c>
       <c r="D144" t="n">
-        <v>117.4199981689453</v>
+        <v>119.7910003662109</v>
       </c>
       <c r="E144" t="n">
-        <v>122.7799987792969</v>
+        <v>126.6800003051758</v>
       </c>
       <c r="F144" t="n">
-        <v>7837700</v>
+        <v>5125100</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B145" t="n">
-        <v>126.0599975585938</v>
+        <v>127.3199996948242</v>
       </c>
       <c r="C145" t="n">
-        <v>127.25</v>
+        <v>128.1649932861328</v>
       </c>
       <c r="D145" t="n">
-        <v>124.6600036621094</v>
+        <v>125.1650009155273</v>
       </c>
       <c r="E145" t="n">
-        <v>124.8499984741211</v>
+        <v>126.25</v>
       </c>
       <c r="F145" t="n">
-        <v>5037700</v>
+        <v>3033100</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B146" t="n">
-        <v>121.0999984741211</v>
+        <v>127.8499984741211</v>
       </c>
       <c r="C146" t="n">
-        <v>127.1999969482422</v>
+        <v>133.6999969482422</v>
       </c>
       <c r="D146" t="n">
-        <v>119.7910003662109</v>
+        <v>127.5500030517578</v>
       </c>
       <c r="E146" t="n">
-        <v>126.6800003051758</v>
+        <v>133.6399993896484</v>
       </c>
       <c r="F146" t="n">
-        <v>5125100</v>
+        <v>5758000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B147" t="n">
-        <v>127.3199996948242</v>
+        <v>143</v>
       </c>
       <c r="C147" t="n">
-        <v>128.1649932861328</v>
+        <v>146.1600036621094</v>
       </c>
       <c r="D147" t="n">
-        <v>125.1650009155273</v>
+        <v>141.1199951171875</v>
       </c>
       <c r="E147" t="n">
-        <v>126.25</v>
+        <v>145.0700073242188</v>
       </c>
       <c r="F147" t="n">
-        <v>3033100</v>
+        <v>12136800</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B148" t="n">
-        <v>127.8499984741211</v>
+        <v>145.1100006103516</v>
       </c>
       <c r="C148" t="n">
-        <v>133.6999969482422</v>
+        <v>146.1900024414062</v>
       </c>
       <c r="D148" t="n">
-        <v>127.5500030517578</v>
+        <v>141.1100006103516</v>
       </c>
       <c r="E148" t="n">
-        <v>133.6399993896484</v>
+        <v>146.0500030517578</v>
       </c>
       <c r="F148" t="n">
-        <v>5758000</v>
+        <v>7266100</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B149" t="n">
-        <v>143</v>
+        <v>147.5399932861328</v>
       </c>
       <c r="C149" t="n">
-        <v>146.1600036621094</v>
+        <v>149.3399963378906</v>
       </c>
       <c r="D149" t="n">
-        <v>141.1199951171875</v>
+        <v>145.3999938964844</v>
       </c>
       <c r="E149" t="n">
-        <v>145.0700073242188</v>
+        <v>147.3500061035156</v>
       </c>
       <c r="F149" t="n">
-        <v>12136800</v>
+        <v>7054100</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B150" t="n">
-        <v>145.1100006103516</v>
+        <v>146.7299957275391</v>
       </c>
       <c r="C150" t="n">
-        <v>146.1900024414062</v>
+        <v>152.1399993896484</v>
       </c>
       <c r="D150" t="n">
-        <v>141.1100006103516</v>
+        <v>144.7960052490234</v>
       </c>
       <c r="E150" t="n">
-        <v>146.0500030517578</v>
+        <v>152.0200042724609</v>
       </c>
       <c r="F150" t="n">
-        <v>7266100</v>
+        <v>7217900</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B151" t="n">
-        <v>147.5399932861328</v>
+        <v>153.9900054931641</v>
       </c>
       <c r="C151" t="n">
-        <v>149.3399963378906</v>
+        <v>155.4100036621094</v>
       </c>
       <c r="D151" t="n">
-        <v>145.3999938964844</v>
+        <v>150.9859924316406</v>
       </c>
       <c r="E151" t="n">
-        <v>147.3500061035156</v>
+        <v>154.3699951171875</v>
       </c>
       <c r="F151" t="n">
-        <v>7054100</v>
+        <v>7114000</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B152" t="n">
-        <v>146.7299957275391</v>
+        <v>154.8200073242188</v>
       </c>
       <c r="C152" t="n">
-        <v>152.1399993896484</v>
+        <v>155.2250061035156</v>
       </c>
       <c r="D152" t="n">
-        <v>144.7960052490234</v>
+        <v>150.5200042724609</v>
       </c>
       <c r="E152" t="n">
-        <v>152.0200042724609</v>
+        <v>154.3300018310547</v>
       </c>
       <c r="F152" t="n">
-        <v>7217900</v>
+        <v>5835300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B153" t="n">
-        <v>153.9900054931641</v>
+        <v>155.9199981689453</v>
       </c>
       <c r="C153" t="n">
-        <v>155.4100036621094</v>
+        <v>161.0099945068359</v>
       </c>
       <c r="D153" t="n">
-        <v>150.9859924316406</v>
+        <v>153.3600006103516</v>
       </c>
       <c r="E153" t="n">
-        <v>154.3699951171875</v>
+        <v>161.0099945068359</v>
       </c>
       <c r="F153" t="n">
-        <v>7114000</v>
+        <v>7205600</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B154" t="n">
-        <v>154.8200073242188</v>
+        <v>162.2350006103516</v>
       </c>
       <c r="C154" t="n">
-        <v>155.2250061035156</v>
+        <v>165.2799987792969</v>
       </c>
       <c r="D154" t="n">
-        <v>150.5200042724609</v>
+        <v>160.4700012207031</v>
       </c>
       <c r="E154" t="n">
-        <v>154.3300018310547</v>
+        <v>164.2299957275391</v>
       </c>
       <c r="F154" t="n">
-        <v>5835300</v>
+        <v>8216400</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B155" t="n">
-        <v>155.9199981689453</v>
+        <v>165</v>
       </c>
       <c r="C155" t="n">
-        <v>161.0099945068359</v>
+        <v>167.8999938964844</v>
       </c>
       <c r="D155" t="n">
-        <v>153.3600006103516</v>
+        <v>164.4900054931641</v>
       </c>
       <c r="E155" t="n">
-        <v>161.0099945068359</v>
+        <v>166.8500061035156</v>
       </c>
       <c r="F155" t="n">
-        <v>7205600</v>
+        <v>6113300</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B156" t="n">
-        <v>162.2350006103516</v>
+        <v>170</v>
       </c>
       <c r="C156" t="n">
-        <v>165.2799987792969</v>
+        <v>173.8500061035156</v>
       </c>
       <c r="D156" t="n">
-        <v>160.4700012207031</v>
+        <v>167.2200012207031</v>
       </c>
       <c r="E156" t="n">
-        <v>164.2299957275391</v>
+        <v>172.8600006103516</v>
       </c>
       <c r="F156" t="n">
-        <v>8216400</v>
+        <v>8918900</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B157" t="n">
-        <v>165</v>
+        <v>174.3999938964844</v>
       </c>
       <c r="C157" t="n">
-        <v>167.8999938964844</v>
+        <v>178.4799957275391</v>
       </c>
       <c r="D157" t="n">
-        <v>164.4900054931641</v>
+        <v>171.1399993896484</v>
       </c>
       <c r="E157" t="n">
-        <v>166.8500061035156</v>
+        <v>177.7299957275391</v>
       </c>
       <c r="F157" t="n">
-        <v>6113300</v>
+        <v>8699400</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B158" t="n">
-        <v>170</v>
+        <v>177.5</v>
       </c>
       <c r="C158" t="n">
-        <v>173.8500061035156</v>
+        <v>177.75</v>
       </c>
       <c r="D158" t="n">
-        <v>167.2200012207031</v>
+        <v>169.3800048828125</v>
       </c>
       <c r="E158" t="n">
-        <v>172.8600006103516</v>
+        <v>172.5500030517578</v>
       </c>
       <c r="F158" t="n">
-        <v>8918900</v>
+        <v>7428000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B159" t="n">
-        <v>174.3999938964844</v>
+        <v>174.5299987792969</v>
       </c>
       <c r="C159" t="n">
-        <v>178.4799957275391</v>
+        <v>179.8000030517578</v>
       </c>
       <c r="D159" t="n">
-        <v>171.1399993896484</v>
+        <v>173.5200042724609</v>
       </c>
       <c r="E159" t="n">
-        <v>177.7299957275391</v>
+        <v>176.9100036621094</v>
       </c>
       <c r="F159" t="n">
-        <v>8699400</v>
+        <v>7508000</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B160" t="n">
-        <v>177.5</v>
+        <v>176.7200012207031</v>
       </c>
       <c r="C160" t="n">
-        <v>177.75</v>
+        <v>176.7599945068359</v>
       </c>
       <c r="D160" t="n">
-        <v>169.3800048828125</v>
+        <v>168.5099945068359</v>
       </c>
       <c r="E160" t="n">
-        <v>172.5500030517578</v>
+        <v>172.4700012207031</v>
       </c>
       <c r="F160" t="n">
-        <v>7428000</v>
+        <v>6782500</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B161" t="n">
-        <v>174.5299987792969</v>
+        <v>166.4799957275391</v>
       </c>
       <c r="C161" t="n">
-        <v>179.8000030517578</v>
+        <v>167.8200073242188</v>
       </c>
       <c r="D161" t="n">
-        <v>173.5200042724609</v>
+        <v>162.25</v>
       </c>
       <c r="E161" t="n">
-        <v>176.9100036621094</v>
+        <v>165.2899932861328</v>
       </c>
       <c r="F161" t="n">
-        <v>7508000</v>
+        <v>7414100</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B162" t="n">
-        <v>176.7200012207031</v>
+        <v>166.1000061035156</v>
       </c>
       <c r="C162" t="n">
-        <v>176.7599945068359</v>
+        <v>168.7299957275391</v>
       </c>
       <c r="D162" t="n">
-        <v>168.5099945068359</v>
+        <v>163.4199981689453</v>
       </c>
       <c r="E162" t="n">
-        <v>172.4700012207031</v>
+        <v>168.6799926757812</v>
       </c>
       <c r="F162" t="n">
-        <v>6782500</v>
+        <v>6270500</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B163" t="n">
-        <v>166.4799957275391</v>
+        <v>172.0099945068359</v>
       </c>
       <c r="C163" t="n">
-        <v>167.8200073242188</v>
+        <v>173.5800018310547</v>
       </c>
       <c r="D163" t="n">
-        <v>162.25</v>
+        <v>167.7599945068359</v>
       </c>
       <c r="E163" t="n">
-        <v>165.2899932861328</v>
+        <v>172.7100067138672</v>
       </c>
       <c r="F163" t="n">
-        <v>7414100</v>
+        <v>6141700</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B164" t="n">
-        <v>166.1000061035156</v>
+        <v>172.9900054931641</v>
       </c>
       <c r="C164" t="n">
-        <v>168.7299957275391</v>
+        <v>177.1799926757812</v>
       </c>
       <c r="D164" t="n">
-        <v>163.4199981689453</v>
+        <v>172</v>
       </c>
       <c r="E164" t="n">
-        <v>168.6799926757812</v>
+        <v>172.6999969482422</v>
       </c>
       <c r="F164" t="n">
-        <v>6270500</v>
+        <v>7652400</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B165" t="n">
-        <v>172.0099945068359</v>
+        <v>175.6799926757812</v>
       </c>
       <c r="C165" t="n">
-        <v>173.5800018310547</v>
+        <v>179.1000061035156</v>
       </c>
       <c r="D165" t="n">
-        <v>167.7599945068359</v>
+        <v>172.2850036621094</v>
       </c>
       <c r="E165" t="n">
-        <v>172.7100067138672</v>
+        <v>172.6199951171875</v>
       </c>
       <c r="F165" t="n">
-        <v>6141700</v>
+        <v>7167900</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B166" t="n">
-        <v>172.9900054931641</v>
+        <v>177</v>
       </c>
       <c r="C166" t="n">
-        <v>177.1799926757812</v>
+        <v>177.2200012207031</v>
       </c>
       <c r="D166" t="n">
-        <v>172</v>
+        <v>169.8899993896484</v>
       </c>
       <c r="E166" t="n">
-        <v>172.6999969482422</v>
+        <v>170.2200012207031</v>
       </c>
       <c r="F166" t="n">
-        <v>7652400</v>
+        <v>15684800</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B167" t="n">
-        <v>175.6799926757812</v>
+        <v>153</v>
       </c>
       <c r="C167" t="n">
-        <v>179.1000061035156</v>
+        <v>154.8300018310547</v>
       </c>
       <c r="D167" t="n">
-        <v>172.2850036621094</v>
+        <v>140.5800018310547</v>
       </c>
       <c r="E167" t="n">
-        <v>172.6199951171875</v>
+        <v>147.0599975585938</v>
       </c>
       <c r="F167" t="n">
-        <v>7167900</v>
+        <v>35627200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B168" t="n">
-        <v>177</v>
+        <v>149.2200012207031</v>
       </c>
       <c r="C168" t="n">
-        <v>177.2200012207031</v>
+        <v>149.4400024414062</v>
       </c>
       <c r="D168" t="n">
-        <v>169.8899993896484</v>
+        <v>139.6799926757812</v>
       </c>
       <c r="E168" t="n">
-        <v>170.2200012207031</v>
+        <v>141.75</v>
       </c>
       <c r="F168" t="n">
-        <v>15684800</v>
+        <v>18255700</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B169" t="n">
-        <v>153</v>
+        <v>142.6499938964844</v>
       </c>
       <c r="C169" t="n">
-        <v>154.8300018310547</v>
+        <v>143.9900054931641</v>
       </c>
       <c r="D169" t="n">
-        <v>140.5800018310547</v>
+        <v>138.6000061035156</v>
       </c>
       <c r="E169" t="n">
-        <v>147.0599975585938</v>
+        <v>141.7700042724609</v>
       </c>
       <c r="F169" t="n">
-        <v>35627200</v>
+        <v>20371600</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B170" t="n">
-        <v>149.2200012207031</v>
+        <v>141.3999938964844</v>
       </c>
       <c r="C170" t="n">
-        <v>149.4400024414062</v>
+        <v>142.6199951171875</v>
       </c>
       <c r="D170" t="n">
-        <v>139.6799926757812</v>
+        <v>135.1300048828125</v>
       </c>
       <c r="E170" t="n">
-        <v>141.75</v>
+        <v>136.4299926757812</v>
       </c>
       <c r="F170" t="n">
-        <v>18255700</v>
+        <v>18520900</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B171" t="n">
-        <v>142.6499938964844</v>
+        <v>136.7799987792969</v>
       </c>
       <c r="C171" t="n">
-        <v>143.9900054931641</v>
+        <v>142.9400024414062</v>
       </c>
       <c r="D171" t="n">
-        <v>138.6000061035156</v>
+        <v>135.3699951171875</v>
       </c>
       <c r="E171" t="n">
-        <v>141.7700042724609</v>
+        <v>142.5399932861328</v>
       </c>
       <c r="F171" t="n">
-        <v>20371600</v>
+        <v>12796100</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B172" t="n">
-        <v>141.3999938964844</v>
+        <v>144.8000030517578</v>
       </c>
       <c r="C172" t="n">
-        <v>142.6199951171875</v>
+        <v>147.3099975585938</v>
       </c>
       <c r="D172" t="n">
-        <v>135.1300048828125</v>
+        <v>140.3000030517578</v>
       </c>
       <c r="E172" t="n">
-        <v>136.4299926757812</v>
+        <v>140.6900024414062</v>
       </c>
       <c r="F172" t="n">
-        <v>18520900</v>
+        <v>14164600</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B173" t="n">
-        <v>136.7799987792969</v>
+        <v>142.5</v>
       </c>
       <c r="C173" t="n">
-        <v>142.9400024414062</v>
+        <v>147.8899993896484</v>
       </c>
       <c r="D173" t="n">
-        <v>135.3699951171875</v>
+        <v>141</v>
       </c>
       <c r="E173" t="n">
-        <v>142.5399932861328</v>
+        <v>147.8099975585938</v>
       </c>
       <c r="F173" t="n">
-        <v>12796100</v>
+        <v>15728200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B174" t="n">
-        <v>144.8000030517578</v>
+        <v>144.9900054931641</v>
       </c>
       <c r="C174" t="n">
-        <v>147.3099975585938</v>
+        <v>145.8999938964844</v>
       </c>
       <c r="D174" t="n">
-        <v>140.3000030517578</v>
+        <v>141.7799987792969</v>
       </c>
       <c r="E174" t="n">
-        <v>140.6900024414062</v>
+        <v>141.9700012207031</v>
       </c>
       <c r="F174" t="n">
-        <v>14164600</v>
+        <v>10833000</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B175" t="n">
-        <v>142.5</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="C175" t="n">
-        <v>147.8899993896484</v>
+        <v>143.6699981689453</v>
       </c>
       <c r="D175" t="n">
-        <v>141</v>
+        <v>138.6399993896484</v>
       </c>
       <c r="E175" t="n">
-        <v>147.8099975585938</v>
+        <v>141.7100067138672</v>
       </c>
       <c r="F175" t="n">
-        <v>15728200</v>
+        <v>8634500</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B176" t="n">
-        <v>144.9900054931641</v>
+        <v>139.5800018310547</v>
       </c>
       <c r="C176" t="n">
-        <v>145.8999938964844</v>
+        <v>142.5</v>
       </c>
       <c r="D176" t="n">
-        <v>141.7799987792969</v>
+        <v>137</v>
       </c>
       <c r="E176" t="n">
-        <v>141.9700012207031</v>
+        <v>141.5800018310547</v>
       </c>
       <c r="F176" t="n">
-        <v>10833000</v>
+        <v>8800800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B177" t="n">
-        <v>143.0200042724609</v>
+        <v>142</v>
       </c>
       <c r="C177" t="n">
-        <v>143.6699981689453</v>
+        <v>143.2599945068359</v>
       </c>
       <c r="D177" t="n">
-        <v>138.6399993896484</v>
+        <v>137.5</v>
       </c>
       <c r="E177" t="n">
-        <v>141.7100067138672</v>
+        <v>140.4900054931641</v>
       </c>
       <c r="F177" t="n">
-        <v>8634500</v>
+        <v>9617000</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B178" t="n">
-        <v>139.5800018310547</v>
+        <v>139.3000030517578</v>
       </c>
       <c r="C178" t="n">
-        <v>142.5</v>
+        <v>148.9900054931641</v>
       </c>
       <c r="D178" t="n">
-        <v>137</v>
+        <v>139.125</v>
       </c>
       <c r="E178" t="n">
-        <v>141.5800018310547</v>
+        <v>148.5899963378906</v>
       </c>
       <c r="F178" t="n">
-        <v>8800800</v>
+        <v>11620600</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B179" t="n">
-        <v>142</v>
+        <v>152.2599945068359</v>
       </c>
       <c r="C179" t="n">
-        <v>143.2599945068359</v>
+        <v>154.3899993896484</v>
       </c>
       <c r="D179" t="n">
-        <v>137.5</v>
+        <v>149</v>
       </c>
       <c r="E179" t="n">
-        <v>140.4900054931641</v>
+        <v>154.0299987792969</v>
       </c>
       <c r="F179" t="n">
-        <v>9617000</v>
+        <v>10554600</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B180" t="n">
-        <v>139.3000030517578</v>
+        <v>157.5050048828125</v>
       </c>
       <c r="C180" t="n">
-        <v>148.9900054931641</v>
+        <v>160.1399993896484</v>
       </c>
       <c r="D180" t="n">
-        <v>139.125</v>
+        <v>153.8899993896484</v>
       </c>
       <c r="E180" t="n">
-        <v>148.5899963378906</v>
+        <v>158.0099945068359</v>
       </c>
       <c r="F180" t="n">
-        <v>11620600</v>
+        <v>11835300</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B181" t="n">
-        <v>152.2599945068359</v>
+        <v>157.8500061035156</v>
       </c>
       <c r="C181" t="n">
-        <v>154.3899993896484</v>
+        <v>158.1100006103516</v>
       </c>
       <c r="D181" t="n">
-        <v>149</v>
+        <v>153.5700073242188</v>
       </c>
       <c r="E181" t="n">
-        <v>154.0299987792969</v>
+        <v>154.3099975585938</v>
       </c>
       <c r="F181" t="n">
-        <v>10554600</v>
+        <v>6982200</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B182" t="n">
-        <v>157.5050048828125</v>
+        <v>154</v>
       </c>
       <c r="C182" t="n">
-        <v>160.1399993896484</v>
+        <v>156.3800048828125</v>
       </c>
       <c r="D182" t="n">
-        <v>153.8899993896484</v>
+        <v>150.6600036621094</v>
       </c>
       <c r="E182" t="n">
-        <v>158.0099945068359</v>
+        <v>155.2700042724609</v>
       </c>
       <c r="F182" t="n">
-        <v>11835300</v>
+        <v>7194300</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B183" t="n">
-        <v>157.8500061035156</v>
+        <v>157.3999938964844</v>
       </c>
       <c r="C183" t="n">
-        <v>158.1100006103516</v>
+        <v>161.5</v>
       </c>
       <c r="D183" t="n">
-        <v>153.5700073242188</v>
+        <v>155.8000030517578</v>
       </c>
       <c r="E183" t="n">
-        <v>154.3099975585938</v>
+        <v>159.4700012207031</v>
       </c>
       <c r="F183" t="n">
-        <v>6982200</v>
+        <v>15385900</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B184" t="n">
-        <v>154</v>
+        <v>162.1399993896484</v>
       </c>
       <c r="C184" t="n">
-        <v>156.3800048828125</v>
+        <v>172.3300018310547</v>
       </c>
       <c r="D184" t="n">
-        <v>150.6600036621094</v>
+        <v>161.2799987792969</v>
       </c>
       <c r="E184" t="n">
-        <v>155.2700042724609</v>
+        <v>170.6799926757812</v>
       </c>
       <c r="F184" t="n">
-        <v>7194300</v>
+        <v>9991500</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B185" t="n">
-        <v>157.3999938964844</v>
+        <v>170.6999969482422</v>
       </c>
       <c r="C185" t="n">
-        <v>161.5</v>
+        <v>177.4799957275391</v>
       </c>
       <c r="D185" t="n">
-        <v>155.8000030517578</v>
+        <v>170.6900024414062</v>
       </c>
       <c r="E185" t="n">
-        <v>159.4700012207031</v>
+        <v>175.3300018310547</v>
       </c>
       <c r="F185" t="n">
-        <v>15385900</v>
+        <v>9144300</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B186" t="n">
-        <v>162.1399993896484</v>
+        <v>175.4900054931641</v>
       </c>
       <c r="C186" t="n">
-        <v>172.3300018310547</v>
+        <v>177.4799957275391</v>
       </c>
       <c r="D186" t="n">
-        <v>161.2799987792969</v>
+        <v>168.7100067138672</v>
       </c>
       <c r="E186" t="n">
-        <v>170.6799926757812</v>
+        <v>174.3699951171875</v>
       </c>
       <c r="F186" t="n">
-        <v>9991500</v>
+        <v>8069700</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B187" t="n">
-        <v>170.6999969482422</v>
+        <v>163.0800018310547</v>
       </c>
       <c r="C187" t="n">
-        <v>177.4799957275391</v>
+        <v>167.7899932861328</v>
       </c>
       <c r="D187" t="n">
-        <v>170.6900024414062</v>
+        <v>157.3999938964844</v>
       </c>
       <c r="E187" t="n">
-        <v>175.3300018310547</v>
+        <v>166.0099945068359</v>
       </c>
       <c r="F187" t="n">
-        <v>9144300</v>
+        <v>10214000</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B188" t="n">
-        <v>175.4900054931641</v>
+        <v>159.4600067138672</v>
       </c>
       <c r="C188" t="n">
-        <v>177.4799957275391</v>
+        <v>161.1929931640625</v>
       </c>
       <c r="D188" t="n">
-        <v>168.7100067138672</v>
+        <v>152.1900024414062</v>
       </c>
       <c r="E188" t="n">
-        <v>174.3699951171875</v>
+        <v>154.2700042724609</v>
       </c>
       <c r="F188" t="n">
-        <v>8069700</v>
+        <v>9094700</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B189" t="n">
-        <v>163.0800018310547</v>
+        <v>157.9499969482422</v>
       </c>
       <c r="C189" t="n">
-        <v>167.7899932861328</v>
+        <v>159.2299957275391</v>
       </c>
       <c r="D189" t="n">
-        <v>157.3999938964844</v>
+        <v>153.2530059814453</v>
       </c>
       <c r="E189" t="n">
-        <v>166.0099945068359</v>
+        <v>156.3999938964844</v>
       </c>
       <c r="F189" t="n">
-        <v>10214000</v>
+        <v>6043100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B190" t="n">
-        <v>159.4600067138672</v>
+        <v>157.75</v>
       </c>
       <c r="C190" t="n">
-        <v>161.1929931640625</v>
+        <v>158.9900054931641</v>
       </c>
       <c r="D190" t="n">
-        <v>152.1900024414062</v>
+        <v>145.3200073242188</v>
       </c>
       <c r="E190" t="n">
-        <v>154.2700042724609</v>
+        <v>152.1600036621094</v>
       </c>
       <c r="F190" t="n">
-        <v>9094700</v>
+        <v>7334100</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B191" t="n">
-        <v>157.9499969482422</v>
+        <v>151</v>
       </c>
       <c r="C191" t="n">
-        <v>159.2299957275391</v>
+        <v>154.9700012207031</v>
       </c>
       <c r="D191" t="n">
-        <v>153.2530059814453</v>
+        <v>149</v>
       </c>
       <c r="E191" t="n">
-        <v>156.3999938964844</v>
+        <v>151.7599945068359</v>
       </c>
       <c r="F191" t="n">
-        <v>6043100</v>
+        <v>6867400</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B192" t="n">
-        <v>157.75</v>
+        <v>153.5800018310547</v>
       </c>
       <c r="C192" t="n">
-        <v>158.9900054931641</v>
+        <v>157.0700073242188</v>
       </c>
       <c r="D192" t="n">
-        <v>145.3200073242188</v>
+        <v>150.2799987792969</v>
       </c>
       <c r="E192" t="n">
-        <v>152.1600036621094</v>
+        <v>156.3999938964844</v>
       </c>
       <c r="F192" t="n">
-        <v>7334100</v>
+        <v>5326700</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B193" t="n">
-        <v>151</v>
+        <v>160.1100006103516</v>
       </c>
       <c r="C193" t="n">
-        <v>154.9700012207031</v>
+        <v>165.25</v>
       </c>
       <c r="D193" t="n">
-        <v>149</v>
+        <v>159.1349945068359</v>
       </c>
       <c r="E193" t="n">
-        <v>151.7599945068359</v>
+        <v>163.2400054931641</v>
       </c>
       <c r="F193" t="n">
-        <v>6867400</v>
+        <v>6052500</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B194" t="n">
-        <v>153.5800018310547</v>
+        <v>165.9600067138672</v>
       </c>
       <c r="C194" t="n">
-        <v>157.0700073242188</v>
+        <v>169.2799987792969</v>
       </c>
       <c r="D194" t="n">
-        <v>150.2799987792969</v>
+        <v>163.5099945068359</v>
       </c>
       <c r="E194" t="n">
-        <v>156.3999938964844</v>
+        <v>169.0899963378906</v>
       </c>
       <c r="F194" t="n">
-        <v>5326700</v>
+        <v>7240800</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B195" t="n">
-        <v>160.1100006103516</v>
+        <v>169.3000030517578</v>
       </c>
       <c r="C195" t="n">
-        <v>165.25</v>
+        <v>171.2100067138672</v>
       </c>
       <c r="D195" t="n">
-        <v>159.1349945068359</v>
+        <v>166.7799987792969</v>
       </c>
       <c r="E195" t="n">
-        <v>163.2400054931641</v>
+        <v>168.0099945068359</v>
       </c>
       <c r="F195" t="n">
-        <v>6052500</v>
+        <v>8090900</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B196" t="n">
-        <v>165.9600067138672</v>
+        <v>169.8899993896484</v>
       </c>
       <c r="C196" t="n">
-        <v>169.2799987792969</v>
+        <v>171.2899932861328</v>
       </c>
       <c r="D196" t="n">
-        <v>163.5099945068359</v>
+        <v>163.9299926757812</v>
       </c>
       <c r="E196" t="n">
-        <v>169.0899963378906</v>
+        <v>164.9299926757812</v>
       </c>
       <c r="F196" t="n">
-        <v>7240800</v>
+        <v>6229500</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B197" t="n">
-        <v>169.3000030517578</v>
+        <v>171.1999969482422</v>
       </c>
       <c r="C197" t="n">
-        <v>171.2100067138672</v>
+        <v>172</v>
       </c>
       <c r="D197" t="n">
-        <v>166.7799987792969</v>
+        <v>167.5850067138672</v>
       </c>
       <c r="E197" t="n">
-        <v>168.0099945068359</v>
+        <v>169.6699981689453</v>
       </c>
       <c r="F197" t="n">
-        <v>8090900</v>
+        <v>11130400</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B198" t="n">
-        <v>169.8899993896484</v>
+        <v>170.1100006103516</v>
       </c>
       <c r="C198" t="n">
-        <v>171.2899932861328</v>
+        <v>175.1999969482422</v>
       </c>
       <c r="D198" t="n">
-        <v>163.9299926757812</v>
+        <v>166.6600036621094</v>
       </c>
       <c r="E198" t="n">
-        <v>164.9299926757812</v>
+        <v>174.5599975585938</v>
       </c>
       <c r="F198" t="n">
-        <v>6229500</v>
+        <v>9494400</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B199" t="n">
-        <v>171.1999969482422</v>
+        <v>165.4299926757812</v>
       </c>
       <c r="C199" t="n">
-        <v>172</v>
+        <v>165.4299926757812</v>
       </c>
       <c r="D199" t="n">
-        <v>167.5850067138672</v>
+        <v>159.3600006103516</v>
       </c>
       <c r="E199" t="n">
-        <v>169.6699981689453</v>
+        <v>162.1999969482422</v>
       </c>
       <c r="F199" t="n">
-        <v>11130400</v>
+        <v>7770100</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B200" t="n">
-        <v>170.1100006103516</v>
+        <v>162.3249969482422</v>
       </c>
       <c r="C200" t="n">
-        <v>175.1999969482422</v>
+        <v>165.6799926757812</v>
       </c>
       <c r="D200" t="n">
-        <v>166.6600036621094</v>
+        <v>160.5700073242188</v>
       </c>
       <c r="E200" t="n">
-        <v>174.5599975585938</v>
+        <v>161.7400054931641</v>
       </c>
       <c r="F200" t="n">
-        <v>9494400</v>
+        <v>6350600</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B201" t="n">
-        <v>165.4299926757812</v>
+        <v>167.7599945068359</v>
       </c>
       <c r="C201" t="n">
-        <v>165.4299926757812</v>
+        <v>170.1600036621094</v>
       </c>
       <c r="D201" t="n">
-        <v>159.3600006103516</v>
+        <v>159.4600067138672</v>
       </c>
       <c r="E201" t="n">
-        <v>162.1999969482422</v>
+        <v>165.4499969482422</v>
       </c>
       <c r="F201" t="n">
-        <v>7770100</v>
+        <v>8231200</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B202" t="n">
-        <v>162.3249969482422</v>
+        <v>159.9400024414062</v>
       </c>
       <c r="C202" t="n">
-        <v>165.6799926757812</v>
+        <v>161.2299957275391</v>
       </c>
       <c r="D202" t="n">
-        <v>160.5700073242188</v>
+        <v>154.7400054931641</v>
       </c>
       <c r="E202" t="n">
-        <v>161.7400054931641</v>
+        <v>157.6000061035156</v>
       </c>
       <c r="F202" t="n">
-        <v>6350600</v>
+        <v>11865200</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B203" t="n">
-        <v>167.7599945068359</v>
+        <v>158.8600006103516</v>
       </c>
       <c r="C203" t="n">
-        <v>170.1600036621094</v>
+        <v>165.6600036621094</v>
       </c>
       <c r="D203" t="n">
-        <v>159.4600067138672</v>
+        <v>155.2200012207031</v>
       </c>
       <c r="E203" t="n">
-        <v>165.4499969482422</v>
+        <v>164.1000061035156</v>
       </c>
       <c r="F203" t="n">
-        <v>8231200</v>
+        <v>8535700</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B204" t="n">
-        <v>159.9400024414062</v>
+        <v>164.1100006103516</v>
       </c>
       <c r="C204" t="n">
-        <v>161.2299957275391</v>
+        <v>172.5489959716797</v>
       </c>
       <c r="D204" t="n">
-        <v>154.7400054931641</v>
+        <v>162.6999969482422</v>
       </c>
       <c r="E204" t="n">
-        <v>157.6000061035156</v>
+        <v>169.8800048828125</v>
       </c>
       <c r="F204" t="n">
-        <v>11865200</v>
+        <v>10281800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B205" t="n">
-        <v>158.8600006103516</v>
+        <v>165.5549926757812</v>
       </c>
       <c r="C205" t="n">
-        <v>165.6600036621094</v>
+        <v>170.5</v>
       </c>
       <c r="D205" t="n">
-        <v>155.2200012207031</v>
+        <v>159.1999969482422</v>
       </c>
       <c r="E205" t="n">
-        <v>164.1000061035156</v>
+        <v>166.6199951171875</v>
       </c>
       <c r="F205" t="n">
-        <v>8535700</v>
+        <v>9098200</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B206" t="n">
-        <v>164.1100006103516</v>
+        <v>166.3600006103516</v>
       </c>
       <c r="C206" t="n">
-        <v>172.5489959716797</v>
+        <v>167.7350006103516</v>
       </c>
       <c r="D206" t="n">
-        <v>162.6999969482422</v>
+        <v>156.6499938964844</v>
       </c>
       <c r="E206" t="n">
-        <v>169.8800048828125</v>
+        <v>159.9900054931641</v>
       </c>
       <c r="F206" t="n">
-        <v>10281800</v>
+        <v>9764500</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B207" t="n">
-        <v>165.5549926757812</v>
+        <v>162.8650054931641</v>
       </c>
       <c r="C207" t="n">
-        <v>170.5</v>
+        <v>177.1999969482422</v>
       </c>
       <c r="D207" t="n">
-        <v>159.1999969482422</v>
+        <v>161.3600006103516</v>
       </c>
       <c r="E207" t="n">
-        <v>166.6199951171875</v>
+        <v>173.2799987792969</v>
       </c>
       <c r="F207" t="n">
-        <v>9098200</v>
+        <v>8509300</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B208" t="n">
-        <v>166.3600006103516</v>
+        <v>169.1000061035156</v>
       </c>
       <c r="C208" t="n">
-        <v>167.7350006103516</v>
+        <v>169.2299957275391</v>
       </c>
       <c r="D208" t="n">
-        <v>156.6499938964844</v>
+        <v>162.5899963378906</v>
       </c>
       <c r="E208" t="n">
-        <v>159.9900054931641</v>
+        <v>166.4600067138672</v>
       </c>
       <c r="F208" t="n">
-        <v>9764500</v>
+        <v>8969200</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B209" t="n">
-        <v>162.8650054931641</v>
+        <v>166.1799926757812</v>
       </c>
       <c r="C209" t="n">
-        <v>177.1999969482422</v>
+        <v>181.2700042724609</v>
       </c>
       <c r="D209" t="n">
-        <v>161.3600006103516</v>
+        <v>165.9900054931641</v>
       </c>
       <c r="E209" t="n">
-        <v>173.2799987792969</v>
+        <v>181.0500030517578</v>
       </c>
       <c r="F209" t="n">
-        <v>8509300</v>
+        <v>11912800</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B210" t="n">
-        <v>169.1000061035156</v>
+        <v>187</v>
       </c>
       <c r="C210" t="n">
-        <v>169.2299957275391</v>
+        <v>189.8170013427734</v>
       </c>
       <c r="D210" t="n">
-        <v>162.5899963378906</v>
+        <v>179.8000030517578</v>
       </c>
       <c r="E210" t="n">
-        <v>166.4600067138672</v>
+        <v>184.6900024414062</v>
       </c>
       <c r="F210" t="n">
-        <v>8969200</v>
+        <v>9932000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B211" t="n">
-        <v>166.1799926757812</v>
+        <v>185.2969970703125</v>
       </c>
       <c r="C211" t="n">
-        <v>181.2700042724609</v>
+        <v>187.6199951171875</v>
       </c>
       <c r="D211" t="n">
-        <v>165.9900054931641</v>
+        <v>182.5</v>
       </c>
       <c r="E211" t="n">
-        <v>181.0500030517578</v>
+        <v>186.9600067138672</v>
       </c>
       <c r="F211" t="n">
-        <v>11912800</v>
+        <v>5592500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B212" t="n">
-        <v>187</v>
+        <v>186.2649993896484</v>
       </c>
       <c r="C212" t="n">
-        <v>189.8170013427734</v>
+        <v>189.5599975585938</v>
       </c>
       <c r="D212" t="n">
-        <v>179.8000030517578</v>
+        <v>180.5</v>
       </c>
       <c r="E212" t="n">
-        <v>184.6900024414062</v>
+        <v>181.1499938964844</v>
       </c>
       <c r="F212" t="n">
-        <v>9932000</v>
+        <v>9149500</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B213" t="n">
-        <v>185.2969970703125</v>
+        <v>183.8999938964844</v>
       </c>
       <c r="C213" t="n">
-        <v>187.6199951171875</v>
+        <v>185.6000061035156</v>
       </c>
       <c r="D213" t="n">
-        <v>182.5</v>
+        <v>175.6900024414062</v>
       </c>
       <c r="E213" t="n">
-        <v>186.9600067138672</v>
+        <v>182.5700073242188</v>
       </c>
       <c r="F213" t="n">
-        <v>5592500</v>
+        <v>7566300</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B214" t="n">
-        <v>186.2649993896484</v>
+        <v>184</v>
       </c>
       <c r="C214" t="n">
-        <v>189.5599975585938</v>
+        <v>186.2100067138672</v>
       </c>
       <c r="D214" t="n">
-        <v>180.5</v>
+        <v>166.5</v>
       </c>
       <c r="E214" t="n">
-        <v>181.1499938964844</v>
+        <v>171.9199981689453</v>
       </c>
       <c r="F214" t="n">
-        <v>9149500</v>
+        <v>8095900</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B215" t="n">
-        <v>183.8999938964844</v>
+        <v>169.2100067138672</v>
       </c>
       <c r="C215" t="n">
-        <v>185.6000061035156</v>
+        <v>170.281005859375</v>
       </c>
       <c r="D215" t="n">
-        <v>175.6900024414062</v>
+        <v>163.6799926757812</v>
       </c>
       <c r="E215" t="n">
-        <v>182.5700073242188</v>
+        <v>168.5599975585938</v>
       </c>
       <c r="F215" t="n">
-        <v>7566300</v>
+        <v>8412300</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B216" t="n">
-        <v>184</v>
+        <v>163.1049957275391</v>
       </c>
       <c r="C216" t="n">
-        <v>186.2100067138672</v>
+        <v>171.4299926757812</v>
       </c>
       <c r="D216" t="n">
-        <v>166.5</v>
+        <v>157.1300048828125</v>
       </c>
       <c r="E216" t="n">
-        <v>171.9199981689453</v>
+        <v>168.6100006103516</v>
       </c>
       <c r="F216" t="n">
-        <v>8095900</v>
+        <v>7560400</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B217" t="n">
-        <v>169.2100067138672</v>
+        <v>168.9400024414062</v>
       </c>
       <c r="C217" t="n">
-        <v>170.281005859375</v>
+        <v>172.6000061035156</v>
       </c>
       <c r="D217" t="n">
-        <v>163.6799926757812</v>
+        <v>168.3200073242188</v>
       </c>
       <c r="E217" t="n">
-        <v>168.5599975585938</v>
+        <v>169.3500061035156</v>
       </c>
       <c r="F217" t="n">
-        <v>8412300</v>
+        <v>6025900</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B218" t="n">
-        <v>163.1049957275391</v>
+        <v>174.4400024414062</v>
       </c>
       <c r="C218" t="n">
-        <v>171.4299926757812</v>
+        <v>177.8800048828125</v>
       </c>
       <c r="D218" t="n">
-        <v>157.1300048828125</v>
+        <v>172.1000061035156</v>
       </c>
       <c r="E218" t="n">
-        <v>168.6100006103516</v>
+        <v>174.5800018310547</v>
       </c>
       <c r="F218" t="n">
-        <v>7560400</v>
+        <v>6357800</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B219" t="n">
-        <v>168.9400024414062</v>
+        <v>171.1349945068359</v>
       </c>
       <c r="C219" t="n">
-        <v>172.6000061035156</v>
+        <v>176.4100036621094</v>
       </c>
       <c r="D219" t="n">
-        <v>168.3200073242188</v>
+        <v>170</v>
       </c>
       <c r="E219" t="n">
-        <v>169.3500061035156</v>
+        <v>174.8699951171875</v>
       </c>
       <c r="F219" t="n">
-        <v>6025900</v>
+        <v>3342900</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B220" t="n">
-        <v>174.4400024414062</v>
+        <v>172.7700042724609</v>
       </c>
       <c r="C220" t="n">
-        <v>177.8800048828125</v>
+        <v>179.4799957275391</v>
       </c>
       <c r="D220" t="n">
-        <v>172.1000061035156</v>
+        <v>172.7700042724609</v>
       </c>
       <c r="E220" t="n">
-        <v>174.5800018310547</v>
+        <v>176.6100006103516</v>
       </c>
       <c r="F220" t="n">
-        <v>6357800</v>
+        <v>4338800</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B221" t="n">
-        <v>171.1349945068359</v>
+        <v>174</v>
       </c>
       <c r="C221" t="n">
-        <v>176.4100036621094</v>
+        <v>177.5130004882812</v>
       </c>
       <c r="D221" t="n">
-        <v>170</v>
+        <v>170.9089965820312</v>
       </c>
       <c r="E221" t="n">
-        <v>174.8699951171875</v>
+        <v>173.9900054931641</v>
       </c>
       <c r="F221" t="n">
-        <v>3342900</v>
+        <v>4721500</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B222" t="n">
-        <v>172.7700042724609</v>
+        <v>175.2100067138672</v>
       </c>
       <c r="C222" t="n">
-        <v>179.4799957275391</v>
+        <v>176.7299957275391</v>
       </c>
       <c r="D222" t="n">
-        <v>172.7700042724609</v>
+        <v>165.8999938964844</v>
       </c>
       <c r="E222" t="n">
-        <v>176.6100006103516</v>
+        <v>170.7599945068359</v>
       </c>
       <c r="F222" t="n">
-        <v>4338800</v>
+        <v>6023000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B223" t="n">
-        <v>174</v>
+        <v>165.5700073242188</v>
       </c>
       <c r="C223" t="n">
-        <v>177.5130004882812</v>
+        <v>169.9700012207031</v>
       </c>
       <c r="D223" t="n">
-        <v>170.9089965820312</v>
+        <v>159.2700042724609</v>
       </c>
       <c r="E223" t="n">
-        <v>173.9900054931641</v>
+        <v>169.7100067138672</v>
       </c>
       <c r="F223" t="n">
-        <v>4721500</v>
+        <v>8561600</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B224" t="n">
-        <v>175.2100067138672</v>
+        <v>168.4499969482422</v>
       </c>
       <c r="C224" t="n">
-        <v>176.7299957275391</v>
+        <v>169.3300018310547</v>
       </c>
       <c r="D224" t="n">
-        <v>165.8999938964844</v>
+        <v>156.8399963378906</v>
       </c>
       <c r="E224" t="n">
-        <v>170.7599945068359</v>
+        <v>157.9700012207031</v>
       </c>
       <c r="F224" t="n">
-        <v>6023000</v>
+        <v>8189500</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B225" t="n">
-        <v>165.5700073242188</v>
+        <v>164.5599975585938</v>
       </c>
       <c r="C225" t="n">
-        <v>169.9700012207031</v>
+        <v>171.5099945068359</v>
       </c>
       <c r="D225" t="n">
-        <v>159.2700042724609</v>
+        <v>164.4850006103516</v>
       </c>
       <c r="E225" t="n">
-        <v>169.7100067138672</v>
+        <v>171.0200042724609</v>
       </c>
       <c r="F225" t="n">
-        <v>8561600</v>
+        <v>7284700</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B226" t="n">
-        <v>168.4499969482422</v>
+        <v>177.6000061035156</v>
       </c>
       <c r="C226" t="n">
-        <v>169.3300018310547</v>
+        <v>183.5200042724609</v>
       </c>
       <c r="D226" t="n">
-        <v>156.8399963378906</v>
+        <v>175.6999969482422</v>
       </c>
       <c r="E226" t="n">
-        <v>157.9700012207031</v>
+        <v>180.3500061035156</v>
       </c>
       <c r="F226" t="n">
-        <v>8189500</v>
+        <v>8472300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B227" t="n">
-        <v>164.5599975585938</v>
+        <v>174.4199981689453</v>
       </c>
       <c r="C227" t="n">
-        <v>171.5099945068359</v>
+        <v>186.5700073242188</v>
       </c>
       <c r="D227" t="n">
-        <v>164.4850006103516</v>
+        <v>173.4499969482422</v>
       </c>
       <c r="E227" t="n">
-        <v>171.0200042724609</v>
+        <v>184.8899993896484</v>
       </c>
       <c r="F227" t="n">
-        <v>7284700</v>
+        <v>8335700</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B228" t="n">
-        <v>177.6000061035156</v>
+        <v>187.6999969482422</v>
       </c>
       <c r="C228" t="n">
-        <v>183.5200042724609</v>
+        <v>194.3500061035156</v>
       </c>
       <c r="D228" t="n">
-        <v>175.6999969482422</v>
+        <v>187.0110015869141</v>
       </c>
       <c r="E228" t="n">
-        <v>180.3500061035156</v>
+        <v>190.5099945068359</v>
       </c>
       <c r="F228" t="n">
-        <v>8472300</v>
+        <v>14097400</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B229" t="n">
-        <v>174.4199981689453</v>
+        <v>210.1900024414062</v>
       </c>
       <c r="C229" t="n">
-        <v>186.5700073242188</v>
+        <v>214.8899993896484</v>
       </c>
       <c r="D229" t="n">
-        <v>173.4499969482422</v>
+        <v>191.0099945068359</v>
       </c>
       <c r="E229" t="n">
-        <v>184.8899993896484</v>
+        <v>197.3099975585938</v>
       </c>
       <c r="F229" t="n">
-        <v>8335700</v>
+        <v>20227000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B230" t="n">
-        <v>187.6999969482422</v>
+        <v>192.4100036621094</v>
       </c>
       <c r="C230" t="n">
-        <v>194.3500061035156</v>
+        <v>197.1100006103516</v>
       </c>
       <c r="D230" t="n">
-        <v>187.0110015869141</v>
+        <v>189.4299926757812</v>
       </c>
       <c r="E230" t="n">
-        <v>190.5099945068359</v>
+        <v>192.3200073242188</v>
       </c>
       <c r="F230" t="n">
-        <v>14097400</v>
+        <v>7774600</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B231" t="n">
-        <v>210.1900024414062</v>
+        <v>198</v>
       </c>
       <c r="C231" t="n">
-        <v>214.8899993896484</v>
+        <v>198</v>
       </c>
       <c r="D231" t="n">
-        <v>191.0099945068359</v>
+        <v>187.5</v>
       </c>
       <c r="E231" t="n">
-        <v>197.3099975585938</v>
+        <v>188.6699981689453</v>
       </c>
       <c r="F231" t="n">
-        <v>20227000</v>
+        <v>7208500</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B232" t="n">
-        <v>192.4100036621094</v>
+        <v>192.4900054931641</v>
       </c>
       <c r="C232" t="n">
-        <v>197.1100006103516</v>
+        <v>195.6999969482422</v>
       </c>
       <c r="D232" t="n">
-        <v>189.4299926757812</v>
+        <v>187.0299987792969</v>
       </c>
       <c r="E232" t="n">
-        <v>192.3200073242188</v>
+        <v>191.5200042724609</v>
       </c>
       <c r="F232" t="n">
-        <v>7774600</v>
+        <v>5434100</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B233" t="n">
-        <v>198</v>
+        <v>194.5650024414062</v>
       </c>
       <c r="C233" t="n">
-        <v>198</v>
+        <v>198.9199981689453</v>
       </c>
       <c r="D233" t="n">
-        <v>187.5</v>
+        <v>190.4799957275391</v>
       </c>
       <c r="E233" t="n">
-        <v>188.6699981689453</v>
+        <v>197.8500061035156</v>
       </c>
       <c r="F233" t="n">
-        <v>7208500</v>
+        <v>6277300</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B234" t="n">
-        <v>192.4900054931641</v>
+        <v>205.4700012207031</v>
       </c>
       <c r="C234" t="n">
-        <v>195.6999969482422</v>
+        <v>211.4499969482422</v>
       </c>
       <c r="D234" t="n">
-        <v>187.0299987792969</v>
+        <v>203.7599945068359</v>
       </c>
       <c r="E234" t="n">
-        <v>191.5200042724609</v>
+        <v>210.5</v>
       </c>
       <c r="F234" t="n">
-        <v>5434100</v>
+        <v>10008600</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B235" t="n">
-        <v>194.5650024414062</v>
+        <v>209.7899932861328</v>
       </c>
       <c r="C235" t="n">
-        <v>198.9199981689453</v>
+        <v>210.1100006103516</v>
       </c>
       <c r="D235" t="n">
-        <v>190.4799957275391</v>
+        <v>203.5500030517578</v>
       </c>
       <c r="E235" t="n">
-        <v>197.8500061035156</v>
+        <v>203.6199951171875</v>
       </c>
       <c r="F235" t="n">
-        <v>6277300</v>
+        <v>7907800</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B236" t="n">
-        <v>205.4700012207031</v>
+        <v>205.2700042724609</v>
       </c>
       <c r="C236" t="n">
-        <v>211.4499969482422</v>
+        <v>205.2700042724609</v>
       </c>
       <c r="D236" t="n">
-        <v>203.7599945068359</v>
+        <v>198.2449951171875</v>
       </c>
       <c r="E236" t="n">
-        <v>210.5</v>
+        <v>198.8200073242188</v>
       </c>
       <c r="F236" t="n">
-        <v>10008600</v>
+        <v>4707400</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B237" t="n">
-        <v>209.7899932861328</v>
+        <v>201.1600036621094</v>
       </c>
       <c r="C237" t="n">
-        <v>210.1100006103516</v>
+        <v>202.2649993896484</v>
       </c>
       <c r="D237" t="n">
-        <v>203.5500030517578</v>
+        <v>198.3399963378906</v>
       </c>
       <c r="E237" t="n">
-        <v>203.6199951171875</v>
+        <v>201.8000030517578</v>
       </c>
       <c r="F237" t="n">
-        <v>7907800</v>
+        <v>5683900</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B238" t="n">
-        <v>205.2700042724609</v>
+        <v>196</v>
       </c>
       <c r="C238" t="n">
-        <v>205.2700042724609</v>
+        <v>197.9900054931641</v>
       </c>
       <c r="D238" t="n">
-        <v>198.2449951171875</v>
+        <v>189.6699981689453</v>
       </c>
       <c r="E238" t="n">
-        <v>198.8200073242188</v>
+        <v>193.1799926757812</v>
       </c>
       <c r="F238" t="n">
-        <v>4707400</v>
+        <v>8886900</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B239" t="n">
-        <v>201.1600036621094</v>
+        <v>195.0399932861328</v>
       </c>
       <c r="C239" t="n">
-        <v>202.2649993896484</v>
+        <v>195.5</v>
       </c>
       <c r="D239" t="n">
-        <v>198.3399963378906</v>
+        <v>184.5099945068359</v>
       </c>
       <c r="E239" t="n">
-        <v>201.8000030517578</v>
+        <v>186.4499969482422</v>
       </c>
       <c r="F239" t="n">
-        <v>5683900</v>
+        <v>5740500</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B240" t="n">
-        <v>196</v>
+        <v>185.3099975585938</v>
       </c>
       <c r="C240" t="n">
-        <v>197.9900054931641</v>
+        <v>187.2799987792969</v>
       </c>
       <c r="D240" t="n">
-        <v>189.6699981689453</v>
+        <v>182.8300018310547</v>
       </c>
       <c r="E240" t="n">
-        <v>193.1799926757812</v>
+        <v>183.75</v>
       </c>
       <c r="F240" t="n">
-        <v>8886900</v>
+        <v>4207300</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B241" t="n">
-        <v>195.0399932861328</v>
+        <v>183.7700042724609</v>
       </c>
       <c r="C241" t="n">
-        <v>195.5</v>
+        <v>190.4400024414062</v>
       </c>
       <c r="D241" t="n">
-        <v>184.5099945068359</v>
+        <v>183.5899963378906</v>
       </c>
       <c r="E241" t="n">
-        <v>186.4499969482422</v>
+        <v>188.6499938964844</v>
       </c>
       <c r="F241" t="n">
-        <v>5740500</v>
+        <v>8123600</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B242" t="n">
-        <v>185.3099975585938</v>
+        <v>186</v>
       </c>
       <c r="C242" t="n">
-        <v>187.2799987792969</v>
+        <v>190.25</v>
       </c>
       <c r="D242" t="n">
-        <v>182.8300018310547</v>
+        <v>186</v>
       </c>
       <c r="E242" t="n">
-        <v>183.75</v>
+        <v>188.1499938964844</v>
       </c>
       <c r="F242" t="n">
-        <v>4207300</v>
+        <v>5306400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B243" t="n">
-        <v>183.7700042724609</v>
+        <v>192.3399963378906</v>
       </c>
       <c r="C243" t="n">
-        <v>190.4400024414062</v>
+        <v>193.1499938964844</v>
       </c>
       <c r="D243" t="n">
-        <v>183.5899963378906</v>
+        <v>188.0599975585938</v>
       </c>
       <c r="E243" t="n">
-        <v>188.6499938964844</v>
+        <v>190.9400024414062</v>
       </c>
       <c r="F243" t="n">
-        <v>8123600</v>
+        <v>4385100</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B244" t="n">
-        <v>186</v>
+        <v>190.9049987792969</v>
       </c>
       <c r="C244" t="n">
-        <v>190.25</v>
+        <v>203.3600006103516</v>
       </c>
       <c r="D244" t="n">
-        <v>186</v>
+        <v>190.9049987792969</v>
       </c>
       <c r="E244" t="n">
-        <v>188.1499938964844</v>
+        <v>202.25</v>
       </c>
       <c r="F244" t="n">
-        <v>5306400</v>
+        <v>7664600</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B245" t="n">
-        <v>192.3399963378906</v>
+        <v>205.8999938964844</v>
       </c>
       <c r="C245" t="n">
-        <v>193.1499938964844</v>
+        <v>206.1300048828125</v>
       </c>
       <c r="D245" t="n">
-        <v>188.0599975585938</v>
+        <v>199.2149963378906</v>
       </c>
       <c r="E245" t="n">
-        <v>190.9400024414062</v>
+        <v>201.0899963378906</v>
       </c>
       <c r="F245" t="n">
-        <v>4385100</v>
+        <v>4692700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B246" t="n">
-        <v>190.9049987792969</v>
+        <v>200</v>
       </c>
       <c r="C246" t="n">
-        <v>203.3600006103516</v>
+        <v>200.1000061035156</v>
       </c>
       <c r="D246" t="n">
-        <v>190.9049987792969</v>
+        <v>194.6100006103516</v>
       </c>
       <c r="E246" t="n">
-        <v>202.25</v>
+        <v>195.3800048828125</v>
       </c>
       <c r="F246" t="n">
-        <v>7664600</v>
+        <v>3063000</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B247" t="n">
-        <v>205.8999938964844</v>
+        <v>195.5</v>
       </c>
       <c r="C247" t="n">
-        <v>206.1300048828125</v>
+        <v>197.9900054931641</v>
       </c>
       <c r="D247" t="n">
-        <v>199.2149963378906</v>
+        <v>193.9100036621094</v>
       </c>
       <c r="E247" t="n">
-        <v>201.0899963378906</v>
+        <v>195.6900024414062</v>
       </c>
       <c r="F247" t="n">
-        <v>4692700</v>
+        <v>5021700</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B248" t="n">
-        <v>200</v>
+        <v>195.7700042724609</v>
       </c>
       <c r="C248" t="n">
-        <v>200.1000061035156</v>
+        <v>196.5</v>
       </c>
       <c r="D248" t="n">
-        <v>194.6100006103516</v>
+        <v>188.5599975585938</v>
       </c>
       <c r="E248" t="n">
-        <v>195.3800048828125</v>
+        <v>189.2599945068359</v>
       </c>
       <c r="F248" t="n">
-        <v>3063000</v>
+        <v>4369200</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B249" t="n">
-        <v>195.5</v>
+        <v>188</v>
       </c>
       <c r="C249" t="n">
-        <v>197.9900054931641</v>
+        <v>189.8899993896484</v>
       </c>
       <c r="D249" t="n">
-        <v>193.9100036621094</v>
+        <v>184.0800018310547</v>
       </c>
       <c r="E249" t="n">
-        <v>195.6900024414062</v>
+        <v>186.1000061035156</v>
       </c>
       <c r="F249" t="n">
-        <v>5021700</v>
+        <v>4363800</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B250" t="n">
-        <v>195.7700042724609</v>
+        <v>185.25</v>
       </c>
       <c r="C250" t="n">
-        <v>196.5</v>
+        <v>192</v>
       </c>
       <c r="D250" t="n">
-        <v>188.5599975585938</v>
+        <v>181.2700042724609</v>
       </c>
       <c r="E250" t="n">
-        <v>189.2599945068359</v>
+        <v>191.4400024414062</v>
       </c>
       <c r="F250" t="n">
-        <v>4369200</v>
+        <v>4108500</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B251" t="n">
-        <v>188</v>
+        <v>192.8200073242188</v>
       </c>
       <c r="C251" t="n">
-        <v>189.8899993896484</v>
+        <v>197.1000061035156</v>
       </c>
       <c r="D251" t="n">
-        <v>184.0800018310547</v>
+        <v>190.5599975585938</v>
       </c>
       <c r="E251" t="n">
-        <v>186.1000061035156</v>
+        <v>193.7799987792969</v>
       </c>
       <c r="F251" t="n">
-        <v>4363800</v>
+        <v>4204100</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,53 +6969,19 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B252" t="n">
-        <v>185.25</v>
-      </c>
-      <c r="C252" t="n">
-        <v>192</v>
-      </c>
-      <c r="D252" t="n">
-        <v>181.2700042724609</v>
-      </c>
-      <c r="E252" t="n">
-        <v>191.4400024414062</v>
-      </c>
+        <v>46273</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>4108500</v>
+        <v>4695079</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B253" t="n">
-        <v>192.8200073242188</v>
-      </c>
-      <c r="C253" t="n">
-        <v>197.1000061035156</v>
-      </c>
-      <c r="D253" t="n">
-        <v>190.5599975585938</v>
-      </c>
-      <c r="E253" t="n">
-        <v>193.7799987792969</v>
-      </c>
-      <c r="F253" t="n">
-        <v>4204100</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10544,34 +10510,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>194.96</v>
+      </c>
+      <c r="D2" t="n">
         <v>193.78</v>
       </c>
-      <c r="D2" t="n">
-        <v>191.44</v>
-      </c>
       <c r="E2" t="n">
-        <v>192.82</v>
+        <v>196.82</v>
       </c>
       <c r="F2" t="n">
-        <v>197.1</v>
+        <v>200.67</v>
       </c>
       <c r="G2" t="n">
-        <v>190.56</v>
+        <v>194.72</v>
       </c>
       <c r="H2" t="n">
-        <v>4190753</v>
+        <v>4695079</v>
       </c>
       <c r="I2" t="n">
-        <v>7405158</v>
+        <v>7427127</v>
       </c>
       <c r="J2" t="n">
-        <v>244400128000</v>
+        <v>245888368640</v>
       </c>
       <c r="K2" t="n">
-        <v>61.322784</v>
+        <v>61.6962</v>
       </c>
       <c r="L2" t="n">
-        <v>37.552223</v>
+        <v>37.780895</v>
       </c>
       <c r="M2" t="n">
         <v>3.16</v>
@@ -10614,7 +10580,7 @@
         <v>11.733</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.51581</v>
+        <v>16.616383</v>
       </c>
       <c r="Z2" t="n">
         <v>0.357</v>
@@ -10653,7 +10619,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-08 08:53:08</t>
+          <t>2026-09-09 09:16:06</t>
         </is>
       </c>
     </row>

--- a/data/ANET_data.xlsx
+++ b/data/ANET_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="B2" t="n">
-        <v>140.9700012207031</v>
+        <v>145.5599975585938</v>
       </c>
       <c r="C2" t="n">
-        <v>142.8809967041016</v>
+        <v>151.7100067138672</v>
       </c>
       <c r="D2" t="n">
-        <v>139.5099945068359</v>
+        <v>144.8999938964844</v>
       </c>
       <c r="E2" t="n">
-        <v>141.9100036621094</v>
+        <v>150.7200012207031</v>
       </c>
       <c r="F2" t="n">
-        <v>6158500</v>
+        <v>19772500</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B3" t="n">
-        <v>145.5599975585938</v>
+        <v>151.9900054931641</v>
       </c>
       <c r="C3" t="n">
-        <v>151.7100067138672</v>
+        <v>156.3200073242188</v>
       </c>
       <c r="D3" t="n">
-        <v>144.8999938964844</v>
+        <v>150.3600006103516</v>
       </c>
       <c r="E3" t="n">
-        <v>150.7200012207031</v>
+        <v>153.0399932861328</v>
       </c>
       <c r="F3" t="n">
-        <v>19772500</v>
+        <v>13666200</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B4" t="n">
-        <v>151.9900054931641</v>
+        <v>149.1799926757812</v>
       </c>
       <c r="C4" t="n">
-        <v>156.3200073242188</v>
+        <v>149.4700012207031</v>
       </c>
       <c r="D4" t="n">
-        <v>150.3600006103516</v>
+        <v>139.0200042724609</v>
       </c>
       <c r="E4" t="n">
-        <v>153.0399932861328</v>
+        <v>139.3899993896484</v>
       </c>
       <c r="F4" t="n">
-        <v>13666200</v>
+        <v>17920400</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B5" t="n">
-        <v>149.1799926757812</v>
+        <v>139.6000061035156</v>
       </c>
       <c r="C5" t="n">
-        <v>149.4700012207031</v>
+        <v>146.8999938964844</v>
       </c>
       <c r="D5" t="n">
-        <v>139.0200042724609</v>
+        <v>139.1699981689453</v>
       </c>
       <c r="E5" t="n">
-        <v>139.3899993896484</v>
+        <v>145.4299926757812</v>
       </c>
       <c r="F5" t="n">
-        <v>17920400</v>
+        <v>12140800</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B6" t="n">
-        <v>139.6000061035156</v>
+        <v>145.2599945068359</v>
       </c>
       <c r="C6" t="n">
-        <v>146.8999938964844</v>
+        <v>147.3699951171875</v>
       </c>
       <c r="D6" t="n">
-        <v>139.1699981689453</v>
+        <v>141</v>
       </c>
       <c r="E6" t="n">
-        <v>145.4299926757812</v>
+        <v>142.1600036621094</v>
       </c>
       <c r="F6" t="n">
-        <v>12140800</v>
+        <v>9382400</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B7" t="n">
-        <v>145.2599945068359</v>
+        <v>142.6349945068359</v>
       </c>
       <c r="C7" t="n">
-        <v>147.3699951171875</v>
+        <v>143.4250030517578</v>
       </c>
       <c r="D7" t="n">
-        <v>141</v>
+        <v>138.5</v>
       </c>
       <c r="E7" t="n">
-        <v>142.1600036621094</v>
+        <v>142.8399963378906</v>
       </c>
       <c r="F7" t="n">
-        <v>9382400</v>
+        <v>8295400</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B8" t="n">
-        <v>142.6349945068359</v>
+        <v>144</v>
       </c>
       <c r="C8" t="n">
+        <v>146.7200012207031</v>
+      </c>
+      <c r="D8" t="n">
         <v>143.4250030517578</v>
       </c>
-      <c r="D8" t="n">
-        <v>138.5</v>
-      </c>
       <c r="E8" t="n">
-        <v>142.8399963378906</v>
+        <v>146.6600036621094</v>
       </c>
       <c r="F8" t="n">
-        <v>8295400</v>
+        <v>6939000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B9" t="n">
-        <v>144</v>
+        <v>148.8999938964844</v>
       </c>
       <c r="C9" t="n">
-        <v>146.7200012207031</v>
+        <v>150.25</v>
       </c>
       <c r="D9" t="n">
-        <v>143.4250030517578</v>
+        <v>146.6699981689453</v>
       </c>
       <c r="E9" t="n">
-        <v>146.6600036621094</v>
+        <v>149.6100006103516</v>
       </c>
       <c r="F9" t="n">
-        <v>6939000</v>
+        <v>17810900</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B10" t="n">
-        <v>148.8999938964844</v>
+        <v>148.7799987792969</v>
       </c>
       <c r="C10" t="n">
-        <v>150.25</v>
+        <v>149.7100067138672</v>
       </c>
       <c r="D10" t="n">
-        <v>146.6699981689453</v>
+        <v>145.0549926757812</v>
       </c>
       <c r="E10" t="n">
-        <v>149.6100006103516</v>
+        <v>145.3999938964844</v>
       </c>
       <c r="F10" t="n">
-        <v>17810900</v>
+        <v>8675200</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B11" t="n">
-        <v>148.7799987792969</v>
+        <v>144.8600006103516</v>
       </c>
       <c r="C11" t="n">
-        <v>149.7100067138672</v>
+        <v>147.4600067138672</v>
       </c>
       <c r="D11" t="n">
-        <v>145.0549926757812</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="E11" t="n">
-        <v>145.3999938964844</v>
+        <v>144.0899963378906</v>
       </c>
       <c r="F11" t="n">
-        <v>8675200</v>
+        <v>8215500</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B12" t="n">
-        <v>144.8600006103516</v>
+        <v>144.6799926757812</v>
       </c>
       <c r="C12" t="n">
-        <v>147.4600067138672</v>
+        <v>144.6799926757812</v>
       </c>
       <c r="D12" t="n">
-        <v>143.0200042724609</v>
+        <v>141.2899932861328</v>
       </c>
       <c r="E12" t="n">
-        <v>144.0899963378906</v>
+        <v>142.6399993896484</v>
       </c>
       <c r="F12" t="n">
-        <v>8215500</v>
+        <v>7035700</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B13" t="n">
-        <v>144.6799926757812</v>
+        <v>141.6900024414062</v>
       </c>
       <c r="C13" t="n">
-        <v>144.6799926757812</v>
+        <v>143.2400054931641</v>
       </c>
       <c r="D13" t="n">
-        <v>141.2899932861328</v>
+        <v>139.2299957275391</v>
       </c>
       <c r="E13" t="n">
-        <v>142.6399993896484</v>
+        <v>143.0599975585938</v>
       </c>
       <c r="F13" t="n">
-        <v>7035700</v>
+        <v>6325300</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B14" t="n">
-        <v>141.6900024414062</v>
+        <v>144.0899963378906</v>
       </c>
       <c r="C14" t="n">
-        <v>143.2400054931641</v>
+        <v>144.3999938964844</v>
       </c>
       <c r="D14" t="n">
-        <v>139.2299957275391</v>
+        <v>140.7599945068359</v>
       </c>
       <c r="E14" t="n">
-        <v>143.0599975585938</v>
+        <v>142.5</v>
       </c>
       <c r="F14" t="n">
-        <v>6325300</v>
+        <v>4867700</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B15" t="n">
-        <v>144.0899963378906</v>
+        <v>144.9199981689453</v>
       </c>
       <c r="C15" t="n">
-        <v>144.3999938964844</v>
+        <v>147.8000030517578</v>
       </c>
       <c r="D15" t="n">
-        <v>140.7599945068359</v>
+        <v>142.6199951171875</v>
       </c>
       <c r="E15" t="n">
-        <v>142.5</v>
+        <v>143.3699951171875</v>
       </c>
       <c r="F15" t="n">
-        <v>4867700</v>
+        <v>6183600</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B16" t="n">
-        <v>144.9199981689453</v>
+        <v>143.4299926757812</v>
       </c>
       <c r="C16" t="n">
-        <v>147.8000030517578</v>
+        <v>145.8399963378906</v>
       </c>
       <c r="D16" t="n">
-        <v>142.6199951171875</v>
+        <v>143.1600036621094</v>
       </c>
       <c r="E16" t="n">
-        <v>143.3699951171875</v>
+        <v>145.7100067138672</v>
       </c>
       <c r="F16" t="n">
-        <v>6183600</v>
+        <v>5828900</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B17" t="n">
-        <v>143.4299926757812</v>
+        <v>144.6499938964844</v>
       </c>
       <c r="C17" t="n">
-        <v>145.8399963378906</v>
+        <v>149.9499969482422</v>
       </c>
       <c r="D17" t="n">
-        <v>143.1600036621094</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="E17" t="n">
-        <v>145.7100067138672</v>
+        <v>149.2700042724609</v>
       </c>
       <c r="F17" t="n">
-        <v>5828900</v>
+        <v>7820700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B18" t="n">
-        <v>144.6499938964844</v>
+        <v>150</v>
       </c>
       <c r="C18" t="n">
-        <v>149.9499969482422</v>
+        <v>150.5399932861328</v>
       </c>
       <c r="D18" t="n">
-        <v>143.0200042724609</v>
+        <v>141.25</v>
       </c>
       <c r="E18" t="n">
-        <v>149.2700042724609</v>
+        <v>144.4600067138672</v>
       </c>
       <c r="F18" t="n">
-        <v>7820700</v>
+        <v>9473800</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B19" t="n">
-        <v>150</v>
+        <v>146.0099945068359</v>
       </c>
       <c r="C19" t="n">
-        <v>150.5399932861328</v>
+        <v>149.0899963378906</v>
       </c>
       <c r="D19" t="n">
-        <v>141.25</v>
+        <v>144.1000061035156</v>
       </c>
       <c r="E19" t="n">
-        <v>144.4600067138672</v>
+        <v>145.5</v>
       </c>
       <c r="F19" t="n">
-        <v>9473800</v>
+        <v>7178600</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B20" t="n">
-        <v>146.0099945068359</v>
+        <v>151.6000061035156</v>
       </c>
       <c r="C20" t="n">
-        <v>149.0899963378906</v>
+        <v>153.7299957275391</v>
       </c>
       <c r="D20" t="n">
-        <v>144.1000061035156</v>
+        <v>149.5</v>
       </c>
       <c r="E20" t="n">
-        <v>145.5</v>
+        <v>149.5</v>
       </c>
       <c r="F20" t="n">
-        <v>7178600</v>
+        <v>7277600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B21" t="n">
-        <v>151.6000061035156</v>
+        <v>150.4799957275391</v>
       </c>
       <c r="C21" t="n">
-        <v>153.7299957275391</v>
+        <v>151.5500030517578</v>
       </c>
       <c r="D21" t="n">
-        <v>149.5</v>
+        <v>143.2799987792969</v>
       </c>
       <c r="E21" t="n">
-        <v>149.5</v>
+        <v>145.2899932861328</v>
       </c>
       <c r="F21" t="n">
-        <v>7277600</v>
+        <v>7348700</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B22" t="n">
-        <v>150.4799957275391</v>
+        <v>147.9900054931641</v>
       </c>
       <c r="C22" t="n">
-        <v>151.5500030517578</v>
+        <v>158.5099945068359</v>
       </c>
       <c r="D22" t="n">
-        <v>143.2799987792969</v>
+        <v>147.4049987792969</v>
       </c>
       <c r="E22" t="n">
-        <v>145.2899932861328</v>
+        <v>157.3600006103516</v>
       </c>
       <c r="F22" t="n">
-        <v>7348700</v>
+        <v>11283400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B23" t="n">
-        <v>147.9900054931641</v>
+        <v>157</v>
       </c>
       <c r="C23" t="n">
-        <v>158.5099945068359</v>
+        <v>159.8000030517578</v>
       </c>
       <c r="D23" t="n">
-        <v>147.4049987792969</v>
+        <v>154.6009979248047</v>
       </c>
       <c r="E23" t="n">
-        <v>157.3600006103516</v>
+        <v>158.2299957275391</v>
       </c>
       <c r="F23" t="n">
-        <v>11283400</v>
+        <v>8459900</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B24" t="n">
-        <v>157</v>
+        <v>159.8600006103516</v>
       </c>
       <c r="C24" t="n">
-        <v>159.8000030517578</v>
+        <v>162.6799926757812</v>
       </c>
       <c r="D24" t="n">
-        <v>154.6009979248047</v>
+        <v>153.7400054931641</v>
       </c>
       <c r="E24" t="n">
-        <v>158.2299957275391</v>
+        <v>154.1000061035156</v>
       </c>
       <c r="F24" t="n">
-        <v>8459900</v>
+        <v>10459300</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B25" t="n">
-        <v>159.8600006103516</v>
+        <v>160.7599945068359</v>
       </c>
       <c r="C25" t="n">
-        <v>162.6799926757812</v>
+        <v>162</v>
       </c>
       <c r="D25" t="n">
-        <v>153.7400054931641</v>
+        <v>145.0899963378906</v>
       </c>
       <c r="E25" t="n">
-        <v>154.1000061035156</v>
+        <v>147.4499969482422</v>
       </c>
       <c r="F25" t="n">
-        <v>10459300</v>
+        <v>14233900</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B26" t="n">
-        <v>160.7599945068359</v>
+        <v>142.9850006103516</v>
       </c>
       <c r="C26" t="n">
-        <v>162</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="D26" t="n">
-        <v>145.0899963378906</v>
+        <v>136.7899932861328</v>
       </c>
       <c r="E26" t="n">
-        <v>147.4499969482422</v>
+        <v>138.7899932861328</v>
       </c>
       <c r="F26" t="n">
-        <v>14233900</v>
+        <v>13672400</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B27" t="n">
-        <v>142.9850006103516</v>
+        <v>140.4199981689453</v>
       </c>
       <c r="C27" t="n">
-        <v>143.0200042724609</v>
+        <v>145.3899993896484</v>
       </c>
       <c r="D27" t="n">
-        <v>136.7899932861328</v>
+        <v>140.1100006103516</v>
       </c>
       <c r="E27" t="n">
-        <v>138.7899932861328</v>
+        <v>143.3800048828125</v>
       </c>
       <c r="F27" t="n">
-        <v>13672400</v>
+        <v>8687000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B28" t="n">
-        <v>140.4199981689453</v>
+        <v>144.8999938964844</v>
       </c>
       <c r="C28" t="n">
-        <v>145.3899993896484</v>
+        <v>147.6499938964844</v>
       </c>
       <c r="D28" t="n">
-        <v>140.1100006103516</v>
+        <v>143.8600006103516</v>
       </c>
       <c r="E28" t="n">
-        <v>143.3800048828125</v>
+        <v>146.0099945068359</v>
       </c>
       <c r="F28" t="n">
-        <v>8687000</v>
+        <v>6909500</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B29" t="n">
-        <v>144.8999938964844</v>
+        <v>143.0099945068359</v>
       </c>
       <c r="C29" t="n">
-        <v>147.6499938964844</v>
+        <v>144.5</v>
       </c>
       <c r="D29" t="n">
-        <v>143.8600006103516</v>
+        <v>139.2400054931641</v>
       </c>
       <c r="E29" t="n">
-        <v>146.0099945068359</v>
+        <v>143.1000061035156</v>
       </c>
       <c r="F29" t="n">
-        <v>6909500</v>
+        <v>6533900</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B30" t="n">
-        <v>143.0099945068359</v>
+        <v>146.3249969482422</v>
       </c>
       <c r="C30" t="n">
-        <v>144.5</v>
+        <v>149.8800048828125</v>
       </c>
       <c r="D30" t="n">
-        <v>139.2400054931641</v>
+        <v>146.1900024414062</v>
       </c>
       <c r="E30" t="n">
-        <v>143.1000061035156</v>
+        <v>146.4799957275391</v>
       </c>
       <c r="F30" t="n">
-        <v>6533900</v>
+        <v>6120700</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B31" t="n">
-        <v>146.3249969482422</v>
+        <v>145.4499969482422</v>
       </c>
       <c r="C31" t="n">
-        <v>149.8800048828125</v>
+        <v>147.6100006103516</v>
       </c>
       <c r="D31" t="n">
-        <v>146.1900024414062</v>
+        <v>144.1399993896484</v>
       </c>
       <c r="E31" t="n">
-        <v>146.4799957275391</v>
+        <v>145.9400024414062</v>
       </c>
       <c r="F31" t="n">
-        <v>6120700</v>
+        <v>3648900</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B32" t="n">
-        <v>145.4499969482422</v>
+        <v>145.8650054931641</v>
       </c>
       <c r="C32" t="n">
-        <v>147.6100006103516</v>
+        <v>147.4900054931641</v>
       </c>
       <c r="D32" t="n">
-        <v>144.1399993896484</v>
+        <v>141.6799926757812</v>
       </c>
       <c r="E32" t="n">
-        <v>145.9400024414062</v>
+        <v>146.5899963378906</v>
       </c>
       <c r="F32" t="n">
-        <v>3648900</v>
+        <v>7349200</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B33" t="n">
-        <v>145.8650054931641</v>
+        <v>146.7799987792969</v>
       </c>
       <c r="C33" t="n">
-        <v>147.4900054931641</v>
+        <v>153.9499969482422</v>
       </c>
       <c r="D33" t="n">
-        <v>141.6799926757812</v>
+        <v>146.6399993896484</v>
       </c>
       <c r="E33" t="n">
-        <v>146.5899963378906</v>
+        <v>152.7599945068359</v>
       </c>
       <c r="F33" t="n">
-        <v>7349200</v>
+        <v>7327400</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B34" t="n">
-        <v>146.7799987792969</v>
+        <v>155</v>
       </c>
       <c r="C34" t="n">
-        <v>153.9499969482422</v>
+        <v>155.8300018310547</v>
       </c>
       <c r="D34" t="n">
-        <v>146.6399993896484</v>
+        <v>152.2969970703125</v>
       </c>
       <c r="E34" t="n">
-        <v>152.7599945068359</v>
+        <v>153.8200073242188</v>
       </c>
       <c r="F34" t="n">
-        <v>7327400</v>
+        <v>5170800</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B35" t="n">
-        <v>155</v>
+        <v>157.4100036621094</v>
       </c>
       <c r="C35" t="n">
-        <v>155.8300018310547</v>
+        <v>157.6999969482422</v>
       </c>
       <c r="D35" t="n">
-        <v>152.2969970703125</v>
+        <v>155.0099945068359</v>
       </c>
       <c r="E35" t="n">
-        <v>153.8200073242188</v>
+        <v>156.8099975585938</v>
       </c>
       <c r="F35" t="n">
-        <v>5170800</v>
+        <v>5509100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B36" t="n">
-        <v>157.4100036621094</v>
+        <v>156.6199951171875</v>
       </c>
       <c r="C36" t="n">
-        <v>157.6999969482422</v>
+        <v>158.6600036621094</v>
       </c>
       <c r="D36" t="n">
-        <v>155.0099945068359</v>
+        <v>152.3300018310547</v>
       </c>
       <c r="E36" t="n">
-        <v>156.8099975585938</v>
+        <v>156.7700042724609</v>
       </c>
       <c r="F36" t="n">
-        <v>5509100</v>
+        <v>5037400</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B37" t="n">
-        <v>156.6199951171875</v>
+        <v>157.2100067138672</v>
       </c>
       <c r="C37" t="n">
-        <v>158.6600036621094</v>
+        <v>162.3999938964844</v>
       </c>
       <c r="D37" t="n">
-        <v>152.3300018310547</v>
+        <v>156.7799987792969</v>
       </c>
       <c r="E37" t="n">
-        <v>156.7700042724609</v>
+        <v>162.0299987792969</v>
       </c>
       <c r="F37" t="n">
-        <v>5037400</v>
+        <v>6901400</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B38" t="n">
-        <v>157.2100067138672</v>
+        <v>162.4700012207031</v>
       </c>
       <c r="C38" t="n">
-        <v>162.3999938964844</v>
+        <v>164.9400024414062</v>
       </c>
       <c r="D38" t="n">
-        <v>156.7799987792969</v>
+        <v>158.3999938964844</v>
       </c>
       <c r="E38" t="n">
-        <v>162.0299987792969</v>
+        <v>158.4400024414062</v>
       </c>
       <c r="F38" t="n">
-        <v>6901400</v>
+        <v>6911300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B39" t="n">
-        <v>162.4700012207031</v>
+        <v>161.0899963378906</v>
       </c>
       <c r="C39" t="n">
-        <v>164.9400024414062</v>
+        <v>162.1150054931641</v>
       </c>
       <c r="D39" t="n">
-        <v>158.3999938964844</v>
+        <v>155.7400054931641</v>
       </c>
       <c r="E39" t="n">
-        <v>158.4400024414062</v>
+        <v>157.6900024414062</v>
       </c>
       <c r="F39" t="n">
-        <v>6911300</v>
+        <v>6209300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B40" t="n">
-        <v>161.0899963378906</v>
+        <v>160.5</v>
       </c>
       <c r="C40" t="n">
-        <v>162.1150054931641</v>
+        <v>160.8999938964844</v>
       </c>
       <c r="D40" t="n">
-        <v>155.7400054931641</v>
+        <v>155.4199981689453</v>
       </c>
       <c r="E40" t="n">
-        <v>157.6900024414062</v>
+        <v>157.5899963378906</v>
       </c>
       <c r="F40" t="n">
-        <v>6209300</v>
+        <v>6422600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B41" t="n">
-        <v>160.5</v>
+        <v>152.8600006103516</v>
       </c>
       <c r="C41" t="n">
-        <v>160.8999938964844</v>
+        <v>157.0249938964844</v>
       </c>
       <c r="D41" t="n">
-        <v>155.4199981689453</v>
+        <v>150.9900054931641</v>
       </c>
       <c r="E41" t="n">
-        <v>157.5899963378906</v>
+        <v>153.5500030517578</v>
       </c>
       <c r="F41" t="n">
-        <v>6422600</v>
+        <v>9026400</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B42" t="n">
-        <v>152.8600006103516</v>
+        <v>142.6699981689453</v>
       </c>
       <c r="C42" t="n">
-        <v>157.0249938964844</v>
+        <v>148</v>
       </c>
       <c r="D42" t="n">
-        <v>150.9900054931641</v>
+        <v>140.0200042724609</v>
       </c>
       <c r="E42" t="n">
-        <v>153.5500030517578</v>
+        <v>140.4199981689453</v>
       </c>
       <c r="F42" t="n">
-        <v>9026400</v>
+        <v>15901000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B43" t="n">
-        <v>142.6699981689453</v>
+        <v>140.6499938964844</v>
       </c>
       <c r="C43" t="n">
-        <v>148</v>
+        <v>141.9900054931641</v>
       </c>
       <c r="D43" t="n">
-        <v>140.0200042724609</v>
+        <v>132.5899963378906</v>
       </c>
       <c r="E43" t="n">
-        <v>140.4199981689453</v>
+        <v>134.0200042724609</v>
       </c>
       <c r="F43" t="n">
-        <v>15901000</v>
+        <v>13296100</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B44" t="n">
-        <v>140.6499938964844</v>
+        <v>134.4100036621094</v>
       </c>
       <c r="C44" t="n">
-        <v>141.9900054931641</v>
+        <v>136.6100006103516</v>
       </c>
       <c r="D44" t="n">
-        <v>132.5899963378906</v>
+        <v>132.4499969482422</v>
       </c>
       <c r="E44" t="n">
-        <v>134.0200042724609</v>
+        <v>134.6499938964844</v>
       </c>
       <c r="F44" t="n">
-        <v>13296100</v>
+        <v>11341600</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B45" t="n">
-        <v>134.4100036621094</v>
+        <v>137.5</v>
       </c>
       <c r="C45" t="n">
-        <v>136.6100006103516</v>
+        <v>138.9799957275391</v>
       </c>
       <c r="D45" t="n">
-        <v>132.4499969482422</v>
+        <v>134.5870056152344</v>
       </c>
       <c r="E45" t="n">
-        <v>134.6499938964844</v>
+        <v>137.2599945068359</v>
       </c>
       <c r="F45" t="n">
-        <v>11341600</v>
+        <v>6974300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B46" t="n">
-        <v>137.5</v>
+        <v>134.8699951171875</v>
       </c>
       <c r="C46" t="n">
-        <v>138.9799957275391</v>
+        <v>136.375</v>
       </c>
       <c r="D46" t="n">
-        <v>134.5870056152344</v>
+        <v>132.4100036621094</v>
       </c>
       <c r="E46" t="n">
-        <v>137.2599945068359</v>
+        <v>134.9299926757812</v>
       </c>
       <c r="F46" t="n">
-        <v>6974300</v>
+        <v>7189300</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B47" t="n">
-        <v>134.8699951171875</v>
+        <v>136.2200012207031</v>
       </c>
       <c r="C47" t="n">
-        <v>136.375</v>
+        <v>136.5980072021484</v>
       </c>
       <c r="D47" t="n">
-        <v>132.4100036621094</v>
+        <v>133.7779998779297</v>
       </c>
       <c r="E47" t="n">
-        <v>134.9299926757812</v>
+        <v>134.9799957275391</v>
       </c>
       <c r="F47" t="n">
-        <v>7189300</v>
+        <v>6471400</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B48" t="n">
-        <v>136.2200012207031</v>
+        <v>134.4299926757812</v>
       </c>
       <c r="C48" t="n">
-        <v>136.5980072021484</v>
+        <v>135.5800018310547</v>
       </c>
       <c r="D48" t="n">
-        <v>133.7779998779297</v>
+        <v>129.1699981689453</v>
       </c>
       <c r="E48" t="n">
-        <v>134.9799957275391</v>
+        <v>130.3000030517578</v>
       </c>
       <c r="F48" t="n">
-        <v>6471400</v>
+        <v>10471400</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B49" t="n">
-        <v>134.4299926757812</v>
+        <v>127.0599975585938</v>
       </c>
       <c r="C49" t="n">
-        <v>135.5800018310547</v>
+        <v>135.3699951171875</v>
       </c>
       <c r="D49" t="n">
-        <v>129.1699981689453</v>
+        <v>125.3600006103516</v>
       </c>
       <c r="E49" t="n">
-        <v>130.3000030517578</v>
+        <v>131.3699951171875</v>
       </c>
       <c r="F49" t="n">
-        <v>10471400</v>
+        <v>10672500</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B50" t="n">
-        <v>127.0599975585938</v>
+        <v>131.3500061035156</v>
       </c>
       <c r="C50" t="n">
-        <v>135.3699951171875</v>
+        <v>133.3200073242188</v>
       </c>
       <c r="D50" t="n">
-        <v>125.3600006103516</v>
+        <v>125.4000015258789</v>
       </c>
       <c r="E50" t="n">
-        <v>131.3699951171875</v>
+        <v>127.2600021362305</v>
       </c>
       <c r="F50" t="n">
-        <v>10672500</v>
+        <v>12455900</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B51" t="n">
-        <v>131.3500061035156</v>
+        <v>125.75</v>
       </c>
       <c r="C51" t="n">
-        <v>133.3200073242188</v>
+        <v>127.5500030517578</v>
       </c>
       <c r="D51" t="n">
-        <v>125.4000015258789</v>
+        <v>122.0800018310547</v>
       </c>
       <c r="E51" t="n">
-        <v>127.2600021362305</v>
+        <v>123.4499969482422</v>
       </c>
       <c r="F51" t="n">
-        <v>12455900</v>
+        <v>12561100</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B52" t="n">
-        <v>125.75</v>
+        <v>123.0500030517578</v>
       </c>
       <c r="C52" t="n">
-        <v>127.5500030517578</v>
+        <v>126.5699996948242</v>
       </c>
       <c r="D52" t="n">
-        <v>122.0800018310547</v>
+        <v>122.9000015258789</v>
       </c>
       <c r="E52" t="n">
-        <v>123.4499969482422</v>
+        <v>124.8099975585938</v>
       </c>
       <c r="F52" t="n">
-        <v>12561100</v>
+        <v>7703500</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B53" t="n">
-        <v>123.0500030517578</v>
+        <v>129.8899993896484</v>
       </c>
       <c r="C53" t="n">
-        <v>126.5699996948242</v>
+        <v>131.7899932861328</v>
       </c>
       <c r="D53" t="n">
-        <v>122.9000015258789</v>
+        <v>118.9000015258789</v>
       </c>
       <c r="E53" t="n">
-        <v>124.8099975585938</v>
+        <v>119.5899963378906</v>
       </c>
       <c r="F53" t="n">
-        <v>7703500</v>
+        <v>12642000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B54" t="n">
-        <v>129.8899993896484</v>
+        <v>118.4199981689453</v>
       </c>
       <c r="C54" t="n">
-        <v>131.7899932861328</v>
+        <v>120.004997253418</v>
       </c>
       <c r="D54" t="n">
-        <v>118.9000015258789</v>
+        <v>114.5199966430664</v>
       </c>
       <c r="E54" t="n">
-        <v>119.5899963378906</v>
+        <v>117.4300003051758</v>
       </c>
       <c r="F54" t="n">
-        <v>12642000</v>
+        <v>16704100</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B55" t="n">
-        <v>118.4199981689453</v>
+        <v>118.9150009155273</v>
       </c>
       <c r="C55" t="n">
-        <v>120.004997253418</v>
+        <v>122.4199981689453</v>
       </c>
       <c r="D55" t="n">
-        <v>114.5199966430664</v>
+        <v>118.1999969482422</v>
       </c>
       <c r="E55" t="n">
-        <v>117.4300003051758</v>
+        <v>122.1699981689453</v>
       </c>
       <c r="F55" t="n">
-        <v>16704100</v>
+        <v>12758600</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B56" t="n">
-        <v>118.9150009155273</v>
+        <v>122.4000015258789</v>
       </c>
       <c r="C56" t="n">
-        <v>122.4199981689453</v>
+        <v>125.9100036621094</v>
       </c>
       <c r="D56" t="n">
-        <v>118.1999969482422</v>
+        <v>122.3199996948242</v>
       </c>
       <c r="E56" t="n">
-        <v>122.1699981689453</v>
+        <v>125.0400009155273</v>
       </c>
       <c r="F56" t="n">
-        <v>12758600</v>
+        <v>7143400</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B57" t="n">
-        <v>122.4000015258789</v>
+        <v>127.4749984741211</v>
       </c>
       <c r="C57" t="n">
-        <v>125.9100036621094</v>
+        <v>128.4750061035156</v>
       </c>
       <c r="D57" t="n">
-        <v>122.3199996948242</v>
+        <v>125.2460021972656</v>
       </c>
       <c r="E57" t="n">
-        <v>125.0400009155273</v>
+        <v>127.6500015258789</v>
       </c>
       <c r="F57" t="n">
-        <v>7143400</v>
+        <v>5995000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B58" t="n">
-        <v>127.4749984741211</v>
+        <v>130</v>
       </c>
       <c r="C58" t="n">
-        <v>128.4750061035156</v>
+        <v>131.4049987792969</v>
       </c>
       <c r="D58" t="n">
-        <v>125.2460021972656</v>
+        <v>128.1150054931641</v>
       </c>
       <c r="E58" t="n">
-        <v>127.6500015258789</v>
+        <v>130.6799926757812</v>
       </c>
       <c r="F58" t="n">
-        <v>5995000</v>
+        <v>3895000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B59" t="n">
-        <v>130</v>
+        <v>128.9799957275391</v>
       </c>
       <c r="C59" t="n">
-        <v>131.4049987792969</v>
+        <v>129.5039978027344</v>
       </c>
       <c r="D59" t="n">
-        <v>128.1150054931641</v>
+        <v>126.1399993896484</v>
       </c>
       <c r="E59" t="n">
-        <v>130.6799926757812</v>
+        <v>128.1100006103516</v>
       </c>
       <c r="F59" t="n">
-        <v>3895000</v>
+        <v>4690600</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B60" t="n">
-        <v>128.9799957275391</v>
+        <v>129.75</v>
       </c>
       <c r="C60" t="n">
-        <v>129.5039978027344</v>
+        <v>131.0399932861328</v>
       </c>
       <c r="D60" t="n">
-        <v>126.1399993896484</v>
+        <v>126.2699966430664</v>
       </c>
       <c r="E60" t="n">
-        <v>128.1100006103516</v>
+        <v>127.2200012207031</v>
       </c>
       <c r="F60" t="n">
-        <v>4690600</v>
+        <v>5619000</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B61" t="n">
-        <v>129.75</v>
+        <v>126.1600036621094</v>
       </c>
       <c r="C61" t="n">
-        <v>131.0399932861328</v>
+        <v>128.5</v>
       </c>
       <c r="D61" t="n">
-        <v>126.2699966430664</v>
+        <v>123.75</v>
       </c>
       <c r="E61" t="n">
-        <v>127.2200012207031</v>
+        <v>127.8000030517578</v>
       </c>
       <c r="F61" t="n">
-        <v>5619000</v>
+        <v>5286300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B62" t="n">
-        <v>126.1600036621094</v>
+        <v>127.0800018310547</v>
       </c>
       <c r="C62" t="n">
-        <v>128.5</v>
+        <v>130.7799987792969</v>
       </c>
       <c r="D62" t="n">
-        <v>123.75</v>
+        <v>126.7399978637695</v>
       </c>
       <c r="E62" t="n">
-        <v>127.8000030517578</v>
+        <v>128.5500030517578</v>
       </c>
       <c r="F62" t="n">
-        <v>5286300</v>
+        <v>4516400</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B63" t="n">
-        <v>127.0800018310547</v>
+        <v>128.5</v>
       </c>
       <c r="C63" t="n">
-        <v>130.7799987792969</v>
+        <v>129.6600036621094</v>
       </c>
       <c r="D63" t="n">
-        <v>126.7399978637695</v>
+        <v>126.8399963378906</v>
       </c>
       <c r="E63" t="n">
-        <v>128.5500030517578</v>
+        <v>128.5899963378906</v>
       </c>
       <c r="F63" t="n">
-        <v>4516400</v>
+        <v>5166300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B64" t="n">
-        <v>128.5</v>
+        <v>129.7299957275391</v>
       </c>
       <c r="C64" t="n">
-        <v>129.6600036621094</v>
+        <v>133.5700073242188</v>
       </c>
       <c r="D64" t="n">
-        <v>126.8399963378906</v>
+        <v>128.2100067138672</v>
       </c>
       <c r="E64" t="n">
-        <v>128.5899963378906</v>
+        <v>129.1100006103516</v>
       </c>
       <c r="F64" t="n">
-        <v>5166300</v>
+        <v>7813800</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B65" t="n">
-        <v>129.7299957275391</v>
+        <v>128.6999969482422</v>
       </c>
       <c r="C65" t="n">
-        <v>133.5700073242188</v>
+        <v>130.8000030517578</v>
       </c>
       <c r="D65" t="n">
-        <v>128.2100067138672</v>
+        <v>127.3199996948242</v>
       </c>
       <c r="E65" t="n">
-        <v>129.1100006103516</v>
+        <v>130.0399932861328</v>
       </c>
       <c r="F65" t="n">
-        <v>7813800</v>
+        <v>5227900</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B66" t="n">
-        <v>128.6999969482422</v>
+        <v>131.0500030517578</v>
       </c>
       <c r="C66" t="n">
-        <v>130.8000030517578</v>
+        <v>134.4400024414062</v>
       </c>
       <c r="D66" t="n">
-        <v>127.3199996948242</v>
+        <v>130.25</v>
       </c>
       <c r="E66" t="n">
-        <v>130.0399932861328</v>
+        <v>132.3600006103516</v>
       </c>
       <c r="F66" t="n">
-        <v>5227900</v>
+        <v>5921300</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B67" t="n">
-        <v>131.0500030517578</v>
+        <v>135.5299987792969</v>
       </c>
       <c r="C67" t="n">
-        <v>134.4400024414062</v>
+        <v>136.3999938964844</v>
       </c>
       <c r="D67" t="n">
-        <v>130.25</v>
+        <v>128.9499969482422</v>
       </c>
       <c r="E67" t="n">
-        <v>132.3600006103516</v>
+        <v>134.3899993896484</v>
       </c>
       <c r="F67" t="n">
-        <v>5921300</v>
+        <v>6679500</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B68" t="n">
-        <v>135.5299987792969</v>
+        <v>132.4799957275391</v>
       </c>
       <c r="C68" t="n">
-        <v>136.3999938964844</v>
+        <v>134.0500030517578</v>
       </c>
       <c r="D68" t="n">
-        <v>128.9499969482422</v>
+        <v>124.3000030517578</v>
       </c>
       <c r="E68" t="n">
-        <v>134.3899993896484</v>
+        <v>124.7600021362305</v>
       </c>
       <c r="F68" t="n">
-        <v>6679500</v>
+        <v>8508700</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B69" t="n">
-        <v>132.4799957275391</v>
+        <v>125.5</v>
       </c>
       <c r="C69" t="n">
-        <v>134.0500030517578</v>
+        <v>127.3600006103516</v>
       </c>
       <c r="D69" t="n">
-        <v>124.3000030517578</v>
+        <v>123.6100006103516</v>
       </c>
       <c r="E69" t="n">
-        <v>124.7600021362305</v>
+        <v>125.8899993896484</v>
       </c>
       <c r="F69" t="n">
-        <v>8508700</v>
+        <v>6441900</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B70" t="n">
-        <v>125.5</v>
+        <v>126.1399993896484</v>
       </c>
       <c r="C70" t="n">
-        <v>127.3600006103516</v>
+        <v>127.8399963378906</v>
       </c>
       <c r="D70" t="n">
-        <v>123.6100006103516</v>
+        <v>124.1999969482422</v>
       </c>
       <c r="E70" t="n">
-        <v>125.8899993896484</v>
+        <v>126.129997253418</v>
       </c>
       <c r="F70" t="n">
-        <v>6441900</v>
+        <v>6656100</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B71" t="n">
-        <v>126.1399993896484</v>
+        <v>125.9400024414062</v>
       </c>
       <c r="C71" t="n">
-        <v>127.8399963378906</v>
+        <v>126.8300018310547</v>
       </c>
       <c r="D71" t="n">
-        <v>124.1999969482422</v>
+        <v>121.629997253418</v>
       </c>
       <c r="E71" t="n">
-        <v>126.129997253418</v>
+        <v>122.3600006103516</v>
       </c>
       <c r="F71" t="n">
-        <v>6656100</v>
+        <v>8589200</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B72" t="n">
-        <v>125.9400024414062</v>
+        <v>125</v>
       </c>
       <c r="C72" t="n">
-        <v>126.8300018310547</v>
+        <v>127.1600036621094</v>
       </c>
       <c r="D72" t="n">
-        <v>121.629997253418</v>
+        <v>123.879997253418</v>
       </c>
       <c r="E72" t="n">
-        <v>122.3600006103516</v>
+        <v>124.620002746582</v>
       </c>
       <c r="F72" t="n">
-        <v>8589200</v>
+        <v>5515200</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B73" t="n">
-        <v>125</v>
+        <v>125.0100021362305</v>
       </c>
       <c r="C73" t="n">
-        <v>127.1600036621094</v>
+        <v>132.5200042724609</v>
       </c>
       <c r="D73" t="n">
-        <v>123.879997253418</v>
+        <v>125.0100021362305</v>
       </c>
       <c r="E73" t="n">
-        <v>124.620002746582</v>
+        <v>131.1199951171875</v>
       </c>
       <c r="F73" t="n">
-        <v>5515200</v>
+        <v>12713100</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B74" t="n">
-        <v>125.0100021362305</v>
+        <v>133.4299926757812</v>
       </c>
       <c r="C74" t="n">
-        <v>132.5200042724609</v>
+        <v>134</v>
       </c>
       <c r="D74" t="n">
-        <v>125.0100021362305</v>
+        <v>130.2200012207031</v>
       </c>
       <c r="E74" t="n">
-        <v>131.1199951171875</v>
+        <v>130.7299957275391</v>
       </c>
       <c r="F74" t="n">
-        <v>12713100</v>
+        <v>5547300</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B75" t="n">
-        <v>133.4299926757812</v>
+        <v>129.3200073242188</v>
       </c>
       <c r="C75" t="n">
-        <v>134</v>
+        <v>131.7200012207031</v>
       </c>
       <c r="D75" t="n">
-        <v>130.2200012207031</v>
+        <v>129.25</v>
       </c>
       <c r="E75" t="n">
-        <v>130.7299957275391</v>
+        <v>131.3200073242188</v>
       </c>
       <c r="F75" t="n">
-        <v>5547300</v>
+        <v>2884300</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B76" t="n">
-        <v>129.3200073242188</v>
+        <v>131.1300048828125</v>
       </c>
       <c r="C76" t="n">
-        <v>131.7200012207031</v>
+        <v>131.5</v>
       </c>
       <c r="D76" t="n">
-        <v>129.25</v>
+        <v>130.1100006103516</v>
       </c>
       <c r="E76" t="n">
-        <v>131.3200073242188</v>
+        <v>130.7700042724609</v>
       </c>
       <c r="F76" t="n">
-        <v>2884300</v>
+        <v>1642400</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B77" t="n">
-        <v>131.1300048828125</v>
+        <v>131</v>
       </c>
       <c r="C77" t="n">
-        <v>131.5</v>
+        <v>132.125</v>
       </c>
       <c r="D77" t="n">
-        <v>130.1100006103516</v>
+        <v>130.4499969482422</v>
       </c>
       <c r="E77" t="n">
-        <v>130.7700042724609</v>
+        <v>131.8399963378906</v>
       </c>
       <c r="F77" t="n">
-        <v>1642400</v>
+        <v>2308400</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B78" t="n">
-        <v>131</v>
+        <v>131.1499938964844</v>
       </c>
       <c r="C78" t="n">
-        <v>132.125</v>
+        <v>135.2989959716797</v>
       </c>
       <c r="D78" t="n">
-        <v>130.4499969482422</v>
+        <v>131.0399932861328</v>
       </c>
       <c r="E78" t="n">
-        <v>131.8399963378906</v>
+        <v>134.1499938964844</v>
       </c>
       <c r="F78" t="n">
-        <v>2308400</v>
+        <v>6199700</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B79" t="n">
-        <v>131.1499938964844</v>
+        <v>134.25</v>
       </c>
       <c r="C79" t="n">
-        <v>135.2989959716797</v>
+        <v>134.4499969482422</v>
       </c>
       <c r="D79" t="n">
-        <v>131.0399932861328</v>
+        <v>132.3699951171875</v>
       </c>
       <c r="E79" t="n">
-        <v>134.1499938964844</v>
+        <v>132.4400024414062</v>
       </c>
       <c r="F79" t="n">
-        <v>6199700</v>
+        <v>4081100</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B80" t="n">
-        <v>134.25</v>
+        <v>132.5</v>
       </c>
       <c r="C80" t="n">
-        <v>134.4499969482422</v>
+        <v>132.8300018310547</v>
       </c>
       <c r="D80" t="n">
-        <v>132.3699951171875</v>
+        <v>130.8800048828125</v>
       </c>
       <c r="E80" t="n">
-        <v>132.4400024414062</v>
+        <v>131.0299987792969</v>
       </c>
       <c r="F80" t="n">
-        <v>4081100</v>
+        <v>3821600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B81" t="n">
-        <v>132.5</v>
+        <v>134.0500030517578</v>
       </c>
       <c r="C81" t="n">
-        <v>132.8300018310547</v>
+        <v>136.0899963378906</v>
       </c>
       <c r="D81" t="n">
-        <v>130.8800048828125</v>
+        <v>132.1849975585938</v>
       </c>
       <c r="E81" t="n">
-        <v>131.0299987792969</v>
+        <v>133.6000061035156</v>
       </c>
       <c r="F81" t="n">
-        <v>3821600</v>
+        <v>4707400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B82" t="n">
-        <v>134.0500030517578</v>
+        <v>138.3399963378906</v>
       </c>
       <c r="C82" t="n">
-        <v>136.0899963378906</v>
+        <v>141.4100036621094</v>
       </c>
       <c r="D82" t="n">
-        <v>132.1849975585938</v>
+        <v>134.5099945068359</v>
       </c>
       <c r="E82" t="n">
-        <v>133.6000061035156</v>
+        <v>137.1900024414062</v>
       </c>
       <c r="F82" t="n">
-        <v>4707400</v>
+        <v>9691900</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B83" t="n">
-        <v>138.3399963378906</v>
+        <v>137.8999938964844</v>
       </c>
       <c r="C83" t="n">
-        <v>141.4100036621094</v>
+        <v>137.9299926757812</v>
       </c>
       <c r="D83" t="n">
-        <v>134.5099945068359</v>
+        <v>132.5</v>
       </c>
       <c r="E83" t="n">
-        <v>137.1900024414062</v>
+        <v>132.5800018310547</v>
       </c>
       <c r="F83" t="n">
-        <v>9691900</v>
+        <v>8004000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B84" t="n">
-        <v>137.8999938964844</v>
+        <v>130.0099945068359</v>
       </c>
       <c r="C84" t="n">
-        <v>137.9299926757812</v>
+        <v>131.6549987792969</v>
       </c>
       <c r="D84" t="n">
-        <v>132.5</v>
+        <v>128.6399993896484</v>
       </c>
       <c r="E84" t="n">
-        <v>132.5800018310547</v>
+        <v>130.0800018310547</v>
       </c>
       <c r="F84" t="n">
-        <v>8004000</v>
+        <v>7550700</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B85" t="n">
-        <v>130.0099945068359</v>
+        <v>129.3699951171875</v>
       </c>
       <c r="C85" t="n">
-        <v>131.6549987792969</v>
+        <v>129.6000061035156</v>
       </c>
       <c r="D85" t="n">
-        <v>128.6399993896484</v>
+        <v>122.8099975585938</v>
       </c>
       <c r="E85" t="n">
-        <v>130.0800018310547</v>
+        <v>123.7200012207031</v>
       </c>
       <c r="F85" t="n">
-        <v>7550700</v>
+        <v>8944200</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B86" t="n">
-        <v>129.3699951171875</v>
+        <v>124.5699996948242</v>
       </c>
       <c r="C86" t="n">
-        <v>129.6000061035156</v>
+        <v>124.8300018310547</v>
       </c>
       <c r="D86" t="n">
-        <v>122.8099975585938</v>
+        <v>121.9000015258789</v>
       </c>
       <c r="E86" t="n">
-        <v>123.7200012207031</v>
+        <v>122.8899993896484</v>
       </c>
       <c r="F86" t="n">
-        <v>8944200</v>
+        <v>8989700</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B87" t="n">
-        <v>124.5699996948242</v>
+        <v>121.5999984741211</v>
       </c>
       <c r="C87" t="n">
-        <v>124.8300018310547</v>
+        <v>124.4550018310547</v>
       </c>
       <c r="D87" t="n">
-        <v>121.9000015258789</v>
+        <v>120</v>
       </c>
       <c r="E87" t="n">
-        <v>122.8899993896484</v>
+        <v>123.4199981689453</v>
       </c>
       <c r="F87" t="n">
-        <v>8989700</v>
+        <v>8795900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B88" t="n">
-        <v>121.5999984741211</v>
+        <v>123.6999969482422</v>
       </c>
       <c r="C88" t="n">
-        <v>124.4550018310547</v>
+        <v>130.6900024414062</v>
       </c>
       <c r="D88" t="n">
-        <v>120</v>
+        <v>123.0500030517578</v>
       </c>
       <c r="E88" t="n">
-        <v>123.4199981689453</v>
+        <v>129.9299926757812</v>
       </c>
       <c r="F88" t="n">
-        <v>8795900</v>
+        <v>8638900</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B89" t="n">
-        <v>123.6999969482422</v>
+        <v>128.7599945068359</v>
       </c>
       <c r="C89" t="n">
-        <v>130.6900024414062</v>
+        <v>129.7599945068359</v>
       </c>
       <c r="D89" t="n">
-        <v>123.0500030517578</v>
+        <v>123.3399963378906</v>
       </c>
       <c r="E89" t="n">
-        <v>129.9299926757812</v>
+        <v>125.0899963378906</v>
       </c>
       <c r="F89" t="n">
-        <v>8638900</v>
+        <v>7414600</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B90" t="n">
-        <v>128.7599945068359</v>
+        <v>127.5899963378906</v>
       </c>
       <c r="C90" t="n">
-        <v>129.7599945068359</v>
+        <v>133.3399963378906</v>
       </c>
       <c r="D90" t="n">
-        <v>123.3399963378906</v>
+        <v>127.370002746582</v>
       </c>
       <c r="E90" t="n">
-        <v>125.0899963378906</v>
+        <v>130.5899963378906</v>
       </c>
       <c r="F90" t="n">
-        <v>7414600</v>
+        <v>8562300</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B91" t="n">
-        <v>127.5899963378906</v>
+        <v>132.1799926757812</v>
       </c>
       <c r="C91" t="n">
-        <v>133.3399963378906</v>
+        <v>132.9400024414062</v>
       </c>
       <c r="D91" t="n">
-        <v>127.370002746582</v>
+        <v>129.3300018310547</v>
       </c>
       <c r="E91" t="n">
-        <v>130.5899963378906</v>
+        <v>129.8300018310547</v>
       </c>
       <c r="F91" t="n">
-        <v>8562300</v>
+        <v>5987000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B92" t="n">
-        <v>132.1799926757812</v>
+        <v>126.4899978637695</v>
       </c>
       <c r="C92" t="n">
-        <v>132.9400024414062</v>
+        <v>130.3800048828125</v>
       </c>
       <c r="D92" t="n">
-        <v>129.3300018310547</v>
+        <v>125.7799987792969</v>
       </c>
       <c r="E92" t="n">
-        <v>129.8300018310547</v>
+        <v>127.5199966430664</v>
       </c>
       <c r="F92" t="n">
-        <v>5987000</v>
+        <v>6371300</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B93" t="n">
-        <v>126.4899978637695</v>
+        <v>127.8600006103516</v>
       </c>
       <c r="C93" t="n">
-        <v>130.3800048828125</v>
+        <v>129.5500030517578</v>
       </c>
       <c r="D93" t="n">
-        <v>125.7799987792969</v>
+        <v>125.0400009155273</v>
       </c>
       <c r="E93" t="n">
-        <v>127.5199966430664</v>
+        <v>127.2900009155273</v>
       </c>
       <c r="F93" t="n">
-        <v>6371300</v>
+        <v>5931000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B94" t="n">
-        <v>127.8600006103516</v>
+        <v>139.8399963378906</v>
       </c>
       <c r="C94" t="n">
-        <v>129.5500030517578</v>
+        <v>146.3999938964844</v>
       </c>
       <c r="D94" t="n">
-        <v>125.0400009155273</v>
+        <v>137.4199981689453</v>
       </c>
       <c r="E94" t="n">
-        <v>127.2900009155273</v>
+        <v>138.4100036621094</v>
       </c>
       <c r="F94" t="n">
-        <v>5931000</v>
+        <v>14906700</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B95" t="n">
-        <v>139.8399963378906</v>
+        <v>138.3699951171875</v>
       </c>
       <c r="C95" t="n">
-        <v>146.3999938964844</v>
+        <v>138.8999938964844</v>
       </c>
       <c r="D95" t="n">
-        <v>137.4199981689453</v>
+        <v>134.8600006103516</v>
       </c>
       <c r="E95" t="n">
-        <v>138.4100036621094</v>
+        <v>136.3399963378906</v>
       </c>
       <c r="F95" t="n">
-        <v>14906700</v>
+        <v>8053900</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B96" t="n">
-        <v>138.3699951171875</v>
+        <v>139.3200073242188</v>
       </c>
       <c r="C96" t="n">
-        <v>138.8999938964844</v>
+        <v>146.4049987792969</v>
       </c>
       <c r="D96" t="n">
-        <v>134.8600006103516</v>
+        <v>139.2400054931641</v>
       </c>
       <c r="E96" t="n">
-        <v>136.3399963378906</v>
+        <v>143.7200012207031</v>
       </c>
       <c r="F96" t="n">
-        <v>8053900</v>
+        <v>10658200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B97" t="n">
-        <v>139.3200073242188</v>
+        <v>144.8600006103516</v>
       </c>
       <c r="C97" t="n">
-        <v>146.4049987792969</v>
+        <v>149.2700042724609</v>
       </c>
       <c r="D97" t="n">
-        <v>139.2400054931641</v>
+        <v>143.8000030517578</v>
       </c>
       <c r="E97" t="n">
-        <v>143.7200012207031</v>
+        <v>146.6900024414062</v>
       </c>
       <c r="F97" t="n">
-        <v>10658200</v>
+        <v>8697000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B98" t="n">
-        <v>144.8600006103516</v>
+        <v>150.3500061035156</v>
       </c>
       <c r="C98" t="n">
-        <v>149.2700042724609</v>
+        <v>151.8000030517578</v>
       </c>
       <c r="D98" t="n">
-        <v>143.8000030517578</v>
+        <v>145.5700073242188</v>
       </c>
       <c r="E98" t="n">
-        <v>146.6900024414062</v>
+        <v>150.1499938964844</v>
       </c>
       <c r="F98" t="n">
-        <v>8697000</v>
+        <v>8568200</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B99" t="n">
-        <v>150.3500061035156</v>
+        <v>150.1499938964844</v>
       </c>
       <c r="C99" t="n">
-        <v>151.8000030517578</v>
+        <v>151.5500030517578</v>
       </c>
       <c r="D99" t="n">
-        <v>145.5700073242188</v>
+        <v>145.3300018310547</v>
       </c>
       <c r="E99" t="n">
-        <v>150.1499938964844</v>
+        <v>148.1499938964844</v>
       </c>
       <c r="F99" t="n">
-        <v>8568200</v>
+        <v>8915300</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B100" t="n">
-        <v>150.1499938964844</v>
+        <v>145.8500061035156</v>
       </c>
       <c r="C100" t="n">
-        <v>151.5500030517578</v>
+        <v>148.0599975585938</v>
       </c>
       <c r="D100" t="n">
-        <v>145.3300018310547</v>
+        <v>141.4400024414062</v>
       </c>
       <c r="E100" t="n">
-        <v>148.1499938964844</v>
+        <v>141.7400054931641</v>
       </c>
       <c r="F100" t="n">
-        <v>8915300</v>
+        <v>6364000</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B101" t="n">
-        <v>145.8500061035156</v>
+        <v>141.3200073242188</v>
       </c>
       <c r="C101" t="n">
-        <v>148.0599975585938</v>
+        <v>143.1100006103516</v>
       </c>
       <c r="D101" t="n">
-        <v>141.4400024414062</v>
+        <v>138.2200012207031</v>
       </c>
       <c r="E101" t="n">
-        <v>141.7400054931641</v>
+        <v>138.3699951171875</v>
       </c>
       <c r="F101" t="n">
-        <v>6364000</v>
+        <v>7719200</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B102" t="n">
-        <v>141.3200073242188</v>
+        <v>140.7149963378906</v>
       </c>
       <c r="C102" t="n">
-        <v>143.1100006103516</v>
+        <v>143.2720031738281</v>
       </c>
       <c r="D102" t="n">
-        <v>138.2200012207031</v>
+        <v>135.3300018310547</v>
       </c>
       <c r="E102" t="n">
-        <v>138.3699951171875</v>
+        <v>139.3899993896484</v>
       </c>
       <c r="F102" t="n">
-        <v>7719200</v>
+        <v>8202300</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B103" t="n">
-        <v>140.7149963378906</v>
+        <v>138</v>
       </c>
       <c r="C103" t="n">
-        <v>143.2720031738281</v>
+        <v>139.3699951171875</v>
       </c>
       <c r="D103" t="n">
-        <v>135.3300018310547</v>
+        <v>129.2400054931641</v>
       </c>
       <c r="E103" t="n">
-        <v>139.3899993896484</v>
+        <v>130.2799987792969</v>
       </c>
       <c r="F103" t="n">
-        <v>8202300</v>
+        <v>13313800</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B104" t="n">
-        <v>138</v>
+        <v>127.7300033569336</v>
       </c>
       <c r="C104" t="n">
-        <v>139.3699951171875</v>
+        <v>130.3099975585938</v>
       </c>
       <c r="D104" t="n">
-        <v>129.2400054931641</v>
+        <v>125.3399963378906</v>
       </c>
       <c r="E104" t="n">
-        <v>130.2799987792969</v>
+        <v>128.6699981689453</v>
       </c>
       <c r="F104" t="n">
-        <v>13313800</v>
+        <v>9640500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B105" t="n">
-        <v>127.7300033569336</v>
+        <v>131.3999938964844</v>
       </c>
       <c r="C105" t="n">
-        <v>130.3099975585938</v>
+        <v>137.6100006103516</v>
       </c>
       <c r="D105" t="n">
-        <v>125.3399963378906</v>
+        <v>130.3200073242188</v>
       </c>
       <c r="E105" t="n">
-        <v>128.6699981689453</v>
+        <v>137.4900054931641</v>
       </c>
       <c r="F105" t="n">
-        <v>9640500</v>
+        <v>8986800</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B106" t="n">
-        <v>131.3999938964844</v>
+        <v>138.2799987792969</v>
       </c>
       <c r="C106" t="n">
-        <v>137.6100006103516</v>
+        <v>142.2700042724609</v>
       </c>
       <c r="D106" t="n">
-        <v>130.3200073242188</v>
+        <v>136.0549926757812</v>
       </c>
       <c r="E106" t="n">
-        <v>137.4900054931641</v>
+        <v>141.7400054931641</v>
       </c>
       <c r="F106" t="n">
-        <v>8986800</v>
+        <v>6801400</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B107" t="n">
-        <v>138.2799987792969</v>
+        <v>144.3249969482422</v>
       </c>
       <c r="C107" t="n">
-        <v>142.2700042724609</v>
+        <v>145.0350036621094</v>
       </c>
       <c r="D107" t="n">
-        <v>136.0549926757812</v>
+        <v>141.8000030517578</v>
       </c>
       <c r="E107" t="n">
-        <v>141.7400054931641</v>
+        <v>143.4499969482422</v>
       </c>
       <c r="F107" t="n">
-        <v>6801400</v>
+        <v>6138100</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B108" t="n">
-        <v>144.3249969482422</v>
+        <v>145.1100006103516</v>
       </c>
       <c r="C108" t="n">
-        <v>145.0350036621094</v>
+        <v>145.2400054931641</v>
       </c>
       <c r="D108" t="n">
-        <v>141.8000030517578</v>
+        <v>138.2200012207031</v>
       </c>
       <c r="E108" t="n">
-        <v>143.4499969482422</v>
+        <v>140.6600036621094</v>
       </c>
       <c r="F108" t="n">
-        <v>6138100</v>
+        <v>6942400</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B109" t="n">
-        <v>145.1100006103516</v>
+        <v>138</v>
       </c>
       <c r="C109" t="n">
-        <v>145.2400054931641</v>
+        <v>138.5</v>
       </c>
       <c r="D109" t="n">
-        <v>138.2200012207031</v>
+        <v>132.0099945068359</v>
       </c>
       <c r="E109" t="n">
-        <v>140.6600036621094</v>
+        <v>135.1199951171875</v>
       </c>
       <c r="F109" t="n">
-        <v>6942400</v>
+        <v>16322100</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B110" t="n">
+        <v>145.8200073242188</v>
+      </c>
+      <c r="C110" t="n">
+        <v>148.7700042724609</v>
+      </c>
+      <c r="D110" t="n">
         <v>138</v>
       </c>
-      <c r="C110" t="n">
-        <v>138.5</v>
-      </c>
-      <c r="D110" t="n">
-        <v>132.0099945068359</v>
-      </c>
       <c r="E110" t="n">
-        <v>135.1199951171875</v>
+        <v>141.5899963378906</v>
       </c>
       <c r="F110" t="n">
-        <v>16322100</v>
+        <v>21823000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B111" t="n">
-        <v>145.8200073242188</v>
+        <v>140.6399993896484</v>
       </c>
       <c r="C111" t="n">
-        <v>148.7700042724609</v>
+        <v>145</v>
       </c>
       <c r="D111" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E111" t="n">
-        <v>141.5899963378906</v>
+        <v>142.5800018310547</v>
       </c>
       <c r="F111" t="n">
-        <v>21823000</v>
+        <v>8724200</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B112" t="n">
-        <v>140.6399993896484</v>
+        <v>140.4600067138672</v>
       </c>
       <c r="C112" t="n">
-        <v>145</v>
+        <v>142.5</v>
       </c>
       <c r="D112" t="n">
-        <v>140</v>
+        <v>136.6900024414062</v>
       </c>
       <c r="E112" t="n">
-        <v>142.5800018310547</v>
+        <v>139.5399932861328</v>
       </c>
       <c r="F112" t="n">
-        <v>8724200</v>
+        <v>9955700</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B113" t="n">
-        <v>140.4600067138672</v>
+        <v>138.6100006103516</v>
       </c>
       <c r="C113" t="n">
-        <v>142.5</v>
+        <v>140.3200073242188</v>
       </c>
       <c r="D113" t="n">
-        <v>136.6900024414062</v>
+        <v>135.3699951171875</v>
       </c>
       <c r="E113" t="n">
-        <v>139.5399932861328</v>
+        <v>137.2299957275391</v>
       </c>
       <c r="F113" t="n">
-        <v>9955700</v>
+        <v>5260600</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B114" t="n">
-        <v>138.6100006103516</v>
+        <v>136.0200042724609</v>
       </c>
       <c r="C114" t="n">
-        <v>140.3200073242188</v>
+        <v>138.3300018310547</v>
       </c>
       <c r="D114" t="n">
-        <v>135.3699951171875</v>
+        <v>132.1499938964844</v>
       </c>
       <c r="E114" t="n">
-        <v>137.2299957275391</v>
+        <v>132.7899932861328</v>
       </c>
       <c r="F114" t="n">
-        <v>5260600</v>
+        <v>8309000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B115" t="n">
-        <v>136.0200042724609</v>
+        <v>131.2250061035156</v>
       </c>
       <c r="C115" t="n">
-        <v>138.3300018310547</v>
+        <v>131.6349945068359</v>
       </c>
       <c r="D115" t="n">
-        <v>132.1499938964844</v>
+        <v>126.2600021362305</v>
       </c>
       <c r="E115" t="n">
-        <v>132.7899932861328</v>
+        <v>127.4300003051758</v>
       </c>
       <c r="F115" t="n">
-        <v>8309000</v>
+        <v>9706800</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B116" t="n">
-        <v>131.2250061035156</v>
+        <v>130.25</v>
       </c>
       <c r="C116" t="n">
-        <v>131.6349945068359</v>
+        <v>130.7299957275391</v>
       </c>
       <c r="D116" t="n">
-        <v>126.2600021362305</v>
+        <v>124.379997253418</v>
       </c>
       <c r="E116" t="n">
-        <v>127.4300003051758</v>
+        <v>128.7700042724609</v>
       </c>
       <c r="F116" t="n">
-        <v>9706800</v>
+        <v>8120000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B117" t="n">
-        <v>130.25</v>
+        <v>129.3699951171875</v>
       </c>
       <c r="C117" t="n">
-        <v>130.7299957275391</v>
+        <v>133.7799987792969</v>
       </c>
       <c r="D117" t="n">
-        <v>124.379997253418</v>
+        <v>128.6399993896484</v>
       </c>
       <c r="E117" t="n">
-        <v>128.7700042724609</v>
+        <v>132.8899993896484</v>
       </c>
       <c r="F117" t="n">
-        <v>8120000</v>
+        <v>7611600</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B118" t="n">
-        <v>129.3699951171875</v>
+        <v>132</v>
       </c>
       <c r="C118" t="n">
-        <v>133.7799987792969</v>
+        <v>132.2200012207031</v>
       </c>
       <c r="D118" t="n">
-        <v>128.6399993896484</v>
+        <v>126.9199981689453</v>
       </c>
       <c r="E118" t="n">
-        <v>132.8899993896484</v>
+        <v>130.25</v>
       </c>
       <c r="F118" t="n">
-        <v>7611600</v>
+        <v>6360700</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B119" t="n">
-        <v>132</v>
+        <v>127.5199966430664</v>
       </c>
       <c r="C119" t="n">
-        <v>132.2200012207031</v>
+        <v>133.5800018310547</v>
       </c>
       <c r="D119" t="n">
-        <v>126.9199981689453</v>
+        <v>127.5</v>
       </c>
       <c r="E119" t="n">
-        <v>130.25</v>
+        <v>133.5</v>
       </c>
       <c r="F119" t="n">
-        <v>6360700</v>
+        <v>9043300</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B120" t="n">
-        <v>127.5199966430664</v>
+        <v>129.6499938964844</v>
       </c>
       <c r="C120" t="n">
-        <v>133.5800018310547</v>
+        <v>130.6900024414062</v>
       </c>
       <c r="D120" t="n">
-        <v>127.5</v>
+        <v>127.2600021362305</v>
       </c>
       <c r="E120" t="n">
-        <v>133.5</v>
+        <v>129.3000030517578</v>
       </c>
       <c r="F120" t="n">
-        <v>9043300</v>
+        <v>6875000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B121" t="n">
-        <v>129.6499938964844</v>
+        <v>125.3300018310547</v>
       </c>
       <c r="C121" t="n">
-        <v>130.6900024414062</v>
+        <v>126.8300018310547</v>
       </c>
       <c r="D121" t="n">
-        <v>127.2600021362305</v>
+        <v>122.370002746582</v>
       </c>
       <c r="E121" t="n">
-        <v>129.3000030517578</v>
+        <v>124.5999984741211</v>
       </c>
       <c r="F121" t="n">
-        <v>6875000</v>
+        <v>6119700</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B122" t="n">
-        <v>125.3300018310547</v>
+        <v>127.870002746582</v>
       </c>
       <c r="C122" t="n">
-        <v>126.8300018310547</v>
+        <v>135.5599975585938</v>
       </c>
       <c r="D122" t="n">
-        <v>122.370002746582</v>
+        <v>127.4000015258789</v>
       </c>
       <c r="E122" t="n">
-        <v>124.5999984741211</v>
+        <v>134.8300018310547</v>
       </c>
       <c r="F122" t="n">
-        <v>6119700</v>
+        <v>6897700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B123" t="n">
-        <v>127.870002746582</v>
+        <v>135.1150054931641</v>
       </c>
       <c r="C123" t="n">
-        <v>135.5599975585938</v>
+        <v>139.4799957275391</v>
       </c>
       <c r="D123" t="n">
-        <v>127.4000015258789</v>
+        <v>134</v>
       </c>
       <c r="E123" t="n">
-        <v>134.8300018310547</v>
+        <v>139.3999938964844</v>
       </c>
       <c r="F123" t="n">
-        <v>6897700</v>
+        <v>8384600</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B124" t="n">
-        <v>135.1150054931641</v>
+        <v>136.3899993896484</v>
       </c>
       <c r="C124" t="n">
-        <v>139.4799957275391</v>
+        <v>139.0579986572266</v>
       </c>
       <c r="D124" t="n">
-        <v>134</v>
+        <v>132.7299957275391</v>
       </c>
       <c r="E124" t="n">
-        <v>139.3999938964844</v>
+        <v>132.8899993896484</v>
       </c>
       <c r="F124" t="n">
-        <v>8384600</v>
+        <v>6282000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B125" t="n">
-        <v>136.3899993896484</v>
+        <v>130.4049987792969</v>
       </c>
       <c r="C125" t="n">
-        <v>139.0579986572266</v>
+        <v>137.6750030517578</v>
       </c>
       <c r="D125" t="n">
-        <v>132.7299957275391</v>
+        <v>129.7899932861328</v>
       </c>
       <c r="E125" t="n">
-        <v>132.8899993896484</v>
+        <v>137.1699981689453</v>
       </c>
       <c r="F125" t="n">
-        <v>6282000</v>
+        <v>6715200</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B126" t="n">
-        <v>130.4049987792969</v>
+        <v>138</v>
       </c>
       <c r="C126" t="n">
-        <v>137.6750030517578</v>
+        <v>141.7700042724609</v>
       </c>
       <c r="D126" t="n">
-        <v>129.7899932861328</v>
+        <v>137.8899993896484</v>
       </c>
       <c r="E126" t="n">
-        <v>137.1699981689453</v>
+        <v>139.6199951171875</v>
       </c>
       <c r="F126" t="n">
-        <v>6715200</v>
+        <v>5435800</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B127" t="n">
-        <v>138</v>
+        <v>139.1600036621094</v>
       </c>
       <c r="C127" t="n">
-        <v>141.7700042724609</v>
+        <v>141.1399993896484</v>
       </c>
       <c r="D127" t="n">
-        <v>137.8899993896484</v>
+        <v>137.6540069580078</v>
       </c>
       <c r="E127" t="n">
-        <v>139.6199951171875</v>
+        <v>138.2299957275391</v>
       </c>
       <c r="F127" t="n">
-        <v>5435800</v>
+        <v>4165100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B128" t="n">
-        <v>139.1600036621094</v>
+        <v>137.7400054931641</v>
       </c>
       <c r="C128" t="n">
-        <v>141.1399993896484</v>
+        <v>137.7799987792969</v>
       </c>
       <c r="D128" t="n">
-        <v>137.6540069580078</v>
+        <v>133.6900024414062</v>
       </c>
       <c r="E128" t="n">
-        <v>138.2299957275391</v>
+        <v>134.0299987792969</v>
       </c>
       <c r="F128" t="n">
-        <v>4165100</v>
+        <v>5494200</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B129" t="n">
-        <v>137.7400054931641</v>
+        <v>134.8200073242188</v>
       </c>
       <c r="C129" t="n">
-        <v>137.7799987792969</v>
+        <v>137.5950012207031</v>
       </c>
       <c r="D129" t="n">
-        <v>133.6900024414062</v>
+        <v>130.5099945068359</v>
       </c>
       <c r="E129" t="n">
-        <v>134.0299987792969</v>
+        <v>133.5700073242188</v>
       </c>
       <c r="F129" t="n">
-        <v>5494200</v>
+        <v>5364800</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B130" t="n">
-        <v>134.8200073242188</v>
+        <v>133.8699951171875</v>
       </c>
       <c r="C130" t="n">
-        <v>137.5950012207031</v>
+        <v>136.2799987792969</v>
       </c>
       <c r="D130" t="n">
-        <v>130.5099945068359</v>
+        <v>131.9100036621094</v>
       </c>
       <c r="E130" t="n">
-        <v>133.5700073242188</v>
+        <v>135.3500061035156</v>
       </c>
       <c r="F130" t="n">
-        <v>5364800</v>
+        <v>7884200</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B131" t="n">
-        <v>133.8699951171875</v>
+        <v>135.0099945068359</v>
       </c>
       <c r="C131" t="n">
-        <v>136.2799987792969</v>
+        <v>136.6999969482422</v>
       </c>
       <c r="D131" t="n">
-        <v>131.9100036621094</v>
+        <v>132.3099975585938</v>
       </c>
       <c r="E131" t="n">
-        <v>135.3500061035156</v>
+        <v>133.0700073242188</v>
       </c>
       <c r="F131" t="n">
-        <v>7884200</v>
+        <v>5959000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B132" t="n">
-        <v>135.0099945068359</v>
+        <v>133.5</v>
       </c>
       <c r="C132" t="n">
-        <v>136.6999969482422</v>
+        <v>137.5599975585938</v>
       </c>
       <c r="D132" t="n">
-        <v>132.3099975585938</v>
+        <v>133.5</v>
       </c>
       <c r="E132" t="n">
-        <v>133.0700073242188</v>
+        <v>136.0700073242188</v>
       </c>
       <c r="F132" t="n">
-        <v>5959000</v>
+        <v>5264100</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B133" t="n">
-        <v>133.5</v>
+        <v>133.7400054931641</v>
       </c>
       <c r="C133" t="n">
-        <v>137.5599975585938</v>
+        <v>136.5700073242188</v>
       </c>
       <c r="D133" t="n">
-        <v>133.5</v>
+        <v>132.3500061035156</v>
       </c>
       <c r="E133" t="n">
-        <v>136.0700073242188</v>
+        <v>136.2599945068359</v>
       </c>
       <c r="F133" t="n">
-        <v>5264100</v>
+        <v>4418900</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B134" t="n">
-        <v>133.7400054931641</v>
+        <v>134</v>
       </c>
       <c r="C134" t="n">
-        <v>136.5700073242188</v>
+        <v>135.3000030517578</v>
       </c>
       <c r="D134" t="n">
-        <v>132.3500061035156</v>
+        <v>128.8999938964844</v>
       </c>
       <c r="E134" t="n">
-        <v>136.2599945068359</v>
+        <v>131.2200012207031</v>
       </c>
       <c r="F134" t="n">
-        <v>4418900</v>
+        <v>11351600</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B135" t="n">
-        <v>134</v>
+        <v>133.4799957275391</v>
       </c>
       <c r="C135" t="n">
-        <v>135.3000030517578</v>
+        <v>138.2100067138672</v>
       </c>
       <c r="D135" t="n">
-        <v>128.8999938964844</v>
+        <v>132.1999969482422</v>
       </c>
       <c r="E135" t="n">
-        <v>131.2200012207031</v>
+        <v>135.8800048828125</v>
       </c>
       <c r="F135" t="n">
-        <v>11351600</v>
+        <v>6402200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B136" t="n">
-        <v>133.4799957275391</v>
+        <v>134.2100067138672</v>
       </c>
       <c r="C136" t="n">
-        <v>138.2100067138672</v>
+        <v>135.6999969482422</v>
       </c>
       <c r="D136" t="n">
-        <v>132.1999969482422</v>
+        <v>129.1900024414062</v>
       </c>
       <c r="E136" t="n">
-        <v>135.8800048828125</v>
+        <v>130.8000030517578</v>
       </c>
       <c r="F136" t="n">
-        <v>6402200</v>
+        <v>7858900</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B137" t="n">
-        <v>134.2100067138672</v>
+        <v>133.2100067138672</v>
       </c>
       <c r="C137" t="n">
-        <v>135.6999969482422</v>
+        <v>135.0800018310547</v>
       </c>
       <c r="D137" t="n">
-        <v>129.1900024414062</v>
+        <v>131.1499938964844</v>
       </c>
       <c r="E137" t="n">
-        <v>130.8000030517578</v>
+        <v>135.0099945068359</v>
       </c>
       <c r="F137" t="n">
-        <v>7858900</v>
+        <v>5353300</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B138" t="n">
-        <v>133.2100067138672</v>
+        <v>131.7899932861328</v>
       </c>
       <c r="C138" t="n">
-        <v>135.0800018310547</v>
+        <v>132.5</v>
       </c>
       <c r="D138" t="n">
-        <v>131.1499938964844</v>
+        <v>122.5100021362305</v>
       </c>
       <c r="E138" t="n">
-        <v>135.0099945068359</v>
+        <v>122.5500030517578</v>
       </c>
       <c r="F138" t="n">
-        <v>5353300</v>
+        <v>7553500</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B139" t="n">
-        <v>131.7899932861328</v>
+        <v>121.3399963378906</v>
       </c>
       <c r="C139" t="n">
-        <v>132.5</v>
+        <v>123.7200012207031</v>
       </c>
       <c r="D139" t="n">
-        <v>122.5100021362305</v>
+        <v>120.3420028686523</v>
       </c>
       <c r="E139" t="n">
-        <v>122.5500030517578</v>
+        <v>120.7699966430664</v>
       </c>
       <c r="F139" t="n">
-        <v>7553500</v>
+        <v>5940200</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B140" t="n">
-        <v>121.3399963378906</v>
+        <v>122.0100021362305</v>
       </c>
       <c r="C140" t="n">
-        <v>123.7200012207031</v>
+        <v>123.3399963378906</v>
       </c>
       <c r="D140" t="n">
-        <v>120.3420028686523</v>
+        <v>115.4199981689453</v>
       </c>
       <c r="E140" t="n">
-        <v>120.7699966430664</v>
+        <v>116.129997253418</v>
       </c>
       <c r="F140" t="n">
-        <v>5940200</v>
+        <v>7540500</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B141" t="n">
-        <v>122.0100021362305</v>
+        <v>118.620002746582</v>
       </c>
       <c r="C141" t="n">
-        <v>123.3399963378906</v>
+        <v>123.4599990844727</v>
       </c>
       <c r="D141" t="n">
-        <v>115.4199981689453</v>
+        <v>117.4199981689453</v>
       </c>
       <c r="E141" t="n">
-        <v>116.129997253418</v>
+        <v>122.7799987792969</v>
       </c>
       <c r="F141" t="n">
-        <v>7540500</v>
+        <v>7837700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B142" t="n">
-        <v>118.620002746582</v>
+        <v>126.0599975585938</v>
       </c>
       <c r="C142" t="n">
-        <v>123.4599990844727</v>
+        <v>127.25</v>
       </c>
       <c r="D142" t="n">
-        <v>117.4199981689453</v>
+        <v>124.6600036621094</v>
       </c>
       <c r="E142" t="n">
-        <v>122.7799987792969</v>
+        <v>124.8499984741211</v>
       </c>
       <c r="F142" t="n">
-        <v>7837700</v>
+        <v>5037700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B143" t="n">
-        <v>126.0599975585938</v>
+        <v>121.0999984741211</v>
       </c>
       <c r="C143" t="n">
-        <v>127.25</v>
+        <v>127.1999969482422</v>
       </c>
       <c r="D143" t="n">
-        <v>124.6600036621094</v>
+        <v>119.7910003662109</v>
       </c>
       <c r="E143" t="n">
-        <v>124.8499984741211</v>
+        <v>126.6800003051758</v>
       </c>
       <c r="F143" t="n">
-        <v>5037700</v>
+        <v>5125100</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B144" t="n">
-        <v>121.0999984741211</v>
+        <v>127.3199996948242</v>
       </c>
       <c r="C144" t="n">
-        <v>127.1999969482422</v>
+        <v>128.1649932861328</v>
       </c>
       <c r="D144" t="n">
-        <v>119.7910003662109</v>
+        <v>125.1650009155273</v>
       </c>
       <c r="E144" t="n">
-        <v>126.6800003051758</v>
+        <v>126.25</v>
       </c>
       <c r="F144" t="n">
-        <v>5125100</v>
+        <v>3033100</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B145" t="n">
-        <v>127.3199996948242</v>
+        <v>127.8499984741211</v>
       </c>
       <c r="C145" t="n">
-        <v>128.1649932861328</v>
+        <v>133.6999969482422</v>
       </c>
       <c r="D145" t="n">
-        <v>125.1650009155273</v>
+        <v>127.5500030517578</v>
       </c>
       <c r="E145" t="n">
-        <v>126.25</v>
+        <v>133.6399993896484</v>
       </c>
       <c r="F145" t="n">
-        <v>3033100</v>
+        <v>5758000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B146" t="n">
-        <v>127.8499984741211</v>
+        <v>143</v>
       </c>
       <c r="C146" t="n">
-        <v>133.6999969482422</v>
+        <v>146.1600036621094</v>
       </c>
       <c r="D146" t="n">
-        <v>127.5500030517578</v>
+        <v>141.1199951171875</v>
       </c>
       <c r="E146" t="n">
-        <v>133.6399993896484</v>
+        <v>145.0700073242188</v>
       </c>
       <c r="F146" t="n">
-        <v>5758000</v>
+        <v>12136800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B147" t="n">
-        <v>143</v>
+        <v>145.1100006103516</v>
       </c>
       <c r="C147" t="n">
-        <v>146.1600036621094</v>
+        <v>146.1900024414062</v>
       </c>
       <c r="D147" t="n">
-        <v>141.1199951171875</v>
+        <v>141.1100006103516</v>
       </c>
       <c r="E147" t="n">
-        <v>145.0700073242188</v>
+        <v>146.0500030517578</v>
       </c>
       <c r="F147" t="n">
-        <v>12136800</v>
+        <v>7266100</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B148" t="n">
-        <v>145.1100006103516</v>
+        <v>147.5399932861328</v>
       </c>
       <c r="C148" t="n">
-        <v>146.1900024414062</v>
+        <v>149.3399963378906</v>
       </c>
       <c r="D148" t="n">
-        <v>141.1100006103516</v>
+        <v>145.3999938964844</v>
       </c>
       <c r="E148" t="n">
-        <v>146.0500030517578</v>
+        <v>147.3500061035156</v>
       </c>
       <c r="F148" t="n">
-        <v>7266100</v>
+        <v>7054100</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B149" t="n">
-        <v>147.5399932861328</v>
+        <v>146.7299957275391</v>
       </c>
       <c r="C149" t="n">
-        <v>149.3399963378906</v>
+        <v>152.1399993896484</v>
       </c>
       <c r="D149" t="n">
-        <v>145.3999938964844</v>
+        <v>144.7960052490234</v>
       </c>
       <c r="E149" t="n">
-        <v>147.3500061035156</v>
+        <v>152.0200042724609</v>
       </c>
       <c r="F149" t="n">
-        <v>7054100</v>
+        <v>7217900</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B150" t="n">
-        <v>146.7299957275391</v>
+        <v>153.9900054931641</v>
       </c>
       <c r="C150" t="n">
-        <v>152.1399993896484</v>
+        <v>155.4100036621094</v>
       </c>
       <c r="D150" t="n">
-        <v>144.7960052490234</v>
+        <v>150.9859924316406</v>
       </c>
       <c r="E150" t="n">
-        <v>152.0200042724609</v>
+        <v>154.3699951171875</v>
       </c>
       <c r="F150" t="n">
-        <v>7217900</v>
+        <v>7114000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B151" t="n">
-        <v>153.9900054931641</v>
+        <v>154.8200073242188</v>
       </c>
       <c r="C151" t="n">
-        <v>155.4100036621094</v>
+        <v>155.2250061035156</v>
       </c>
       <c r="D151" t="n">
-        <v>150.9859924316406</v>
+        <v>150.5200042724609</v>
       </c>
       <c r="E151" t="n">
-        <v>154.3699951171875</v>
+        <v>154.3300018310547</v>
       </c>
       <c r="F151" t="n">
-        <v>7114000</v>
+        <v>5835300</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B152" t="n">
-        <v>154.8200073242188</v>
+        <v>155.9199981689453</v>
       </c>
       <c r="C152" t="n">
-        <v>155.2250061035156</v>
+        <v>161.0099945068359</v>
       </c>
       <c r="D152" t="n">
-        <v>150.5200042724609</v>
+        <v>153.3600006103516</v>
       </c>
       <c r="E152" t="n">
-        <v>154.3300018310547</v>
+        <v>161.0099945068359</v>
       </c>
       <c r="F152" t="n">
-        <v>5835300</v>
+        <v>7205600</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B153" t="n">
-        <v>155.9199981689453</v>
+        <v>162.2350006103516</v>
       </c>
       <c r="C153" t="n">
-        <v>161.0099945068359</v>
+        <v>165.2799987792969</v>
       </c>
       <c r="D153" t="n">
-        <v>153.3600006103516</v>
+        <v>160.4700012207031</v>
       </c>
       <c r="E153" t="n">
-        <v>161.0099945068359</v>
+        <v>164.2299957275391</v>
       </c>
       <c r="F153" t="n">
-        <v>7205600</v>
+        <v>8216400</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B154" t="n">
-        <v>162.2350006103516</v>
+        <v>165</v>
       </c>
       <c r="C154" t="n">
-        <v>165.2799987792969</v>
+        <v>167.8999938964844</v>
       </c>
       <c r="D154" t="n">
-        <v>160.4700012207031</v>
+        <v>164.4900054931641</v>
       </c>
       <c r="E154" t="n">
-        <v>164.2299957275391</v>
+        <v>166.8500061035156</v>
       </c>
       <c r="F154" t="n">
-        <v>8216400</v>
+        <v>6113300</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B155" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C155" t="n">
-        <v>167.8999938964844</v>
+        <v>173.8500061035156</v>
       </c>
       <c r="D155" t="n">
-        <v>164.4900054931641</v>
+        <v>167.2200012207031</v>
       </c>
       <c r="E155" t="n">
-        <v>166.8500061035156</v>
+        <v>172.8600006103516</v>
       </c>
       <c r="F155" t="n">
-        <v>6113300</v>
+        <v>8918900</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B156" t="n">
-        <v>170</v>
+        <v>174.3999938964844</v>
       </c>
       <c r="C156" t="n">
-        <v>173.8500061035156</v>
+        <v>178.4799957275391</v>
       </c>
       <c r="D156" t="n">
-        <v>167.2200012207031</v>
+        <v>171.1399993896484</v>
       </c>
       <c r="E156" t="n">
-        <v>172.8600006103516</v>
+        <v>177.7299957275391</v>
       </c>
       <c r="F156" t="n">
-        <v>8918900</v>
+        <v>8699400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B157" t="n">
-        <v>174.3999938964844</v>
+        <v>177.5</v>
       </c>
       <c r="C157" t="n">
-        <v>178.4799957275391</v>
+        <v>177.75</v>
       </c>
       <c r="D157" t="n">
-        <v>171.1399993896484</v>
+        <v>169.3800048828125</v>
       </c>
       <c r="E157" t="n">
-        <v>177.7299957275391</v>
+        <v>172.5500030517578</v>
       </c>
       <c r="F157" t="n">
-        <v>8699400</v>
+        <v>7428000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B158" t="n">
-        <v>177.5</v>
+        <v>174.5299987792969</v>
       </c>
       <c r="C158" t="n">
-        <v>177.75</v>
+        <v>179.8000030517578</v>
       </c>
       <c r="D158" t="n">
-        <v>169.3800048828125</v>
+        <v>173.5200042724609</v>
       </c>
       <c r="E158" t="n">
-        <v>172.5500030517578</v>
+        <v>176.9100036621094</v>
       </c>
       <c r="F158" t="n">
-        <v>7428000</v>
+        <v>7508000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B159" t="n">
-        <v>174.5299987792969</v>
+        <v>176.7200012207031</v>
       </c>
       <c r="C159" t="n">
-        <v>179.8000030517578</v>
+        <v>176.7599945068359</v>
       </c>
       <c r="D159" t="n">
-        <v>173.5200042724609</v>
+        <v>168.5099945068359</v>
       </c>
       <c r="E159" t="n">
-        <v>176.9100036621094</v>
+        <v>172.4700012207031</v>
       </c>
       <c r="F159" t="n">
-        <v>7508000</v>
+        <v>6782500</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B160" t="n">
-        <v>176.7200012207031</v>
+        <v>166.4799957275391</v>
       </c>
       <c r="C160" t="n">
-        <v>176.7599945068359</v>
+        <v>167.8200073242188</v>
       </c>
       <c r="D160" t="n">
-        <v>168.5099945068359</v>
+        <v>162.25</v>
       </c>
       <c r="E160" t="n">
-        <v>172.4700012207031</v>
+        <v>165.2899932861328</v>
       </c>
       <c r="F160" t="n">
-        <v>6782500</v>
+        <v>7414100</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B161" t="n">
-        <v>166.4799957275391</v>
+        <v>166.1000061035156</v>
       </c>
       <c r="C161" t="n">
-        <v>167.8200073242188</v>
+        <v>168.7299957275391</v>
       </c>
       <c r="D161" t="n">
-        <v>162.25</v>
+        <v>163.4199981689453</v>
       </c>
       <c r="E161" t="n">
-        <v>165.2899932861328</v>
+        <v>168.6799926757812</v>
       </c>
       <c r="F161" t="n">
-        <v>7414100</v>
+        <v>6270500</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B162" t="n">
-        <v>166.1000061035156</v>
+        <v>172.0099945068359</v>
       </c>
       <c r="C162" t="n">
-        <v>168.7299957275391</v>
+        <v>173.5800018310547</v>
       </c>
       <c r="D162" t="n">
-        <v>163.4199981689453</v>
+        <v>167.7599945068359</v>
       </c>
       <c r="E162" t="n">
-        <v>168.6799926757812</v>
+        <v>172.7100067138672</v>
       </c>
       <c r="F162" t="n">
-        <v>6270500</v>
+        <v>6141700</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B163" t="n">
-        <v>172.0099945068359</v>
+        <v>172.9900054931641</v>
       </c>
       <c r="C163" t="n">
-        <v>173.5800018310547</v>
+        <v>177.1799926757812</v>
       </c>
       <c r="D163" t="n">
-        <v>167.7599945068359</v>
+        <v>172</v>
       </c>
       <c r="E163" t="n">
-        <v>172.7100067138672</v>
+        <v>172.6999969482422</v>
       </c>
       <c r="F163" t="n">
-        <v>6141700</v>
+        <v>7652400</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B164" t="n">
-        <v>172.9900054931641</v>
+        <v>175.6799926757812</v>
       </c>
       <c r="C164" t="n">
-        <v>177.1799926757812</v>
+        <v>179.1000061035156</v>
       </c>
       <c r="D164" t="n">
-        <v>172</v>
+        <v>172.2850036621094</v>
       </c>
       <c r="E164" t="n">
-        <v>172.6999969482422</v>
+        <v>172.6199951171875</v>
       </c>
       <c r="F164" t="n">
-        <v>7652400</v>
+        <v>7167900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B165" t="n">
-        <v>175.6799926757812</v>
+        <v>177</v>
       </c>
       <c r="C165" t="n">
-        <v>179.1000061035156</v>
+        <v>177.2200012207031</v>
       </c>
       <c r="D165" t="n">
-        <v>172.2850036621094</v>
+        <v>169.8899993896484</v>
       </c>
       <c r="E165" t="n">
-        <v>172.6199951171875</v>
+        <v>170.2200012207031</v>
       </c>
       <c r="F165" t="n">
-        <v>7167900</v>
+        <v>15684800</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B166" t="n">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="C166" t="n">
-        <v>177.2200012207031</v>
+        <v>154.8300018310547</v>
       </c>
       <c r="D166" t="n">
-        <v>169.8899993896484</v>
+        <v>140.5800018310547</v>
       </c>
       <c r="E166" t="n">
-        <v>170.2200012207031</v>
+        <v>147.0599975585938</v>
       </c>
       <c r="F166" t="n">
-        <v>15684800</v>
+        <v>35627200</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B167" t="n">
-        <v>153</v>
+        <v>149.2200012207031</v>
       </c>
       <c r="C167" t="n">
-        <v>154.8300018310547</v>
+        <v>149.4400024414062</v>
       </c>
       <c r="D167" t="n">
-        <v>140.5800018310547</v>
+        <v>139.6799926757812</v>
       </c>
       <c r="E167" t="n">
-        <v>147.0599975585938</v>
+        <v>141.75</v>
       </c>
       <c r="F167" t="n">
-        <v>35627200</v>
+        <v>18255700</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B168" t="n">
-        <v>149.2200012207031</v>
+        <v>142.6499938964844</v>
       </c>
       <c r="C168" t="n">
-        <v>149.4400024414062</v>
+        <v>143.9900054931641</v>
       </c>
       <c r="D168" t="n">
-        <v>139.6799926757812</v>
+        <v>138.6000061035156</v>
       </c>
       <c r="E168" t="n">
-        <v>141.75</v>
+        <v>141.7700042724609</v>
       </c>
       <c r="F168" t="n">
-        <v>18255700</v>
+        <v>20371600</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B169" t="n">
-        <v>142.6499938964844</v>
+        <v>141.3999938964844</v>
       </c>
       <c r="C169" t="n">
-        <v>143.9900054931641</v>
+        <v>142.6199951171875</v>
       </c>
       <c r="D169" t="n">
-        <v>138.6000061035156</v>
+        <v>135.1300048828125</v>
       </c>
       <c r="E169" t="n">
-        <v>141.7700042724609</v>
+        <v>136.4299926757812</v>
       </c>
       <c r="F169" t="n">
-        <v>20371600</v>
+        <v>18520900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B170" t="n">
-        <v>141.3999938964844</v>
+        <v>136.7799987792969</v>
       </c>
       <c r="C170" t="n">
-        <v>142.6199951171875</v>
+        <v>142.9400024414062</v>
       </c>
       <c r="D170" t="n">
-        <v>135.1300048828125</v>
+        <v>135.3699951171875</v>
       </c>
       <c r="E170" t="n">
-        <v>136.4299926757812</v>
+        <v>142.5399932861328</v>
       </c>
       <c r="F170" t="n">
-        <v>18520900</v>
+        <v>12796100</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B171" t="n">
-        <v>136.7799987792969</v>
+        <v>144.8000030517578</v>
       </c>
       <c r="C171" t="n">
-        <v>142.9400024414062</v>
+        <v>147.3099975585938</v>
       </c>
       <c r="D171" t="n">
-        <v>135.3699951171875</v>
+        <v>140.3000030517578</v>
       </c>
       <c r="E171" t="n">
-        <v>142.5399932861328</v>
+        <v>140.6900024414062</v>
       </c>
       <c r="F171" t="n">
-        <v>12796100</v>
+        <v>14164600</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B172" t="n">
-        <v>144.8000030517578</v>
+        <v>142.5</v>
       </c>
       <c r="C172" t="n">
-        <v>147.3099975585938</v>
+        <v>147.8899993896484</v>
       </c>
       <c r="D172" t="n">
-        <v>140.3000030517578</v>
+        <v>141</v>
       </c>
       <c r="E172" t="n">
-        <v>140.6900024414062</v>
+        <v>147.8099975585938</v>
       </c>
       <c r="F172" t="n">
-        <v>14164600</v>
+        <v>15728200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B173" t="n">
-        <v>142.5</v>
+        <v>144.9900054931641</v>
       </c>
       <c r="C173" t="n">
-        <v>147.8899993896484</v>
+        <v>145.8999938964844</v>
       </c>
       <c r="D173" t="n">
-        <v>141</v>
+        <v>141.7799987792969</v>
       </c>
       <c r="E173" t="n">
-        <v>147.8099975585938</v>
+        <v>141.9700012207031</v>
       </c>
       <c r="F173" t="n">
-        <v>15728200</v>
+        <v>10833000</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B174" t="n">
-        <v>144.9900054931641</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="C174" t="n">
-        <v>145.8999938964844</v>
+        <v>143.6699981689453</v>
       </c>
       <c r="D174" t="n">
-        <v>141.7799987792969</v>
+        <v>138.6399993896484</v>
       </c>
       <c r="E174" t="n">
-        <v>141.9700012207031</v>
+        <v>141.7100067138672</v>
       </c>
       <c r="F174" t="n">
-        <v>10833000</v>
+        <v>8634500</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B175" t="n">
-        <v>143.0200042724609</v>
+        <v>139.5800018310547</v>
       </c>
       <c r="C175" t="n">
-        <v>143.6699981689453</v>
+        <v>142.5</v>
       </c>
       <c r="D175" t="n">
-        <v>138.6399993896484</v>
+        <v>137</v>
       </c>
       <c r="E175" t="n">
-        <v>141.7100067138672</v>
+        <v>141.5800018310547</v>
       </c>
       <c r="F175" t="n">
-        <v>8634500</v>
+        <v>8800800</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B176" t="n">
-        <v>139.5800018310547</v>
+        <v>142</v>
       </c>
       <c r="C176" t="n">
-        <v>142.5</v>
+        <v>143.2599945068359</v>
       </c>
       <c r="D176" t="n">
-        <v>137</v>
+        <v>137.5</v>
       </c>
       <c r="E176" t="n">
-        <v>141.5800018310547</v>
+        <v>140.4900054931641</v>
       </c>
       <c r="F176" t="n">
-        <v>8800800</v>
+        <v>9617000</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B177" t="n">
-        <v>142</v>
+        <v>139.3000030517578</v>
       </c>
       <c r="C177" t="n">
-        <v>143.2599945068359</v>
+        <v>148.9900054931641</v>
       </c>
       <c r="D177" t="n">
-        <v>137.5</v>
+        <v>139.125</v>
       </c>
       <c r="E177" t="n">
-        <v>140.4900054931641</v>
+        <v>148.5899963378906</v>
       </c>
       <c r="F177" t="n">
-        <v>9617000</v>
+        <v>11620600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B178" t="n">
-        <v>139.3000030517578</v>
+        <v>152.2599945068359</v>
       </c>
       <c r="C178" t="n">
-        <v>148.9900054931641</v>
+        <v>154.3899993896484</v>
       </c>
       <c r="D178" t="n">
-        <v>139.125</v>
+        <v>149</v>
       </c>
       <c r="E178" t="n">
-        <v>148.5899963378906</v>
+        <v>154.0299987792969</v>
       </c>
       <c r="F178" t="n">
-        <v>11620600</v>
+        <v>10554600</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B179" t="n">
-        <v>152.2599945068359</v>
+        <v>157.5050048828125</v>
       </c>
       <c r="C179" t="n">
-        <v>154.3899993896484</v>
+        <v>160.1399993896484</v>
       </c>
       <c r="D179" t="n">
-        <v>149</v>
+        <v>153.8899993896484</v>
       </c>
       <c r="E179" t="n">
-        <v>154.0299987792969</v>
+        <v>158.0099945068359</v>
       </c>
       <c r="F179" t="n">
-        <v>10554600</v>
+        <v>11835300</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B180" t="n">
-        <v>157.5050048828125</v>
+        <v>157.8500061035156</v>
       </c>
       <c r="C180" t="n">
-        <v>160.1399993896484</v>
+        <v>158.1100006103516</v>
       </c>
       <c r="D180" t="n">
-        <v>153.8899993896484</v>
+        <v>153.5700073242188</v>
       </c>
       <c r="E180" t="n">
-        <v>158.0099945068359</v>
+        <v>154.3099975585938</v>
       </c>
       <c r="F180" t="n">
-        <v>11835300</v>
+        <v>6982200</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B181" t="n">
-        <v>157.8500061035156</v>
+        <v>154</v>
       </c>
       <c r="C181" t="n">
-        <v>158.1100006103516</v>
+        <v>156.3800048828125</v>
       </c>
       <c r="D181" t="n">
-        <v>153.5700073242188</v>
+        <v>150.6600036621094</v>
       </c>
       <c r="E181" t="n">
-        <v>154.3099975585938</v>
+        <v>155.2700042724609</v>
       </c>
       <c r="F181" t="n">
-        <v>6982200</v>
+        <v>7194300</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B182" t="n">
-        <v>154</v>
+        <v>157.3999938964844</v>
       </c>
       <c r="C182" t="n">
-        <v>156.3800048828125</v>
+        <v>161.5</v>
       </c>
       <c r="D182" t="n">
-        <v>150.6600036621094</v>
+        <v>155.8000030517578</v>
       </c>
       <c r="E182" t="n">
-        <v>155.2700042724609</v>
+        <v>159.4700012207031</v>
       </c>
       <c r="F182" t="n">
-        <v>7194300</v>
+        <v>15385900</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B183" t="n">
-        <v>157.3999938964844</v>
+        <v>162.1399993896484</v>
       </c>
       <c r="C183" t="n">
-        <v>161.5</v>
+        <v>172.3300018310547</v>
       </c>
       <c r="D183" t="n">
-        <v>155.8000030517578</v>
+        <v>161.2799987792969</v>
       </c>
       <c r="E183" t="n">
-        <v>159.4700012207031</v>
+        <v>170.6799926757812</v>
       </c>
       <c r="F183" t="n">
-        <v>15385900</v>
+        <v>9991500</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B184" t="n">
-        <v>162.1399993896484</v>
+        <v>170.6999969482422</v>
       </c>
       <c r="C184" t="n">
-        <v>172.3300018310547</v>
+        <v>177.4799957275391</v>
       </c>
       <c r="D184" t="n">
-        <v>161.2799987792969</v>
+        <v>170.6900024414062</v>
       </c>
       <c r="E184" t="n">
-        <v>170.6799926757812</v>
+        <v>175.3300018310547</v>
       </c>
       <c r="F184" t="n">
-        <v>9991500</v>
+        <v>9144300</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B185" t="n">
-        <v>170.6999969482422</v>
+        <v>175.4900054931641</v>
       </c>
       <c r="C185" t="n">
         <v>177.4799957275391</v>
       </c>
       <c r="D185" t="n">
-        <v>170.6900024414062</v>
+        <v>168.7100067138672</v>
       </c>
       <c r="E185" t="n">
-        <v>175.3300018310547</v>
+        <v>174.3699951171875</v>
       </c>
       <c r="F185" t="n">
-        <v>9144300</v>
+        <v>8069700</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B186" t="n">
-        <v>175.4900054931641</v>
+        <v>163.0800018310547</v>
       </c>
       <c r="C186" t="n">
-        <v>177.4799957275391</v>
+        <v>167.7899932861328</v>
       </c>
       <c r="D186" t="n">
-        <v>168.7100067138672</v>
+        <v>157.3999938964844</v>
       </c>
       <c r="E186" t="n">
-        <v>174.3699951171875</v>
+        <v>166.0099945068359</v>
       </c>
       <c r="F186" t="n">
-        <v>8069700</v>
+        <v>10214000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B187" t="n">
-        <v>163.0800018310547</v>
+        <v>159.4600067138672</v>
       </c>
       <c r="C187" t="n">
-        <v>167.7899932861328</v>
+        <v>161.1929931640625</v>
       </c>
       <c r="D187" t="n">
-        <v>157.3999938964844</v>
+        <v>152.1900024414062</v>
       </c>
       <c r="E187" t="n">
-        <v>166.0099945068359</v>
+        <v>154.2700042724609</v>
       </c>
       <c r="F187" t="n">
-        <v>10214000</v>
+        <v>9094700</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B188" t="n">
-        <v>159.4600067138672</v>
+        <v>157.9499969482422</v>
       </c>
       <c r="C188" t="n">
-        <v>161.1929931640625</v>
+        <v>159.2299957275391</v>
       </c>
       <c r="D188" t="n">
-        <v>152.1900024414062</v>
+        <v>153.2530059814453</v>
       </c>
       <c r="E188" t="n">
-        <v>154.2700042724609</v>
+        <v>156.3999938964844</v>
       </c>
       <c r="F188" t="n">
-        <v>9094700</v>
+        <v>6043100</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B189" t="n">
-        <v>157.9499969482422</v>
+        <v>157.75</v>
       </c>
       <c r="C189" t="n">
-        <v>159.2299957275391</v>
+        <v>158.9900054931641</v>
       </c>
       <c r="D189" t="n">
-        <v>153.2530059814453</v>
+        <v>145.3200073242188</v>
       </c>
       <c r="E189" t="n">
-        <v>156.3999938964844</v>
+        <v>152.1600036621094</v>
       </c>
       <c r="F189" t="n">
-        <v>6043100</v>
+        <v>7334100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B190" t="n">
-        <v>157.75</v>
+        <v>151</v>
       </c>
       <c r="C190" t="n">
-        <v>158.9900054931641</v>
+        <v>154.9700012207031</v>
       </c>
       <c r="D190" t="n">
-        <v>145.3200073242188</v>
+        <v>149</v>
       </c>
       <c r="E190" t="n">
-        <v>152.1600036621094</v>
+        <v>151.7599945068359</v>
       </c>
       <c r="F190" t="n">
-        <v>7334100</v>
+        <v>6867400</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B191" t="n">
-        <v>151</v>
+        <v>153.5800018310547</v>
       </c>
       <c r="C191" t="n">
-        <v>154.9700012207031</v>
+        <v>157.0700073242188</v>
       </c>
       <c r="D191" t="n">
-        <v>149</v>
+        <v>150.2799987792969</v>
       </c>
       <c r="E191" t="n">
-        <v>151.7599945068359</v>
+        <v>156.3999938964844</v>
       </c>
       <c r="F191" t="n">
-        <v>6867400</v>
+        <v>5326700</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B192" t="n">
-        <v>153.5800018310547</v>
+        <v>160.1100006103516</v>
       </c>
       <c r="C192" t="n">
-        <v>157.0700073242188</v>
+        <v>165.25</v>
       </c>
       <c r="D192" t="n">
-        <v>150.2799987792969</v>
+        <v>159.1349945068359</v>
       </c>
       <c r="E192" t="n">
-        <v>156.3999938964844</v>
+        <v>163.2400054931641</v>
       </c>
       <c r="F192" t="n">
-        <v>5326700</v>
+        <v>6052500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B193" t="n">
-        <v>160.1100006103516</v>
+        <v>165.9600067138672</v>
       </c>
       <c r="C193" t="n">
-        <v>165.25</v>
+        <v>169.2799987792969</v>
       </c>
       <c r="D193" t="n">
-        <v>159.1349945068359</v>
+        <v>163.5099945068359</v>
       </c>
       <c r="E193" t="n">
-        <v>163.2400054931641</v>
+        <v>169.0899963378906</v>
       </c>
       <c r="F193" t="n">
-        <v>6052500</v>
+        <v>7240800</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B194" t="n">
-        <v>165.9600067138672</v>
+        <v>169.3000030517578</v>
       </c>
       <c r="C194" t="n">
-        <v>169.2799987792969</v>
+        <v>171.2100067138672</v>
       </c>
       <c r="D194" t="n">
-        <v>163.5099945068359</v>
+        <v>166.7799987792969</v>
       </c>
       <c r="E194" t="n">
-        <v>169.0899963378906</v>
+        <v>168.0099945068359</v>
       </c>
       <c r="F194" t="n">
-        <v>7240800</v>
+        <v>8090900</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B195" t="n">
-        <v>169.3000030517578</v>
+        <v>169.8899993896484</v>
       </c>
       <c r="C195" t="n">
-        <v>171.2100067138672</v>
+        <v>171.2899932861328</v>
       </c>
       <c r="D195" t="n">
-        <v>166.7799987792969</v>
+        <v>163.9299926757812</v>
       </c>
       <c r="E195" t="n">
-        <v>168.0099945068359</v>
+        <v>164.9299926757812</v>
       </c>
       <c r="F195" t="n">
-        <v>8090900</v>
+        <v>6229500</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B196" t="n">
-        <v>169.8899993896484</v>
+        <v>171.1999969482422</v>
       </c>
       <c r="C196" t="n">
-        <v>171.2899932861328</v>
+        <v>172</v>
       </c>
       <c r="D196" t="n">
-        <v>163.9299926757812</v>
+        <v>167.5850067138672</v>
       </c>
       <c r="E196" t="n">
-        <v>164.9299926757812</v>
+        <v>169.6699981689453</v>
       </c>
       <c r="F196" t="n">
-        <v>6229500</v>
+        <v>11130400</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B197" t="n">
-        <v>171.1999969482422</v>
+        <v>170.1100006103516</v>
       </c>
       <c r="C197" t="n">
-        <v>172</v>
+        <v>175.1999969482422</v>
       </c>
       <c r="D197" t="n">
-        <v>167.5850067138672</v>
+        <v>166.6600036621094</v>
       </c>
       <c r="E197" t="n">
-        <v>169.6699981689453</v>
+        <v>174.5599975585938</v>
       </c>
       <c r="F197" t="n">
-        <v>11130400</v>
+        <v>9494400</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B198" t="n">
-        <v>170.1100006103516</v>
+        <v>165.4299926757812</v>
       </c>
       <c r="C198" t="n">
-        <v>175.1999969482422</v>
+        <v>165.4299926757812</v>
       </c>
       <c r="D198" t="n">
-        <v>166.6600036621094</v>
+        <v>159.3600006103516</v>
       </c>
       <c r="E198" t="n">
-        <v>174.5599975585938</v>
+        <v>162.1999969482422</v>
       </c>
       <c r="F198" t="n">
-        <v>9494400</v>
+        <v>7770100</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B199" t="n">
-        <v>165.4299926757812</v>
+        <v>162.3249969482422</v>
       </c>
       <c r="C199" t="n">
-        <v>165.4299926757812</v>
+        <v>165.6799926757812</v>
       </c>
       <c r="D199" t="n">
-        <v>159.3600006103516</v>
+        <v>160.5700073242188</v>
       </c>
       <c r="E199" t="n">
-        <v>162.1999969482422</v>
+        <v>161.7400054931641</v>
       </c>
       <c r="F199" t="n">
-        <v>7770100</v>
+        <v>6350600</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B200" t="n">
-        <v>162.3249969482422</v>
+        <v>167.7599945068359</v>
       </c>
       <c r="C200" t="n">
-        <v>165.6799926757812</v>
+        <v>170.1600036621094</v>
       </c>
       <c r="D200" t="n">
-        <v>160.5700073242188</v>
+        <v>159.4600067138672</v>
       </c>
       <c r="E200" t="n">
-        <v>161.7400054931641</v>
+        <v>165.4499969482422</v>
       </c>
       <c r="F200" t="n">
-        <v>6350600</v>
+        <v>8231200</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B201" t="n">
-        <v>167.7599945068359</v>
+        <v>159.9400024414062</v>
       </c>
       <c r="C201" t="n">
-        <v>170.1600036621094</v>
+        <v>161.2299957275391</v>
       </c>
       <c r="D201" t="n">
-        <v>159.4600067138672</v>
+        <v>154.7400054931641</v>
       </c>
       <c r="E201" t="n">
-        <v>165.4499969482422</v>
+        <v>157.6000061035156</v>
       </c>
       <c r="F201" t="n">
-        <v>8231200</v>
+        <v>11865200</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B202" t="n">
-        <v>159.9400024414062</v>
+        <v>158.8600006103516</v>
       </c>
       <c r="C202" t="n">
-        <v>161.2299957275391</v>
+        <v>165.6600036621094</v>
       </c>
       <c r="D202" t="n">
-        <v>154.7400054931641</v>
+        <v>155.2200012207031</v>
       </c>
       <c r="E202" t="n">
-        <v>157.6000061035156</v>
+        <v>164.1000061035156</v>
       </c>
       <c r="F202" t="n">
-        <v>11865200</v>
+        <v>8535700</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B203" t="n">
-        <v>158.8600006103516</v>
+        <v>164.1100006103516</v>
       </c>
       <c r="C203" t="n">
-        <v>165.6600036621094</v>
+        <v>172.5489959716797</v>
       </c>
       <c r="D203" t="n">
-        <v>155.2200012207031</v>
+        <v>162.6999969482422</v>
       </c>
       <c r="E203" t="n">
-        <v>164.1000061035156</v>
+        <v>169.8800048828125</v>
       </c>
       <c r="F203" t="n">
-        <v>8535700</v>
+        <v>10281800</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B204" t="n">
-        <v>164.1100006103516</v>
+        <v>165.5549926757812</v>
       </c>
       <c r="C204" t="n">
-        <v>172.5489959716797</v>
+        <v>170.5</v>
       </c>
       <c r="D204" t="n">
-        <v>162.6999969482422</v>
+        <v>159.1999969482422</v>
       </c>
       <c r="E204" t="n">
-        <v>169.8800048828125</v>
+        <v>166.6199951171875</v>
       </c>
       <c r="F204" t="n">
-        <v>10281800</v>
+        <v>9098200</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B205" t="n">
-        <v>165.5549926757812</v>
+        <v>166.3600006103516</v>
       </c>
       <c r="C205" t="n">
-        <v>170.5</v>
+        <v>167.7350006103516</v>
       </c>
       <c r="D205" t="n">
-        <v>159.1999969482422</v>
+        <v>156.6499938964844</v>
       </c>
       <c r="E205" t="n">
-        <v>166.6199951171875</v>
+        <v>159.9900054931641</v>
       </c>
       <c r="F205" t="n">
-        <v>9098200</v>
+        <v>9764500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B206" t="n">
-        <v>166.3600006103516</v>
+        <v>162.8650054931641</v>
       </c>
       <c r="C206" t="n">
-        <v>167.7350006103516</v>
+        <v>177.1999969482422</v>
       </c>
       <c r="D206" t="n">
-        <v>156.6499938964844</v>
+        <v>161.3600006103516</v>
       </c>
       <c r="E206" t="n">
-        <v>159.9900054931641</v>
+        <v>173.2799987792969</v>
       </c>
       <c r="F206" t="n">
-        <v>9764500</v>
+        <v>8509300</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B207" t="n">
-        <v>162.8650054931641</v>
+        <v>169.1000061035156</v>
       </c>
       <c r="C207" t="n">
-        <v>177.1999969482422</v>
+        <v>169.2299957275391</v>
       </c>
       <c r="D207" t="n">
-        <v>161.3600006103516</v>
+        <v>162.5899963378906</v>
       </c>
       <c r="E207" t="n">
-        <v>173.2799987792969</v>
+        <v>166.4600067138672</v>
       </c>
       <c r="F207" t="n">
-        <v>8509300</v>
+        <v>8969200</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B208" t="n">
-        <v>169.1000061035156</v>
+        <v>166.1799926757812</v>
       </c>
       <c r="C208" t="n">
-        <v>169.2299957275391</v>
+        <v>181.2700042724609</v>
       </c>
       <c r="D208" t="n">
-        <v>162.5899963378906</v>
+        <v>165.9900054931641</v>
       </c>
       <c r="E208" t="n">
-        <v>166.4600067138672</v>
+        <v>181.0500030517578</v>
       </c>
       <c r="F208" t="n">
-        <v>8969200</v>
+        <v>11912800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B209" t="n">
-        <v>166.1799926757812</v>
+        <v>187</v>
       </c>
       <c r="C209" t="n">
-        <v>181.2700042724609</v>
+        <v>189.8170013427734</v>
       </c>
       <c r="D209" t="n">
-        <v>165.9900054931641</v>
+        <v>179.8000030517578</v>
       </c>
       <c r="E209" t="n">
-        <v>181.0500030517578</v>
+        <v>184.6900024414062</v>
       </c>
       <c r="F209" t="n">
-        <v>11912800</v>
+        <v>9932000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B210" t="n">
-        <v>187</v>
+        <v>185.2969970703125</v>
       </c>
       <c r="C210" t="n">
-        <v>189.8170013427734</v>
+        <v>187.6199951171875</v>
       </c>
       <c r="D210" t="n">
-        <v>179.8000030517578</v>
+        <v>182.5</v>
       </c>
       <c r="E210" t="n">
-        <v>184.6900024414062</v>
+        <v>186.9600067138672</v>
       </c>
       <c r="F210" t="n">
-        <v>9932000</v>
+        <v>5592500</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B211" t="n">
-        <v>185.2969970703125</v>
+        <v>186.2649993896484</v>
       </c>
       <c r="C211" t="n">
-        <v>187.6199951171875</v>
+        <v>189.5599975585938</v>
       </c>
       <c r="D211" t="n">
-        <v>182.5</v>
+        <v>180.5</v>
       </c>
       <c r="E211" t="n">
-        <v>186.9600067138672</v>
+        <v>181.1499938964844</v>
       </c>
       <c r="F211" t="n">
-        <v>5592500</v>
+        <v>9149500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B212" t="n">
-        <v>186.2649993896484</v>
+        <v>183.8999938964844</v>
       </c>
       <c r="C212" t="n">
-        <v>189.5599975585938</v>
+        <v>185.6000061035156</v>
       </c>
       <c r="D212" t="n">
-        <v>180.5</v>
+        <v>175.6900024414062</v>
       </c>
       <c r="E212" t="n">
-        <v>181.1499938964844</v>
+        <v>182.5700073242188</v>
       </c>
       <c r="F212" t="n">
-        <v>9149500</v>
+        <v>7566300</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B213" t="n">
-        <v>183.8999938964844</v>
+        <v>184</v>
       </c>
       <c r="C213" t="n">
-        <v>185.6000061035156</v>
+        <v>186.2100067138672</v>
       </c>
       <c r="D213" t="n">
-        <v>175.6900024414062</v>
+        <v>166.5</v>
       </c>
       <c r="E213" t="n">
-        <v>182.5700073242188</v>
+        <v>171.9199981689453</v>
       </c>
       <c r="F213" t="n">
-        <v>7566300</v>
+        <v>8095900</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B214" t="n">
-        <v>184</v>
+        <v>169.2100067138672</v>
       </c>
       <c r="C214" t="n">
-        <v>186.2100067138672</v>
+        <v>170.281005859375</v>
       </c>
       <c r="D214" t="n">
-        <v>166.5</v>
+        <v>163.6799926757812</v>
       </c>
       <c r="E214" t="n">
-        <v>171.9199981689453</v>
+        <v>168.5599975585938</v>
       </c>
       <c r="F214" t="n">
-        <v>8095900</v>
+        <v>8412300</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B215" t="n">
-        <v>169.2100067138672</v>
+        <v>163.1049957275391</v>
       </c>
       <c r="C215" t="n">
-        <v>170.281005859375</v>
+        <v>171.4299926757812</v>
       </c>
       <c r="D215" t="n">
-        <v>163.6799926757812</v>
+        <v>157.1300048828125</v>
       </c>
       <c r="E215" t="n">
-        <v>168.5599975585938</v>
+        <v>168.6100006103516</v>
       </c>
       <c r="F215" t="n">
-        <v>8412300</v>
+        <v>7560400</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B216" t="n">
-        <v>163.1049957275391</v>
+        <v>168.9400024414062</v>
       </c>
       <c r="C216" t="n">
-        <v>171.4299926757812</v>
+        <v>172.6000061035156</v>
       </c>
       <c r="D216" t="n">
-        <v>157.1300048828125</v>
+        <v>168.3200073242188</v>
       </c>
       <c r="E216" t="n">
-        <v>168.6100006103516</v>
+        <v>169.3500061035156</v>
       </c>
       <c r="F216" t="n">
-        <v>7560400</v>
+        <v>6025900</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B217" t="n">
-        <v>168.9400024414062</v>
+        <v>174.4400024414062</v>
       </c>
       <c r="C217" t="n">
-        <v>172.6000061035156</v>
+        <v>177.8800048828125</v>
       </c>
       <c r="D217" t="n">
-        <v>168.3200073242188</v>
+        <v>172.1000061035156</v>
       </c>
       <c r="E217" t="n">
-        <v>169.3500061035156</v>
+        <v>174.5800018310547</v>
       </c>
       <c r="F217" t="n">
-        <v>6025900</v>
+        <v>6357800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B218" t="n">
-        <v>174.4400024414062</v>
+        <v>171.1349945068359</v>
       </c>
       <c r="C218" t="n">
-        <v>177.8800048828125</v>
+        <v>176.4100036621094</v>
       </c>
       <c r="D218" t="n">
-        <v>172.1000061035156</v>
+        <v>170</v>
       </c>
       <c r="E218" t="n">
-        <v>174.5800018310547</v>
+        <v>174.8699951171875</v>
       </c>
       <c r="F218" t="n">
-        <v>6357800</v>
+        <v>3342900</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B219" t="n">
-        <v>171.1349945068359</v>
+        <v>172.7700042724609</v>
       </c>
       <c r="C219" t="n">
-        <v>176.4100036621094</v>
+        <v>179.4799957275391</v>
       </c>
       <c r="D219" t="n">
-        <v>170</v>
+        <v>172.7700042724609</v>
       </c>
       <c r="E219" t="n">
-        <v>174.8699951171875</v>
+        <v>176.6100006103516</v>
       </c>
       <c r="F219" t="n">
-        <v>3342900</v>
+        <v>4338800</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B220" t="n">
-        <v>172.7700042724609</v>
+        <v>174</v>
       </c>
       <c r="C220" t="n">
-        <v>179.4799957275391</v>
+        <v>177.5130004882812</v>
       </c>
       <c r="D220" t="n">
-        <v>172.7700042724609</v>
+        <v>170.9089965820312</v>
       </c>
       <c r="E220" t="n">
-        <v>176.6100006103516</v>
+        <v>173.9900054931641</v>
       </c>
       <c r="F220" t="n">
-        <v>4338800</v>
+        <v>4721500</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B221" t="n">
-        <v>174</v>
+        <v>175.2100067138672</v>
       </c>
       <c r="C221" t="n">
-        <v>177.5130004882812</v>
+        <v>176.7299957275391</v>
       </c>
       <c r="D221" t="n">
-        <v>170.9089965820312</v>
+        <v>165.8999938964844</v>
       </c>
       <c r="E221" t="n">
-        <v>173.9900054931641</v>
+        <v>170.7599945068359</v>
       </c>
       <c r="F221" t="n">
-        <v>4721500</v>
+        <v>6023000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B222" t="n">
-        <v>175.2100067138672</v>
+        <v>165.5700073242188</v>
       </c>
       <c r="C222" t="n">
-        <v>176.7299957275391</v>
+        <v>169.9700012207031</v>
       </c>
       <c r="D222" t="n">
-        <v>165.8999938964844</v>
+        <v>159.2700042724609</v>
       </c>
       <c r="E222" t="n">
-        <v>170.7599945068359</v>
+        <v>169.7100067138672</v>
       </c>
       <c r="F222" t="n">
-        <v>6023000</v>
+        <v>8561600</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B223" t="n">
-        <v>165.5700073242188</v>
+        <v>168.4499969482422</v>
       </c>
       <c r="C223" t="n">
-        <v>169.9700012207031</v>
+        <v>169.3300018310547</v>
       </c>
       <c r="D223" t="n">
-        <v>159.2700042724609</v>
+        <v>156.8399963378906</v>
       </c>
       <c r="E223" t="n">
-        <v>169.7100067138672</v>
+        <v>157.9700012207031</v>
       </c>
       <c r="F223" t="n">
-        <v>8561600</v>
+        <v>8189500</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B224" t="n">
-        <v>168.4499969482422</v>
+        <v>164.5599975585938</v>
       </c>
       <c r="C224" t="n">
-        <v>169.3300018310547</v>
+        <v>171.5099945068359</v>
       </c>
       <c r="D224" t="n">
-        <v>156.8399963378906</v>
+        <v>164.4850006103516</v>
       </c>
       <c r="E224" t="n">
-        <v>157.9700012207031</v>
+        <v>171.0200042724609</v>
       </c>
       <c r="F224" t="n">
-        <v>8189500</v>
+        <v>7284700</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B225" t="n">
-        <v>164.5599975585938</v>
+        <v>177.6000061035156</v>
       </c>
       <c r="C225" t="n">
-        <v>171.5099945068359</v>
+        <v>183.5200042724609</v>
       </c>
       <c r="D225" t="n">
-        <v>164.4850006103516</v>
+        <v>175.6999969482422</v>
       </c>
       <c r="E225" t="n">
-        <v>171.0200042724609</v>
+        <v>180.3500061035156</v>
       </c>
       <c r="F225" t="n">
-        <v>7284700</v>
+        <v>8472300</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B226" t="n">
-        <v>177.6000061035156</v>
+        <v>174.4199981689453</v>
       </c>
       <c r="C226" t="n">
-        <v>183.5200042724609</v>
+        <v>186.5700073242188</v>
       </c>
       <c r="D226" t="n">
-        <v>175.6999969482422</v>
+        <v>173.4499969482422</v>
       </c>
       <c r="E226" t="n">
-        <v>180.3500061035156</v>
+        <v>184.8899993896484</v>
       </c>
       <c r="F226" t="n">
-        <v>8472300</v>
+        <v>8335700</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B227" t="n">
-        <v>174.4199981689453</v>
+        <v>187.6999969482422</v>
       </c>
       <c r="C227" t="n">
-        <v>186.5700073242188</v>
+        <v>194.3500061035156</v>
       </c>
       <c r="D227" t="n">
-        <v>173.4499969482422</v>
+        <v>187.0110015869141</v>
       </c>
       <c r="E227" t="n">
-        <v>184.8899993896484</v>
+        <v>190.5099945068359</v>
       </c>
       <c r="F227" t="n">
-        <v>8335700</v>
+        <v>14097400</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B228" t="n">
-        <v>187.6999969482422</v>
+        <v>210.1900024414062</v>
       </c>
       <c r="C228" t="n">
-        <v>194.3500061035156</v>
+        <v>214.8899993896484</v>
       </c>
       <c r="D228" t="n">
-        <v>187.0110015869141</v>
+        <v>191.0099945068359</v>
       </c>
       <c r="E228" t="n">
-        <v>190.5099945068359</v>
+        <v>197.3099975585938</v>
       </c>
       <c r="F228" t="n">
-        <v>14097400</v>
+        <v>20227000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B229" t="n">
-        <v>210.1900024414062</v>
+        <v>192.4100036621094</v>
       </c>
       <c r="C229" t="n">
-        <v>214.8899993896484</v>
+        <v>197.1100006103516</v>
       </c>
       <c r="D229" t="n">
-        <v>191.0099945068359</v>
+        <v>189.4299926757812</v>
       </c>
       <c r="E229" t="n">
-        <v>197.3099975585938</v>
+        <v>192.3200073242188</v>
       </c>
       <c r="F229" t="n">
-        <v>20227000</v>
+        <v>7774600</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B230" t="n">
-        <v>192.4100036621094</v>
+        <v>198</v>
       </c>
       <c r="C230" t="n">
-        <v>197.1100006103516</v>
+        <v>198</v>
       </c>
       <c r="D230" t="n">
-        <v>189.4299926757812</v>
+        <v>187.5</v>
       </c>
       <c r="E230" t="n">
-        <v>192.3200073242188</v>
+        <v>188.6699981689453</v>
       </c>
       <c r="F230" t="n">
-        <v>7774600</v>
+        <v>7208500</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B231" t="n">
-        <v>198</v>
+        <v>192.4900054931641</v>
       </c>
       <c r="C231" t="n">
-        <v>198</v>
+        <v>195.6999969482422</v>
       </c>
       <c r="D231" t="n">
-        <v>187.5</v>
+        <v>187.0299987792969</v>
       </c>
       <c r="E231" t="n">
-        <v>188.6699981689453</v>
+        <v>191.5200042724609</v>
       </c>
       <c r="F231" t="n">
-        <v>7208500</v>
+        <v>5434100</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B232" t="n">
-        <v>192.4900054931641</v>
+        <v>194.5650024414062</v>
       </c>
       <c r="C232" t="n">
-        <v>195.6999969482422</v>
+        <v>198.9199981689453</v>
       </c>
       <c r="D232" t="n">
-        <v>187.0299987792969</v>
+        <v>190.4799957275391</v>
       </c>
       <c r="E232" t="n">
-        <v>191.5200042724609</v>
+        <v>197.8500061035156</v>
       </c>
       <c r="F232" t="n">
-        <v>5434100</v>
+        <v>6277300</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B233" t="n">
-        <v>194.5650024414062</v>
+        <v>205.4700012207031</v>
       </c>
       <c r="C233" t="n">
-        <v>198.9199981689453</v>
+        <v>211.4499969482422</v>
       </c>
       <c r="D233" t="n">
-        <v>190.4799957275391</v>
+        <v>203.7599945068359</v>
       </c>
       <c r="E233" t="n">
-        <v>197.8500061035156</v>
+        <v>210.5</v>
       </c>
       <c r="F233" t="n">
-        <v>6277300</v>
+        <v>10008600</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B234" t="n">
-        <v>205.4700012207031</v>
+        <v>209.7899932861328</v>
       </c>
       <c r="C234" t="n">
-        <v>211.4499969482422</v>
+        <v>210.1100006103516</v>
       </c>
       <c r="D234" t="n">
-        <v>203.7599945068359</v>
+        <v>203.5500030517578</v>
       </c>
       <c r="E234" t="n">
-        <v>210.5</v>
+        <v>203.6199951171875</v>
       </c>
       <c r="F234" t="n">
-        <v>10008600</v>
+        <v>7907800</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B235" t="n">
-        <v>209.7899932861328</v>
+        <v>205.2700042724609</v>
       </c>
       <c r="C235" t="n">
-        <v>210.1100006103516</v>
+        <v>205.2700042724609</v>
       </c>
       <c r="D235" t="n">
-        <v>203.5500030517578</v>
+        <v>198.2449951171875</v>
       </c>
       <c r="E235" t="n">
-        <v>203.6199951171875</v>
+        <v>198.8200073242188</v>
       </c>
       <c r="F235" t="n">
-        <v>7907800</v>
+        <v>4707400</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B236" t="n">
-        <v>205.2700042724609</v>
+        <v>201.1600036621094</v>
       </c>
       <c r="C236" t="n">
-        <v>205.2700042724609</v>
+        <v>202.2649993896484</v>
       </c>
       <c r="D236" t="n">
-        <v>198.2449951171875</v>
+        <v>198.3399963378906</v>
       </c>
       <c r="E236" t="n">
-        <v>198.8200073242188</v>
+        <v>201.8000030517578</v>
       </c>
       <c r="F236" t="n">
-        <v>4707400</v>
+        <v>5683900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B237" t="n">
-        <v>201.1600036621094</v>
+        <v>196</v>
       </c>
       <c r="C237" t="n">
-        <v>202.2649993896484</v>
+        <v>197.9900054931641</v>
       </c>
       <c r="D237" t="n">
-        <v>198.3399963378906</v>
+        <v>189.6699981689453</v>
       </c>
       <c r="E237" t="n">
-        <v>201.8000030517578</v>
+        <v>193.1799926757812</v>
       </c>
       <c r="F237" t="n">
-        <v>5683900</v>
+        <v>8886900</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B238" t="n">
-        <v>196</v>
+        <v>195.0399932861328</v>
       </c>
       <c r="C238" t="n">
-        <v>197.9900054931641</v>
+        <v>195.5</v>
       </c>
       <c r="D238" t="n">
-        <v>189.6699981689453</v>
+        <v>184.5099945068359</v>
       </c>
       <c r="E238" t="n">
-        <v>193.1799926757812</v>
+        <v>186.4499969482422</v>
       </c>
       <c r="F238" t="n">
-        <v>8886900</v>
+        <v>5740500</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B239" t="n">
-        <v>195.0399932861328</v>
+        <v>185.3099975585938</v>
       </c>
       <c r="C239" t="n">
-        <v>195.5</v>
+        <v>187.2799987792969</v>
       </c>
       <c r="D239" t="n">
-        <v>184.5099945068359</v>
+        <v>182.8300018310547</v>
       </c>
       <c r="E239" t="n">
-        <v>186.4499969482422</v>
+        <v>183.75</v>
       </c>
       <c r="F239" t="n">
-        <v>5740500</v>
+        <v>4207300</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B240" t="n">
-        <v>185.3099975585938</v>
+        <v>183.7700042724609</v>
       </c>
       <c r="C240" t="n">
-        <v>187.2799987792969</v>
+        <v>190.4400024414062</v>
       </c>
       <c r="D240" t="n">
-        <v>182.8300018310547</v>
+        <v>183.5899963378906</v>
       </c>
       <c r="E240" t="n">
-        <v>183.75</v>
+        <v>188.6499938964844</v>
       </c>
       <c r="F240" t="n">
-        <v>4207300</v>
+        <v>8123600</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B241" t="n">
-        <v>183.7700042724609</v>
+        <v>186</v>
       </c>
       <c r="C241" t="n">
-        <v>190.4400024414062</v>
+        <v>190.25</v>
       </c>
       <c r="D241" t="n">
-        <v>183.5899963378906</v>
+        <v>186</v>
       </c>
       <c r="E241" t="n">
-        <v>188.6499938964844</v>
+        <v>188.1499938964844</v>
       </c>
       <c r="F241" t="n">
-        <v>8123600</v>
+        <v>5306400</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B242" t="n">
-        <v>186</v>
+        <v>192.3399963378906</v>
       </c>
       <c r="C242" t="n">
-        <v>190.25</v>
+        <v>193.1499938964844</v>
       </c>
       <c r="D242" t="n">
-        <v>186</v>
+        <v>188.0599975585938</v>
       </c>
       <c r="E242" t="n">
-        <v>188.1499938964844</v>
+        <v>190.9400024414062</v>
       </c>
       <c r="F242" t="n">
-        <v>5306400</v>
+        <v>4385100</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B243" t="n">
-        <v>192.3399963378906</v>
+        <v>190.9049987792969</v>
       </c>
       <c r="C243" t="n">
-        <v>193.1499938964844</v>
+        <v>203.3600006103516</v>
       </c>
       <c r="D243" t="n">
-        <v>188.0599975585938</v>
+        <v>190.9049987792969</v>
       </c>
       <c r="E243" t="n">
-        <v>190.9400024414062</v>
+        <v>202.25</v>
       </c>
       <c r="F243" t="n">
-        <v>4385100</v>
+        <v>7664600</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B244" t="n">
-        <v>190.9049987792969</v>
+        <v>205.8999938964844</v>
       </c>
       <c r="C244" t="n">
-        <v>203.3600006103516</v>
+        <v>206.1300048828125</v>
       </c>
       <c r="D244" t="n">
-        <v>190.9049987792969</v>
+        <v>199.2149963378906</v>
       </c>
       <c r="E244" t="n">
-        <v>202.25</v>
+        <v>201.0899963378906</v>
       </c>
       <c r="F244" t="n">
-        <v>7664600</v>
+        <v>4692700</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B245" t="n">
-        <v>205.8999938964844</v>
+        <v>200</v>
       </c>
       <c r="C245" t="n">
-        <v>206.1300048828125</v>
+        <v>200.1000061035156</v>
       </c>
       <c r="D245" t="n">
-        <v>199.2149963378906</v>
+        <v>194.6100006103516</v>
       </c>
       <c r="E245" t="n">
-        <v>201.0899963378906</v>
+        <v>195.3800048828125</v>
       </c>
       <c r="F245" t="n">
-        <v>4692700</v>
+        <v>3063000</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B246" t="n">
-        <v>200</v>
+        <v>195.5</v>
       </c>
       <c r="C246" t="n">
-        <v>200.1000061035156</v>
+        <v>197.9900054931641</v>
       </c>
       <c r="D246" t="n">
-        <v>194.6100006103516</v>
+        <v>193.9100036621094</v>
       </c>
       <c r="E246" t="n">
-        <v>195.3800048828125</v>
+        <v>195.6900024414062</v>
       </c>
       <c r="F246" t="n">
-        <v>3063000</v>
+        <v>5021700</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B247" t="n">
-        <v>195.5</v>
+        <v>195.7700042724609</v>
       </c>
       <c r="C247" t="n">
-        <v>197.9900054931641</v>
+        <v>196.5</v>
       </c>
       <c r="D247" t="n">
-        <v>193.9100036621094</v>
+        <v>188.5599975585938</v>
       </c>
       <c r="E247" t="n">
-        <v>195.6900024414062</v>
+        <v>189.2599945068359</v>
       </c>
       <c r="F247" t="n">
-        <v>5021700</v>
+        <v>4369200</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B248" t="n">
-        <v>195.7700042724609</v>
+        <v>188</v>
       </c>
       <c r="C248" t="n">
-        <v>196.5</v>
+        <v>189.8899993896484</v>
       </c>
       <c r="D248" t="n">
-        <v>188.5599975585938</v>
+        <v>184.0800018310547</v>
       </c>
       <c r="E248" t="n">
-        <v>189.2599945068359</v>
+        <v>186.1000061035156</v>
       </c>
       <c r="F248" t="n">
-        <v>4369200</v>
+        <v>4363800</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B249" t="n">
-        <v>188</v>
+        <v>185.25</v>
       </c>
       <c r="C249" t="n">
-        <v>189.8899993896484</v>
+        <v>192</v>
       </c>
       <c r="D249" t="n">
-        <v>184.0800018310547</v>
+        <v>181.2700042724609</v>
       </c>
       <c r="E249" t="n">
-        <v>186.1000061035156</v>
+        <v>191.4400024414062</v>
       </c>
       <c r="F249" t="n">
-        <v>4363800</v>
+        <v>4108500</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B250" t="n">
-        <v>185.25</v>
+        <v>192.8200073242188</v>
       </c>
       <c r="C250" t="n">
-        <v>192</v>
+        <v>197.1000061035156</v>
       </c>
       <c r="D250" t="n">
-        <v>181.2700042724609</v>
+        <v>190.5599975585938</v>
       </c>
       <c r="E250" t="n">
-        <v>191.4400024414062</v>
+        <v>193.7799987792969</v>
       </c>
       <c r="F250" t="n">
-        <v>4108500</v>
+        <v>4204100</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B251" t="n">
-        <v>192.8200073242188</v>
+        <v>196.8200073242188</v>
       </c>
       <c r="C251" t="n">
-        <v>197.1000061035156</v>
+        <v>200.6750030517578</v>
       </c>
       <c r="D251" t="n">
-        <v>190.5599975585938</v>
+        <v>194.7200012207031</v>
       </c>
       <c r="E251" t="n">
-        <v>193.7799987792969</v>
+        <v>194.9600067138672</v>
       </c>
       <c r="F251" t="n">
-        <v>4204100</v>
+        <v>4741600</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,14 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+        <v>46274</v>
+      </c>
+      <c r="B252" t="n">
+        <v>194.8549957275391</v>
+      </c>
+      <c r="C252" t="n">
+        <v>196.9600067138672</v>
+      </c>
+      <c r="D252" t="n">
+        <v>192.0500030517578</v>
+      </c>
+      <c r="E252" t="n">
+        <v>192.9299926757812</v>
+      </c>
       <c r="F252" t="n">
-        <v>4695079</v>
+        <v>3673900</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10510,37 +10518,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>192.93</v>
+      </c>
+      <c r="D2" t="n">
         <v>194.96</v>
       </c>
-      <c r="D2" t="n">
-        <v>193.78</v>
-      </c>
       <c r="E2" t="n">
-        <v>196.82</v>
+        <v>194.855</v>
       </c>
       <c r="F2" t="n">
-        <v>200.67</v>
+        <v>196.96</v>
       </c>
       <c r="G2" t="n">
-        <v>194.72</v>
+        <v>192.06</v>
       </c>
       <c r="H2" t="n">
-        <v>4695079</v>
+        <v>3673079</v>
       </c>
       <c r="I2" t="n">
-        <v>7427127</v>
+        <v>7393803</v>
       </c>
       <c r="J2" t="n">
-        <v>245888368640</v>
+        <v>243328073728</v>
       </c>
       <c r="K2" t="n">
-        <v>61.6962</v>
+        <v>61.638973</v>
       </c>
       <c r="L2" t="n">
-        <v>37.780895</v>
+        <v>37.387505</v>
       </c>
       <c r="M2" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="N2" t="n">
         <v>214.89</v>
@@ -10580,7 +10588,7 @@
         <v>11.733</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.616383</v>
+        <v>16.443365</v>
       </c>
       <c r="Z2" t="n">
         <v>0.357</v>
@@ -10592,7 +10600,7 @@
         <v>10540800000</v>
       </c>
       <c r="AC2" t="n">
-        <v>231056818176</v>
+        <v>229984763904</v>
       </c>
       <c r="AD2" t="n">
         <v>4639600128</v>
@@ -10619,7 +10627,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-09 09:16:06</t>
+          <t>2026-09-10 19:00:24</t>
         </is>
       </c>
     </row>

--- a/data/ANET_data.xlsx
+++ b/data/ANET_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B2" t="n">
-        <v>145.5599975585938</v>
+        <v>151.9900054931641</v>
       </c>
       <c r="C2" t="n">
-        <v>151.7100067138672</v>
+        <v>156.3200073242188</v>
       </c>
       <c r="D2" t="n">
-        <v>144.8999938964844</v>
+        <v>150.3600006103516</v>
       </c>
       <c r="E2" t="n">
-        <v>150.7200012207031</v>
+        <v>153.0399932861328</v>
       </c>
       <c r="F2" t="n">
-        <v>19772500</v>
+        <v>13666200</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B3" t="n">
-        <v>151.9900054931641</v>
+        <v>149.1799926757812</v>
       </c>
       <c r="C3" t="n">
-        <v>156.3200073242188</v>
+        <v>149.4700012207031</v>
       </c>
       <c r="D3" t="n">
-        <v>150.3600006103516</v>
+        <v>139.0200042724609</v>
       </c>
       <c r="E3" t="n">
-        <v>153.0399932861328</v>
+        <v>139.3899993896484</v>
       </c>
       <c r="F3" t="n">
-        <v>13666200</v>
+        <v>17920400</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B4" t="n">
-        <v>149.1799926757812</v>
+        <v>139.6000061035156</v>
       </c>
       <c r="C4" t="n">
-        <v>149.4700012207031</v>
+        <v>146.8999938964844</v>
       </c>
       <c r="D4" t="n">
-        <v>139.0200042724609</v>
+        <v>139.1699981689453</v>
       </c>
       <c r="E4" t="n">
-        <v>139.3899993896484</v>
+        <v>145.4299926757812</v>
       </c>
       <c r="F4" t="n">
-        <v>17920400</v>
+        <v>12140800</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B5" t="n">
-        <v>139.6000061035156</v>
+        <v>145.2599945068359</v>
       </c>
       <c r="C5" t="n">
-        <v>146.8999938964844</v>
+        <v>147.3699951171875</v>
       </c>
       <c r="D5" t="n">
-        <v>139.1699981689453</v>
+        <v>141</v>
       </c>
       <c r="E5" t="n">
-        <v>145.4299926757812</v>
+        <v>142.1600036621094</v>
       </c>
       <c r="F5" t="n">
-        <v>12140800</v>
+        <v>9382400</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B6" t="n">
-        <v>145.2599945068359</v>
+        <v>142.6349945068359</v>
       </c>
       <c r="C6" t="n">
-        <v>147.3699951171875</v>
+        <v>143.4250030517578</v>
       </c>
       <c r="D6" t="n">
-        <v>141</v>
+        <v>138.5</v>
       </c>
       <c r="E6" t="n">
-        <v>142.1600036621094</v>
+        <v>142.8399963378906</v>
       </c>
       <c r="F6" t="n">
-        <v>9382400</v>
+        <v>8295400</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B7" t="n">
-        <v>142.6349945068359</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
+        <v>146.7200012207031</v>
+      </c>
+      <c r="D7" t="n">
         <v>143.4250030517578</v>
       </c>
-      <c r="D7" t="n">
-        <v>138.5</v>
-      </c>
       <c r="E7" t="n">
-        <v>142.8399963378906</v>
+        <v>146.6600036621094</v>
       </c>
       <c r="F7" t="n">
-        <v>8295400</v>
+        <v>6939000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B8" t="n">
-        <v>144</v>
+        <v>148.8999938964844</v>
       </c>
       <c r="C8" t="n">
-        <v>146.7200012207031</v>
+        <v>150.25</v>
       </c>
       <c r="D8" t="n">
-        <v>143.4250030517578</v>
+        <v>146.6699981689453</v>
       </c>
       <c r="E8" t="n">
-        <v>146.6600036621094</v>
+        <v>149.6100006103516</v>
       </c>
       <c r="F8" t="n">
-        <v>6939000</v>
+        <v>17810900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B9" t="n">
-        <v>148.8999938964844</v>
+        <v>148.7799987792969</v>
       </c>
       <c r="C9" t="n">
-        <v>150.25</v>
+        <v>149.7100067138672</v>
       </c>
       <c r="D9" t="n">
-        <v>146.6699981689453</v>
+        <v>145.0549926757812</v>
       </c>
       <c r="E9" t="n">
-        <v>149.6100006103516</v>
+        <v>145.3999938964844</v>
       </c>
       <c r="F9" t="n">
-        <v>17810900</v>
+        <v>8675200</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B10" t="n">
-        <v>148.7799987792969</v>
+        <v>144.8600006103516</v>
       </c>
       <c r="C10" t="n">
-        <v>149.7100067138672</v>
+        <v>147.4600067138672</v>
       </c>
       <c r="D10" t="n">
-        <v>145.0549926757812</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="E10" t="n">
-        <v>145.3999938964844</v>
+        <v>144.0899963378906</v>
       </c>
       <c r="F10" t="n">
-        <v>8675200</v>
+        <v>8215500</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B11" t="n">
-        <v>144.8600006103516</v>
+        <v>144.6799926757812</v>
       </c>
       <c r="C11" t="n">
-        <v>147.4600067138672</v>
+        <v>144.6799926757812</v>
       </c>
       <c r="D11" t="n">
-        <v>143.0200042724609</v>
+        <v>141.2899932861328</v>
       </c>
       <c r="E11" t="n">
-        <v>144.0899963378906</v>
+        <v>142.6399993896484</v>
       </c>
       <c r="F11" t="n">
-        <v>8215500</v>
+        <v>7035700</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B12" t="n">
-        <v>144.6799926757812</v>
+        <v>141.6900024414062</v>
       </c>
       <c r="C12" t="n">
-        <v>144.6799926757812</v>
+        <v>143.2400054931641</v>
       </c>
       <c r="D12" t="n">
-        <v>141.2899932861328</v>
+        <v>139.2299957275391</v>
       </c>
       <c r="E12" t="n">
-        <v>142.6399993896484</v>
+        <v>143.0599975585938</v>
       </c>
       <c r="F12" t="n">
-        <v>7035700</v>
+        <v>6325300</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B13" t="n">
-        <v>141.6900024414062</v>
+        <v>144.0899963378906</v>
       </c>
       <c r="C13" t="n">
-        <v>143.2400054931641</v>
+        <v>144.3999938964844</v>
       </c>
       <c r="D13" t="n">
-        <v>139.2299957275391</v>
+        <v>140.7599945068359</v>
       </c>
       <c r="E13" t="n">
-        <v>143.0599975585938</v>
+        <v>142.5</v>
       </c>
       <c r="F13" t="n">
-        <v>6325300</v>
+        <v>4867700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B14" t="n">
-        <v>144.0899963378906</v>
+        <v>144.9199981689453</v>
       </c>
       <c r="C14" t="n">
-        <v>144.3999938964844</v>
+        <v>147.8000030517578</v>
       </c>
       <c r="D14" t="n">
-        <v>140.7599945068359</v>
+        <v>142.6199951171875</v>
       </c>
       <c r="E14" t="n">
-        <v>142.5</v>
+        <v>143.3699951171875</v>
       </c>
       <c r="F14" t="n">
-        <v>4867700</v>
+        <v>6183600</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B15" t="n">
-        <v>144.9199981689453</v>
+        <v>143.4299926757812</v>
       </c>
       <c r="C15" t="n">
-        <v>147.8000030517578</v>
+        <v>145.8399963378906</v>
       </c>
       <c r="D15" t="n">
-        <v>142.6199951171875</v>
+        <v>143.1600036621094</v>
       </c>
       <c r="E15" t="n">
-        <v>143.3699951171875</v>
+        <v>145.7100067138672</v>
       </c>
       <c r="F15" t="n">
-        <v>6183600</v>
+        <v>5828900</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B16" t="n">
-        <v>143.4299926757812</v>
+        <v>144.6499938964844</v>
       </c>
       <c r="C16" t="n">
-        <v>145.8399963378906</v>
+        <v>149.9499969482422</v>
       </c>
       <c r="D16" t="n">
-        <v>143.1600036621094</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="E16" t="n">
-        <v>145.7100067138672</v>
+        <v>149.2700042724609</v>
       </c>
       <c r="F16" t="n">
-        <v>5828900</v>
+        <v>7820700</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B17" t="n">
-        <v>144.6499938964844</v>
+        <v>150</v>
       </c>
       <c r="C17" t="n">
-        <v>149.9499969482422</v>
+        <v>150.5399932861328</v>
       </c>
       <c r="D17" t="n">
-        <v>143.0200042724609</v>
+        <v>141.25</v>
       </c>
       <c r="E17" t="n">
-        <v>149.2700042724609</v>
+        <v>144.4600067138672</v>
       </c>
       <c r="F17" t="n">
-        <v>7820700</v>
+        <v>9473800</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B18" t="n">
-        <v>150</v>
+        <v>146.0099945068359</v>
       </c>
       <c r="C18" t="n">
-        <v>150.5399932861328</v>
+        <v>149.0899963378906</v>
       </c>
       <c r="D18" t="n">
-        <v>141.25</v>
+        <v>144.1000061035156</v>
       </c>
       <c r="E18" t="n">
-        <v>144.4600067138672</v>
+        <v>145.5</v>
       </c>
       <c r="F18" t="n">
-        <v>9473800</v>
+        <v>7178600</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B19" t="n">
-        <v>146.0099945068359</v>
+        <v>151.6000061035156</v>
       </c>
       <c r="C19" t="n">
-        <v>149.0899963378906</v>
+        <v>153.7299957275391</v>
       </c>
       <c r="D19" t="n">
-        <v>144.1000061035156</v>
+        <v>149.5</v>
       </c>
       <c r="E19" t="n">
-        <v>145.5</v>
+        <v>149.5</v>
       </c>
       <c r="F19" t="n">
-        <v>7178600</v>
+        <v>7277600</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B20" t="n">
-        <v>151.6000061035156</v>
+        <v>150.4799957275391</v>
       </c>
       <c r="C20" t="n">
-        <v>153.7299957275391</v>
+        <v>151.5500030517578</v>
       </c>
       <c r="D20" t="n">
-        <v>149.5</v>
+        <v>143.2799987792969</v>
       </c>
       <c r="E20" t="n">
-        <v>149.5</v>
+        <v>145.2899932861328</v>
       </c>
       <c r="F20" t="n">
-        <v>7277600</v>
+        <v>7348700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B21" t="n">
-        <v>150.4799957275391</v>
+        <v>147.9900054931641</v>
       </c>
       <c r="C21" t="n">
-        <v>151.5500030517578</v>
+        <v>158.5099945068359</v>
       </c>
       <c r="D21" t="n">
-        <v>143.2799987792969</v>
+        <v>147.4049987792969</v>
       </c>
       <c r="E21" t="n">
-        <v>145.2899932861328</v>
+        <v>157.3600006103516</v>
       </c>
       <c r="F21" t="n">
-        <v>7348700</v>
+        <v>11283400</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B22" t="n">
-        <v>147.9900054931641</v>
+        <v>157</v>
       </c>
       <c r="C22" t="n">
-        <v>158.5099945068359</v>
+        <v>159.8000030517578</v>
       </c>
       <c r="D22" t="n">
-        <v>147.4049987792969</v>
+        <v>154.6009979248047</v>
       </c>
       <c r="E22" t="n">
-        <v>157.3600006103516</v>
+        <v>158.2299957275391</v>
       </c>
       <c r="F22" t="n">
-        <v>11283400</v>
+        <v>8459900</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B23" t="n">
-        <v>157</v>
+        <v>159.8600006103516</v>
       </c>
       <c r="C23" t="n">
-        <v>159.8000030517578</v>
+        <v>162.6799926757812</v>
       </c>
       <c r="D23" t="n">
-        <v>154.6009979248047</v>
+        <v>153.7400054931641</v>
       </c>
       <c r="E23" t="n">
-        <v>158.2299957275391</v>
+        <v>154.1000061035156</v>
       </c>
       <c r="F23" t="n">
-        <v>8459900</v>
+        <v>10459300</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B24" t="n">
-        <v>159.8600006103516</v>
+        <v>160.7599945068359</v>
       </c>
       <c r="C24" t="n">
-        <v>162.6799926757812</v>
+        <v>162</v>
       </c>
       <c r="D24" t="n">
-        <v>153.7400054931641</v>
+        <v>145.0899963378906</v>
       </c>
       <c r="E24" t="n">
-        <v>154.1000061035156</v>
+        <v>147.4499969482422</v>
       </c>
       <c r="F24" t="n">
-        <v>10459300</v>
+        <v>14233900</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B25" t="n">
-        <v>160.7599945068359</v>
+        <v>142.9850006103516</v>
       </c>
       <c r="C25" t="n">
-        <v>162</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="D25" t="n">
-        <v>145.0899963378906</v>
+        <v>136.7899932861328</v>
       </c>
       <c r="E25" t="n">
-        <v>147.4499969482422</v>
+        <v>138.7899932861328</v>
       </c>
       <c r="F25" t="n">
-        <v>14233900</v>
+        <v>13672400</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B26" t="n">
-        <v>142.9850006103516</v>
+        <v>140.4199981689453</v>
       </c>
       <c r="C26" t="n">
-        <v>143.0200042724609</v>
+        <v>145.3899993896484</v>
       </c>
       <c r="D26" t="n">
-        <v>136.7899932861328</v>
+        <v>140.1100006103516</v>
       </c>
       <c r="E26" t="n">
-        <v>138.7899932861328</v>
+        <v>143.3800048828125</v>
       </c>
       <c r="F26" t="n">
-        <v>13672400</v>
+        <v>8687000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B27" t="n">
-        <v>140.4199981689453</v>
+        <v>144.8999938964844</v>
       </c>
       <c r="C27" t="n">
-        <v>145.3899993896484</v>
+        <v>147.6499938964844</v>
       </c>
       <c r="D27" t="n">
-        <v>140.1100006103516</v>
+        <v>143.8600006103516</v>
       </c>
       <c r="E27" t="n">
-        <v>143.3800048828125</v>
+        <v>146.0099945068359</v>
       </c>
       <c r="F27" t="n">
-        <v>8687000</v>
+        <v>6909500</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B28" t="n">
-        <v>144.8999938964844</v>
+        <v>143.0099945068359</v>
       </c>
       <c r="C28" t="n">
-        <v>147.6499938964844</v>
+        <v>144.5</v>
       </c>
       <c r="D28" t="n">
-        <v>143.8600006103516</v>
+        <v>139.2400054931641</v>
       </c>
       <c r="E28" t="n">
-        <v>146.0099945068359</v>
+        <v>143.1000061035156</v>
       </c>
       <c r="F28" t="n">
-        <v>6909500</v>
+        <v>6533900</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B29" t="n">
-        <v>143.0099945068359</v>
+        <v>146.3249969482422</v>
       </c>
       <c r="C29" t="n">
-        <v>144.5</v>
+        <v>149.8800048828125</v>
       </c>
       <c r="D29" t="n">
-        <v>139.2400054931641</v>
+        <v>146.1900024414062</v>
       </c>
       <c r="E29" t="n">
-        <v>143.1000061035156</v>
+        <v>146.4799957275391</v>
       </c>
       <c r="F29" t="n">
-        <v>6533900</v>
+        <v>6120700</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B30" t="n">
-        <v>146.3249969482422</v>
+        <v>145.4499969482422</v>
       </c>
       <c r="C30" t="n">
-        <v>149.8800048828125</v>
+        <v>147.6100006103516</v>
       </c>
       <c r="D30" t="n">
-        <v>146.1900024414062</v>
+        <v>144.1399993896484</v>
       </c>
       <c r="E30" t="n">
-        <v>146.4799957275391</v>
+        <v>145.9400024414062</v>
       </c>
       <c r="F30" t="n">
-        <v>6120700</v>
+        <v>3648900</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B31" t="n">
-        <v>145.4499969482422</v>
+        <v>145.8650054931641</v>
       </c>
       <c r="C31" t="n">
-        <v>147.6100006103516</v>
+        <v>147.4900054931641</v>
       </c>
       <c r="D31" t="n">
-        <v>144.1399993896484</v>
+        <v>141.6799926757812</v>
       </c>
       <c r="E31" t="n">
-        <v>145.9400024414062</v>
+        <v>146.5899963378906</v>
       </c>
       <c r="F31" t="n">
-        <v>3648900</v>
+        <v>7349200</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B32" t="n">
-        <v>145.8650054931641</v>
+        <v>146.7799987792969</v>
       </c>
       <c r="C32" t="n">
-        <v>147.4900054931641</v>
+        <v>153.9499969482422</v>
       </c>
       <c r="D32" t="n">
-        <v>141.6799926757812</v>
+        <v>146.6399993896484</v>
       </c>
       <c r="E32" t="n">
-        <v>146.5899963378906</v>
+        <v>152.7599945068359</v>
       </c>
       <c r="F32" t="n">
-        <v>7349200</v>
+        <v>7327400</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B33" t="n">
-        <v>146.7799987792969</v>
+        <v>155</v>
       </c>
       <c r="C33" t="n">
-        <v>153.9499969482422</v>
+        <v>155.8300018310547</v>
       </c>
       <c r="D33" t="n">
-        <v>146.6399993896484</v>
+        <v>152.2969970703125</v>
       </c>
       <c r="E33" t="n">
-        <v>152.7599945068359</v>
+        <v>153.8200073242188</v>
       </c>
       <c r="F33" t="n">
-        <v>7327400</v>
+        <v>5170800</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B34" t="n">
-        <v>155</v>
+        <v>157.4100036621094</v>
       </c>
       <c r="C34" t="n">
-        <v>155.8300018310547</v>
+        <v>157.6999969482422</v>
       </c>
       <c r="D34" t="n">
-        <v>152.2969970703125</v>
+        <v>155.0099945068359</v>
       </c>
       <c r="E34" t="n">
-        <v>153.8200073242188</v>
+        <v>156.8099975585938</v>
       </c>
       <c r="F34" t="n">
-        <v>5170800</v>
+        <v>5509100</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B35" t="n">
-        <v>157.4100036621094</v>
+        <v>156.6199951171875</v>
       </c>
       <c r="C35" t="n">
-        <v>157.6999969482422</v>
+        <v>158.6600036621094</v>
       </c>
       <c r="D35" t="n">
-        <v>155.0099945068359</v>
+        <v>152.3300018310547</v>
       </c>
       <c r="E35" t="n">
-        <v>156.8099975585938</v>
+        <v>156.7700042724609</v>
       </c>
       <c r="F35" t="n">
-        <v>5509100</v>
+        <v>5037400</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B36" t="n">
-        <v>156.6199951171875</v>
+        <v>157.2100067138672</v>
       </c>
       <c r="C36" t="n">
-        <v>158.6600036621094</v>
+        <v>162.3999938964844</v>
       </c>
       <c r="D36" t="n">
-        <v>152.3300018310547</v>
+        <v>156.7799987792969</v>
       </c>
       <c r="E36" t="n">
-        <v>156.7700042724609</v>
+        <v>162.0299987792969</v>
       </c>
       <c r="F36" t="n">
-        <v>5037400</v>
+        <v>6901400</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B37" t="n">
-        <v>157.2100067138672</v>
+        <v>162.4700012207031</v>
       </c>
       <c r="C37" t="n">
-        <v>162.3999938964844</v>
+        <v>164.9400024414062</v>
       </c>
       <c r="D37" t="n">
-        <v>156.7799987792969</v>
+        <v>158.3999938964844</v>
       </c>
       <c r="E37" t="n">
-        <v>162.0299987792969</v>
+        <v>158.4400024414062</v>
       </c>
       <c r="F37" t="n">
-        <v>6901400</v>
+        <v>6911300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B38" t="n">
-        <v>162.4700012207031</v>
+        <v>161.0899963378906</v>
       </c>
       <c r="C38" t="n">
-        <v>164.9400024414062</v>
+        <v>162.1150054931641</v>
       </c>
       <c r="D38" t="n">
-        <v>158.3999938964844</v>
+        <v>155.7400054931641</v>
       </c>
       <c r="E38" t="n">
-        <v>158.4400024414062</v>
+        <v>157.6900024414062</v>
       </c>
       <c r="F38" t="n">
-        <v>6911300</v>
+        <v>6209300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B39" t="n">
-        <v>161.0899963378906</v>
+        <v>160.5</v>
       </c>
       <c r="C39" t="n">
-        <v>162.1150054931641</v>
+        <v>160.8999938964844</v>
       </c>
       <c r="D39" t="n">
-        <v>155.7400054931641</v>
+        <v>155.4199981689453</v>
       </c>
       <c r="E39" t="n">
-        <v>157.6900024414062</v>
+        <v>157.5899963378906</v>
       </c>
       <c r="F39" t="n">
-        <v>6209300</v>
+        <v>6422600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B40" t="n">
-        <v>160.5</v>
+        <v>152.8600006103516</v>
       </c>
       <c r="C40" t="n">
-        <v>160.8999938964844</v>
+        <v>157.0249938964844</v>
       </c>
       <c r="D40" t="n">
-        <v>155.4199981689453</v>
+        <v>150.9900054931641</v>
       </c>
       <c r="E40" t="n">
-        <v>157.5899963378906</v>
+        <v>153.5500030517578</v>
       </c>
       <c r="F40" t="n">
-        <v>6422600</v>
+        <v>9026400</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B41" t="n">
-        <v>152.8600006103516</v>
+        <v>142.6699981689453</v>
       </c>
       <c r="C41" t="n">
-        <v>157.0249938964844</v>
+        <v>148</v>
       </c>
       <c r="D41" t="n">
-        <v>150.9900054931641</v>
+        <v>140.0200042724609</v>
       </c>
       <c r="E41" t="n">
-        <v>153.5500030517578</v>
+        <v>140.4199981689453</v>
       </c>
       <c r="F41" t="n">
-        <v>9026400</v>
+        <v>15901000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B42" t="n">
-        <v>142.6699981689453</v>
+        <v>140.6499938964844</v>
       </c>
       <c r="C42" t="n">
-        <v>148</v>
+        <v>141.9900054931641</v>
       </c>
       <c r="D42" t="n">
-        <v>140.0200042724609</v>
+        <v>132.5899963378906</v>
       </c>
       <c r="E42" t="n">
-        <v>140.4199981689453</v>
+        <v>134.0200042724609</v>
       </c>
       <c r="F42" t="n">
-        <v>15901000</v>
+        <v>13296100</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B43" t="n">
-        <v>140.6499938964844</v>
+        <v>134.4100036621094</v>
       </c>
       <c r="C43" t="n">
-        <v>141.9900054931641</v>
+        <v>136.6100006103516</v>
       </c>
       <c r="D43" t="n">
-        <v>132.5899963378906</v>
+        <v>132.4499969482422</v>
       </c>
       <c r="E43" t="n">
-        <v>134.0200042724609</v>
+        <v>134.6499938964844</v>
       </c>
       <c r="F43" t="n">
-        <v>13296100</v>
+        <v>11341600</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B44" t="n">
-        <v>134.4100036621094</v>
+        <v>137.5</v>
       </c>
       <c r="C44" t="n">
-        <v>136.6100006103516</v>
+        <v>138.9799957275391</v>
       </c>
       <c r="D44" t="n">
-        <v>132.4499969482422</v>
+        <v>134.5870056152344</v>
       </c>
       <c r="E44" t="n">
-        <v>134.6499938964844</v>
+        <v>137.2599945068359</v>
       </c>
       <c r="F44" t="n">
-        <v>11341600</v>
+        <v>6974300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B45" t="n">
-        <v>137.5</v>
+        <v>134.8699951171875</v>
       </c>
       <c r="C45" t="n">
-        <v>138.9799957275391</v>
+        <v>136.375</v>
       </c>
       <c r="D45" t="n">
-        <v>134.5870056152344</v>
+        <v>132.4100036621094</v>
       </c>
       <c r="E45" t="n">
-        <v>137.2599945068359</v>
+        <v>134.9299926757812</v>
       </c>
       <c r="F45" t="n">
-        <v>6974300</v>
+        <v>7189300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B46" t="n">
-        <v>134.8699951171875</v>
+        <v>136.2200012207031</v>
       </c>
       <c r="C46" t="n">
-        <v>136.375</v>
+        <v>136.5980072021484</v>
       </c>
       <c r="D46" t="n">
-        <v>132.4100036621094</v>
+        <v>133.7779998779297</v>
       </c>
       <c r="E46" t="n">
-        <v>134.9299926757812</v>
+        <v>134.9799957275391</v>
       </c>
       <c r="F46" t="n">
-        <v>7189300</v>
+        <v>6471400</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B47" t="n">
-        <v>136.2200012207031</v>
+        <v>134.4299926757812</v>
       </c>
       <c r="C47" t="n">
-        <v>136.5980072021484</v>
+        <v>135.5800018310547</v>
       </c>
       <c r="D47" t="n">
-        <v>133.7779998779297</v>
+        <v>129.1699981689453</v>
       </c>
       <c r="E47" t="n">
-        <v>134.9799957275391</v>
+        <v>130.3000030517578</v>
       </c>
       <c r="F47" t="n">
-        <v>6471400</v>
+        <v>10471400</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B48" t="n">
-        <v>134.4299926757812</v>
+        <v>127.0599975585938</v>
       </c>
       <c r="C48" t="n">
-        <v>135.5800018310547</v>
+        <v>135.3699951171875</v>
       </c>
       <c r="D48" t="n">
-        <v>129.1699981689453</v>
+        <v>125.3600006103516</v>
       </c>
       <c r="E48" t="n">
-        <v>130.3000030517578</v>
+        <v>131.3699951171875</v>
       </c>
       <c r="F48" t="n">
-        <v>10471400</v>
+        <v>10672500</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B49" t="n">
-        <v>127.0599975585938</v>
+        <v>131.3500061035156</v>
       </c>
       <c r="C49" t="n">
-        <v>135.3699951171875</v>
+        <v>133.3200073242188</v>
       </c>
       <c r="D49" t="n">
-        <v>125.3600006103516</v>
+        <v>125.4000015258789</v>
       </c>
       <c r="E49" t="n">
-        <v>131.3699951171875</v>
+        <v>127.2600021362305</v>
       </c>
       <c r="F49" t="n">
-        <v>10672500</v>
+        <v>12455900</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B50" t="n">
-        <v>131.3500061035156</v>
+        <v>125.75</v>
       </c>
       <c r="C50" t="n">
-        <v>133.3200073242188</v>
+        <v>127.5500030517578</v>
       </c>
       <c r="D50" t="n">
-        <v>125.4000015258789</v>
+        <v>122.0800018310547</v>
       </c>
       <c r="E50" t="n">
-        <v>127.2600021362305</v>
+        <v>123.4499969482422</v>
       </c>
       <c r="F50" t="n">
-        <v>12455900</v>
+        <v>12561100</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B51" t="n">
-        <v>125.75</v>
+        <v>123.0500030517578</v>
       </c>
       <c r="C51" t="n">
-        <v>127.5500030517578</v>
+        <v>126.5699996948242</v>
       </c>
       <c r="D51" t="n">
-        <v>122.0800018310547</v>
+        <v>122.9000015258789</v>
       </c>
       <c r="E51" t="n">
-        <v>123.4499969482422</v>
+        <v>124.8099975585938</v>
       </c>
       <c r="F51" t="n">
-        <v>12561100</v>
+        <v>7703500</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B52" t="n">
-        <v>123.0500030517578</v>
+        <v>129.8899993896484</v>
       </c>
       <c r="C52" t="n">
-        <v>126.5699996948242</v>
+        <v>131.7899932861328</v>
       </c>
       <c r="D52" t="n">
-        <v>122.9000015258789</v>
+        <v>118.9000015258789</v>
       </c>
       <c r="E52" t="n">
-        <v>124.8099975585938</v>
+        <v>119.5899963378906</v>
       </c>
       <c r="F52" t="n">
-        <v>7703500</v>
+        <v>12642000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B53" t="n">
-        <v>129.8899993896484</v>
+        <v>118.4199981689453</v>
       </c>
       <c r="C53" t="n">
-        <v>131.7899932861328</v>
+        <v>120.004997253418</v>
       </c>
       <c r="D53" t="n">
-        <v>118.9000015258789</v>
+        <v>114.5199966430664</v>
       </c>
       <c r="E53" t="n">
-        <v>119.5899963378906</v>
+        <v>117.4300003051758</v>
       </c>
       <c r="F53" t="n">
-        <v>12642000</v>
+        <v>16704100</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B54" t="n">
-        <v>118.4199981689453</v>
+        <v>118.9150009155273</v>
       </c>
       <c r="C54" t="n">
-        <v>120.004997253418</v>
+        <v>122.4199981689453</v>
       </c>
       <c r="D54" t="n">
-        <v>114.5199966430664</v>
+        <v>118.1999969482422</v>
       </c>
       <c r="E54" t="n">
-        <v>117.4300003051758</v>
+        <v>122.1699981689453</v>
       </c>
       <c r="F54" t="n">
-        <v>16704100</v>
+        <v>12758600</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B55" t="n">
-        <v>118.9150009155273</v>
+        <v>122.4000015258789</v>
       </c>
       <c r="C55" t="n">
-        <v>122.4199981689453</v>
+        <v>125.9100036621094</v>
       </c>
       <c r="D55" t="n">
-        <v>118.1999969482422</v>
+        <v>122.3199996948242</v>
       </c>
       <c r="E55" t="n">
-        <v>122.1699981689453</v>
+        <v>125.0400009155273</v>
       </c>
       <c r="F55" t="n">
-        <v>12758600</v>
+        <v>7143400</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B56" t="n">
-        <v>122.4000015258789</v>
+        <v>127.4749984741211</v>
       </c>
       <c r="C56" t="n">
-        <v>125.9100036621094</v>
+        <v>128.4750061035156</v>
       </c>
       <c r="D56" t="n">
-        <v>122.3199996948242</v>
+        <v>125.2460021972656</v>
       </c>
       <c r="E56" t="n">
-        <v>125.0400009155273</v>
+        <v>127.6500015258789</v>
       </c>
       <c r="F56" t="n">
-        <v>7143400</v>
+        <v>5995000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B57" t="n">
-        <v>127.4749984741211</v>
+        <v>130</v>
       </c>
       <c r="C57" t="n">
-        <v>128.4750061035156</v>
+        <v>131.4049987792969</v>
       </c>
       <c r="D57" t="n">
-        <v>125.2460021972656</v>
+        <v>128.1150054931641</v>
       </c>
       <c r="E57" t="n">
-        <v>127.6500015258789</v>
+        <v>130.6799926757812</v>
       </c>
       <c r="F57" t="n">
-        <v>5995000</v>
+        <v>3895000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B58" t="n">
-        <v>130</v>
+        <v>128.9799957275391</v>
       </c>
       <c r="C58" t="n">
-        <v>131.4049987792969</v>
+        <v>129.5039978027344</v>
       </c>
       <c r="D58" t="n">
-        <v>128.1150054931641</v>
+        <v>126.1399993896484</v>
       </c>
       <c r="E58" t="n">
-        <v>130.6799926757812</v>
+        <v>128.1100006103516</v>
       </c>
       <c r="F58" t="n">
-        <v>3895000</v>
+        <v>4690600</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B59" t="n">
-        <v>128.9799957275391</v>
+        <v>129.75</v>
       </c>
       <c r="C59" t="n">
-        <v>129.5039978027344</v>
+        <v>131.0399932861328</v>
       </c>
       <c r="D59" t="n">
-        <v>126.1399993896484</v>
+        <v>126.2699966430664</v>
       </c>
       <c r="E59" t="n">
-        <v>128.1100006103516</v>
+        <v>127.2200012207031</v>
       </c>
       <c r="F59" t="n">
-        <v>4690600</v>
+        <v>5619000</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B60" t="n">
-        <v>129.75</v>
+        <v>126.1600036621094</v>
       </c>
       <c r="C60" t="n">
-        <v>131.0399932861328</v>
+        <v>128.5</v>
       </c>
       <c r="D60" t="n">
-        <v>126.2699966430664</v>
+        <v>123.75</v>
       </c>
       <c r="E60" t="n">
-        <v>127.2200012207031</v>
+        <v>127.8000030517578</v>
       </c>
       <c r="F60" t="n">
-        <v>5619000</v>
+        <v>5286300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B61" t="n">
-        <v>126.1600036621094</v>
+        <v>127.0800018310547</v>
       </c>
       <c r="C61" t="n">
-        <v>128.5</v>
+        <v>130.7799987792969</v>
       </c>
       <c r="D61" t="n">
-        <v>123.75</v>
+        <v>126.7399978637695</v>
       </c>
       <c r="E61" t="n">
-        <v>127.8000030517578</v>
+        <v>128.5500030517578</v>
       </c>
       <c r="F61" t="n">
-        <v>5286300</v>
+        <v>4516400</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B62" t="n">
-        <v>127.0800018310547</v>
+        <v>128.5</v>
       </c>
       <c r="C62" t="n">
-        <v>130.7799987792969</v>
+        <v>129.6600036621094</v>
       </c>
       <c r="D62" t="n">
-        <v>126.7399978637695</v>
+        <v>126.8399963378906</v>
       </c>
       <c r="E62" t="n">
-        <v>128.5500030517578</v>
+        <v>128.5899963378906</v>
       </c>
       <c r="F62" t="n">
-        <v>4516400</v>
+        <v>5166300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B63" t="n">
-        <v>128.5</v>
+        <v>129.7299957275391</v>
       </c>
       <c r="C63" t="n">
-        <v>129.6600036621094</v>
+        <v>133.5700073242188</v>
       </c>
       <c r="D63" t="n">
-        <v>126.8399963378906</v>
+        <v>128.2100067138672</v>
       </c>
       <c r="E63" t="n">
-        <v>128.5899963378906</v>
+        <v>129.1100006103516</v>
       </c>
       <c r="F63" t="n">
-        <v>5166300</v>
+        <v>7813800</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B64" t="n">
-        <v>129.7299957275391</v>
+        <v>128.6999969482422</v>
       </c>
       <c r="C64" t="n">
-        <v>133.5700073242188</v>
+        <v>130.8000030517578</v>
       </c>
       <c r="D64" t="n">
-        <v>128.2100067138672</v>
+        <v>127.3199996948242</v>
       </c>
       <c r="E64" t="n">
-        <v>129.1100006103516</v>
+        <v>130.0399932861328</v>
       </c>
       <c r="F64" t="n">
-        <v>7813800</v>
+        <v>5227900</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B65" t="n">
-        <v>128.6999969482422</v>
+        <v>131.0500030517578</v>
       </c>
       <c r="C65" t="n">
-        <v>130.8000030517578</v>
+        <v>134.4400024414062</v>
       </c>
       <c r="D65" t="n">
-        <v>127.3199996948242</v>
+        <v>130.25</v>
       </c>
       <c r="E65" t="n">
-        <v>130.0399932861328</v>
+        <v>132.3600006103516</v>
       </c>
       <c r="F65" t="n">
-        <v>5227900</v>
+        <v>5921300</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B66" t="n">
-        <v>131.0500030517578</v>
+        <v>135.5299987792969</v>
       </c>
       <c r="C66" t="n">
-        <v>134.4400024414062</v>
+        <v>136.3999938964844</v>
       </c>
       <c r="D66" t="n">
-        <v>130.25</v>
+        <v>128.9499969482422</v>
       </c>
       <c r="E66" t="n">
-        <v>132.3600006103516</v>
+        <v>134.3899993896484</v>
       </c>
       <c r="F66" t="n">
-        <v>5921300</v>
+        <v>6679500</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B67" t="n">
-        <v>135.5299987792969</v>
+        <v>132.4799957275391</v>
       </c>
       <c r="C67" t="n">
-        <v>136.3999938964844</v>
+        <v>134.0500030517578</v>
       </c>
       <c r="D67" t="n">
-        <v>128.9499969482422</v>
+        <v>124.3000030517578</v>
       </c>
       <c r="E67" t="n">
-        <v>134.3899993896484</v>
+        <v>124.7600021362305</v>
       </c>
       <c r="F67" t="n">
-        <v>6679500</v>
+        <v>8508700</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B68" t="n">
-        <v>132.4799957275391</v>
+        <v>125.5</v>
       </c>
       <c r="C68" t="n">
-        <v>134.0500030517578</v>
+        <v>127.3600006103516</v>
       </c>
       <c r="D68" t="n">
-        <v>124.3000030517578</v>
+        <v>123.6100006103516</v>
       </c>
       <c r="E68" t="n">
-        <v>124.7600021362305</v>
+        <v>125.8899993896484</v>
       </c>
       <c r="F68" t="n">
-        <v>8508700</v>
+        <v>6441900</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B69" t="n">
-        <v>125.5</v>
+        <v>126.1399993896484</v>
       </c>
       <c r="C69" t="n">
-        <v>127.3600006103516</v>
+        <v>127.8399963378906</v>
       </c>
       <c r="D69" t="n">
-        <v>123.6100006103516</v>
+        <v>124.1999969482422</v>
       </c>
       <c r="E69" t="n">
-        <v>125.8899993896484</v>
+        <v>126.129997253418</v>
       </c>
       <c r="F69" t="n">
-        <v>6441900</v>
+        <v>6656100</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B70" t="n">
-        <v>126.1399993896484</v>
+        <v>125.9400024414062</v>
       </c>
       <c r="C70" t="n">
-        <v>127.8399963378906</v>
+        <v>126.8300018310547</v>
       </c>
       <c r="D70" t="n">
-        <v>124.1999969482422</v>
+        <v>121.629997253418</v>
       </c>
       <c r="E70" t="n">
-        <v>126.129997253418</v>
+        <v>122.3600006103516</v>
       </c>
       <c r="F70" t="n">
-        <v>6656100</v>
+        <v>8589200</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B71" t="n">
-        <v>125.9400024414062</v>
+        <v>125</v>
       </c>
       <c r="C71" t="n">
-        <v>126.8300018310547</v>
+        <v>127.1600036621094</v>
       </c>
       <c r="D71" t="n">
-        <v>121.629997253418</v>
+        <v>123.879997253418</v>
       </c>
       <c r="E71" t="n">
-        <v>122.3600006103516</v>
+        <v>124.620002746582</v>
       </c>
       <c r="F71" t="n">
-        <v>8589200</v>
+        <v>5515200</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B72" t="n">
-        <v>125</v>
+        <v>125.0100021362305</v>
       </c>
       <c r="C72" t="n">
-        <v>127.1600036621094</v>
+        <v>132.5200042724609</v>
       </c>
       <c r="D72" t="n">
-        <v>123.879997253418</v>
+        <v>125.0100021362305</v>
       </c>
       <c r="E72" t="n">
-        <v>124.620002746582</v>
+        <v>131.1199951171875</v>
       </c>
       <c r="F72" t="n">
-        <v>5515200</v>
+        <v>12713100</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B73" t="n">
-        <v>125.0100021362305</v>
+        <v>133.4299926757812</v>
       </c>
       <c r="C73" t="n">
-        <v>132.5200042724609</v>
+        <v>134</v>
       </c>
       <c r="D73" t="n">
-        <v>125.0100021362305</v>
+        <v>130.2200012207031</v>
       </c>
       <c r="E73" t="n">
-        <v>131.1199951171875</v>
+        <v>130.7299957275391</v>
       </c>
       <c r="F73" t="n">
-        <v>12713100</v>
+        <v>5547300</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B74" t="n">
-        <v>133.4299926757812</v>
+        <v>129.3200073242188</v>
       </c>
       <c r="C74" t="n">
-        <v>134</v>
+        <v>131.7200012207031</v>
       </c>
       <c r="D74" t="n">
-        <v>130.2200012207031</v>
+        <v>129.25</v>
       </c>
       <c r="E74" t="n">
-        <v>130.7299957275391</v>
+        <v>131.3200073242188</v>
       </c>
       <c r="F74" t="n">
-        <v>5547300</v>
+        <v>2884300</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B75" t="n">
-        <v>129.3200073242188</v>
+        <v>131.1300048828125</v>
       </c>
       <c r="C75" t="n">
-        <v>131.7200012207031</v>
+        <v>131.5</v>
       </c>
       <c r="D75" t="n">
-        <v>129.25</v>
+        <v>130.1100006103516</v>
       </c>
       <c r="E75" t="n">
-        <v>131.3200073242188</v>
+        <v>130.7700042724609</v>
       </c>
       <c r="F75" t="n">
-        <v>2884300</v>
+        <v>1642400</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B76" t="n">
-        <v>131.1300048828125</v>
+        <v>131</v>
       </c>
       <c r="C76" t="n">
-        <v>131.5</v>
+        <v>132.125</v>
       </c>
       <c r="D76" t="n">
-        <v>130.1100006103516</v>
+        <v>130.4499969482422</v>
       </c>
       <c r="E76" t="n">
-        <v>130.7700042724609</v>
+        <v>131.8399963378906</v>
       </c>
       <c r="F76" t="n">
-        <v>1642400</v>
+        <v>2308400</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B77" t="n">
-        <v>131</v>
+        <v>131.1499938964844</v>
       </c>
       <c r="C77" t="n">
-        <v>132.125</v>
+        <v>135.2989959716797</v>
       </c>
       <c r="D77" t="n">
-        <v>130.4499969482422</v>
+        <v>131.0399932861328</v>
       </c>
       <c r="E77" t="n">
-        <v>131.8399963378906</v>
+        <v>134.1499938964844</v>
       </c>
       <c r="F77" t="n">
-        <v>2308400</v>
+        <v>6199700</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B78" t="n">
-        <v>131.1499938964844</v>
+        <v>134.25</v>
       </c>
       <c r="C78" t="n">
-        <v>135.2989959716797</v>
+        <v>134.4499969482422</v>
       </c>
       <c r="D78" t="n">
-        <v>131.0399932861328</v>
+        <v>132.3699951171875</v>
       </c>
       <c r="E78" t="n">
-        <v>134.1499938964844</v>
+        <v>132.4400024414062</v>
       </c>
       <c r="F78" t="n">
-        <v>6199700</v>
+        <v>4081100</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B79" t="n">
-        <v>134.25</v>
+        <v>132.5</v>
       </c>
       <c r="C79" t="n">
-        <v>134.4499969482422</v>
+        <v>132.8300018310547</v>
       </c>
       <c r="D79" t="n">
-        <v>132.3699951171875</v>
+        <v>130.8800048828125</v>
       </c>
       <c r="E79" t="n">
-        <v>132.4400024414062</v>
+        <v>131.0299987792969</v>
       </c>
       <c r="F79" t="n">
-        <v>4081100</v>
+        <v>3821600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B80" t="n">
-        <v>132.5</v>
+        <v>134.0500030517578</v>
       </c>
       <c r="C80" t="n">
-        <v>132.8300018310547</v>
+        <v>136.0899963378906</v>
       </c>
       <c r="D80" t="n">
-        <v>130.8800048828125</v>
+        <v>132.1849975585938</v>
       </c>
       <c r="E80" t="n">
-        <v>131.0299987792969</v>
+        <v>133.6000061035156</v>
       </c>
       <c r="F80" t="n">
-        <v>3821600</v>
+        <v>4707400</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B81" t="n">
-        <v>134.0500030517578</v>
+        <v>138.3399963378906</v>
       </c>
       <c r="C81" t="n">
-        <v>136.0899963378906</v>
+        <v>141.4100036621094</v>
       </c>
       <c r="D81" t="n">
-        <v>132.1849975585938</v>
+        <v>134.5099945068359</v>
       </c>
       <c r="E81" t="n">
-        <v>133.6000061035156</v>
+        <v>137.1900024414062</v>
       </c>
       <c r="F81" t="n">
-        <v>4707400</v>
+        <v>9691900</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B82" t="n">
-        <v>138.3399963378906</v>
+        <v>137.8999938964844</v>
       </c>
       <c r="C82" t="n">
-        <v>141.4100036621094</v>
+        <v>137.9299926757812</v>
       </c>
       <c r="D82" t="n">
-        <v>134.5099945068359</v>
+        <v>132.5</v>
       </c>
       <c r="E82" t="n">
-        <v>137.1900024414062</v>
+        <v>132.5800018310547</v>
       </c>
       <c r="F82" t="n">
-        <v>9691900</v>
+        <v>8004000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B83" t="n">
-        <v>137.8999938964844</v>
+        <v>130.0099945068359</v>
       </c>
       <c r="C83" t="n">
-        <v>137.9299926757812</v>
+        <v>131.6549987792969</v>
       </c>
       <c r="D83" t="n">
-        <v>132.5</v>
+        <v>128.6399993896484</v>
       </c>
       <c r="E83" t="n">
-        <v>132.5800018310547</v>
+        <v>130.0800018310547</v>
       </c>
       <c r="F83" t="n">
-        <v>8004000</v>
+        <v>7550700</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B84" t="n">
-        <v>130.0099945068359</v>
+        <v>129.3699951171875</v>
       </c>
       <c r="C84" t="n">
-        <v>131.6549987792969</v>
+        <v>129.6000061035156</v>
       </c>
       <c r="D84" t="n">
-        <v>128.6399993896484</v>
+        <v>122.8099975585938</v>
       </c>
       <c r="E84" t="n">
-        <v>130.0800018310547</v>
+        <v>123.7200012207031</v>
       </c>
       <c r="F84" t="n">
-        <v>7550700</v>
+        <v>8944200</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B85" t="n">
-        <v>129.3699951171875</v>
+        <v>124.5699996948242</v>
       </c>
       <c r="C85" t="n">
-        <v>129.6000061035156</v>
+        <v>124.8300018310547</v>
       </c>
       <c r="D85" t="n">
-        <v>122.8099975585938</v>
+        <v>121.9000015258789</v>
       </c>
       <c r="E85" t="n">
-        <v>123.7200012207031</v>
+        <v>122.8899993896484</v>
       </c>
       <c r="F85" t="n">
-        <v>8944200</v>
+        <v>8989700</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B86" t="n">
-        <v>124.5699996948242</v>
+        <v>121.5999984741211</v>
       </c>
       <c r="C86" t="n">
-        <v>124.8300018310547</v>
+        <v>124.4550018310547</v>
       </c>
       <c r="D86" t="n">
-        <v>121.9000015258789</v>
+        <v>120</v>
       </c>
       <c r="E86" t="n">
-        <v>122.8899993896484</v>
+        <v>123.4199981689453</v>
       </c>
       <c r="F86" t="n">
-        <v>8989700</v>
+        <v>8795900</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B87" t="n">
-        <v>121.5999984741211</v>
+        <v>123.6999969482422</v>
       </c>
       <c r="C87" t="n">
-        <v>124.4550018310547</v>
+        <v>130.6900024414062</v>
       </c>
       <c r="D87" t="n">
-        <v>120</v>
+        <v>123.0500030517578</v>
       </c>
       <c r="E87" t="n">
-        <v>123.4199981689453</v>
+        <v>129.9299926757812</v>
       </c>
       <c r="F87" t="n">
-        <v>8795900</v>
+        <v>8638900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B88" t="n">
-        <v>123.6999969482422</v>
+        <v>128.7599945068359</v>
       </c>
       <c r="C88" t="n">
-        <v>130.6900024414062</v>
+        <v>129.7599945068359</v>
       </c>
       <c r="D88" t="n">
-        <v>123.0500030517578</v>
+        <v>123.3399963378906</v>
       </c>
       <c r="E88" t="n">
-        <v>129.9299926757812</v>
+        <v>125.0899963378906</v>
       </c>
       <c r="F88" t="n">
-        <v>8638900</v>
+        <v>7414600</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B89" t="n">
-        <v>128.7599945068359</v>
+        <v>127.5899963378906</v>
       </c>
       <c r="C89" t="n">
-        <v>129.7599945068359</v>
+        <v>133.3399963378906</v>
       </c>
       <c r="D89" t="n">
-        <v>123.3399963378906</v>
+        <v>127.370002746582</v>
       </c>
       <c r="E89" t="n">
-        <v>125.0899963378906</v>
+        <v>130.5899963378906</v>
       </c>
       <c r="F89" t="n">
-        <v>7414600</v>
+        <v>8562300</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B90" t="n">
-        <v>127.5899963378906</v>
+        <v>132.1799926757812</v>
       </c>
       <c r="C90" t="n">
-        <v>133.3399963378906</v>
+        <v>132.9400024414062</v>
       </c>
       <c r="D90" t="n">
-        <v>127.370002746582</v>
+        <v>129.3300018310547</v>
       </c>
       <c r="E90" t="n">
-        <v>130.5899963378906</v>
+        <v>129.8300018310547</v>
       </c>
       <c r="F90" t="n">
-        <v>8562300</v>
+        <v>5987000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B91" t="n">
-        <v>132.1799926757812</v>
+        <v>126.4899978637695</v>
       </c>
       <c r="C91" t="n">
-        <v>132.9400024414062</v>
+        <v>130.3800048828125</v>
       </c>
       <c r="D91" t="n">
-        <v>129.3300018310547</v>
+        <v>125.7799987792969</v>
       </c>
       <c r="E91" t="n">
-        <v>129.8300018310547</v>
+        <v>127.5199966430664</v>
       </c>
       <c r="F91" t="n">
-        <v>5987000</v>
+        <v>6371300</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B92" t="n">
-        <v>126.4899978637695</v>
+        <v>127.8600006103516</v>
       </c>
       <c r="C92" t="n">
-        <v>130.3800048828125</v>
+        <v>129.5500030517578</v>
       </c>
       <c r="D92" t="n">
-        <v>125.7799987792969</v>
+        <v>125.0400009155273</v>
       </c>
       <c r="E92" t="n">
-        <v>127.5199966430664</v>
+        <v>127.2900009155273</v>
       </c>
       <c r="F92" t="n">
-        <v>6371300</v>
+        <v>5931000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B93" t="n">
-        <v>127.8600006103516</v>
+        <v>139.8399963378906</v>
       </c>
       <c r="C93" t="n">
-        <v>129.5500030517578</v>
+        <v>146.3999938964844</v>
       </c>
       <c r="D93" t="n">
-        <v>125.0400009155273</v>
+        <v>137.4199981689453</v>
       </c>
       <c r="E93" t="n">
-        <v>127.2900009155273</v>
+        <v>138.4100036621094</v>
       </c>
       <c r="F93" t="n">
-        <v>5931000</v>
+        <v>14906700</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B94" t="n">
-        <v>139.8399963378906</v>
+        <v>138.3699951171875</v>
       </c>
       <c r="C94" t="n">
-        <v>146.3999938964844</v>
+        <v>138.8999938964844</v>
       </c>
       <c r="D94" t="n">
-        <v>137.4199981689453</v>
+        <v>134.8600006103516</v>
       </c>
       <c r="E94" t="n">
-        <v>138.4100036621094</v>
+        <v>136.3399963378906</v>
       </c>
       <c r="F94" t="n">
-        <v>14906700</v>
+        <v>8053900</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B95" t="n">
-        <v>138.3699951171875</v>
+        <v>139.3200073242188</v>
       </c>
       <c r="C95" t="n">
-        <v>138.8999938964844</v>
+        <v>146.4049987792969</v>
       </c>
       <c r="D95" t="n">
-        <v>134.8600006103516</v>
+        <v>139.2400054931641</v>
       </c>
       <c r="E95" t="n">
-        <v>136.3399963378906</v>
+        <v>143.7200012207031</v>
       </c>
       <c r="F95" t="n">
-        <v>8053900</v>
+        <v>10658200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B96" t="n">
-        <v>139.3200073242188</v>
+        <v>144.8600006103516</v>
       </c>
       <c r="C96" t="n">
-        <v>146.4049987792969</v>
+        <v>149.2700042724609</v>
       </c>
       <c r="D96" t="n">
-        <v>139.2400054931641</v>
+        <v>143.8000030517578</v>
       </c>
       <c r="E96" t="n">
-        <v>143.7200012207031</v>
+        <v>146.6900024414062</v>
       </c>
       <c r="F96" t="n">
-        <v>10658200</v>
+        <v>8697000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B97" t="n">
-        <v>144.8600006103516</v>
+        <v>150.3500061035156</v>
       </c>
       <c r="C97" t="n">
-        <v>149.2700042724609</v>
+        <v>151.8000030517578</v>
       </c>
       <c r="D97" t="n">
-        <v>143.8000030517578</v>
+        <v>145.5700073242188</v>
       </c>
       <c r="E97" t="n">
-        <v>146.6900024414062</v>
+        <v>150.1499938964844</v>
       </c>
       <c r="F97" t="n">
-        <v>8697000</v>
+        <v>8568200</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B98" t="n">
-        <v>150.3500061035156</v>
+        <v>150.1499938964844</v>
       </c>
       <c r="C98" t="n">
-        <v>151.8000030517578</v>
+        <v>151.5500030517578</v>
       </c>
       <c r="D98" t="n">
-        <v>145.5700073242188</v>
+        <v>145.3300018310547</v>
       </c>
       <c r="E98" t="n">
-        <v>150.1499938964844</v>
+        <v>148.1499938964844</v>
       </c>
       <c r="F98" t="n">
-        <v>8568200</v>
+        <v>8915300</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B99" t="n">
-        <v>150.1499938964844</v>
+        <v>145.8500061035156</v>
       </c>
       <c r="C99" t="n">
-        <v>151.5500030517578</v>
+        <v>148.0599975585938</v>
       </c>
       <c r="D99" t="n">
-        <v>145.3300018310547</v>
+        <v>141.4400024414062</v>
       </c>
       <c r="E99" t="n">
-        <v>148.1499938964844</v>
+        <v>141.7400054931641</v>
       </c>
       <c r="F99" t="n">
-        <v>8915300</v>
+        <v>6364000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B100" t="n">
-        <v>145.8500061035156</v>
+        <v>141.3200073242188</v>
       </c>
       <c r="C100" t="n">
-        <v>148.0599975585938</v>
+        <v>143.1100006103516</v>
       </c>
       <c r="D100" t="n">
-        <v>141.4400024414062</v>
+        <v>138.2200012207031</v>
       </c>
       <c r="E100" t="n">
-        <v>141.7400054931641</v>
+        <v>138.3699951171875</v>
       </c>
       <c r="F100" t="n">
-        <v>6364000</v>
+        <v>7719200</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B101" t="n">
-        <v>141.3200073242188</v>
+        <v>140.7149963378906</v>
       </c>
       <c r="C101" t="n">
-        <v>143.1100006103516</v>
+        <v>143.2720031738281</v>
       </c>
       <c r="D101" t="n">
-        <v>138.2200012207031</v>
+        <v>135.3300018310547</v>
       </c>
       <c r="E101" t="n">
-        <v>138.3699951171875</v>
+        <v>139.3899993896484</v>
       </c>
       <c r="F101" t="n">
-        <v>7719200</v>
+        <v>8202300</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B102" t="n">
-        <v>140.7149963378906</v>
+        <v>138</v>
       </c>
       <c r="C102" t="n">
-        <v>143.2720031738281</v>
+        <v>139.3699951171875</v>
       </c>
       <c r="D102" t="n">
-        <v>135.3300018310547</v>
+        <v>129.2400054931641</v>
       </c>
       <c r="E102" t="n">
-        <v>139.3899993896484</v>
+        <v>130.2799987792969</v>
       </c>
       <c r="F102" t="n">
-        <v>8202300</v>
+        <v>13313800</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B103" t="n">
-        <v>138</v>
+        <v>127.7300033569336</v>
       </c>
       <c r="C103" t="n">
-        <v>139.3699951171875</v>
+        <v>130.3099975585938</v>
       </c>
       <c r="D103" t="n">
-        <v>129.2400054931641</v>
+        <v>125.3399963378906</v>
       </c>
       <c r="E103" t="n">
-        <v>130.2799987792969</v>
+        <v>128.6699981689453</v>
       </c>
       <c r="F103" t="n">
-        <v>13313800</v>
+        <v>9640500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B104" t="n">
-        <v>127.7300033569336</v>
+        <v>131.3999938964844</v>
       </c>
       <c r="C104" t="n">
-        <v>130.3099975585938</v>
+        <v>137.6100006103516</v>
       </c>
       <c r="D104" t="n">
-        <v>125.3399963378906</v>
+        <v>130.3200073242188</v>
       </c>
       <c r="E104" t="n">
-        <v>128.6699981689453</v>
+        <v>137.4900054931641</v>
       </c>
       <c r="F104" t="n">
-        <v>9640500</v>
+        <v>8986800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B105" t="n">
-        <v>131.3999938964844</v>
+        <v>138.2799987792969</v>
       </c>
       <c r="C105" t="n">
-        <v>137.6100006103516</v>
+        <v>142.2700042724609</v>
       </c>
       <c r="D105" t="n">
-        <v>130.3200073242188</v>
+        <v>136.0549926757812</v>
       </c>
       <c r="E105" t="n">
-        <v>137.4900054931641</v>
+        <v>141.7400054931641</v>
       </c>
       <c r="F105" t="n">
-        <v>8986800</v>
+        <v>6801400</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B106" t="n">
-        <v>138.2799987792969</v>
+        <v>144.3249969482422</v>
       </c>
       <c r="C106" t="n">
-        <v>142.2700042724609</v>
+        <v>145.0350036621094</v>
       </c>
       <c r="D106" t="n">
-        <v>136.0549926757812</v>
+        <v>141.8000030517578</v>
       </c>
       <c r="E106" t="n">
-        <v>141.7400054931641</v>
+        <v>143.4499969482422</v>
       </c>
       <c r="F106" t="n">
-        <v>6801400</v>
+        <v>6138100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B107" t="n">
-        <v>144.3249969482422</v>
+        <v>145.1100006103516</v>
       </c>
       <c r="C107" t="n">
-        <v>145.0350036621094</v>
+        <v>145.2400054931641</v>
       </c>
       <c r="D107" t="n">
-        <v>141.8000030517578</v>
+        <v>138.2200012207031</v>
       </c>
       <c r="E107" t="n">
-        <v>143.4499969482422</v>
+        <v>140.6600036621094</v>
       </c>
       <c r="F107" t="n">
-        <v>6138100</v>
+        <v>6942400</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B108" t="n">
-        <v>145.1100006103516</v>
+        <v>138</v>
       </c>
       <c r="C108" t="n">
-        <v>145.2400054931641</v>
+        <v>138.5</v>
       </c>
       <c r="D108" t="n">
-        <v>138.2200012207031</v>
+        <v>132.0099945068359</v>
       </c>
       <c r="E108" t="n">
-        <v>140.6600036621094</v>
+        <v>135.1199951171875</v>
       </c>
       <c r="F108" t="n">
-        <v>6942400</v>
+        <v>16322100</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B109" t="n">
+        <v>145.8200073242188</v>
+      </c>
+      <c r="C109" t="n">
+        <v>148.7700042724609</v>
+      </c>
+      <c r="D109" t="n">
         <v>138</v>
       </c>
-      <c r="C109" t="n">
-        <v>138.5</v>
-      </c>
-      <c r="D109" t="n">
-        <v>132.0099945068359</v>
-      </c>
       <c r="E109" t="n">
-        <v>135.1199951171875</v>
+        <v>141.5899963378906</v>
       </c>
       <c r="F109" t="n">
-        <v>16322100</v>
+        <v>21823000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B110" t="n">
-        <v>145.8200073242188</v>
+        <v>140.6399993896484</v>
       </c>
       <c r="C110" t="n">
-        <v>148.7700042724609</v>
+        <v>145</v>
       </c>
       <c r="D110" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E110" t="n">
-        <v>141.5899963378906</v>
+        <v>142.5800018310547</v>
       </c>
       <c r="F110" t="n">
-        <v>21823000</v>
+        <v>8724200</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B111" t="n">
-        <v>140.6399993896484</v>
+        <v>140.4600067138672</v>
       </c>
       <c r="C111" t="n">
-        <v>145</v>
+        <v>142.5</v>
       </c>
       <c r="D111" t="n">
-        <v>140</v>
+        <v>136.6900024414062</v>
       </c>
       <c r="E111" t="n">
-        <v>142.5800018310547</v>
+        <v>139.5399932861328</v>
       </c>
       <c r="F111" t="n">
-        <v>8724200</v>
+        <v>9955700</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B112" t="n">
-        <v>140.4600067138672</v>
+        <v>138.6100006103516</v>
       </c>
       <c r="C112" t="n">
-        <v>142.5</v>
+        <v>140.3200073242188</v>
       </c>
       <c r="D112" t="n">
-        <v>136.6900024414062</v>
+        <v>135.3699951171875</v>
       </c>
       <c r="E112" t="n">
-        <v>139.5399932861328</v>
+        <v>137.2299957275391</v>
       </c>
       <c r="F112" t="n">
-        <v>9955700</v>
+        <v>5260600</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B113" t="n">
-        <v>138.6100006103516</v>
+        <v>136.0200042724609</v>
       </c>
       <c r="C113" t="n">
-        <v>140.3200073242188</v>
+        <v>138.3300018310547</v>
       </c>
       <c r="D113" t="n">
-        <v>135.3699951171875</v>
+        <v>132.1499938964844</v>
       </c>
       <c r="E113" t="n">
-        <v>137.2299957275391</v>
+        <v>132.7899932861328</v>
       </c>
       <c r="F113" t="n">
-        <v>5260600</v>
+        <v>8309000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B114" t="n">
-        <v>136.0200042724609</v>
+        <v>131.2250061035156</v>
       </c>
       <c r="C114" t="n">
-        <v>138.3300018310547</v>
+        <v>131.6349945068359</v>
       </c>
       <c r="D114" t="n">
-        <v>132.1499938964844</v>
+        <v>126.2600021362305</v>
       </c>
       <c r="E114" t="n">
-        <v>132.7899932861328</v>
+        <v>127.4300003051758</v>
       </c>
       <c r="F114" t="n">
-        <v>8309000</v>
+        <v>9706800</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B115" t="n">
-        <v>131.2250061035156</v>
+        <v>130.25</v>
       </c>
       <c r="C115" t="n">
-        <v>131.6349945068359</v>
+        <v>130.7299957275391</v>
       </c>
       <c r="D115" t="n">
-        <v>126.2600021362305</v>
+        <v>124.379997253418</v>
       </c>
       <c r="E115" t="n">
-        <v>127.4300003051758</v>
+        <v>128.7700042724609</v>
       </c>
       <c r="F115" t="n">
-        <v>9706800</v>
+        <v>8120000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B116" t="n">
-        <v>130.25</v>
+        <v>129.3699951171875</v>
       </c>
       <c r="C116" t="n">
-        <v>130.7299957275391</v>
+        <v>133.7799987792969</v>
       </c>
       <c r="D116" t="n">
-        <v>124.379997253418</v>
+        <v>128.6399993896484</v>
       </c>
       <c r="E116" t="n">
-        <v>128.7700042724609</v>
+        <v>132.8899993896484</v>
       </c>
       <c r="F116" t="n">
-        <v>8120000</v>
+        <v>7611600</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B117" t="n">
-        <v>129.3699951171875</v>
+        <v>132</v>
       </c>
       <c r="C117" t="n">
-        <v>133.7799987792969</v>
+        <v>132.2200012207031</v>
       </c>
       <c r="D117" t="n">
-        <v>128.6399993896484</v>
+        <v>126.9199981689453</v>
       </c>
       <c r="E117" t="n">
-        <v>132.8899993896484</v>
+        <v>130.25</v>
       </c>
       <c r="F117" t="n">
-        <v>7611600</v>
+        <v>6360700</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B118" t="n">
-        <v>132</v>
+        <v>127.5199966430664</v>
       </c>
       <c r="C118" t="n">
-        <v>132.2200012207031</v>
+        <v>133.5800018310547</v>
       </c>
       <c r="D118" t="n">
-        <v>126.9199981689453</v>
+        <v>127.5</v>
       </c>
       <c r="E118" t="n">
-        <v>130.25</v>
+        <v>133.5</v>
       </c>
       <c r="F118" t="n">
-        <v>6360700</v>
+        <v>9043300</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B119" t="n">
-        <v>127.5199966430664</v>
+        <v>129.6499938964844</v>
       </c>
       <c r="C119" t="n">
-        <v>133.5800018310547</v>
+        <v>130.6900024414062</v>
       </c>
       <c r="D119" t="n">
-        <v>127.5</v>
+        <v>127.2600021362305</v>
       </c>
       <c r="E119" t="n">
-        <v>133.5</v>
+        <v>129.3000030517578</v>
       </c>
       <c r="F119" t="n">
-        <v>9043300</v>
+        <v>6875000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B120" t="n">
-        <v>129.6499938964844</v>
+        <v>125.3300018310547</v>
       </c>
       <c r="C120" t="n">
-        <v>130.6900024414062</v>
+        <v>126.8300018310547</v>
       </c>
       <c r="D120" t="n">
-        <v>127.2600021362305</v>
+        <v>122.370002746582</v>
       </c>
       <c r="E120" t="n">
-        <v>129.3000030517578</v>
+        <v>124.5999984741211</v>
       </c>
       <c r="F120" t="n">
-        <v>6875000</v>
+        <v>6119700</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B121" t="n">
-        <v>125.3300018310547</v>
+        <v>127.870002746582</v>
       </c>
       <c r="C121" t="n">
-        <v>126.8300018310547</v>
+        <v>135.5599975585938</v>
       </c>
       <c r="D121" t="n">
-        <v>122.370002746582</v>
+        <v>127.4000015258789</v>
       </c>
       <c r="E121" t="n">
-        <v>124.5999984741211</v>
+        <v>134.8300018310547</v>
       </c>
       <c r="F121" t="n">
-        <v>6119700</v>
+        <v>6897700</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B122" t="n">
-        <v>127.870002746582</v>
+        <v>135.1150054931641</v>
       </c>
       <c r="C122" t="n">
-        <v>135.5599975585938</v>
+        <v>139.4799957275391</v>
       </c>
       <c r="D122" t="n">
-        <v>127.4000015258789</v>
+        <v>134</v>
       </c>
       <c r="E122" t="n">
-        <v>134.8300018310547</v>
+        <v>139.3999938964844</v>
       </c>
       <c r="F122" t="n">
-        <v>6897700</v>
+        <v>8384600</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B123" t="n">
-        <v>135.1150054931641</v>
+        <v>136.3899993896484</v>
       </c>
       <c r="C123" t="n">
-        <v>139.4799957275391</v>
+        <v>139.0579986572266</v>
       </c>
       <c r="D123" t="n">
-        <v>134</v>
+        <v>132.7299957275391</v>
       </c>
       <c r="E123" t="n">
-        <v>139.3999938964844</v>
+        <v>132.8899993896484</v>
       </c>
       <c r="F123" t="n">
-        <v>8384600</v>
+        <v>6282000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B124" t="n">
-        <v>136.3899993896484</v>
+        <v>130.4049987792969</v>
       </c>
       <c r="C124" t="n">
-        <v>139.0579986572266</v>
+        <v>137.6750030517578</v>
       </c>
       <c r="D124" t="n">
-        <v>132.7299957275391</v>
+        <v>129.7899932861328</v>
       </c>
       <c r="E124" t="n">
-        <v>132.8899993896484</v>
+        <v>137.1699981689453</v>
       </c>
       <c r="F124" t="n">
-        <v>6282000</v>
+        <v>6715200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B125" t="n">
-        <v>130.4049987792969</v>
+        <v>138</v>
       </c>
       <c r="C125" t="n">
-        <v>137.6750030517578</v>
+        <v>141.7700042724609</v>
       </c>
       <c r="D125" t="n">
-        <v>129.7899932861328</v>
+        <v>137.8899993896484</v>
       </c>
       <c r="E125" t="n">
-        <v>137.1699981689453</v>
+        <v>139.6199951171875</v>
       </c>
       <c r="F125" t="n">
-        <v>6715200</v>
+        <v>5435800</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B126" t="n">
-        <v>138</v>
+        <v>139.1600036621094</v>
       </c>
       <c r="C126" t="n">
-        <v>141.7700042724609</v>
+        <v>141.1399993896484</v>
       </c>
       <c r="D126" t="n">
-        <v>137.8899993896484</v>
+        <v>137.6540069580078</v>
       </c>
       <c r="E126" t="n">
-        <v>139.6199951171875</v>
+        <v>138.2299957275391</v>
       </c>
       <c r="F126" t="n">
-        <v>5435800</v>
+        <v>4165100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B127" t="n">
-        <v>139.1600036621094</v>
+        <v>137.7400054931641</v>
       </c>
       <c r="C127" t="n">
-        <v>141.1399993896484</v>
+        <v>137.7799987792969</v>
       </c>
       <c r="D127" t="n">
-        <v>137.6540069580078</v>
+        <v>133.6900024414062</v>
       </c>
       <c r="E127" t="n">
-        <v>138.2299957275391</v>
+        <v>134.0299987792969</v>
       </c>
       <c r="F127" t="n">
-        <v>4165100</v>
+        <v>5494200</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B128" t="n">
-        <v>137.7400054931641</v>
+        <v>134.8200073242188</v>
       </c>
       <c r="C128" t="n">
-        <v>137.7799987792969</v>
+        <v>137.5950012207031</v>
       </c>
       <c r="D128" t="n">
-        <v>133.6900024414062</v>
+        <v>130.5099945068359</v>
       </c>
       <c r="E128" t="n">
-        <v>134.0299987792969</v>
+        <v>133.5700073242188</v>
       </c>
       <c r="F128" t="n">
-        <v>5494200</v>
+        <v>5364800</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B129" t="n">
-        <v>134.8200073242188</v>
+        <v>133.8699951171875</v>
       </c>
       <c r="C129" t="n">
-        <v>137.5950012207031</v>
+        <v>136.2799987792969</v>
       </c>
       <c r="D129" t="n">
-        <v>130.5099945068359</v>
+        <v>131.9100036621094</v>
       </c>
       <c r="E129" t="n">
-        <v>133.5700073242188</v>
+        <v>135.3500061035156</v>
       </c>
       <c r="F129" t="n">
-        <v>5364800</v>
+        <v>7884200</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B130" t="n">
-        <v>133.8699951171875</v>
+        <v>135.0099945068359</v>
       </c>
       <c r="C130" t="n">
-        <v>136.2799987792969</v>
+        <v>136.6999969482422</v>
       </c>
       <c r="D130" t="n">
-        <v>131.9100036621094</v>
+        <v>132.3099975585938</v>
       </c>
       <c r="E130" t="n">
-        <v>135.3500061035156</v>
+        <v>133.0700073242188</v>
       </c>
       <c r="F130" t="n">
-        <v>7884200</v>
+        <v>5959000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B131" t="n">
-        <v>135.0099945068359</v>
+        <v>133.5</v>
       </c>
       <c r="C131" t="n">
-        <v>136.6999969482422</v>
+        <v>137.5599975585938</v>
       </c>
       <c r="D131" t="n">
-        <v>132.3099975585938</v>
+        <v>133.5</v>
       </c>
       <c r="E131" t="n">
-        <v>133.0700073242188</v>
+        <v>136.0700073242188</v>
       </c>
       <c r="F131" t="n">
-        <v>5959000</v>
+        <v>5264100</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B132" t="n">
-        <v>133.5</v>
+        <v>133.7400054931641</v>
       </c>
       <c r="C132" t="n">
-        <v>137.5599975585938</v>
+        <v>136.5700073242188</v>
       </c>
       <c r="D132" t="n">
-        <v>133.5</v>
+        <v>132.3500061035156</v>
       </c>
       <c r="E132" t="n">
-        <v>136.0700073242188</v>
+        <v>136.2599945068359</v>
       </c>
       <c r="F132" t="n">
-        <v>5264100</v>
+        <v>4418900</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B133" t="n">
-        <v>133.7400054931641</v>
+        <v>134</v>
       </c>
       <c r="C133" t="n">
-        <v>136.5700073242188</v>
+        <v>135.3000030517578</v>
       </c>
       <c r="D133" t="n">
-        <v>132.3500061035156</v>
+        <v>128.8999938964844</v>
       </c>
       <c r="E133" t="n">
-        <v>136.2599945068359</v>
+        <v>131.2200012207031</v>
       </c>
       <c r="F133" t="n">
-        <v>4418900</v>
+        <v>11351600</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B134" t="n">
-        <v>134</v>
+        <v>133.4799957275391</v>
       </c>
       <c r="C134" t="n">
-        <v>135.3000030517578</v>
+        <v>138.2100067138672</v>
       </c>
       <c r="D134" t="n">
-        <v>128.8999938964844</v>
+        <v>132.1999969482422</v>
       </c>
       <c r="E134" t="n">
-        <v>131.2200012207031</v>
+        <v>135.8800048828125</v>
       </c>
       <c r="F134" t="n">
-        <v>11351600</v>
+        <v>6402200</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B135" t="n">
-        <v>133.4799957275391</v>
+        <v>134.2100067138672</v>
       </c>
       <c r="C135" t="n">
-        <v>138.2100067138672</v>
+        <v>135.6999969482422</v>
       </c>
       <c r="D135" t="n">
-        <v>132.1999969482422</v>
+        <v>129.1900024414062</v>
       </c>
       <c r="E135" t="n">
-        <v>135.8800048828125</v>
+        <v>130.8000030517578</v>
       </c>
       <c r="F135" t="n">
-        <v>6402200</v>
+        <v>7858900</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B136" t="n">
-        <v>134.2100067138672</v>
+        <v>133.2100067138672</v>
       </c>
       <c r="C136" t="n">
-        <v>135.6999969482422</v>
+        <v>135.0800018310547</v>
       </c>
       <c r="D136" t="n">
-        <v>129.1900024414062</v>
+        <v>131.1499938964844</v>
       </c>
       <c r="E136" t="n">
-        <v>130.8000030517578</v>
+        <v>135.0099945068359</v>
       </c>
       <c r="F136" t="n">
-        <v>7858900</v>
+        <v>5353300</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B137" t="n">
-        <v>133.2100067138672</v>
+        <v>131.7899932861328</v>
       </c>
       <c r="C137" t="n">
-        <v>135.0800018310547</v>
+        <v>132.5</v>
       </c>
       <c r="D137" t="n">
-        <v>131.1499938964844</v>
+        <v>122.5100021362305</v>
       </c>
       <c r="E137" t="n">
-        <v>135.0099945068359</v>
+        <v>122.5500030517578</v>
       </c>
       <c r="F137" t="n">
-        <v>5353300</v>
+        <v>7553500</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B138" t="n">
-        <v>131.7899932861328</v>
+        <v>121.3399963378906</v>
       </c>
       <c r="C138" t="n">
-        <v>132.5</v>
+        <v>123.7200012207031</v>
       </c>
       <c r="D138" t="n">
-        <v>122.5100021362305</v>
+        <v>120.3420028686523</v>
       </c>
       <c r="E138" t="n">
-        <v>122.5500030517578</v>
+        <v>120.7699966430664</v>
       </c>
       <c r="F138" t="n">
-        <v>7553500</v>
+        <v>5940200</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B139" t="n">
-        <v>121.3399963378906</v>
+        <v>122.0100021362305</v>
       </c>
       <c r="C139" t="n">
-        <v>123.7200012207031</v>
+        <v>123.3399963378906</v>
       </c>
       <c r="D139" t="n">
-        <v>120.3420028686523</v>
+        <v>115.4199981689453</v>
       </c>
       <c r="E139" t="n">
-        <v>120.7699966430664</v>
+        <v>116.129997253418</v>
       </c>
       <c r="F139" t="n">
-        <v>5940200</v>
+        <v>7540500</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B140" t="n">
-        <v>122.0100021362305</v>
+        <v>118.620002746582</v>
       </c>
       <c r="C140" t="n">
-        <v>123.3399963378906</v>
+        <v>123.4599990844727</v>
       </c>
       <c r="D140" t="n">
-        <v>115.4199981689453</v>
+        <v>117.4199981689453</v>
       </c>
       <c r="E140" t="n">
-        <v>116.129997253418</v>
+        <v>122.7799987792969</v>
       </c>
       <c r="F140" t="n">
-        <v>7540500</v>
+        <v>7837700</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B141" t="n">
-        <v>118.620002746582</v>
+        <v>126.0599975585938</v>
       </c>
       <c r="C141" t="n">
-        <v>123.4599990844727</v>
+        <v>127.25</v>
       </c>
       <c r="D141" t="n">
-        <v>117.4199981689453</v>
+        <v>124.6600036621094</v>
       </c>
       <c r="E141" t="n">
-        <v>122.7799987792969</v>
+        <v>124.8499984741211</v>
       </c>
       <c r="F141" t="n">
-        <v>7837700</v>
+        <v>5037700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B142" t="n">
-        <v>126.0599975585938</v>
+        <v>121.0999984741211</v>
       </c>
       <c r="C142" t="n">
-        <v>127.25</v>
+        <v>127.1999969482422</v>
       </c>
       <c r="D142" t="n">
-        <v>124.6600036621094</v>
+        <v>119.7910003662109</v>
       </c>
       <c r="E142" t="n">
-        <v>124.8499984741211</v>
+        <v>126.6800003051758</v>
       </c>
       <c r="F142" t="n">
-        <v>5037700</v>
+        <v>5125100</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B143" t="n">
-        <v>121.0999984741211</v>
+        <v>127.3199996948242</v>
       </c>
       <c r="C143" t="n">
-        <v>127.1999969482422</v>
+        <v>128.1649932861328</v>
       </c>
       <c r="D143" t="n">
-        <v>119.7910003662109</v>
+        <v>125.1650009155273</v>
       </c>
       <c r="E143" t="n">
-        <v>126.6800003051758</v>
+        <v>126.25</v>
       </c>
       <c r="F143" t="n">
-        <v>5125100</v>
+        <v>3033100</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B144" t="n">
-        <v>127.3199996948242</v>
+        <v>127.8499984741211</v>
       </c>
       <c r="C144" t="n">
-        <v>128.1649932861328</v>
+        <v>133.6999969482422</v>
       </c>
       <c r="D144" t="n">
-        <v>125.1650009155273</v>
+        <v>127.5500030517578</v>
       </c>
       <c r="E144" t="n">
-        <v>126.25</v>
+        <v>133.6399993896484</v>
       </c>
       <c r="F144" t="n">
-        <v>3033100</v>
+        <v>5758000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B145" t="n">
-        <v>127.8499984741211</v>
+        <v>143</v>
       </c>
       <c r="C145" t="n">
-        <v>133.6999969482422</v>
+        <v>146.1600036621094</v>
       </c>
       <c r="D145" t="n">
-        <v>127.5500030517578</v>
+        <v>141.1199951171875</v>
       </c>
       <c r="E145" t="n">
-        <v>133.6399993896484</v>
+        <v>145.0700073242188</v>
       </c>
       <c r="F145" t="n">
-        <v>5758000</v>
+        <v>12136800</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B146" t="n">
-        <v>143</v>
+        <v>145.1100006103516</v>
       </c>
       <c r="C146" t="n">
-        <v>146.1600036621094</v>
+        <v>146.1900024414062</v>
       </c>
       <c r="D146" t="n">
-        <v>141.1199951171875</v>
+        <v>141.1100006103516</v>
       </c>
       <c r="E146" t="n">
-        <v>145.0700073242188</v>
+        <v>146.0500030517578</v>
       </c>
       <c r="F146" t="n">
-        <v>12136800</v>
+        <v>7266100</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B147" t="n">
-        <v>145.1100006103516</v>
+        <v>147.5399932861328</v>
       </c>
       <c r="C147" t="n">
-        <v>146.1900024414062</v>
+        <v>149.3399963378906</v>
       </c>
       <c r="D147" t="n">
-        <v>141.1100006103516</v>
+        <v>145.3999938964844</v>
       </c>
       <c r="E147" t="n">
-        <v>146.0500030517578</v>
+        <v>147.3500061035156</v>
       </c>
       <c r="F147" t="n">
-        <v>7266100</v>
+        <v>7054100</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B148" t="n">
-        <v>147.5399932861328</v>
+        <v>146.7299957275391</v>
       </c>
       <c r="C148" t="n">
-        <v>149.3399963378906</v>
+        <v>152.1399993896484</v>
       </c>
       <c r="D148" t="n">
-        <v>145.3999938964844</v>
+        <v>144.7960052490234</v>
       </c>
       <c r="E148" t="n">
-        <v>147.3500061035156</v>
+        <v>152.0200042724609</v>
       </c>
       <c r="F148" t="n">
-        <v>7054100</v>
+        <v>7217900</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B149" t="n">
-        <v>146.7299957275391</v>
+        <v>153.9900054931641</v>
       </c>
       <c r="C149" t="n">
-        <v>152.1399993896484</v>
+        <v>155.4100036621094</v>
       </c>
       <c r="D149" t="n">
-        <v>144.7960052490234</v>
+        <v>150.9859924316406</v>
       </c>
       <c r="E149" t="n">
-        <v>152.0200042724609</v>
+        <v>154.3699951171875</v>
       </c>
       <c r="F149" t="n">
-        <v>7217900</v>
+        <v>7114000</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B150" t="n">
-        <v>153.9900054931641</v>
+        <v>154.8200073242188</v>
       </c>
       <c r="C150" t="n">
-        <v>155.4100036621094</v>
+        <v>155.2250061035156</v>
       </c>
       <c r="D150" t="n">
-        <v>150.9859924316406</v>
+        <v>150.5200042724609</v>
       </c>
       <c r="E150" t="n">
-        <v>154.3699951171875</v>
+        <v>154.3300018310547</v>
       </c>
       <c r="F150" t="n">
-        <v>7114000</v>
+        <v>5835300</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B151" t="n">
-        <v>154.8200073242188</v>
+        <v>155.9199981689453</v>
       </c>
       <c r="C151" t="n">
-        <v>155.2250061035156</v>
+        <v>161.0099945068359</v>
       </c>
       <c r="D151" t="n">
-        <v>150.5200042724609</v>
+        <v>153.3600006103516</v>
       </c>
       <c r="E151" t="n">
-        <v>154.3300018310547</v>
+        <v>161.0099945068359</v>
       </c>
       <c r="F151" t="n">
-        <v>5835300</v>
+        <v>7205600</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B152" t="n">
-        <v>155.9199981689453</v>
+        <v>162.2350006103516</v>
       </c>
       <c r="C152" t="n">
-        <v>161.0099945068359</v>
+        <v>165.2799987792969</v>
       </c>
       <c r="D152" t="n">
-        <v>153.3600006103516</v>
+        <v>160.4700012207031</v>
       </c>
       <c r="E152" t="n">
-        <v>161.0099945068359</v>
+        <v>164.2299957275391</v>
       </c>
       <c r="F152" t="n">
-        <v>7205600</v>
+        <v>8216400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B153" t="n">
-        <v>162.2350006103516</v>
+        <v>165</v>
       </c>
       <c r="C153" t="n">
-        <v>165.2799987792969</v>
+        <v>167.8999938964844</v>
       </c>
       <c r="D153" t="n">
-        <v>160.4700012207031</v>
+        <v>164.4900054931641</v>
       </c>
       <c r="E153" t="n">
-        <v>164.2299957275391</v>
+        <v>166.8500061035156</v>
       </c>
       <c r="F153" t="n">
-        <v>8216400</v>
+        <v>6113300</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B154" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C154" t="n">
-        <v>167.8999938964844</v>
+        <v>173.8500061035156</v>
       </c>
       <c r="D154" t="n">
-        <v>164.4900054931641</v>
+        <v>167.2200012207031</v>
       </c>
       <c r="E154" t="n">
-        <v>166.8500061035156</v>
+        <v>172.8600006103516</v>
       </c>
       <c r="F154" t="n">
-        <v>6113300</v>
+        <v>8918900</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B155" t="n">
-        <v>170</v>
+        <v>174.3999938964844</v>
       </c>
       <c r="C155" t="n">
-        <v>173.8500061035156</v>
+        <v>178.4799957275391</v>
       </c>
       <c r="D155" t="n">
-        <v>167.2200012207031</v>
+        <v>171.1399993896484</v>
       </c>
       <c r="E155" t="n">
-        <v>172.8600006103516</v>
+        <v>177.7299957275391</v>
       </c>
       <c r="F155" t="n">
-        <v>8918900</v>
+        <v>8699400</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B156" t="n">
-        <v>174.3999938964844</v>
+        <v>177.5</v>
       </c>
       <c r="C156" t="n">
-        <v>178.4799957275391</v>
+        <v>177.75</v>
       </c>
       <c r="D156" t="n">
-        <v>171.1399993896484</v>
+        <v>169.3800048828125</v>
       </c>
       <c r="E156" t="n">
-        <v>177.7299957275391</v>
+        <v>172.5500030517578</v>
       </c>
       <c r="F156" t="n">
-        <v>8699400</v>
+        <v>7428000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B157" t="n">
-        <v>177.5</v>
+        <v>174.5299987792969</v>
       </c>
       <c r="C157" t="n">
-        <v>177.75</v>
+        <v>179.8000030517578</v>
       </c>
       <c r="D157" t="n">
-        <v>169.3800048828125</v>
+        <v>173.5200042724609</v>
       </c>
       <c r="E157" t="n">
-        <v>172.5500030517578</v>
+        <v>176.9100036621094</v>
       </c>
       <c r="F157" t="n">
-        <v>7428000</v>
+        <v>7508000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B158" t="n">
-        <v>174.5299987792969</v>
+        <v>176.7200012207031</v>
       </c>
       <c r="C158" t="n">
-        <v>179.8000030517578</v>
+        <v>176.7599945068359</v>
       </c>
       <c r="D158" t="n">
-        <v>173.5200042724609</v>
+        <v>168.5099945068359</v>
       </c>
       <c r="E158" t="n">
-        <v>176.9100036621094</v>
+        <v>172.4700012207031</v>
       </c>
       <c r="F158" t="n">
-        <v>7508000</v>
+        <v>6782500</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B159" t="n">
-        <v>176.7200012207031</v>
+        <v>166.4799957275391</v>
       </c>
       <c r="C159" t="n">
-        <v>176.7599945068359</v>
+        <v>167.8200073242188</v>
       </c>
       <c r="D159" t="n">
-        <v>168.5099945068359</v>
+        <v>162.25</v>
       </c>
       <c r="E159" t="n">
-        <v>172.4700012207031</v>
+        <v>165.2899932861328</v>
       </c>
       <c r="F159" t="n">
-        <v>6782500</v>
+        <v>7414100</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B160" t="n">
-        <v>166.4799957275391</v>
+        <v>166.1000061035156</v>
       </c>
       <c r="C160" t="n">
-        <v>167.8200073242188</v>
+        <v>168.7299957275391</v>
       </c>
       <c r="D160" t="n">
-        <v>162.25</v>
+        <v>163.4199981689453</v>
       </c>
       <c r="E160" t="n">
-        <v>165.2899932861328</v>
+        <v>168.6799926757812</v>
       </c>
       <c r="F160" t="n">
-        <v>7414100</v>
+        <v>6270500</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B161" t="n">
-        <v>166.1000061035156</v>
+        <v>172.0099945068359</v>
       </c>
       <c r="C161" t="n">
-        <v>168.7299957275391</v>
+        <v>173.5800018310547</v>
       </c>
       <c r="D161" t="n">
-        <v>163.4199981689453</v>
+        <v>167.7599945068359</v>
       </c>
       <c r="E161" t="n">
-        <v>168.6799926757812</v>
+        <v>172.7100067138672</v>
       </c>
       <c r="F161" t="n">
-        <v>6270500</v>
+        <v>6141700</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B162" t="n">
-        <v>172.0099945068359</v>
+        <v>172.9900054931641</v>
       </c>
       <c r="C162" t="n">
-        <v>173.5800018310547</v>
+        <v>177.1799926757812</v>
       </c>
       <c r="D162" t="n">
-        <v>167.7599945068359</v>
+        <v>172</v>
       </c>
       <c r="E162" t="n">
-        <v>172.7100067138672</v>
+        <v>172.6999969482422</v>
       </c>
       <c r="F162" t="n">
-        <v>6141700</v>
+        <v>7652400</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B163" t="n">
-        <v>172.9900054931641</v>
+        <v>175.6799926757812</v>
       </c>
       <c r="C163" t="n">
-        <v>177.1799926757812</v>
+        <v>179.1000061035156</v>
       </c>
       <c r="D163" t="n">
-        <v>172</v>
+        <v>172.2850036621094</v>
       </c>
       <c r="E163" t="n">
-        <v>172.6999969482422</v>
+        <v>172.6199951171875</v>
       </c>
       <c r="F163" t="n">
-        <v>7652400</v>
+        <v>7167900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B164" t="n">
-        <v>175.6799926757812</v>
+        <v>177</v>
       </c>
       <c r="C164" t="n">
-        <v>179.1000061035156</v>
+        <v>177.2200012207031</v>
       </c>
       <c r="D164" t="n">
-        <v>172.2850036621094</v>
+        <v>169.8899993896484</v>
       </c>
       <c r="E164" t="n">
-        <v>172.6199951171875</v>
+        <v>170.2200012207031</v>
       </c>
       <c r="F164" t="n">
-        <v>7167900</v>
+        <v>15684800</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B165" t="n">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="C165" t="n">
-        <v>177.2200012207031</v>
+        <v>154.8300018310547</v>
       </c>
       <c r="D165" t="n">
-        <v>169.8899993896484</v>
+        <v>140.5800018310547</v>
       </c>
       <c r="E165" t="n">
-        <v>170.2200012207031</v>
+        <v>147.0599975585938</v>
       </c>
       <c r="F165" t="n">
-        <v>15684800</v>
+        <v>35627200</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B166" t="n">
-        <v>153</v>
+        <v>149.2200012207031</v>
       </c>
       <c r="C166" t="n">
-        <v>154.8300018310547</v>
+        <v>149.4400024414062</v>
       </c>
       <c r="D166" t="n">
-        <v>140.5800018310547</v>
+        <v>139.6799926757812</v>
       </c>
       <c r="E166" t="n">
-        <v>147.0599975585938</v>
+        <v>141.75</v>
       </c>
       <c r="F166" t="n">
-        <v>35627200</v>
+        <v>18255700</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B167" t="n">
-        <v>149.2200012207031</v>
+        <v>142.6499938964844</v>
       </c>
       <c r="C167" t="n">
-        <v>149.4400024414062</v>
+        <v>143.9900054931641</v>
       </c>
       <c r="D167" t="n">
-        <v>139.6799926757812</v>
+        <v>138.6000061035156</v>
       </c>
       <c r="E167" t="n">
-        <v>141.75</v>
+        <v>141.7700042724609</v>
       </c>
       <c r="F167" t="n">
-        <v>18255700</v>
+        <v>20371600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B168" t="n">
-        <v>142.6499938964844</v>
+        <v>141.3999938964844</v>
       </c>
       <c r="C168" t="n">
-        <v>143.9900054931641</v>
+        <v>142.6199951171875</v>
       </c>
       <c r="D168" t="n">
-        <v>138.6000061035156</v>
+        <v>135.1300048828125</v>
       </c>
       <c r="E168" t="n">
-        <v>141.7700042724609</v>
+        <v>136.4299926757812</v>
       </c>
       <c r="F168" t="n">
-        <v>20371600</v>
+        <v>18520900</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B169" t="n">
-        <v>141.3999938964844</v>
+        <v>136.7799987792969</v>
       </c>
       <c r="C169" t="n">
-        <v>142.6199951171875</v>
+        <v>142.9400024414062</v>
       </c>
       <c r="D169" t="n">
-        <v>135.1300048828125</v>
+        <v>135.3699951171875</v>
       </c>
       <c r="E169" t="n">
-        <v>136.4299926757812</v>
+        <v>142.5399932861328</v>
       </c>
       <c r="F169" t="n">
-        <v>18520900</v>
+        <v>12796100</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B170" t="n">
-        <v>136.7799987792969</v>
+        <v>144.8000030517578</v>
       </c>
       <c r="C170" t="n">
-        <v>142.9400024414062</v>
+        <v>147.3099975585938</v>
       </c>
       <c r="D170" t="n">
-        <v>135.3699951171875</v>
+        <v>140.3000030517578</v>
       </c>
       <c r="E170" t="n">
-        <v>142.5399932861328</v>
+        <v>140.6900024414062</v>
       </c>
       <c r="F170" t="n">
-        <v>12796100</v>
+        <v>14164600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B171" t="n">
-        <v>144.8000030517578</v>
+        <v>142.5</v>
       </c>
       <c r="C171" t="n">
-        <v>147.3099975585938</v>
+        <v>147.8899993896484</v>
       </c>
       <c r="D171" t="n">
-        <v>140.3000030517578</v>
+        <v>141</v>
       </c>
       <c r="E171" t="n">
-        <v>140.6900024414062</v>
+        <v>147.8099975585938</v>
       </c>
       <c r="F171" t="n">
-        <v>14164600</v>
+        <v>15728200</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B172" t="n">
-        <v>142.5</v>
+        <v>144.9900054931641</v>
       </c>
       <c r="C172" t="n">
-        <v>147.8899993896484</v>
+        <v>145.8999938964844</v>
       </c>
       <c r="D172" t="n">
-        <v>141</v>
+        <v>141.7799987792969</v>
       </c>
       <c r="E172" t="n">
-        <v>147.8099975585938</v>
+        <v>141.9700012207031</v>
       </c>
       <c r="F172" t="n">
-        <v>15728200</v>
+        <v>10833000</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B173" t="n">
-        <v>144.9900054931641</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="C173" t="n">
-        <v>145.8999938964844</v>
+        <v>143.6699981689453</v>
       </c>
       <c r="D173" t="n">
-        <v>141.7799987792969</v>
+        <v>138.6399993896484</v>
       </c>
       <c r="E173" t="n">
-        <v>141.9700012207031</v>
+        <v>141.7100067138672</v>
       </c>
       <c r="F173" t="n">
-        <v>10833000</v>
+        <v>8634500</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B174" t="n">
-        <v>143.0200042724609</v>
+        <v>139.5800018310547</v>
       </c>
       <c r="C174" t="n">
-        <v>143.6699981689453</v>
+        <v>142.5</v>
       </c>
       <c r="D174" t="n">
-        <v>138.6399993896484</v>
+        <v>137</v>
       </c>
       <c r="E174" t="n">
-        <v>141.7100067138672</v>
+        <v>141.5800018310547</v>
       </c>
       <c r="F174" t="n">
-        <v>8634500</v>
+        <v>8800800</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B175" t="n">
-        <v>139.5800018310547</v>
+        <v>142</v>
       </c>
       <c r="C175" t="n">
-        <v>142.5</v>
+        <v>143.2599945068359</v>
       </c>
       <c r="D175" t="n">
-        <v>137</v>
+        <v>137.5</v>
       </c>
       <c r="E175" t="n">
-        <v>141.5800018310547</v>
+        <v>140.4900054931641</v>
       </c>
       <c r="F175" t="n">
-        <v>8800800</v>
+        <v>9617000</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B176" t="n">
-        <v>142</v>
+        <v>139.3000030517578</v>
       </c>
       <c r="C176" t="n">
-        <v>143.2599945068359</v>
+        <v>148.9900054931641</v>
       </c>
       <c r="D176" t="n">
-        <v>137.5</v>
+        <v>139.125</v>
       </c>
       <c r="E176" t="n">
-        <v>140.4900054931641</v>
+        <v>148.5899963378906</v>
       </c>
       <c r="F176" t="n">
-        <v>9617000</v>
+        <v>11620600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B177" t="n">
-        <v>139.3000030517578</v>
+        <v>152.2599945068359</v>
       </c>
       <c r="C177" t="n">
-        <v>148.9900054931641</v>
+        <v>154.3899993896484</v>
       </c>
       <c r="D177" t="n">
-        <v>139.125</v>
+        <v>149</v>
       </c>
       <c r="E177" t="n">
-        <v>148.5899963378906</v>
+        <v>154.0299987792969</v>
       </c>
       <c r="F177" t="n">
-        <v>11620600</v>
+        <v>10554600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B178" t="n">
-        <v>152.2599945068359</v>
+        <v>157.5050048828125</v>
       </c>
       <c r="C178" t="n">
-        <v>154.3899993896484</v>
+        <v>160.1399993896484</v>
       </c>
       <c r="D178" t="n">
-        <v>149</v>
+        <v>153.8899993896484</v>
       </c>
       <c r="E178" t="n">
-        <v>154.0299987792969</v>
+        <v>158.0099945068359</v>
       </c>
       <c r="F178" t="n">
-        <v>10554600</v>
+        <v>11835300</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B179" t="n">
-        <v>157.5050048828125</v>
+        <v>157.8500061035156</v>
       </c>
       <c r="C179" t="n">
-        <v>160.1399993896484</v>
+        <v>158.1100006103516</v>
       </c>
       <c r="D179" t="n">
-        <v>153.8899993896484</v>
+        <v>153.5700073242188</v>
       </c>
       <c r="E179" t="n">
-        <v>158.0099945068359</v>
+        <v>154.3099975585938</v>
       </c>
       <c r="F179" t="n">
-        <v>11835300</v>
+        <v>6982200</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B180" t="n">
-        <v>157.8500061035156</v>
+        <v>154</v>
       </c>
       <c r="C180" t="n">
-        <v>158.1100006103516</v>
+        <v>156.3800048828125</v>
       </c>
       <c r="D180" t="n">
-        <v>153.5700073242188</v>
+        <v>150.6600036621094</v>
       </c>
       <c r="E180" t="n">
-        <v>154.3099975585938</v>
+        <v>155.2700042724609</v>
       </c>
       <c r="F180" t="n">
-        <v>6982200</v>
+        <v>7194300</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B181" t="n">
-        <v>154</v>
+        <v>157.3999938964844</v>
       </c>
       <c r="C181" t="n">
-        <v>156.3800048828125</v>
+        <v>161.5</v>
       </c>
       <c r="D181" t="n">
-        <v>150.6600036621094</v>
+        <v>155.8000030517578</v>
       </c>
       <c r="E181" t="n">
-        <v>155.2700042724609</v>
+        <v>159.4700012207031</v>
       </c>
       <c r="F181" t="n">
-        <v>7194300</v>
+        <v>15385900</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B182" t="n">
-        <v>157.3999938964844</v>
+        <v>162.1399993896484</v>
       </c>
       <c r="C182" t="n">
-        <v>161.5</v>
+        <v>172.3300018310547</v>
       </c>
       <c r="D182" t="n">
-        <v>155.8000030517578</v>
+        <v>161.2799987792969</v>
       </c>
       <c r="E182" t="n">
-        <v>159.4700012207031</v>
+        <v>170.6799926757812</v>
       </c>
       <c r="F182" t="n">
-        <v>15385900</v>
+        <v>9991500</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B183" t="n">
-        <v>162.1399993896484</v>
+        <v>170.6999969482422</v>
       </c>
       <c r="C183" t="n">
-        <v>172.3300018310547</v>
+        <v>177.4799957275391</v>
       </c>
       <c r="D183" t="n">
-        <v>161.2799987792969</v>
+        <v>170.6900024414062</v>
       </c>
       <c r="E183" t="n">
-        <v>170.6799926757812</v>
+        <v>175.3300018310547</v>
       </c>
       <c r="F183" t="n">
-        <v>9991500</v>
+        <v>9144300</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B184" t="n">
-        <v>170.6999969482422</v>
+        <v>175.4900054931641</v>
       </c>
       <c r="C184" t="n">
         <v>177.4799957275391</v>
       </c>
       <c r="D184" t="n">
-        <v>170.6900024414062</v>
+        <v>168.7100067138672</v>
       </c>
       <c r="E184" t="n">
-        <v>175.3300018310547</v>
+        <v>174.3699951171875</v>
       </c>
       <c r="F184" t="n">
-        <v>9144300</v>
+        <v>8069700</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B185" t="n">
-        <v>175.4900054931641</v>
+        <v>163.0800018310547</v>
       </c>
       <c r="C185" t="n">
-        <v>177.4799957275391</v>
+        <v>167.7899932861328</v>
       </c>
       <c r="D185" t="n">
-        <v>168.7100067138672</v>
+        <v>157.3999938964844</v>
       </c>
       <c r="E185" t="n">
-        <v>174.3699951171875</v>
+        <v>166.0099945068359</v>
       </c>
       <c r="F185" t="n">
-        <v>8069700</v>
+        <v>10214000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B186" t="n">
-        <v>163.0800018310547</v>
+        <v>159.4600067138672</v>
       </c>
       <c r="C186" t="n">
-        <v>167.7899932861328</v>
+        <v>161.1929931640625</v>
       </c>
       <c r="D186" t="n">
-        <v>157.3999938964844</v>
+        <v>152.1900024414062</v>
       </c>
       <c r="E186" t="n">
-        <v>166.0099945068359</v>
+        <v>154.2700042724609</v>
       </c>
       <c r="F186" t="n">
-        <v>10214000</v>
+        <v>9094700</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B187" t="n">
-        <v>159.4600067138672</v>
+        <v>157.9499969482422</v>
       </c>
       <c r="C187" t="n">
-        <v>161.1929931640625</v>
+        <v>159.2299957275391</v>
       </c>
       <c r="D187" t="n">
-        <v>152.1900024414062</v>
+        <v>153.2530059814453</v>
       </c>
       <c r="E187" t="n">
-        <v>154.2700042724609</v>
+        <v>156.3999938964844</v>
       </c>
       <c r="F187" t="n">
-        <v>9094700</v>
+        <v>6043100</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B188" t="n">
-        <v>157.9499969482422</v>
+        <v>157.75</v>
       </c>
       <c r="C188" t="n">
-        <v>159.2299957275391</v>
+        <v>158.9900054931641</v>
       </c>
       <c r="D188" t="n">
-        <v>153.2530059814453</v>
+        <v>145.3200073242188</v>
       </c>
       <c r="E188" t="n">
-        <v>156.3999938964844</v>
+        <v>152.1600036621094</v>
       </c>
       <c r="F188" t="n">
-        <v>6043100</v>
+        <v>7334100</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B189" t="n">
-        <v>157.75</v>
+        <v>151</v>
       </c>
       <c r="C189" t="n">
-        <v>158.9900054931641</v>
+        <v>154.9700012207031</v>
       </c>
       <c r="D189" t="n">
-        <v>145.3200073242188</v>
+        <v>149</v>
       </c>
       <c r="E189" t="n">
-        <v>152.1600036621094</v>
+        <v>151.7599945068359</v>
       </c>
       <c r="F189" t="n">
-        <v>7334100</v>
+        <v>6867400</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B190" t="n">
-        <v>151</v>
+        <v>153.5800018310547</v>
       </c>
       <c r="C190" t="n">
-        <v>154.9700012207031</v>
+        <v>157.0700073242188</v>
       </c>
       <c r="D190" t="n">
-        <v>149</v>
+        <v>150.2799987792969</v>
       </c>
       <c r="E190" t="n">
-        <v>151.7599945068359</v>
+        <v>156.3999938964844</v>
       </c>
       <c r="F190" t="n">
-        <v>6867400</v>
+        <v>5326700</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B191" t="n">
-        <v>153.5800018310547</v>
+        <v>160.1100006103516</v>
       </c>
       <c r="C191" t="n">
-        <v>157.0700073242188</v>
+        <v>165.25</v>
       </c>
       <c r="D191" t="n">
-        <v>150.2799987792969</v>
+        <v>159.1349945068359</v>
       </c>
       <c r="E191" t="n">
-        <v>156.3999938964844</v>
+        <v>163.2400054931641</v>
       </c>
       <c r="F191" t="n">
-        <v>5326700</v>
+        <v>6052500</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B192" t="n">
-        <v>160.1100006103516</v>
+        <v>165.9600067138672</v>
       </c>
       <c r="C192" t="n">
-        <v>165.25</v>
+        <v>169.2799987792969</v>
       </c>
       <c r="D192" t="n">
-        <v>159.1349945068359</v>
+        <v>163.5099945068359</v>
       </c>
       <c r="E192" t="n">
-        <v>163.2400054931641</v>
+        <v>169.0899963378906</v>
       </c>
       <c r="F192" t="n">
-        <v>6052500</v>
+        <v>7240800</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B193" t="n">
-        <v>165.9600067138672</v>
+        <v>169.3000030517578</v>
       </c>
       <c r="C193" t="n">
-        <v>169.2799987792969</v>
+        <v>171.2100067138672</v>
       </c>
       <c r="D193" t="n">
-        <v>163.5099945068359</v>
+        <v>166.7799987792969</v>
       </c>
       <c r="E193" t="n">
-        <v>169.0899963378906</v>
+        <v>168.0099945068359</v>
       </c>
       <c r="F193" t="n">
-        <v>7240800</v>
+        <v>8090900</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B194" t="n">
-        <v>169.3000030517578</v>
+        <v>169.8899993896484</v>
       </c>
       <c r="C194" t="n">
-        <v>171.2100067138672</v>
+        <v>171.2899932861328</v>
       </c>
       <c r="D194" t="n">
-        <v>166.7799987792969</v>
+        <v>163.9299926757812</v>
       </c>
       <c r="E194" t="n">
-        <v>168.0099945068359</v>
+        <v>164.9299926757812</v>
       </c>
       <c r="F194" t="n">
-        <v>8090900</v>
+        <v>6229500</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B195" t="n">
-        <v>169.8899993896484</v>
+        <v>171.1999969482422</v>
       </c>
       <c r="C195" t="n">
-        <v>171.2899932861328</v>
+        <v>172</v>
       </c>
       <c r="D195" t="n">
-        <v>163.9299926757812</v>
+        <v>167.5850067138672</v>
       </c>
       <c r="E195" t="n">
-        <v>164.9299926757812</v>
+        <v>169.6699981689453</v>
       </c>
       <c r="F195" t="n">
-        <v>6229500</v>
+        <v>11130400</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B196" t="n">
-        <v>171.1999969482422</v>
+        <v>170.1100006103516</v>
       </c>
       <c r="C196" t="n">
-        <v>172</v>
+        <v>175.1999969482422</v>
       </c>
       <c r="D196" t="n">
-        <v>167.5850067138672</v>
+        <v>166.6600036621094</v>
       </c>
       <c r="E196" t="n">
-        <v>169.6699981689453</v>
+        <v>174.5599975585938</v>
       </c>
       <c r="F196" t="n">
-        <v>11130400</v>
+        <v>9494400</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B197" t="n">
-        <v>170.1100006103516</v>
+        <v>165.4299926757812</v>
       </c>
       <c r="C197" t="n">
-        <v>175.1999969482422</v>
+        <v>165.4299926757812</v>
       </c>
       <c r="D197" t="n">
-        <v>166.6600036621094</v>
+        <v>159.3600006103516</v>
       </c>
       <c r="E197" t="n">
-        <v>174.5599975585938</v>
+        <v>162.1999969482422</v>
       </c>
       <c r="F197" t="n">
-        <v>9494400</v>
+        <v>7770100</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B198" t="n">
-        <v>165.4299926757812</v>
+        <v>162.3249969482422</v>
       </c>
       <c r="C198" t="n">
-        <v>165.4299926757812</v>
+        <v>165.6799926757812</v>
       </c>
       <c r="D198" t="n">
-        <v>159.3600006103516</v>
+        <v>160.5700073242188</v>
       </c>
       <c r="E198" t="n">
-        <v>162.1999969482422</v>
+        <v>161.7400054931641</v>
       </c>
       <c r="F198" t="n">
-        <v>7770100</v>
+        <v>6350600</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B199" t="n">
-        <v>162.3249969482422</v>
+        <v>167.7599945068359</v>
       </c>
       <c r="C199" t="n">
-        <v>165.6799926757812</v>
+        <v>170.1600036621094</v>
       </c>
       <c r="D199" t="n">
-        <v>160.5700073242188</v>
+        <v>159.4600067138672</v>
       </c>
       <c r="E199" t="n">
-        <v>161.7400054931641</v>
+        <v>165.4499969482422</v>
       </c>
       <c r="F199" t="n">
-        <v>6350600</v>
+        <v>8231200</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B200" t="n">
-        <v>167.7599945068359</v>
+        <v>159.9400024414062</v>
       </c>
       <c r="C200" t="n">
-        <v>170.1600036621094</v>
+        <v>161.2299957275391</v>
       </c>
       <c r="D200" t="n">
-        <v>159.4600067138672</v>
+        <v>154.7400054931641</v>
       </c>
       <c r="E200" t="n">
-        <v>165.4499969482422</v>
+        <v>157.6000061035156</v>
       </c>
       <c r="F200" t="n">
-        <v>8231200</v>
+        <v>11865200</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B201" t="n">
-        <v>159.9400024414062</v>
+        <v>158.8600006103516</v>
       </c>
       <c r="C201" t="n">
-        <v>161.2299957275391</v>
+        <v>165.6600036621094</v>
       </c>
       <c r="D201" t="n">
-        <v>154.7400054931641</v>
+        <v>155.2200012207031</v>
       </c>
       <c r="E201" t="n">
-        <v>157.6000061035156</v>
+        <v>164.1000061035156</v>
       </c>
       <c r="F201" t="n">
-        <v>11865200</v>
+        <v>8535700</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B202" t="n">
-        <v>158.8600006103516</v>
+        <v>164.1100006103516</v>
       </c>
       <c r="C202" t="n">
-        <v>165.6600036621094</v>
+        <v>172.5489959716797</v>
       </c>
       <c r="D202" t="n">
-        <v>155.2200012207031</v>
+        <v>162.6999969482422</v>
       </c>
       <c r="E202" t="n">
-        <v>164.1000061035156</v>
+        <v>169.8800048828125</v>
       </c>
       <c r="F202" t="n">
-        <v>8535700</v>
+        <v>10281800</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B203" t="n">
-        <v>164.1100006103516</v>
+        <v>165.5549926757812</v>
       </c>
       <c r="C203" t="n">
-        <v>172.5489959716797</v>
+        <v>170.5</v>
       </c>
       <c r="D203" t="n">
-        <v>162.6999969482422</v>
+        <v>159.1999969482422</v>
       </c>
       <c r="E203" t="n">
-        <v>169.8800048828125</v>
+        <v>166.6199951171875</v>
       </c>
       <c r="F203" t="n">
-        <v>10281800</v>
+        <v>9098200</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B204" t="n">
-        <v>165.5549926757812</v>
+        <v>166.3600006103516</v>
       </c>
       <c r="C204" t="n">
-        <v>170.5</v>
+        <v>167.7350006103516</v>
       </c>
       <c r="D204" t="n">
-        <v>159.1999969482422</v>
+        <v>156.6499938964844</v>
       </c>
       <c r="E204" t="n">
-        <v>166.6199951171875</v>
+        <v>159.9900054931641</v>
       </c>
       <c r="F204" t="n">
-        <v>9098200</v>
+        <v>9764500</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B205" t="n">
-        <v>166.3600006103516</v>
+        <v>162.8650054931641</v>
       </c>
       <c r="C205" t="n">
-        <v>167.7350006103516</v>
+        <v>177.1999969482422</v>
       </c>
       <c r="D205" t="n">
-        <v>156.6499938964844</v>
+        <v>161.3600006103516</v>
       </c>
       <c r="E205" t="n">
-        <v>159.9900054931641</v>
+        <v>173.2799987792969</v>
       </c>
       <c r="F205" t="n">
-        <v>9764500</v>
+        <v>8509300</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B206" t="n">
-        <v>162.8650054931641</v>
+        <v>169.1000061035156</v>
       </c>
       <c r="C206" t="n">
-        <v>177.1999969482422</v>
+        <v>169.2299957275391</v>
       </c>
       <c r="D206" t="n">
-        <v>161.3600006103516</v>
+        <v>162.5899963378906</v>
       </c>
       <c r="E206" t="n">
-        <v>173.2799987792969</v>
+        <v>166.4600067138672</v>
       </c>
       <c r="F206" t="n">
-        <v>8509300</v>
+        <v>8969200</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B207" t="n">
-        <v>169.1000061035156</v>
+        <v>166.1799926757812</v>
       </c>
       <c r="C207" t="n">
-        <v>169.2299957275391</v>
+        <v>181.2700042724609</v>
       </c>
       <c r="D207" t="n">
-        <v>162.5899963378906</v>
+        <v>165.9900054931641</v>
       </c>
       <c r="E207" t="n">
-        <v>166.4600067138672</v>
+        <v>181.0500030517578</v>
       </c>
       <c r="F207" t="n">
-        <v>8969200</v>
+        <v>11912800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B208" t="n">
-        <v>166.1799926757812</v>
+        <v>187</v>
       </c>
       <c r="C208" t="n">
-        <v>181.2700042724609</v>
+        <v>189.8170013427734</v>
       </c>
       <c r="D208" t="n">
-        <v>165.9900054931641</v>
+        <v>179.8000030517578</v>
       </c>
       <c r="E208" t="n">
-        <v>181.0500030517578</v>
+        <v>184.6900024414062</v>
       </c>
       <c r="F208" t="n">
-        <v>11912800</v>
+        <v>9932000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B209" t="n">
-        <v>187</v>
+        <v>185.2969970703125</v>
       </c>
       <c r="C209" t="n">
-        <v>189.8170013427734</v>
+        <v>187.6199951171875</v>
       </c>
       <c r="D209" t="n">
-        <v>179.8000030517578</v>
+        <v>182.5</v>
       </c>
       <c r="E209" t="n">
-        <v>184.6900024414062</v>
+        <v>186.9600067138672</v>
       </c>
       <c r="F209" t="n">
-        <v>9932000</v>
+        <v>5592500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B210" t="n">
-        <v>185.2969970703125</v>
+        <v>186.2649993896484</v>
       </c>
       <c r="C210" t="n">
-        <v>187.6199951171875</v>
+        <v>189.5599975585938</v>
       </c>
       <c r="D210" t="n">
-        <v>182.5</v>
+        <v>180.5</v>
       </c>
       <c r="E210" t="n">
-        <v>186.9600067138672</v>
+        <v>181.1499938964844</v>
       </c>
       <c r="F210" t="n">
-        <v>5592500</v>
+        <v>9149500</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B211" t="n">
-        <v>186.2649993896484</v>
+        <v>183.8999938964844</v>
       </c>
       <c r="C211" t="n">
-        <v>189.5599975585938</v>
+        <v>185.6000061035156</v>
       </c>
       <c r="D211" t="n">
-        <v>180.5</v>
+        <v>175.6900024414062</v>
       </c>
       <c r="E211" t="n">
-        <v>181.1499938964844</v>
+        <v>182.5700073242188</v>
       </c>
       <c r="F211" t="n">
-        <v>9149500</v>
+        <v>7566300</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B212" t="n">
-        <v>183.8999938964844</v>
+        <v>184</v>
       </c>
       <c r="C212" t="n">
-        <v>185.6000061035156</v>
+        <v>186.2100067138672</v>
       </c>
       <c r="D212" t="n">
-        <v>175.6900024414062</v>
+        <v>166.5</v>
       </c>
       <c r="E212" t="n">
-        <v>182.5700073242188</v>
+        <v>171.9199981689453</v>
       </c>
       <c r="F212" t="n">
-        <v>7566300</v>
+        <v>8095900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B213" t="n">
-        <v>184</v>
+        <v>169.2100067138672</v>
       </c>
       <c r="C213" t="n">
-        <v>186.2100067138672</v>
+        <v>170.281005859375</v>
       </c>
       <c r="D213" t="n">
-        <v>166.5</v>
+        <v>163.6799926757812</v>
       </c>
       <c r="E213" t="n">
-        <v>171.9199981689453</v>
+        <v>168.5599975585938</v>
       </c>
       <c r="F213" t="n">
-        <v>8095900</v>
+        <v>8412300</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B214" t="n">
-        <v>169.2100067138672</v>
+        <v>163.1049957275391</v>
       </c>
       <c r="C214" t="n">
-        <v>170.281005859375</v>
+        <v>171.4299926757812</v>
       </c>
       <c r="D214" t="n">
-        <v>163.6799926757812</v>
+        <v>157.1300048828125</v>
       </c>
       <c r="E214" t="n">
-        <v>168.5599975585938</v>
+        <v>168.6100006103516</v>
       </c>
       <c r="F214" t="n">
-        <v>8412300</v>
+        <v>7560400</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B215" t="n">
-        <v>163.1049957275391</v>
+        <v>168.9400024414062</v>
       </c>
       <c r="C215" t="n">
-        <v>171.4299926757812</v>
+        <v>172.6000061035156</v>
       </c>
       <c r="D215" t="n">
-        <v>157.1300048828125</v>
+        <v>168.3200073242188</v>
       </c>
       <c r="E215" t="n">
-        <v>168.6100006103516</v>
+        <v>169.3500061035156</v>
       </c>
       <c r="F215" t="n">
-        <v>7560400</v>
+        <v>6025900</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B216" t="n">
-        <v>168.9400024414062</v>
+        <v>174.4400024414062</v>
       </c>
       <c r="C216" t="n">
-        <v>172.6000061035156</v>
+        <v>177.8800048828125</v>
       </c>
       <c r="D216" t="n">
-        <v>168.3200073242188</v>
+        <v>172.1000061035156</v>
       </c>
       <c r="E216" t="n">
-        <v>169.3500061035156</v>
+        <v>174.5800018310547</v>
       </c>
       <c r="F216" t="n">
-        <v>6025900</v>
+        <v>6357800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B217" t="n">
-        <v>174.4400024414062</v>
+        <v>171.1349945068359</v>
       </c>
       <c r="C217" t="n">
-        <v>177.8800048828125</v>
+        <v>176.4100036621094</v>
       </c>
       <c r="D217" t="n">
-        <v>172.1000061035156</v>
+        <v>170</v>
       </c>
       <c r="E217" t="n">
-        <v>174.5800018310547</v>
+        <v>174.8699951171875</v>
       </c>
       <c r="F217" t="n">
-        <v>6357800</v>
+        <v>3342900</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B218" t="n">
-        <v>171.1349945068359</v>
+        <v>172.7700042724609</v>
       </c>
       <c r="C218" t="n">
-        <v>176.4100036621094</v>
+        <v>179.4799957275391</v>
       </c>
       <c r="D218" t="n">
-        <v>170</v>
+        <v>172.7700042724609</v>
       </c>
       <c r="E218" t="n">
-        <v>174.8699951171875</v>
+        <v>176.6100006103516</v>
       </c>
       <c r="F218" t="n">
-        <v>3342900</v>
+        <v>4338800</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B219" t="n">
-        <v>172.7700042724609</v>
+        <v>174</v>
       </c>
       <c r="C219" t="n">
-        <v>179.4799957275391</v>
+        <v>177.5130004882812</v>
       </c>
       <c r="D219" t="n">
-        <v>172.7700042724609</v>
+        <v>170.9089965820312</v>
       </c>
       <c r="E219" t="n">
-        <v>176.6100006103516</v>
+        <v>173.9900054931641</v>
       </c>
       <c r="F219" t="n">
-        <v>4338800</v>
+        <v>4721500</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B220" t="n">
-        <v>174</v>
+        <v>175.2100067138672</v>
       </c>
       <c r="C220" t="n">
-        <v>177.5130004882812</v>
+        <v>176.7299957275391</v>
       </c>
       <c r="D220" t="n">
-        <v>170.9089965820312</v>
+        <v>165.8999938964844</v>
       </c>
       <c r="E220" t="n">
-        <v>173.9900054931641</v>
+        <v>170.7599945068359</v>
       </c>
       <c r="F220" t="n">
-        <v>4721500</v>
+        <v>6023000</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B221" t="n">
-        <v>175.2100067138672</v>
+        <v>165.5700073242188</v>
       </c>
       <c r="C221" t="n">
-        <v>176.7299957275391</v>
+        <v>169.9700012207031</v>
       </c>
       <c r="D221" t="n">
-        <v>165.8999938964844</v>
+        <v>159.2700042724609</v>
       </c>
       <c r="E221" t="n">
-        <v>170.7599945068359</v>
+        <v>169.7100067138672</v>
       </c>
       <c r="F221" t="n">
-        <v>6023000</v>
+        <v>8561600</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B222" t="n">
-        <v>165.5700073242188</v>
+        <v>168.4499969482422</v>
       </c>
       <c r="C222" t="n">
-        <v>169.9700012207031</v>
+        <v>169.3300018310547</v>
       </c>
       <c r="D222" t="n">
-        <v>159.2700042724609</v>
+        <v>156.8399963378906</v>
       </c>
       <c r="E222" t="n">
-        <v>169.7100067138672</v>
+        <v>157.9700012207031</v>
       </c>
       <c r="F222" t="n">
-        <v>8561600</v>
+        <v>8189500</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B223" t="n">
-        <v>168.4499969482422</v>
+        <v>164.5599975585938</v>
       </c>
       <c r="C223" t="n">
-        <v>169.3300018310547</v>
+        <v>171.5099945068359</v>
       </c>
       <c r="D223" t="n">
-        <v>156.8399963378906</v>
+        <v>164.4850006103516</v>
       </c>
       <c r="E223" t="n">
-        <v>157.9700012207031</v>
+        <v>171.0200042724609</v>
       </c>
       <c r="F223" t="n">
-        <v>8189500</v>
+        <v>7284700</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B224" t="n">
-        <v>164.5599975585938</v>
+        <v>177.6000061035156</v>
       </c>
       <c r="C224" t="n">
-        <v>171.5099945068359</v>
+        <v>183.5200042724609</v>
       </c>
       <c r="D224" t="n">
-        <v>164.4850006103516</v>
+        <v>175.6999969482422</v>
       </c>
       <c r="E224" t="n">
-        <v>171.0200042724609</v>
+        <v>180.3500061035156</v>
       </c>
       <c r="F224" t="n">
-        <v>7284700</v>
+        <v>8472300</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B225" t="n">
-        <v>177.6000061035156</v>
+        <v>174.4199981689453</v>
       </c>
       <c r="C225" t="n">
-        <v>183.5200042724609</v>
+        <v>186.5700073242188</v>
       </c>
       <c r="D225" t="n">
-        <v>175.6999969482422</v>
+        <v>173.4499969482422</v>
       </c>
       <c r="E225" t="n">
-        <v>180.3500061035156</v>
+        <v>184.8899993896484</v>
       </c>
       <c r="F225" t="n">
-        <v>8472300</v>
+        <v>8335700</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B226" t="n">
-        <v>174.4199981689453</v>
+        <v>187.6999969482422</v>
       </c>
       <c r="C226" t="n">
-        <v>186.5700073242188</v>
+        <v>194.3500061035156</v>
       </c>
       <c r="D226" t="n">
-        <v>173.4499969482422</v>
+        <v>187.0110015869141</v>
       </c>
       <c r="E226" t="n">
-        <v>184.8899993896484</v>
+        <v>190.5099945068359</v>
       </c>
       <c r="F226" t="n">
-        <v>8335700</v>
+        <v>14097400</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B227" t="n">
-        <v>187.6999969482422</v>
+        <v>210.1900024414062</v>
       </c>
       <c r="C227" t="n">
-        <v>194.3500061035156</v>
+        <v>214.8899993896484</v>
       </c>
       <c r="D227" t="n">
-        <v>187.0110015869141</v>
+        <v>191.0099945068359</v>
       </c>
       <c r="E227" t="n">
-        <v>190.5099945068359</v>
+        <v>197.3099975585938</v>
       </c>
       <c r="F227" t="n">
-        <v>14097400</v>
+        <v>20227000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B228" t="n">
-        <v>210.1900024414062</v>
+        <v>192.4100036621094</v>
       </c>
       <c r="C228" t="n">
-        <v>214.8899993896484</v>
+        <v>197.1100006103516</v>
       </c>
       <c r="D228" t="n">
-        <v>191.0099945068359</v>
+        <v>189.4299926757812</v>
       </c>
       <c r="E228" t="n">
-        <v>197.3099975585938</v>
+        <v>192.3200073242188</v>
       </c>
       <c r="F228" t="n">
-        <v>20227000</v>
+        <v>7774600</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B229" t="n">
-        <v>192.4100036621094</v>
+        <v>198</v>
       </c>
       <c r="C229" t="n">
-        <v>197.1100006103516</v>
+        <v>198</v>
       </c>
       <c r="D229" t="n">
-        <v>189.4299926757812</v>
+        <v>187.5</v>
       </c>
       <c r="E229" t="n">
-        <v>192.3200073242188</v>
+        <v>188.6699981689453</v>
       </c>
       <c r="F229" t="n">
-        <v>7774600</v>
+        <v>7208500</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B230" t="n">
-        <v>198</v>
+        <v>192.4900054931641</v>
       </c>
       <c r="C230" t="n">
-        <v>198</v>
+        <v>195.6999969482422</v>
       </c>
       <c r="D230" t="n">
-        <v>187.5</v>
+        <v>187.0299987792969</v>
       </c>
       <c r="E230" t="n">
-        <v>188.6699981689453</v>
+        <v>191.5200042724609</v>
       </c>
       <c r="F230" t="n">
-        <v>7208500</v>
+        <v>5434100</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B231" t="n">
-        <v>192.4900054931641</v>
+        <v>194.5650024414062</v>
       </c>
       <c r="C231" t="n">
-        <v>195.6999969482422</v>
+        <v>198.9199981689453</v>
       </c>
       <c r="D231" t="n">
-        <v>187.0299987792969</v>
+        <v>190.4799957275391</v>
       </c>
       <c r="E231" t="n">
-        <v>191.5200042724609</v>
+        <v>197.8500061035156</v>
       </c>
       <c r="F231" t="n">
-        <v>5434100</v>
+        <v>6277300</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B232" t="n">
-        <v>194.5650024414062</v>
+        <v>205.4700012207031</v>
       </c>
       <c r="C232" t="n">
-        <v>198.9199981689453</v>
+        <v>211.4499969482422</v>
       </c>
       <c r="D232" t="n">
-        <v>190.4799957275391</v>
+        <v>203.7599945068359</v>
       </c>
       <c r="E232" t="n">
-        <v>197.8500061035156</v>
+        <v>210.5</v>
       </c>
       <c r="F232" t="n">
-        <v>6277300</v>
+        <v>10008600</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B233" t="n">
-        <v>205.4700012207031</v>
+        <v>209.7899932861328</v>
       </c>
       <c r="C233" t="n">
-        <v>211.4499969482422</v>
+        <v>210.1100006103516</v>
       </c>
       <c r="D233" t="n">
-        <v>203.7599945068359</v>
+        <v>203.5500030517578</v>
       </c>
       <c r="E233" t="n">
-        <v>210.5</v>
+        <v>203.6199951171875</v>
       </c>
       <c r="F233" t="n">
-        <v>10008600</v>
+        <v>7907800</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B234" t="n">
-        <v>209.7899932861328</v>
+        <v>205.2700042724609</v>
       </c>
       <c r="C234" t="n">
-        <v>210.1100006103516</v>
+        <v>205.2700042724609</v>
       </c>
       <c r="D234" t="n">
-        <v>203.5500030517578</v>
+        <v>198.2449951171875</v>
       </c>
       <c r="E234" t="n">
-        <v>203.6199951171875</v>
+        <v>198.8200073242188</v>
       </c>
       <c r="F234" t="n">
-        <v>7907800</v>
+        <v>4707400</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B235" t="n">
-        <v>205.2700042724609</v>
+        <v>201.1600036621094</v>
       </c>
       <c r="C235" t="n">
-        <v>205.2700042724609</v>
+        <v>202.2649993896484</v>
       </c>
       <c r="D235" t="n">
-        <v>198.2449951171875</v>
+        <v>198.3399963378906</v>
       </c>
       <c r="E235" t="n">
-        <v>198.8200073242188</v>
+        <v>201.8000030517578</v>
       </c>
       <c r="F235" t="n">
-        <v>4707400</v>
+        <v>5683900</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B236" t="n">
-        <v>201.1600036621094</v>
+        <v>196</v>
       </c>
       <c r="C236" t="n">
-        <v>202.2649993896484</v>
+        <v>197.9900054931641</v>
       </c>
       <c r="D236" t="n">
-        <v>198.3399963378906</v>
+        <v>189.6699981689453</v>
       </c>
       <c r="E236" t="n">
-        <v>201.8000030517578</v>
+        <v>193.1799926757812</v>
       </c>
       <c r="F236" t="n">
-        <v>5683900</v>
+        <v>8886900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B237" t="n">
-        <v>196</v>
+        <v>195.0399932861328</v>
       </c>
       <c r="C237" t="n">
-        <v>197.9900054931641</v>
+        <v>195.5</v>
       </c>
       <c r="D237" t="n">
-        <v>189.6699981689453</v>
+        <v>184.5099945068359</v>
       </c>
       <c r="E237" t="n">
-        <v>193.1799926757812</v>
+        <v>186.4499969482422</v>
       </c>
       <c r="F237" t="n">
-        <v>8886900</v>
+        <v>5740500</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B238" t="n">
-        <v>195.0399932861328</v>
+        <v>185.3099975585938</v>
       </c>
       <c r="C238" t="n">
-        <v>195.5</v>
+        <v>187.2799987792969</v>
       </c>
       <c r="D238" t="n">
-        <v>184.5099945068359</v>
+        <v>182.8300018310547</v>
       </c>
       <c r="E238" t="n">
-        <v>186.4499969482422</v>
+        <v>183.75</v>
       </c>
       <c r="F238" t="n">
-        <v>5740500</v>
+        <v>4207300</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B239" t="n">
-        <v>185.3099975585938</v>
+        <v>183.7700042724609</v>
       </c>
       <c r="C239" t="n">
-        <v>187.2799987792969</v>
+        <v>190.4400024414062</v>
       </c>
       <c r="D239" t="n">
-        <v>182.8300018310547</v>
+        <v>183.5899963378906</v>
       </c>
       <c r="E239" t="n">
-        <v>183.75</v>
+        <v>188.6499938964844</v>
       </c>
       <c r="F239" t="n">
-        <v>4207300</v>
+        <v>8123600</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B240" t="n">
-        <v>183.7700042724609</v>
+        <v>186</v>
       </c>
       <c r="C240" t="n">
-        <v>190.4400024414062</v>
+        <v>190.25</v>
       </c>
       <c r="D240" t="n">
-        <v>183.5899963378906</v>
+        <v>186</v>
       </c>
       <c r="E240" t="n">
-        <v>188.6499938964844</v>
+        <v>188.1499938964844</v>
       </c>
       <c r="F240" t="n">
-        <v>8123600</v>
+        <v>5306400</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B241" t="n">
-        <v>186</v>
+        <v>192.3399963378906</v>
       </c>
       <c r="C241" t="n">
-        <v>190.25</v>
+        <v>193.1499938964844</v>
       </c>
       <c r="D241" t="n">
-        <v>186</v>
+        <v>188.0599975585938</v>
       </c>
       <c r="E241" t="n">
-        <v>188.1499938964844</v>
+        <v>190.9400024414062</v>
       </c>
       <c r="F241" t="n">
-        <v>5306400</v>
+        <v>4385100</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B242" t="n">
-        <v>192.3399963378906</v>
+        <v>190.9049987792969</v>
       </c>
       <c r="C242" t="n">
-        <v>193.1499938964844</v>
+        <v>203.3600006103516</v>
       </c>
       <c r="D242" t="n">
-        <v>188.0599975585938</v>
+        <v>190.9049987792969</v>
       </c>
       <c r="E242" t="n">
-        <v>190.9400024414062</v>
+        <v>202.25</v>
       </c>
       <c r="F242" t="n">
-        <v>4385100</v>
+        <v>7664600</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B243" t="n">
-        <v>190.9049987792969</v>
+        <v>205.8999938964844</v>
       </c>
       <c r="C243" t="n">
-        <v>203.3600006103516</v>
+        <v>206.1300048828125</v>
       </c>
       <c r="D243" t="n">
-        <v>190.9049987792969</v>
+        <v>199.2149963378906</v>
       </c>
       <c r="E243" t="n">
-        <v>202.25</v>
+        <v>201.0899963378906</v>
       </c>
       <c r="F243" t="n">
-        <v>7664600</v>
+        <v>4692700</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B244" t="n">
-        <v>205.8999938964844</v>
+        <v>200</v>
       </c>
       <c r="C244" t="n">
-        <v>206.1300048828125</v>
+        <v>200.1000061035156</v>
       </c>
       <c r="D244" t="n">
-        <v>199.2149963378906</v>
+        <v>194.6100006103516</v>
       </c>
       <c r="E244" t="n">
-        <v>201.0899963378906</v>
+        <v>195.3800048828125</v>
       </c>
       <c r="F244" t="n">
-        <v>4692700</v>
+        <v>3063000</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B245" t="n">
-        <v>200</v>
+        <v>195.5</v>
       </c>
       <c r="C245" t="n">
-        <v>200.1000061035156</v>
+        <v>197.9900054931641</v>
       </c>
       <c r="D245" t="n">
-        <v>194.6100006103516</v>
+        <v>193.9100036621094</v>
       </c>
       <c r="E245" t="n">
-        <v>195.3800048828125</v>
+        <v>195.6900024414062</v>
       </c>
       <c r="F245" t="n">
-        <v>3063000</v>
+        <v>5021700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B246" t="n">
-        <v>195.5</v>
+        <v>195.7700042724609</v>
       </c>
       <c r="C246" t="n">
-        <v>197.9900054931641</v>
+        <v>196.5</v>
       </c>
       <c r="D246" t="n">
-        <v>193.9100036621094</v>
+        <v>188.5599975585938</v>
       </c>
       <c r="E246" t="n">
-        <v>195.6900024414062</v>
+        <v>189.2599945068359</v>
       </c>
       <c r="F246" t="n">
-        <v>5021700</v>
+        <v>4369200</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B247" t="n">
-        <v>195.7700042724609</v>
+        <v>188</v>
       </c>
       <c r="C247" t="n">
-        <v>196.5</v>
+        <v>189.8899993896484</v>
       </c>
       <c r="D247" t="n">
-        <v>188.5599975585938</v>
+        <v>184.0800018310547</v>
       </c>
       <c r="E247" t="n">
-        <v>189.2599945068359</v>
+        <v>186.1000061035156</v>
       </c>
       <c r="F247" t="n">
-        <v>4369200</v>
+        <v>4363800</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B248" t="n">
-        <v>188</v>
+        <v>185.25</v>
       </c>
       <c r="C248" t="n">
-        <v>189.8899993896484</v>
+        <v>192</v>
       </c>
       <c r="D248" t="n">
-        <v>184.0800018310547</v>
+        <v>181.2700042724609</v>
       </c>
       <c r="E248" t="n">
-        <v>186.1000061035156</v>
+        <v>191.4400024414062</v>
       </c>
       <c r="F248" t="n">
-        <v>4363800</v>
+        <v>4108500</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B249" t="n">
-        <v>185.25</v>
+        <v>192.8200073242188</v>
       </c>
       <c r="C249" t="n">
-        <v>192</v>
+        <v>197.1000061035156</v>
       </c>
       <c r="D249" t="n">
-        <v>181.2700042724609</v>
+        <v>190.5599975585938</v>
       </c>
       <c r="E249" t="n">
-        <v>191.4400024414062</v>
+        <v>193.7799987792969</v>
       </c>
       <c r="F249" t="n">
-        <v>4108500</v>
+        <v>4204100</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B250" t="n">
-        <v>192.8200073242188</v>
+        <v>196.8200073242188</v>
       </c>
       <c r="C250" t="n">
-        <v>197.1000061035156</v>
+        <v>200.6750030517578</v>
       </c>
       <c r="D250" t="n">
-        <v>190.5599975585938</v>
+        <v>194.7200012207031</v>
       </c>
       <c r="E250" t="n">
-        <v>193.7799987792969</v>
+        <v>194.9600067138672</v>
       </c>
       <c r="F250" t="n">
-        <v>4204100</v>
+        <v>4741600</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B251" t="n">
-        <v>196.8200073242188</v>
+        <v>194.8549957275391</v>
       </c>
       <c r="C251" t="n">
-        <v>200.6750030517578</v>
+        <v>196.9600067138672</v>
       </c>
       <c r="D251" t="n">
-        <v>194.7200012207031</v>
+        <v>192.0500030517578</v>
       </c>
       <c r="E251" t="n">
-        <v>194.9600067138672</v>
+        <v>192.9299926757812</v>
       </c>
       <c r="F251" t="n">
-        <v>4741600</v>
+        <v>3673900</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B252" t="n">
-        <v>194.8549957275391</v>
+        <v>189.3500061035156</v>
       </c>
       <c r="C252" t="n">
-        <v>196.9600067138672</v>
+        <v>193.0399932861328</v>
       </c>
       <c r="D252" t="n">
-        <v>192.0500030517578</v>
+        <v>187.8930053710938</v>
       </c>
       <c r="E252" t="n">
-        <v>192.9299926757812</v>
+        <v>188.9900054931641</v>
       </c>
       <c r="F252" t="n">
-        <v>3673900</v>
+        <v>2810900</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10518,37 +10518,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>188.99</v>
+      </c>
+      <c r="D2" t="n">
         <v>192.93</v>
       </c>
-      <c r="D2" t="n">
-        <v>194.96</v>
-      </c>
       <c r="E2" t="n">
-        <v>194.855</v>
+        <v>189.35</v>
       </c>
       <c r="F2" t="n">
-        <v>196.96</v>
+        <v>193.04</v>
       </c>
       <c r="G2" t="n">
-        <v>192.06</v>
+        <v>187.8926</v>
       </c>
       <c r="H2" t="n">
-        <v>3673079</v>
+        <v>2808298</v>
       </c>
       <c r="I2" t="n">
-        <v>7393803</v>
+        <v>7366708</v>
       </c>
       <c r="J2" t="n">
-        <v>243328073728</v>
+        <v>238358855680</v>
       </c>
       <c r="K2" t="n">
-        <v>61.638973</v>
+        <v>60.96452</v>
       </c>
       <c r="L2" t="n">
-        <v>37.387505</v>
+        <v>36.62398</v>
       </c>
       <c r="M2" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
         <v>214.89</v>
@@ -10588,7 +10588,7 @@
         <v>11.733</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.443365</v>
+        <v>16.107561</v>
       </c>
       <c r="Z2" t="n">
         <v>0.357</v>
@@ -10600,7 +10600,7 @@
         <v>10540800000</v>
       </c>
       <c r="AC2" t="n">
-        <v>229984763904</v>
+        <v>225015545856</v>
       </c>
       <c r="AD2" t="n">
         <v>4639600128</v>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-10 19:00:24</t>
+          <t>2026-09-11 19:03:59</t>
         </is>
       </c>
     </row>

--- a/data/ANET_data.xlsx
+++ b/data/ANET_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B2" t="n">
-        <v>151.9900054931641</v>
+        <v>149.1799926757812</v>
       </c>
       <c r="C2" t="n">
-        <v>156.3200073242188</v>
+        <v>149.4700012207031</v>
       </c>
       <c r="D2" t="n">
-        <v>150.3600006103516</v>
+        <v>139.0200042724609</v>
       </c>
       <c r="E2" t="n">
-        <v>153.0399932861328</v>
+        <v>139.3899993896484</v>
       </c>
       <c r="F2" t="n">
-        <v>13666200</v>
+        <v>17920400</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B3" t="n">
-        <v>149.1799926757812</v>
+        <v>139.6000061035156</v>
       </c>
       <c r="C3" t="n">
-        <v>149.4700012207031</v>
+        <v>146.8999938964844</v>
       </c>
       <c r="D3" t="n">
-        <v>139.0200042724609</v>
+        <v>139.1699981689453</v>
       </c>
       <c r="E3" t="n">
-        <v>139.3899993896484</v>
+        <v>145.4299926757812</v>
       </c>
       <c r="F3" t="n">
-        <v>17920400</v>
+        <v>12140800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B4" t="n">
-        <v>139.6000061035156</v>
+        <v>145.2599945068359</v>
       </c>
       <c r="C4" t="n">
-        <v>146.8999938964844</v>
+        <v>147.3699951171875</v>
       </c>
       <c r="D4" t="n">
-        <v>139.1699981689453</v>
+        <v>141</v>
       </c>
       <c r="E4" t="n">
-        <v>145.4299926757812</v>
+        <v>142.1600036621094</v>
       </c>
       <c r="F4" t="n">
-        <v>12140800</v>
+        <v>9382400</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B5" t="n">
-        <v>145.2599945068359</v>
+        <v>142.6349945068359</v>
       </c>
       <c r="C5" t="n">
-        <v>147.3699951171875</v>
+        <v>143.4250030517578</v>
       </c>
       <c r="D5" t="n">
-        <v>141</v>
+        <v>138.5</v>
       </c>
       <c r="E5" t="n">
-        <v>142.1600036621094</v>
+        <v>142.8399963378906</v>
       </c>
       <c r="F5" t="n">
-        <v>9382400</v>
+        <v>8295400</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B6" t="n">
-        <v>142.6349945068359</v>
+        <v>144</v>
       </c>
       <c r="C6" t="n">
+        <v>146.7200012207031</v>
+      </c>
+      <c r="D6" t="n">
         <v>143.4250030517578</v>
       </c>
-      <c r="D6" t="n">
-        <v>138.5</v>
-      </c>
       <c r="E6" t="n">
-        <v>142.8399963378906</v>
+        <v>146.6600036621094</v>
       </c>
       <c r="F6" t="n">
-        <v>8295400</v>
+        <v>6939000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>148.8999938964844</v>
       </c>
       <c r="C7" t="n">
-        <v>146.7200012207031</v>
+        <v>150.25</v>
       </c>
       <c r="D7" t="n">
-        <v>143.4250030517578</v>
+        <v>146.6699981689453</v>
       </c>
       <c r="E7" t="n">
-        <v>146.6600036621094</v>
+        <v>149.6100006103516</v>
       </c>
       <c r="F7" t="n">
-        <v>6939000</v>
+        <v>17810900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B8" t="n">
-        <v>148.8999938964844</v>
+        <v>148.7799987792969</v>
       </c>
       <c r="C8" t="n">
-        <v>150.25</v>
+        <v>149.7100067138672</v>
       </c>
       <c r="D8" t="n">
-        <v>146.6699981689453</v>
+        <v>145.0549926757812</v>
       </c>
       <c r="E8" t="n">
-        <v>149.6100006103516</v>
+        <v>145.3999938964844</v>
       </c>
       <c r="F8" t="n">
-        <v>17810900</v>
+        <v>8675200</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B9" t="n">
-        <v>148.7799987792969</v>
+        <v>144.8600006103516</v>
       </c>
       <c r="C9" t="n">
-        <v>149.7100067138672</v>
+        <v>147.4600067138672</v>
       </c>
       <c r="D9" t="n">
-        <v>145.0549926757812</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="E9" t="n">
-        <v>145.3999938964844</v>
+        <v>144.0899963378906</v>
       </c>
       <c r="F9" t="n">
-        <v>8675200</v>
+        <v>8215500</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B10" t="n">
-        <v>144.8600006103516</v>
+        <v>144.6799926757812</v>
       </c>
       <c r="C10" t="n">
-        <v>147.4600067138672</v>
+        <v>144.6799926757812</v>
       </c>
       <c r="D10" t="n">
-        <v>143.0200042724609</v>
+        <v>141.2899932861328</v>
       </c>
       <c r="E10" t="n">
-        <v>144.0899963378906</v>
+        <v>142.6399993896484</v>
       </c>
       <c r="F10" t="n">
-        <v>8215500</v>
+        <v>7035700</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B11" t="n">
-        <v>144.6799926757812</v>
+        <v>141.6900024414062</v>
       </c>
       <c r="C11" t="n">
-        <v>144.6799926757812</v>
+        <v>143.2400054931641</v>
       </c>
       <c r="D11" t="n">
-        <v>141.2899932861328</v>
+        <v>139.2299957275391</v>
       </c>
       <c r="E11" t="n">
-        <v>142.6399993896484</v>
+        <v>143.0599975585938</v>
       </c>
       <c r="F11" t="n">
-        <v>7035700</v>
+        <v>6325300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B12" t="n">
-        <v>141.6900024414062</v>
+        <v>144.0899963378906</v>
       </c>
       <c r="C12" t="n">
-        <v>143.2400054931641</v>
+        <v>144.3999938964844</v>
       </c>
       <c r="D12" t="n">
-        <v>139.2299957275391</v>
+        <v>140.7599945068359</v>
       </c>
       <c r="E12" t="n">
-        <v>143.0599975585938</v>
+        <v>142.5</v>
       </c>
       <c r="F12" t="n">
-        <v>6325300</v>
+        <v>4867700</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B13" t="n">
-        <v>144.0899963378906</v>
+        <v>144.9199981689453</v>
       </c>
       <c r="C13" t="n">
-        <v>144.3999938964844</v>
+        <v>147.8000030517578</v>
       </c>
       <c r="D13" t="n">
-        <v>140.7599945068359</v>
+        <v>142.6199951171875</v>
       </c>
       <c r="E13" t="n">
-        <v>142.5</v>
+        <v>143.3699951171875</v>
       </c>
       <c r="F13" t="n">
-        <v>4867700</v>
+        <v>6183600</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B14" t="n">
-        <v>144.9199981689453</v>
+        <v>143.4299926757812</v>
       </c>
       <c r="C14" t="n">
-        <v>147.8000030517578</v>
+        <v>145.8399963378906</v>
       </c>
       <c r="D14" t="n">
-        <v>142.6199951171875</v>
+        <v>143.1600036621094</v>
       </c>
       <c r="E14" t="n">
-        <v>143.3699951171875</v>
+        <v>145.7100067138672</v>
       </c>
       <c r="F14" t="n">
-        <v>6183600</v>
+        <v>5828900</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B15" t="n">
-        <v>143.4299926757812</v>
+        <v>144.6499938964844</v>
       </c>
       <c r="C15" t="n">
-        <v>145.8399963378906</v>
+        <v>149.9499969482422</v>
       </c>
       <c r="D15" t="n">
-        <v>143.1600036621094</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="E15" t="n">
-        <v>145.7100067138672</v>
+        <v>149.2700042724609</v>
       </c>
       <c r="F15" t="n">
-        <v>5828900</v>
+        <v>7820700</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B16" t="n">
-        <v>144.6499938964844</v>
+        <v>150</v>
       </c>
       <c r="C16" t="n">
-        <v>149.9499969482422</v>
+        <v>150.5399932861328</v>
       </c>
       <c r="D16" t="n">
-        <v>143.0200042724609</v>
+        <v>141.25</v>
       </c>
       <c r="E16" t="n">
-        <v>149.2700042724609</v>
+        <v>144.4600067138672</v>
       </c>
       <c r="F16" t="n">
-        <v>7820700</v>
+        <v>9473800</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B17" t="n">
-        <v>150</v>
+        <v>146.0099945068359</v>
       </c>
       <c r="C17" t="n">
-        <v>150.5399932861328</v>
+        <v>149.0899963378906</v>
       </c>
       <c r="D17" t="n">
-        <v>141.25</v>
+        <v>144.1000061035156</v>
       </c>
       <c r="E17" t="n">
-        <v>144.4600067138672</v>
+        <v>145.5</v>
       </c>
       <c r="F17" t="n">
-        <v>9473800</v>
+        <v>7178600</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B18" t="n">
-        <v>146.0099945068359</v>
+        <v>151.6000061035156</v>
       </c>
       <c r="C18" t="n">
-        <v>149.0899963378906</v>
+        <v>153.7299957275391</v>
       </c>
       <c r="D18" t="n">
-        <v>144.1000061035156</v>
+        <v>149.5</v>
       </c>
       <c r="E18" t="n">
-        <v>145.5</v>
+        <v>149.5</v>
       </c>
       <c r="F18" t="n">
-        <v>7178600</v>
+        <v>7277600</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B19" t="n">
-        <v>151.6000061035156</v>
+        <v>150.4799957275391</v>
       </c>
       <c r="C19" t="n">
-        <v>153.7299957275391</v>
+        <v>151.5500030517578</v>
       </c>
       <c r="D19" t="n">
-        <v>149.5</v>
+        <v>143.2799987792969</v>
       </c>
       <c r="E19" t="n">
-        <v>149.5</v>
+        <v>145.2899932861328</v>
       </c>
       <c r="F19" t="n">
-        <v>7277600</v>
+        <v>7348700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B20" t="n">
-        <v>150.4799957275391</v>
+        <v>147.9900054931641</v>
       </c>
       <c r="C20" t="n">
-        <v>151.5500030517578</v>
+        <v>158.5099945068359</v>
       </c>
       <c r="D20" t="n">
-        <v>143.2799987792969</v>
+        <v>147.4049987792969</v>
       </c>
       <c r="E20" t="n">
-        <v>145.2899932861328</v>
+        <v>157.3600006103516</v>
       </c>
       <c r="F20" t="n">
-        <v>7348700</v>
+        <v>11283400</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B21" t="n">
-        <v>147.9900054931641</v>
+        <v>157</v>
       </c>
       <c r="C21" t="n">
-        <v>158.5099945068359</v>
+        <v>159.8000030517578</v>
       </c>
       <c r="D21" t="n">
-        <v>147.4049987792969</v>
+        <v>154.6009979248047</v>
       </c>
       <c r="E21" t="n">
-        <v>157.3600006103516</v>
+        <v>158.2299957275391</v>
       </c>
       <c r="F21" t="n">
-        <v>11283400</v>
+        <v>8459900</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B22" t="n">
-        <v>157</v>
+        <v>159.8600006103516</v>
       </c>
       <c r="C22" t="n">
-        <v>159.8000030517578</v>
+        <v>162.6799926757812</v>
       </c>
       <c r="D22" t="n">
-        <v>154.6009979248047</v>
+        <v>153.7400054931641</v>
       </c>
       <c r="E22" t="n">
-        <v>158.2299957275391</v>
+        <v>154.1000061035156</v>
       </c>
       <c r="F22" t="n">
-        <v>8459900</v>
+        <v>10459300</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B23" t="n">
-        <v>159.8600006103516</v>
+        <v>160.7599945068359</v>
       </c>
       <c r="C23" t="n">
-        <v>162.6799926757812</v>
+        <v>162</v>
       </c>
       <c r="D23" t="n">
-        <v>153.7400054931641</v>
+        <v>145.0899963378906</v>
       </c>
       <c r="E23" t="n">
-        <v>154.1000061035156</v>
+        <v>147.4499969482422</v>
       </c>
       <c r="F23" t="n">
-        <v>10459300</v>
+        <v>14233900</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B24" t="n">
-        <v>160.7599945068359</v>
+        <v>142.9850006103516</v>
       </c>
       <c r="C24" t="n">
-        <v>162</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="D24" t="n">
-        <v>145.0899963378906</v>
+        <v>136.7899932861328</v>
       </c>
       <c r="E24" t="n">
-        <v>147.4499969482422</v>
+        <v>138.7899932861328</v>
       </c>
       <c r="F24" t="n">
-        <v>14233900</v>
+        <v>13672400</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B25" t="n">
-        <v>142.9850006103516</v>
+        <v>140.4199981689453</v>
       </c>
       <c r="C25" t="n">
-        <v>143.0200042724609</v>
+        <v>145.3899993896484</v>
       </c>
       <c r="D25" t="n">
-        <v>136.7899932861328</v>
+        <v>140.1100006103516</v>
       </c>
       <c r="E25" t="n">
-        <v>138.7899932861328</v>
+        <v>143.3800048828125</v>
       </c>
       <c r="F25" t="n">
-        <v>13672400</v>
+        <v>8687000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B26" t="n">
-        <v>140.4199981689453</v>
+        <v>144.8999938964844</v>
       </c>
       <c r="C26" t="n">
-        <v>145.3899993896484</v>
+        <v>147.6499938964844</v>
       </c>
       <c r="D26" t="n">
-        <v>140.1100006103516</v>
+        <v>143.8600006103516</v>
       </c>
       <c r="E26" t="n">
-        <v>143.3800048828125</v>
+        <v>146.0099945068359</v>
       </c>
       <c r="F26" t="n">
-        <v>8687000</v>
+        <v>6909500</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B27" t="n">
-        <v>144.8999938964844</v>
+        <v>143.0099945068359</v>
       </c>
       <c r="C27" t="n">
-        <v>147.6499938964844</v>
+        <v>144.5</v>
       </c>
       <c r="D27" t="n">
-        <v>143.8600006103516</v>
+        <v>139.2400054931641</v>
       </c>
       <c r="E27" t="n">
-        <v>146.0099945068359</v>
+        <v>143.1000061035156</v>
       </c>
       <c r="F27" t="n">
-        <v>6909500</v>
+        <v>6533900</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B28" t="n">
-        <v>143.0099945068359</v>
+        <v>146.3249969482422</v>
       </c>
       <c r="C28" t="n">
-        <v>144.5</v>
+        <v>149.8800048828125</v>
       </c>
       <c r="D28" t="n">
-        <v>139.2400054931641</v>
+        <v>146.1900024414062</v>
       </c>
       <c r="E28" t="n">
-        <v>143.1000061035156</v>
+        <v>146.4799957275391</v>
       </c>
       <c r="F28" t="n">
-        <v>6533900</v>
+        <v>6120700</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B29" t="n">
-        <v>146.3249969482422</v>
+        <v>145.4499969482422</v>
       </c>
       <c r="C29" t="n">
-        <v>149.8800048828125</v>
+        <v>147.6100006103516</v>
       </c>
       <c r="D29" t="n">
-        <v>146.1900024414062</v>
+        <v>144.1399993896484</v>
       </c>
       <c r="E29" t="n">
-        <v>146.4799957275391</v>
+        <v>145.9400024414062</v>
       </c>
       <c r="F29" t="n">
-        <v>6120700</v>
+        <v>3648900</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B30" t="n">
-        <v>145.4499969482422</v>
+        <v>145.8650054931641</v>
       </c>
       <c r="C30" t="n">
-        <v>147.6100006103516</v>
+        <v>147.4900054931641</v>
       </c>
       <c r="D30" t="n">
-        <v>144.1399993896484</v>
+        <v>141.6799926757812</v>
       </c>
       <c r="E30" t="n">
-        <v>145.9400024414062</v>
+        <v>146.5899963378906</v>
       </c>
       <c r="F30" t="n">
-        <v>3648900</v>
+        <v>7349200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B31" t="n">
-        <v>145.8650054931641</v>
+        <v>146.7799987792969</v>
       </c>
       <c r="C31" t="n">
-        <v>147.4900054931641</v>
+        <v>153.9499969482422</v>
       </c>
       <c r="D31" t="n">
-        <v>141.6799926757812</v>
+        <v>146.6399993896484</v>
       </c>
       <c r="E31" t="n">
-        <v>146.5899963378906</v>
+        <v>152.7599945068359</v>
       </c>
       <c r="F31" t="n">
-        <v>7349200</v>
+        <v>7327400</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B32" t="n">
-        <v>146.7799987792969</v>
+        <v>155</v>
       </c>
       <c r="C32" t="n">
-        <v>153.9499969482422</v>
+        <v>155.8300018310547</v>
       </c>
       <c r="D32" t="n">
-        <v>146.6399993896484</v>
+        <v>152.2969970703125</v>
       </c>
       <c r="E32" t="n">
-        <v>152.7599945068359</v>
+        <v>153.8200073242188</v>
       </c>
       <c r="F32" t="n">
-        <v>7327400</v>
+        <v>5170800</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B33" t="n">
-        <v>155</v>
+        <v>157.4100036621094</v>
       </c>
       <c r="C33" t="n">
-        <v>155.8300018310547</v>
+        <v>157.6999969482422</v>
       </c>
       <c r="D33" t="n">
-        <v>152.2969970703125</v>
+        <v>155.0099945068359</v>
       </c>
       <c r="E33" t="n">
-        <v>153.8200073242188</v>
+        <v>156.8099975585938</v>
       </c>
       <c r="F33" t="n">
-        <v>5170800</v>
+        <v>5509100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B34" t="n">
-        <v>157.4100036621094</v>
+        <v>156.6199951171875</v>
       </c>
       <c r="C34" t="n">
-        <v>157.6999969482422</v>
+        <v>158.6600036621094</v>
       </c>
       <c r="D34" t="n">
-        <v>155.0099945068359</v>
+        <v>152.3300018310547</v>
       </c>
       <c r="E34" t="n">
-        <v>156.8099975585938</v>
+        <v>156.7700042724609</v>
       </c>
       <c r="F34" t="n">
-        <v>5509100</v>
+        <v>5037400</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B35" t="n">
-        <v>156.6199951171875</v>
+        <v>157.2100067138672</v>
       </c>
       <c r="C35" t="n">
-        <v>158.6600036621094</v>
+        <v>162.3999938964844</v>
       </c>
       <c r="D35" t="n">
-        <v>152.3300018310547</v>
+        <v>156.7799987792969</v>
       </c>
       <c r="E35" t="n">
-        <v>156.7700042724609</v>
+        <v>162.0299987792969</v>
       </c>
       <c r="F35" t="n">
-        <v>5037400</v>
+        <v>6901400</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B36" t="n">
-        <v>157.2100067138672</v>
+        <v>162.4700012207031</v>
       </c>
       <c r="C36" t="n">
-        <v>162.3999938964844</v>
+        <v>164.9400024414062</v>
       </c>
       <c r="D36" t="n">
-        <v>156.7799987792969</v>
+        <v>158.3999938964844</v>
       </c>
       <c r="E36" t="n">
-        <v>162.0299987792969</v>
+        <v>158.4400024414062</v>
       </c>
       <c r="F36" t="n">
-        <v>6901400</v>
+        <v>6911300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B37" t="n">
-        <v>162.4700012207031</v>
+        <v>161.0899963378906</v>
       </c>
       <c r="C37" t="n">
-        <v>164.9400024414062</v>
+        <v>162.1150054931641</v>
       </c>
       <c r="D37" t="n">
-        <v>158.3999938964844</v>
+        <v>155.7400054931641</v>
       </c>
       <c r="E37" t="n">
-        <v>158.4400024414062</v>
+        <v>157.6900024414062</v>
       </c>
       <c r="F37" t="n">
-        <v>6911300</v>
+        <v>6209300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B38" t="n">
-        <v>161.0899963378906</v>
+        <v>160.5</v>
       </c>
       <c r="C38" t="n">
-        <v>162.1150054931641</v>
+        <v>160.8999938964844</v>
       </c>
       <c r="D38" t="n">
-        <v>155.7400054931641</v>
+        <v>155.4199981689453</v>
       </c>
       <c r="E38" t="n">
-        <v>157.6900024414062</v>
+        <v>157.5899963378906</v>
       </c>
       <c r="F38" t="n">
-        <v>6209300</v>
+        <v>6422600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B39" t="n">
-        <v>160.5</v>
+        <v>152.8600006103516</v>
       </c>
       <c r="C39" t="n">
-        <v>160.8999938964844</v>
+        <v>157.0249938964844</v>
       </c>
       <c r="D39" t="n">
-        <v>155.4199981689453</v>
+        <v>150.9900054931641</v>
       </c>
       <c r="E39" t="n">
-        <v>157.5899963378906</v>
+        <v>153.5500030517578</v>
       </c>
       <c r="F39" t="n">
-        <v>6422600</v>
+        <v>9026400</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B40" t="n">
-        <v>152.8600006103516</v>
+        <v>142.6699981689453</v>
       </c>
       <c r="C40" t="n">
-        <v>157.0249938964844</v>
+        <v>148</v>
       </c>
       <c r="D40" t="n">
-        <v>150.9900054931641</v>
+        <v>140.0200042724609</v>
       </c>
       <c r="E40" t="n">
-        <v>153.5500030517578</v>
+        <v>140.4199981689453</v>
       </c>
       <c r="F40" t="n">
-        <v>9026400</v>
+        <v>15901000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B41" t="n">
-        <v>142.6699981689453</v>
+        <v>140.6499938964844</v>
       </c>
       <c r="C41" t="n">
-        <v>148</v>
+        <v>141.9900054931641</v>
       </c>
       <c r="D41" t="n">
-        <v>140.0200042724609</v>
+        <v>132.5899963378906</v>
       </c>
       <c r="E41" t="n">
-        <v>140.4199981689453</v>
+        <v>134.0200042724609</v>
       </c>
       <c r="F41" t="n">
-        <v>15901000</v>
+        <v>13296100</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B42" t="n">
-        <v>140.6499938964844</v>
+        <v>134.4100036621094</v>
       </c>
       <c r="C42" t="n">
-        <v>141.9900054931641</v>
+        <v>136.6100006103516</v>
       </c>
       <c r="D42" t="n">
-        <v>132.5899963378906</v>
+        <v>132.4499969482422</v>
       </c>
       <c r="E42" t="n">
-        <v>134.0200042724609</v>
+        <v>134.6499938964844</v>
       </c>
       <c r="F42" t="n">
-        <v>13296100</v>
+        <v>11341600</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B43" t="n">
-        <v>134.4100036621094</v>
+        <v>137.5</v>
       </c>
       <c r="C43" t="n">
-        <v>136.6100006103516</v>
+        <v>138.9799957275391</v>
       </c>
       <c r="D43" t="n">
-        <v>132.4499969482422</v>
+        <v>134.5870056152344</v>
       </c>
       <c r="E43" t="n">
-        <v>134.6499938964844</v>
+        <v>137.2599945068359</v>
       </c>
       <c r="F43" t="n">
-        <v>11341600</v>
+        <v>6974300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B44" t="n">
-        <v>137.5</v>
+        <v>134.8699951171875</v>
       </c>
       <c r="C44" t="n">
-        <v>138.9799957275391</v>
+        <v>136.375</v>
       </c>
       <c r="D44" t="n">
-        <v>134.5870056152344</v>
+        <v>132.4100036621094</v>
       </c>
       <c r="E44" t="n">
-        <v>137.2599945068359</v>
+        <v>134.9299926757812</v>
       </c>
       <c r="F44" t="n">
-        <v>6974300</v>
+        <v>7189300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B45" t="n">
-        <v>134.8699951171875</v>
+        <v>136.2200012207031</v>
       </c>
       <c r="C45" t="n">
-        <v>136.375</v>
+        <v>136.5980072021484</v>
       </c>
       <c r="D45" t="n">
-        <v>132.4100036621094</v>
+        <v>133.7779998779297</v>
       </c>
       <c r="E45" t="n">
-        <v>134.9299926757812</v>
+        <v>134.9799957275391</v>
       </c>
       <c r="F45" t="n">
-        <v>7189300</v>
+        <v>6471400</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B46" t="n">
-        <v>136.2200012207031</v>
+        <v>134.4299926757812</v>
       </c>
       <c r="C46" t="n">
-        <v>136.5980072021484</v>
+        <v>135.5800018310547</v>
       </c>
       <c r="D46" t="n">
-        <v>133.7779998779297</v>
+        <v>129.1699981689453</v>
       </c>
       <c r="E46" t="n">
-        <v>134.9799957275391</v>
+        <v>130.3000030517578</v>
       </c>
       <c r="F46" t="n">
-        <v>6471400</v>
+        <v>10471400</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B47" t="n">
-        <v>134.4299926757812</v>
+        <v>127.0599975585938</v>
       </c>
       <c r="C47" t="n">
-        <v>135.5800018310547</v>
+        <v>135.3699951171875</v>
       </c>
       <c r="D47" t="n">
-        <v>129.1699981689453</v>
+        <v>125.3600006103516</v>
       </c>
       <c r="E47" t="n">
-        <v>130.3000030517578</v>
+        <v>131.3699951171875</v>
       </c>
       <c r="F47" t="n">
-        <v>10471400</v>
+        <v>10672500</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B48" t="n">
-        <v>127.0599975585938</v>
+        <v>131.3500061035156</v>
       </c>
       <c r="C48" t="n">
-        <v>135.3699951171875</v>
+        <v>133.3200073242188</v>
       </c>
       <c r="D48" t="n">
-        <v>125.3600006103516</v>
+        <v>125.4000015258789</v>
       </c>
       <c r="E48" t="n">
-        <v>131.3699951171875</v>
+        <v>127.2600021362305</v>
       </c>
       <c r="F48" t="n">
-        <v>10672500</v>
+        <v>12455900</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B49" t="n">
-        <v>131.3500061035156</v>
+        <v>125.75</v>
       </c>
       <c r="C49" t="n">
-        <v>133.3200073242188</v>
+        <v>127.5500030517578</v>
       </c>
       <c r="D49" t="n">
-        <v>125.4000015258789</v>
+        <v>122.0800018310547</v>
       </c>
       <c r="E49" t="n">
-        <v>127.2600021362305</v>
+        <v>123.4499969482422</v>
       </c>
       <c r="F49" t="n">
-        <v>12455900</v>
+        <v>12561100</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B50" t="n">
-        <v>125.75</v>
+        <v>123.0500030517578</v>
       </c>
       <c r="C50" t="n">
-        <v>127.5500030517578</v>
+        <v>126.5699996948242</v>
       </c>
       <c r="D50" t="n">
-        <v>122.0800018310547</v>
+        <v>122.9000015258789</v>
       </c>
       <c r="E50" t="n">
-        <v>123.4499969482422</v>
+        <v>124.8099975585938</v>
       </c>
       <c r="F50" t="n">
-        <v>12561100</v>
+        <v>7703500</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B51" t="n">
-        <v>123.0500030517578</v>
+        <v>129.8899993896484</v>
       </c>
       <c r="C51" t="n">
-        <v>126.5699996948242</v>
+        <v>131.7899932861328</v>
       </c>
       <c r="D51" t="n">
-        <v>122.9000015258789</v>
+        <v>118.9000015258789</v>
       </c>
       <c r="E51" t="n">
-        <v>124.8099975585938</v>
+        <v>119.5899963378906</v>
       </c>
       <c r="F51" t="n">
-        <v>7703500</v>
+        <v>12642000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B52" t="n">
-        <v>129.8899993896484</v>
+        <v>118.4199981689453</v>
       </c>
       <c r="C52" t="n">
-        <v>131.7899932861328</v>
+        <v>120.004997253418</v>
       </c>
       <c r="D52" t="n">
-        <v>118.9000015258789</v>
+        <v>114.5199966430664</v>
       </c>
       <c r="E52" t="n">
-        <v>119.5899963378906</v>
+        <v>117.4300003051758</v>
       </c>
       <c r="F52" t="n">
-        <v>12642000</v>
+        <v>16704100</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B53" t="n">
-        <v>118.4199981689453</v>
+        <v>118.9150009155273</v>
       </c>
       <c r="C53" t="n">
-        <v>120.004997253418</v>
+        <v>122.4199981689453</v>
       </c>
       <c r="D53" t="n">
-        <v>114.5199966430664</v>
+        <v>118.1999969482422</v>
       </c>
       <c r="E53" t="n">
-        <v>117.4300003051758</v>
+        <v>122.1699981689453</v>
       </c>
       <c r="F53" t="n">
-        <v>16704100</v>
+        <v>12758600</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B54" t="n">
-        <v>118.9150009155273</v>
+        <v>122.4000015258789</v>
       </c>
       <c r="C54" t="n">
-        <v>122.4199981689453</v>
+        <v>125.9100036621094</v>
       </c>
       <c r="D54" t="n">
-        <v>118.1999969482422</v>
+        <v>122.3199996948242</v>
       </c>
       <c r="E54" t="n">
-        <v>122.1699981689453</v>
+        <v>125.0400009155273</v>
       </c>
       <c r="F54" t="n">
-        <v>12758600</v>
+        <v>7143400</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B55" t="n">
-        <v>122.4000015258789</v>
+        <v>127.4749984741211</v>
       </c>
       <c r="C55" t="n">
-        <v>125.9100036621094</v>
+        <v>128.4750061035156</v>
       </c>
       <c r="D55" t="n">
-        <v>122.3199996948242</v>
+        <v>125.2460021972656</v>
       </c>
       <c r="E55" t="n">
-        <v>125.0400009155273</v>
+        <v>127.6500015258789</v>
       </c>
       <c r="F55" t="n">
-        <v>7143400</v>
+        <v>5995000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B56" t="n">
-        <v>127.4749984741211</v>
+        <v>130</v>
       </c>
       <c r="C56" t="n">
-        <v>128.4750061035156</v>
+        <v>131.4049987792969</v>
       </c>
       <c r="D56" t="n">
-        <v>125.2460021972656</v>
+        <v>128.1150054931641</v>
       </c>
       <c r="E56" t="n">
-        <v>127.6500015258789</v>
+        <v>130.6799926757812</v>
       </c>
       <c r="F56" t="n">
-        <v>5995000</v>
+        <v>3895000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B57" t="n">
-        <v>130</v>
+        <v>128.9799957275391</v>
       </c>
       <c r="C57" t="n">
-        <v>131.4049987792969</v>
+        <v>129.5039978027344</v>
       </c>
       <c r="D57" t="n">
-        <v>128.1150054931641</v>
+        <v>126.1399993896484</v>
       </c>
       <c r="E57" t="n">
-        <v>130.6799926757812</v>
+        <v>128.1100006103516</v>
       </c>
       <c r="F57" t="n">
-        <v>3895000</v>
+        <v>4690600</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B58" t="n">
-        <v>128.9799957275391</v>
+        <v>129.75</v>
       </c>
       <c r="C58" t="n">
-        <v>129.5039978027344</v>
+        <v>131.0399932861328</v>
       </c>
       <c r="D58" t="n">
-        <v>126.1399993896484</v>
+        <v>126.2699966430664</v>
       </c>
       <c r="E58" t="n">
-        <v>128.1100006103516</v>
+        <v>127.2200012207031</v>
       </c>
       <c r="F58" t="n">
-        <v>4690600</v>
+        <v>5619000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B59" t="n">
-        <v>129.75</v>
+        <v>126.1600036621094</v>
       </c>
       <c r="C59" t="n">
-        <v>131.0399932861328</v>
+        <v>128.5</v>
       </c>
       <c r="D59" t="n">
-        <v>126.2699966430664</v>
+        <v>123.75</v>
       </c>
       <c r="E59" t="n">
-        <v>127.2200012207031</v>
+        <v>127.8000030517578</v>
       </c>
       <c r="F59" t="n">
-        <v>5619000</v>
+        <v>5286300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B60" t="n">
-        <v>126.1600036621094</v>
+        <v>127.0800018310547</v>
       </c>
       <c r="C60" t="n">
-        <v>128.5</v>
+        <v>130.7799987792969</v>
       </c>
       <c r="D60" t="n">
-        <v>123.75</v>
+        <v>126.7399978637695</v>
       </c>
       <c r="E60" t="n">
-        <v>127.8000030517578</v>
+        <v>128.5500030517578</v>
       </c>
       <c r="F60" t="n">
-        <v>5286300</v>
+        <v>4516400</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B61" t="n">
-        <v>127.0800018310547</v>
+        <v>128.5</v>
       </c>
       <c r="C61" t="n">
-        <v>130.7799987792969</v>
+        <v>129.6600036621094</v>
       </c>
       <c r="D61" t="n">
-        <v>126.7399978637695</v>
+        <v>126.8399963378906</v>
       </c>
       <c r="E61" t="n">
-        <v>128.5500030517578</v>
+        <v>128.5899963378906</v>
       </c>
       <c r="F61" t="n">
-        <v>4516400</v>
+        <v>5166300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B62" t="n">
-        <v>128.5</v>
+        <v>129.7299957275391</v>
       </c>
       <c r="C62" t="n">
-        <v>129.6600036621094</v>
+        <v>133.5700073242188</v>
       </c>
       <c r="D62" t="n">
-        <v>126.8399963378906</v>
+        <v>128.2100067138672</v>
       </c>
       <c r="E62" t="n">
-        <v>128.5899963378906</v>
+        <v>129.1100006103516</v>
       </c>
       <c r="F62" t="n">
-        <v>5166300</v>
+        <v>7813800</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B63" t="n">
-        <v>129.7299957275391</v>
+        <v>128.6999969482422</v>
       </c>
       <c r="C63" t="n">
-        <v>133.5700073242188</v>
+        <v>130.8000030517578</v>
       </c>
       <c r="D63" t="n">
-        <v>128.2100067138672</v>
+        <v>127.3199996948242</v>
       </c>
       <c r="E63" t="n">
-        <v>129.1100006103516</v>
+        <v>130.0399932861328</v>
       </c>
       <c r="F63" t="n">
-        <v>7813800</v>
+        <v>5227900</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B64" t="n">
-        <v>128.6999969482422</v>
+        <v>131.0500030517578</v>
       </c>
       <c r="C64" t="n">
-        <v>130.8000030517578</v>
+        <v>134.4400024414062</v>
       </c>
       <c r="D64" t="n">
-        <v>127.3199996948242</v>
+        <v>130.25</v>
       </c>
       <c r="E64" t="n">
-        <v>130.0399932861328</v>
+        <v>132.3600006103516</v>
       </c>
       <c r="F64" t="n">
-        <v>5227900</v>
+        <v>5921300</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B65" t="n">
-        <v>131.0500030517578</v>
+        <v>135.5299987792969</v>
       </c>
       <c r="C65" t="n">
-        <v>134.4400024414062</v>
+        <v>136.3999938964844</v>
       </c>
       <c r="D65" t="n">
-        <v>130.25</v>
+        <v>128.9499969482422</v>
       </c>
       <c r="E65" t="n">
-        <v>132.3600006103516</v>
+        <v>134.3899993896484</v>
       </c>
       <c r="F65" t="n">
-        <v>5921300</v>
+        <v>6679500</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B66" t="n">
-        <v>135.5299987792969</v>
+        <v>132.4799957275391</v>
       </c>
       <c r="C66" t="n">
-        <v>136.3999938964844</v>
+        <v>134.0500030517578</v>
       </c>
       <c r="D66" t="n">
-        <v>128.9499969482422</v>
+        <v>124.3000030517578</v>
       </c>
       <c r="E66" t="n">
-        <v>134.3899993896484</v>
+        <v>124.7600021362305</v>
       </c>
       <c r="F66" t="n">
-        <v>6679500</v>
+        <v>8508700</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B67" t="n">
-        <v>132.4799957275391</v>
+        <v>125.5</v>
       </c>
       <c r="C67" t="n">
-        <v>134.0500030517578</v>
+        <v>127.3600006103516</v>
       </c>
       <c r="D67" t="n">
-        <v>124.3000030517578</v>
+        <v>123.6100006103516</v>
       </c>
       <c r="E67" t="n">
-        <v>124.7600021362305</v>
+        <v>125.8899993896484</v>
       </c>
       <c r="F67" t="n">
-        <v>8508700</v>
+        <v>6441900</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B68" t="n">
-        <v>125.5</v>
+        <v>126.1399993896484</v>
       </c>
       <c r="C68" t="n">
-        <v>127.3600006103516</v>
+        <v>127.8399963378906</v>
       </c>
       <c r="D68" t="n">
-        <v>123.6100006103516</v>
+        <v>124.1999969482422</v>
       </c>
       <c r="E68" t="n">
-        <v>125.8899993896484</v>
+        <v>126.129997253418</v>
       </c>
       <c r="F68" t="n">
-        <v>6441900</v>
+        <v>6656100</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B69" t="n">
-        <v>126.1399993896484</v>
+        <v>125.9400024414062</v>
       </c>
       <c r="C69" t="n">
-        <v>127.8399963378906</v>
+        <v>126.8300018310547</v>
       </c>
       <c r="D69" t="n">
-        <v>124.1999969482422</v>
+        <v>121.629997253418</v>
       </c>
       <c r="E69" t="n">
-        <v>126.129997253418</v>
+        <v>122.3600006103516</v>
       </c>
       <c r="F69" t="n">
-        <v>6656100</v>
+        <v>8589200</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B70" t="n">
-        <v>125.9400024414062</v>
+        <v>125</v>
       </c>
       <c r="C70" t="n">
-        <v>126.8300018310547</v>
+        <v>127.1600036621094</v>
       </c>
       <c r="D70" t="n">
-        <v>121.629997253418</v>
+        <v>123.879997253418</v>
       </c>
       <c r="E70" t="n">
-        <v>122.3600006103516</v>
+        <v>124.620002746582</v>
       </c>
       <c r="F70" t="n">
-        <v>8589200</v>
+        <v>5515200</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B71" t="n">
-        <v>125</v>
+        <v>125.0100021362305</v>
       </c>
       <c r="C71" t="n">
-        <v>127.1600036621094</v>
+        <v>132.5200042724609</v>
       </c>
       <c r="D71" t="n">
-        <v>123.879997253418</v>
+        <v>125.0100021362305</v>
       </c>
       <c r="E71" t="n">
-        <v>124.620002746582</v>
+        <v>131.1199951171875</v>
       </c>
       <c r="F71" t="n">
-        <v>5515200</v>
+        <v>12713100</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B72" t="n">
-        <v>125.0100021362305</v>
+        <v>133.4299926757812</v>
       </c>
       <c r="C72" t="n">
-        <v>132.5200042724609</v>
+        <v>134</v>
       </c>
       <c r="D72" t="n">
-        <v>125.0100021362305</v>
+        <v>130.2200012207031</v>
       </c>
       <c r="E72" t="n">
-        <v>131.1199951171875</v>
+        <v>130.7299957275391</v>
       </c>
       <c r="F72" t="n">
-        <v>12713100</v>
+        <v>5547300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B73" t="n">
-        <v>133.4299926757812</v>
+        <v>129.3200073242188</v>
       </c>
       <c r="C73" t="n">
-        <v>134</v>
+        <v>131.7200012207031</v>
       </c>
       <c r="D73" t="n">
-        <v>130.2200012207031</v>
+        <v>129.25</v>
       </c>
       <c r="E73" t="n">
-        <v>130.7299957275391</v>
+        <v>131.3200073242188</v>
       </c>
       <c r="F73" t="n">
-        <v>5547300</v>
+        <v>2884300</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B74" t="n">
-        <v>129.3200073242188</v>
+        <v>131.1300048828125</v>
       </c>
       <c r="C74" t="n">
-        <v>131.7200012207031</v>
+        <v>131.5</v>
       </c>
       <c r="D74" t="n">
-        <v>129.25</v>
+        <v>130.1100006103516</v>
       </c>
       <c r="E74" t="n">
-        <v>131.3200073242188</v>
+        <v>130.7700042724609</v>
       </c>
       <c r="F74" t="n">
-        <v>2884300</v>
+        <v>1642400</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B75" t="n">
-        <v>131.1300048828125</v>
+        <v>131</v>
       </c>
       <c r="C75" t="n">
-        <v>131.5</v>
+        <v>132.125</v>
       </c>
       <c r="D75" t="n">
-        <v>130.1100006103516</v>
+        <v>130.4499969482422</v>
       </c>
       <c r="E75" t="n">
-        <v>130.7700042724609</v>
+        <v>131.8399963378906</v>
       </c>
       <c r="F75" t="n">
-        <v>1642400</v>
+        <v>2308400</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B76" t="n">
-        <v>131</v>
+        <v>131.1499938964844</v>
       </c>
       <c r="C76" t="n">
-        <v>132.125</v>
+        <v>135.2989959716797</v>
       </c>
       <c r="D76" t="n">
-        <v>130.4499969482422</v>
+        <v>131.0399932861328</v>
       </c>
       <c r="E76" t="n">
-        <v>131.8399963378906</v>
+        <v>134.1499938964844</v>
       </c>
       <c r="F76" t="n">
-        <v>2308400</v>
+        <v>6199700</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B77" t="n">
-        <v>131.1499938964844</v>
+        <v>134.25</v>
       </c>
       <c r="C77" t="n">
-        <v>135.2989959716797</v>
+        <v>134.4499969482422</v>
       </c>
       <c r="D77" t="n">
-        <v>131.0399932861328</v>
+        <v>132.3699951171875</v>
       </c>
       <c r="E77" t="n">
-        <v>134.1499938964844</v>
+        <v>132.4400024414062</v>
       </c>
       <c r="F77" t="n">
-        <v>6199700</v>
+        <v>4081100</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B78" t="n">
-        <v>134.25</v>
+        <v>132.5</v>
       </c>
       <c r="C78" t="n">
-        <v>134.4499969482422</v>
+        <v>132.8300018310547</v>
       </c>
       <c r="D78" t="n">
-        <v>132.3699951171875</v>
+        <v>130.8800048828125</v>
       </c>
       <c r="E78" t="n">
-        <v>132.4400024414062</v>
+        <v>131.0299987792969</v>
       </c>
       <c r="F78" t="n">
-        <v>4081100</v>
+        <v>3821600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B79" t="n">
-        <v>132.5</v>
+        <v>134.0500030517578</v>
       </c>
       <c r="C79" t="n">
-        <v>132.8300018310547</v>
+        <v>136.0899963378906</v>
       </c>
       <c r="D79" t="n">
-        <v>130.8800048828125</v>
+        <v>132.1849975585938</v>
       </c>
       <c r="E79" t="n">
-        <v>131.0299987792969</v>
+        <v>133.6000061035156</v>
       </c>
       <c r="F79" t="n">
-        <v>3821600</v>
+        <v>4707400</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B80" t="n">
-        <v>134.0500030517578</v>
+        <v>138.3399963378906</v>
       </c>
       <c r="C80" t="n">
-        <v>136.0899963378906</v>
+        <v>141.4100036621094</v>
       </c>
       <c r="D80" t="n">
-        <v>132.1849975585938</v>
+        <v>134.5099945068359</v>
       </c>
       <c r="E80" t="n">
-        <v>133.6000061035156</v>
+        <v>137.1900024414062</v>
       </c>
       <c r="F80" t="n">
-        <v>4707400</v>
+        <v>9691900</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B81" t="n">
-        <v>138.3399963378906</v>
+        <v>137.8999938964844</v>
       </c>
       <c r="C81" t="n">
-        <v>141.4100036621094</v>
+        <v>137.9299926757812</v>
       </c>
       <c r="D81" t="n">
-        <v>134.5099945068359</v>
+        <v>132.5</v>
       </c>
       <c r="E81" t="n">
-        <v>137.1900024414062</v>
+        <v>132.5800018310547</v>
       </c>
       <c r="F81" t="n">
-        <v>9691900</v>
+        <v>8004000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B82" t="n">
-        <v>137.8999938964844</v>
+        <v>130.0099945068359</v>
       </c>
       <c r="C82" t="n">
-        <v>137.9299926757812</v>
+        <v>131.6549987792969</v>
       </c>
       <c r="D82" t="n">
-        <v>132.5</v>
+        <v>128.6399993896484</v>
       </c>
       <c r="E82" t="n">
-        <v>132.5800018310547</v>
+        <v>130.0800018310547</v>
       </c>
       <c r="F82" t="n">
-        <v>8004000</v>
+        <v>7550700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B83" t="n">
-        <v>130.0099945068359</v>
+        <v>129.3699951171875</v>
       </c>
       <c r="C83" t="n">
-        <v>131.6549987792969</v>
+        <v>129.6000061035156</v>
       </c>
       <c r="D83" t="n">
-        <v>128.6399993896484</v>
+        <v>122.8099975585938</v>
       </c>
       <c r="E83" t="n">
-        <v>130.0800018310547</v>
+        <v>123.7200012207031</v>
       </c>
       <c r="F83" t="n">
-        <v>7550700</v>
+        <v>8944200</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B84" t="n">
-        <v>129.3699951171875</v>
+        <v>124.5699996948242</v>
       </c>
       <c r="C84" t="n">
-        <v>129.6000061035156</v>
+        <v>124.8300018310547</v>
       </c>
       <c r="D84" t="n">
-        <v>122.8099975585938</v>
+        <v>121.9000015258789</v>
       </c>
       <c r="E84" t="n">
-        <v>123.7200012207031</v>
+        <v>122.8899993896484</v>
       </c>
       <c r="F84" t="n">
-        <v>8944200</v>
+        <v>8989700</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B85" t="n">
-        <v>124.5699996948242</v>
+        <v>121.5999984741211</v>
       </c>
       <c r="C85" t="n">
-        <v>124.8300018310547</v>
+        <v>124.4550018310547</v>
       </c>
       <c r="D85" t="n">
-        <v>121.9000015258789</v>
+        <v>120</v>
       </c>
       <c r="E85" t="n">
-        <v>122.8899993896484</v>
+        <v>123.4199981689453</v>
       </c>
       <c r="F85" t="n">
-        <v>8989700</v>
+        <v>8795900</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B86" t="n">
-        <v>121.5999984741211</v>
+        <v>123.6999969482422</v>
       </c>
       <c r="C86" t="n">
-        <v>124.4550018310547</v>
+        <v>130.6900024414062</v>
       </c>
       <c r="D86" t="n">
-        <v>120</v>
+        <v>123.0500030517578</v>
       </c>
       <c r="E86" t="n">
-        <v>123.4199981689453</v>
+        <v>129.9299926757812</v>
       </c>
       <c r="F86" t="n">
-        <v>8795900</v>
+        <v>8638900</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B87" t="n">
-        <v>123.6999969482422</v>
+        <v>128.7599945068359</v>
       </c>
       <c r="C87" t="n">
-        <v>130.6900024414062</v>
+        <v>129.7599945068359</v>
       </c>
       <c r="D87" t="n">
-        <v>123.0500030517578</v>
+        <v>123.3399963378906</v>
       </c>
       <c r="E87" t="n">
-        <v>129.9299926757812</v>
+        <v>125.0899963378906</v>
       </c>
       <c r="F87" t="n">
-        <v>8638900</v>
+        <v>7414600</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B88" t="n">
-        <v>128.7599945068359</v>
+        <v>127.5899963378906</v>
       </c>
       <c r="C88" t="n">
-        <v>129.7599945068359</v>
+        <v>133.3399963378906</v>
       </c>
       <c r="D88" t="n">
-        <v>123.3399963378906</v>
+        <v>127.370002746582</v>
       </c>
       <c r="E88" t="n">
-        <v>125.0899963378906</v>
+        <v>130.5899963378906</v>
       </c>
       <c r="F88" t="n">
-        <v>7414600</v>
+        <v>8562300</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B89" t="n">
-        <v>127.5899963378906</v>
+        <v>132.1799926757812</v>
       </c>
       <c r="C89" t="n">
-        <v>133.3399963378906</v>
+        <v>132.9400024414062</v>
       </c>
       <c r="D89" t="n">
-        <v>127.370002746582</v>
+        <v>129.3300018310547</v>
       </c>
       <c r="E89" t="n">
-        <v>130.5899963378906</v>
+        <v>129.8300018310547</v>
       </c>
       <c r="F89" t="n">
-        <v>8562300</v>
+        <v>5987000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B90" t="n">
-        <v>132.1799926757812</v>
+        <v>126.4899978637695</v>
       </c>
       <c r="C90" t="n">
-        <v>132.9400024414062</v>
+        <v>130.3800048828125</v>
       </c>
       <c r="D90" t="n">
-        <v>129.3300018310547</v>
+        <v>125.7799987792969</v>
       </c>
       <c r="E90" t="n">
-        <v>129.8300018310547</v>
+        <v>127.5199966430664</v>
       </c>
       <c r="F90" t="n">
-        <v>5987000</v>
+        <v>6371300</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B91" t="n">
-        <v>126.4899978637695</v>
+        <v>127.8600006103516</v>
       </c>
       <c r="C91" t="n">
-        <v>130.3800048828125</v>
+        <v>129.5500030517578</v>
       </c>
       <c r="D91" t="n">
-        <v>125.7799987792969</v>
+        <v>125.0400009155273</v>
       </c>
       <c r="E91" t="n">
-        <v>127.5199966430664</v>
+        <v>127.2900009155273</v>
       </c>
       <c r="F91" t="n">
-        <v>6371300</v>
+        <v>5931000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B92" t="n">
-        <v>127.8600006103516</v>
+        <v>139.8399963378906</v>
       </c>
       <c r="C92" t="n">
-        <v>129.5500030517578</v>
+        <v>146.3999938964844</v>
       </c>
       <c r="D92" t="n">
-        <v>125.0400009155273</v>
+        <v>137.4199981689453</v>
       </c>
       <c r="E92" t="n">
-        <v>127.2900009155273</v>
+        <v>138.4100036621094</v>
       </c>
       <c r="F92" t="n">
-        <v>5931000</v>
+        <v>14906700</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B93" t="n">
-        <v>139.8399963378906</v>
+        <v>138.3699951171875</v>
       </c>
       <c r="C93" t="n">
-        <v>146.3999938964844</v>
+        <v>138.8999938964844</v>
       </c>
       <c r="D93" t="n">
-        <v>137.4199981689453</v>
+        <v>134.8600006103516</v>
       </c>
       <c r="E93" t="n">
-        <v>138.4100036621094</v>
+        <v>136.3399963378906</v>
       </c>
       <c r="F93" t="n">
-        <v>14906700</v>
+        <v>8053900</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B94" t="n">
-        <v>138.3699951171875</v>
+        <v>139.3200073242188</v>
       </c>
       <c r="C94" t="n">
-        <v>138.8999938964844</v>
+        <v>146.4049987792969</v>
       </c>
       <c r="D94" t="n">
-        <v>134.8600006103516</v>
+        <v>139.2400054931641</v>
       </c>
       <c r="E94" t="n">
-        <v>136.3399963378906</v>
+        <v>143.7200012207031</v>
       </c>
       <c r="F94" t="n">
-        <v>8053900</v>
+        <v>10658200</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B95" t="n">
-        <v>139.3200073242188</v>
+        <v>144.8600006103516</v>
       </c>
       <c r="C95" t="n">
-        <v>146.4049987792969</v>
+        <v>149.2700042724609</v>
       </c>
       <c r="D95" t="n">
-        <v>139.2400054931641</v>
+        <v>143.8000030517578</v>
       </c>
       <c r="E95" t="n">
-        <v>143.7200012207031</v>
+        <v>146.6900024414062</v>
       </c>
       <c r="F95" t="n">
-        <v>10658200</v>
+        <v>8697000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B96" t="n">
-        <v>144.8600006103516</v>
+        <v>150.3500061035156</v>
       </c>
       <c r="C96" t="n">
-        <v>149.2700042724609</v>
+        <v>151.8000030517578</v>
       </c>
       <c r="D96" t="n">
-        <v>143.8000030517578</v>
+        <v>145.5700073242188</v>
       </c>
       <c r="E96" t="n">
-        <v>146.6900024414062</v>
+        <v>150.1499938964844</v>
       </c>
       <c r="F96" t="n">
-        <v>8697000</v>
+        <v>8568200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B97" t="n">
-        <v>150.3500061035156</v>
+        <v>150.1499938964844</v>
       </c>
       <c r="C97" t="n">
-        <v>151.8000030517578</v>
+        <v>151.5500030517578</v>
       </c>
       <c r="D97" t="n">
-        <v>145.5700073242188</v>
+        <v>145.3300018310547</v>
       </c>
       <c r="E97" t="n">
-        <v>150.1499938964844</v>
+        <v>148.1499938964844</v>
       </c>
       <c r="F97" t="n">
-        <v>8568200</v>
+        <v>8915300</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B98" t="n">
-        <v>150.1499938964844</v>
+        <v>145.8500061035156</v>
       </c>
       <c r="C98" t="n">
-        <v>151.5500030517578</v>
+        <v>148.0599975585938</v>
       </c>
       <c r="D98" t="n">
-        <v>145.3300018310547</v>
+        <v>141.4400024414062</v>
       </c>
       <c r="E98" t="n">
-        <v>148.1499938964844</v>
+        <v>141.7400054931641</v>
       </c>
       <c r="F98" t="n">
-        <v>8915300</v>
+        <v>6364000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B99" t="n">
-        <v>145.8500061035156</v>
+        <v>141.3200073242188</v>
       </c>
       <c r="C99" t="n">
-        <v>148.0599975585938</v>
+        <v>143.1100006103516</v>
       </c>
       <c r="D99" t="n">
-        <v>141.4400024414062</v>
+        <v>138.2200012207031</v>
       </c>
       <c r="E99" t="n">
-        <v>141.7400054931641</v>
+        <v>138.3699951171875</v>
       </c>
       <c r="F99" t="n">
-        <v>6364000</v>
+        <v>7719200</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B100" t="n">
-        <v>141.3200073242188</v>
+        <v>140.7149963378906</v>
       </c>
       <c r="C100" t="n">
-        <v>143.1100006103516</v>
+        <v>143.2720031738281</v>
       </c>
       <c r="D100" t="n">
-        <v>138.2200012207031</v>
+        <v>135.3300018310547</v>
       </c>
       <c r="E100" t="n">
-        <v>138.3699951171875</v>
+        <v>139.3899993896484</v>
       </c>
       <c r="F100" t="n">
-        <v>7719200</v>
+        <v>8202300</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B101" t="n">
-        <v>140.7149963378906</v>
+        <v>138</v>
       </c>
       <c r="C101" t="n">
-        <v>143.2720031738281</v>
+        <v>139.3699951171875</v>
       </c>
       <c r="D101" t="n">
-        <v>135.3300018310547</v>
+        <v>129.2400054931641</v>
       </c>
       <c r="E101" t="n">
-        <v>139.3899993896484</v>
+        <v>130.2799987792969</v>
       </c>
       <c r="F101" t="n">
-        <v>8202300</v>
+        <v>13313800</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B102" t="n">
-        <v>138</v>
+        <v>127.7300033569336</v>
       </c>
       <c r="C102" t="n">
-        <v>139.3699951171875</v>
+        <v>130.3099975585938</v>
       </c>
       <c r="D102" t="n">
-        <v>129.2400054931641</v>
+        <v>125.3399963378906</v>
       </c>
       <c r="E102" t="n">
-        <v>130.2799987792969</v>
+        <v>128.6699981689453</v>
       </c>
       <c r="F102" t="n">
-        <v>13313800</v>
+        <v>9640500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B103" t="n">
-        <v>127.7300033569336</v>
+        <v>131.3999938964844</v>
       </c>
       <c r="C103" t="n">
-        <v>130.3099975585938</v>
+        <v>137.6100006103516</v>
       </c>
       <c r="D103" t="n">
-        <v>125.3399963378906</v>
+        <v>130.3200073242188</v>
       </c>
       <c r="E103" t="n">
-        <v>128.6699981689453</v>
+        <v>137.4900054931641</v>
       </c>
       <c r="F103" t="n">
-        <v>9640500</v>
+        <v>8986800</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B104" t="n">
-        <v>131.3999938964844</v>
+        <v>138.2799987792969</v>
       </c>
       <c r="C104" t="n">
-        <v>137.6100006103516</v>
+        <v>142.2700042724609</v>
       </c>
       <c r="D104" t="n">
-        <v>130.3200073242188</v>
+        <v>136.0549926757812</v>
       </c>
       <c r="E104" t="n">
-        <v>137.4900054931641</v>
+        <v>141.7400054931641</v>
       </c>
       <c r="F104" t="n">
-        <v>8986800</v>
+        <v>6801400</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B105" t="n">
-        <v>138.2799987792969</v>
+        <v>144.3249969482422</v>
       </c>
       <c r="C105" t="n">
-        <v>142.2700042724609</v>
+        <v>145.0350036621094</v>
       </c>
       <c r="D105" t="n">
-        <v>136.0549926757812</v>
+        <v>141.8000030517578</v>
       </c>
       <c r="E105" t="n">
-        <v>141.7400054931641</v>
+        <v>143.4499969482422</v>
       </c>
       <c r="F105" t="n">
-        <v>6801400</v>
+        <v>6138100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B106" t="n">
-        <v>144.3249969482422</v>
+        <v>145.1100006103516</v>
       </c>
       <c r="C106" t="n">
-        <v>145.0350036621094</v>
+        <v>145.2400054931641</v>
       </c>
       <c r="D106" t="n">
-        <v>141.8000030517578</v>
+        <v>138.2200012207031</v>
       </c>
       <c r="E106" t="n">
-        <v>143.4499969482422</v>
+        <v>140.6600036621094</v>
       </c>
       <c r="F106" t="n">
-        <v>6138100</v>
+        <v>6942400</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B107" t="n">
-        <v>145.1100006103516</v>
+        <v>138</v>
       </c>
       <c r="C107" t="n">
-        <v>145.2400054931641</v>
+        <v>138.5</v>
       </c>
       <c r="D107" t="n">
-        <v>138.2200012207031</v>
+        <v>132.0099945068359</v>
       </c>
       <c r="E107" t="n">
-        <v>140.6600036621094</v>
+        <v>135.1199951171875</v>
       </c>
       <c r="F107" t="n">
-        <v>6942400</v>
+        <v>16322100</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B108" t="n">
+        <v>145.8200073242188</v>
+      </c>
+      <c r="C108" t="n">
+        <v>148.7700042724609</v>
+      </c>
+      <c r="D108" t="n">
         <v>138</v>
       </c>
-      <c r="C108" t="n">
-        <v>138.5</v>
-      </c>
-      <c r="D108" t="n">
-        <v>132.0099945068359</v>
-      </c>
       <c r="E108" t="n">
-        <v>135.1199951171875</v>
+        <v>141.5899963378906</v>
       </c>
       <c r="F108" t="n">
-        <v>16322100</v>
+        <v>21823000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B109" t="n">
-        <v>145.8200073242188</v>
+        <v>140.6399993896484</v>
       </c>
       <c r="C109" t="n">
-        <v>148.7700042724609</v>
+        <v>145</v>
       </c>
       <c r="D109" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E109" t="n">
-        <v>141.5899963378906</v>
+        <v>142.5800018310547</v>
       </c>
       <c r="F109" t="n">
-        <v>21823000</v>
+        <v>8724200</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B110" t="n">
-        <v>140.6399993896484</v>
+        <v>140.4600067138672</v>
       </c>
       <c r="C110" t="n">
-        <v>145</v>
+        <v>142.5</v>
       </c>
       <c r="D110" t="n">
-        <v>140</v>
+        <v>136.6900024414062</v>
       </c>
       <c r="E110" t="n">
-        <v>142.5800018310547</v>
+        <v>139.5399932861328</v>
       </c>
       <c r="F110" t="n">
-        <v>8724200</v>
+        <v>9955700</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B111" t="n">
-        <v>140.4600067138672</v>
+        <v>138.6100006103516</v>
       </c>
       <c r="C111" t="n">
-        <v>142.5</v>
+        <v>140.3200073242188</v>
       </c>
       <c r="D111" t="n">
-        <v>136.6900024414062</v>
+        <v>135.3699951171875</v>
       </c>
       <c r="E111" t="n">
-        <v>139.5399932861328</v>
+        <v>137.2299957275391</v>
       </c>
       <c r="F111" t="n">
-        <v>9955700</v>
+        <v>5260600</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B112" t="n">
-        <v>138.6100006103516</v>
+        <v>136.0200042724609</v>
       </c>
       <c r="C112" t="n">
-        <v>140.3200073242188</v>
+        <v>138.3300018310547</v>
       </c>
       <c r="D112" t="n">
-        <v>135.3699951171875</v>
+        <v>132.1499938964844</v>
       </c>
       <c r="E112" t="n">
-        <v>137.2299957275391</v>
+        <v>132.7899932861328</v>
       </c>
       <c r="F112" t="n">
-        <v>5260600</v>
+        <v>8309000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B113" t="n">
-        <v>136.0200042724609</v>
+        <v>131.2250061035156</v>
       </c>
       <c r="C113" t="n">
-        <v>138.3300018310547</v>
+        <v>131.6349945068359</v>
       </c>
       <c r="D113" t="n">
-        <v>132.1499938964844</v>
+        <v>126.2600021362305</v>
       </c>
       <c r="E113" t="n">
-        <v>132.7899932861328</v>
+        <v>127.4300003051758</v>
       </c>
       <c r="F113" t="n">
-        <v>8309000</v>
+        <v>9706800</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B114" t="n">
-        <v>131.2250061035156</v>
+        <v>130.25</v>
       </c>
       <c r="C114" t="n">
-        <v>131.6349945068359</v>
+        <v>130.7299957275391</v>
       </c>
       <c r="D114" t="n">
-        <v>126.2600021362305</v>
+        <v>124.379997253418</v>
       </c>
       <c r="E114" t="n">
-        <v>127.4300003051758</v>
+        <v>128.7700042724609</v>
       </c>
       <c r="F114" t="n">
-        <v>9706800</v>
+        <v>8120000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B115" t="n">
-        <v>130.25</v>
+        <v>129.3699951171875</v>
       </c>
       <c r="C115" t="n">
-        <v>130.7299957275391</v>
+        <v>133.7799987792969</v>
       </c>
       <c r="D115" t="n">
-        <v>124.379997253418</v>
+        <v>128.6399993896484</v>
       </c>
       <c r="E115" t="n">
-        <v>128.7700042724609</v>
+        <v>132.8899993896484</v>
       </c>
       <c r="F115" t="n">
-        <v>8120000</v>
+        <v>7611600</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B116" t="n">
-        <v>129.3699951171875</v>
+        <v>132</v>
       </c>
       <c r="C116" t="n">
-        <v>133.7799987792969</v>
+        <v>132.2200012207031</v>
       </c>
       <c r="D116" t="n">
-        <v>128.6399993896484</v>
+        <v>126.9199981689453</v>
       </c>
       <c r="E116" t="n">
-        <v>132.8899993896484</v>
+        <v>130.25</v>
       </c>
       <c r="F116" t="n">
-        <v>7611600</v>
+        <v>6360700</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B117" t="n">
-        <v>132</v>
+        <v>127.5199966430664</v>
       </c>
       <c r="C117" t="n">
-        <v>132.2200012207031</v>
+        <v>133.5800018310547</v>
       </c>
       <c r="D117" t="n">
-        <v>126.9199981689453</v>
+        <v>127.5</v>
       </c>
       <c r="E117" t="n">
-        <v>130.25</v>
+        <v>133.5</v>
       </c>
       <c r="F117" t="n">
-        <v>6360700</v>
+        <v>9043300</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B118" t="n">
-        <v>127.5199966430664</v>
+        <v>129.6499938964844</v>
       </c>
       <c r="C118" t="n">
-        <v>133.5800018310547</v>
+        <v>130.6900024414062</v>
       </c>
       <c r="D118" t="n">
-        <v>127.5</v>
+        <v>127.2600021362305</v>
       </c>
       <c r="E118" t="n">
-        <v>133.5</v>
+        <v>129.3000030517578</v>
       </c>
       <c r="F118" t="n">
-        <v>9043300</v>
+        <v>6875000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B119" t="n">
-        <v>129.6499938964844</v>
+        <v>125.3300018310547</v>
       </c>
       <c r="C119" t="n">
-        <v>130.6900024414062</v>
+        <v>126.8300018310547</v>
       </c>
       <c r="D119" t="n">
-        <v>127.2600021362305</v>
+        <v>122.370002746582</v>
       </c>
       <c r="E119" t="n">
-        <v>129.3000030517578</v>
+        <v>124.5999984741211</v>
       </c>
       <c r="F119" t="n">
-        <v>6875000</v>
+        <v>6119700</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B120" t="n">
-        <v>125.3300018310547</v>
+        <v>127.870002746582</v>
       </c>
       <c r="C120" t="n">
-        <v>126.8300018310547</v>
+        <v>135.5599975585938</v>
       </c>
       <c r="D120" t="n">
-        <v>122.370002746582</v>
+        <v>127.4000015258789</v>
       </c>
       <c r="E120" t="n">
-        <v>124.5999984741211</v>
+        <v>134.8300018310547</v>
       </c>
       <c r="F120" t="n">
-        <v>6119700</v>
+        <v>6897700</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B121" t="n">
-        <v>127.870002746582</v>
+        <v>135.1150054931641</v>
       </c>
       <c r="C121" t="n">
-        <v>135.5599975585938</v>
+        <v>139.4799957275391</v>
       </c>
       <c r="D121" t="n">
-        <v>127.4000015258789</v>
+        <v>134</v>
       </c>
       <c r="E121" t="n">
-        <v>134.8300018310547</v>
+        <v>139.3999938964844</v>
       </c>
       <c r="F121" t="n">
-        <v>6897700</v>
+        <v>8384600</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B122" t="n">
-        <v>135.1150054931641</v>
+        <v>136.3899993896484</v>
       </c>
       <c r="C122" t="n">
-        <v>139.4799957275391</v>
+        <v>139.0579986572266</v>
       </c>
       <c r="D122" t="n">
-        <v>134</v>
+        <v>132.7299957275391</v>
       </c>
       <c r="E122" t="n">
-        <v>139.3999938964844</v>
+        <v>132.8899993896484</v>
       </c>
       <c r="F122" t="n">
-        <v>8384600</v>
+        <v>6282000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B123" t="n">
-        <v>136.3899993896484</v>
+        <v>130.4049987792969</v>
       </c>
       <c r="C123" t="n">
-        <v>139.0579986572266</v>
+        <v>137.6750030517578</v>
       </c>
       <c r="D123" t="n">
-        <v>132.7299957275391</v>
+        <v>129.7899932861328</v>
       </c>
       <c r="E123" t="n">
-        <v>132.8899993896484</v>
+        <v>137.1699981689453</v>
       </c>
       <c r="F123" t="n">
-        <v>6282000</v>
+        <v>6715200</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B124" t="n">
-        <v>130.4049987792969</v>
+        <v>138</v>
       </c>
       <c r="C124" t="n">
-        <v>137.6750030517578</v>
+        <v>141.7700042724609</v>
       </c>
       <c r="D124" t="n">
-        <v>129.7899932861328</v>
+        <v>137.8899993896484</v>
       </c>
       <c r="E124" t="n">
-        <v>137.1699981689453</v>
+        <v>139.6199951171875</v>
       </c>
       <c r="F124" t="n">
-        <v>6715200</v>
+        <v>5435800</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B125" t="n">
-        <v>138</v>
+        <v>139.1600036621094</v>
       </c>
       <c r="C125" t="n">
-        <v>141.7700042724609</v>
+        <v>141.1399993896484</v>
       </c>
       <c r="D125" t="n">
-        <v>137.8899993896484</v>
+        <v>137.6540069580078</v>
       </c>
       <c r="E125" t="n">
-        <v>139.6199951171875</v>
+        <v>138.2299957275391</v>
       </c>
       <c r="F125" t="n">
-        <v>5435800</v>
+        <v>4165100</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B126" t="n">
-        <v>139.1600036621094</v>
+        <v>137.7400054931641</v>
       </c>
       <c r="C126" t="n">
-        <v>141.1399993896484</v>
+        <v>137.7799987792969</v>
       </c>
       <c r="D126" t="n">
-        <v>137.6540069580078</v>
+        <v>133.6900024414062</v>
       </c>
       <c r="E126" t="n">
-        <v>138.2299957275391</v>
+        <v>134.0299987792969</v>
       </c>
       <c r="F126" t="n">
-        <v>4165100</v>
+        <v>5494200</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B127" t="n">
-        <v>137.7400054931641</v>
+        <v>134.8200073242188</v>
       </c>
       <c r="C127" t="n">
-        <v>137.7799987792969</v>
+        <v>137.5950012207031</v>
       </c>
       <c r="D127" t="n">
-        <v>133.6900024414062</v>
+        <v>130.5099945068359</v>
       </c>
       <c r="E127" t="n">
-        <v>134.0299987792969</v>
+        <v>133.5700073242188</v>
       </c>
       <c r="F127" t="n">
-        <v>5494200</v>
+        <v>5364800</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B128" t="n">
-        <v>134.8200073242188</v>
+        <v>133.8699951171875</v>
       </c>
       <c r="C128" t="n">
-        <v>137.5950012207031</v>
+        <v>136.2799987792969</v>
       </c>
       <c r="D128" t="n">
-        <v>130.5099945068359</v>
+        <v>131.9100036621094</v>
       </c>
       <c r="E128" t="n">
-        <v>133.5700073242188</v>
+        <v>135.3500061035156</v>
       </c>
       <c r="F128" t="n">
-        <v>5364800</v>
+        <v>7884200</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B129" t="n">
-        <v>133.8699951171875</v>
+        <v>135.0099945068359</v>
       </c>
       <c r="C129" t="n">
-        <v>136.2799987792969</v>
+        <v>136.6999969482422</v>
       </c>
       <c r="D129" t="n">
-        <v>131.9100036621094</v>
+        <v>132.3099975585938</v>
       </c>
       <c r="E129" t="n">
-        <v>135.3500061035156</v>
+        <v>133.0700073242188</v>
       </c>
       <c r="F129" t="n">
-        <v>7884200</v>
+        <v>5959000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B130" t="n">
-        <v>135.0099945068359</v>
+        <v>133.5</v>
       </c>
       <c r="C130" t="n">
-        <v>136.6999969482422</v>
+        <v>137.5599975585938</v>
       </c>
       <c r="D130" t="n">
-        <v>132.3099975585938</v>
+        <v>133.5</v>
       </c>
       <c r="E130" t="n">
-        <v>133.0700073242188</v>
+        <v>136.0700073242188</v>
       </c>
       <c r="F130" t="n">
-        <v>5959000</v>
+        <v>5264100</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B131" t="n">
-        <v>133.5</v>
+        <v>133.7400054931641</v>
       </c>
       <c r="C131" t="n">
-        <v>137.5599975585938</v>
+        <v>136.5700073242188</v>
       </c>
       <c r="D131" t="n">
-        <v>133.5</v>
+        <v>132.3500061035156</v>
       </c>
       <c r="E131" t="n">
-        <v>136.0700073242188</v>
+        <v>136.2599945068359</v>
       </c>
       <c r="F131" t="n">
-        <v>5264100</v>
+        <v>4418900</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B132" t="n">
-        <v>133.7400054931641</v>
+        <v>134</v>
       </c>
       <c r="C132" t="n">
-        <v>136.5700073242188</v>
+        <v>135.3000030517578</v>
       </c>
       <c r="D132" t="n">
-        <v>132.3500061035156</v>
+        <v>128.8999938964844</v>
       </c>
       <c r="E132" t="n">
-        <v>136.2599945068359</v>
+        <v>131.2200012207031</v>
       </c>
       <c r="F132" t="n">
-        <v>4418900</v>
+        <v>11351600</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B133" t="n">
-        <v>134</v>
+        <v>133.4799957275391</v>
       </c>
       <c r="C133" t="n">
-        <v>135.3000030517578</v>
+        <v>138.2100067138672</v>
       </c>
       <c r="D133" t="n">
-        <v>128.8999938964844</v>
+        <v>132.1999969482422</v>
       </c>
       <c r="E133" t="n">
-        <v>131.2200012207031</v>
+        <v>135.8800048828125</v>
       </c>
       <c r="F133" t="n">
-        <v>11351600</v>
+        <v>6402200</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B134" t="n">
-        <v>133.4799957275391</v>
+        <v>134.2100067138672</v>
       </c>
       <c r="C134" t="n">
-        <v>138.2100067138672</v>
+        <v>135.6999969482422</v>
       </c>
       <c r="D134" t="n">
-        <v>132.1999969482422</v>
+        <v>129.1900024414062</v>
       </c>
       <c r="E134" t="n">
-        <v>135.8800048828125</v>
+        <v>130.8000030517578</v>
       </c>
       <c r="F134" t="n">
-        <v>6402200</v>
+        <v>7858900</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B135" t="n">
-        <v>134.2100067138672</v>
+        <v>133.2100067138672</v>
       </c>
       <c r="C135" t="n">
-        <v>135.6999969482422</v>
+        <v>135.0800018310547</v>
       </c>
       <c r="D135" t="n">
-        <v>129.1900024414062</v>
+        <v>131.1499938964844</v>
       </c>
       <c r="E135" t="n">
-        <v>130.8000030517578</v>
+        <v>135.0099945068359</v>
       </c>
       <c r="F135" t="n">
-        <v>7858900</v>
+        <v>5353300</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B136" t="n">
-        <v>133.2100067138672</v>
+        <v>131.7899932861328</v>
       </c>
       <c r="C136" t="n">
-        <v>135.0800018310547</v>
+        <v>132.5</v>
       </c>
       <c r="D136" t="n">
-        <v>131.1499938964844</v>
+        <v>122.5100021362305</v>
       </c>
       <c r="E136" t="n">
-        <v>135.0099945068359</v>
+        <v>122.5500030517578</v>
       </c>
       <c r="F136" t="n">
-        <v>5353300</v>
+        <v>7553500</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B137" t="n">
-        <v>131.7899932861328</v>
+        <v>121.3399963378906</v>
       </c>
       <c r="C137" t="n">
-        <v>132.5</v>
+        <v>123.7200012207031</v>
       </c>
       <c r="D137" t="n">
-        <v>122.5100021362305</v>
+        <v>120.3420028686523</v>
       </c>
       <c r="E137" t="n">
-        <v>122.5500030517578</v>
+        <v>120.7699966430664</v>
       </c>
       <c r="F137" t="n">
-        <v>7553500</v>
+        <v>5940200</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B138" t="n">
-        <v>121.3399963378906</v>
+        <v>122.0100021362305</v>
       </c>
       <c r="C138" t="n">
-        <v>123.7200012207031</v>
+        <v>123.3399963378906</v>
       </c>
       <c r="D138" t="n">
-        <v>120.3420028686523</v>
+        <v>115.4199981689453</v>
       </c>
       <c r="E138" t="n">
-        <v>120.7699966430664</v>
+        <v>116.129997253418</v>
       </c>
       <c r="F138" t="n">
-        <v>5940200</v>
+        <v>7540500</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B139" t="n">
-        <v>122.0100021362305</v>
+        <v>118.620002746582</v>
       </c>
       <c r="C139" t="n">
-        <v>123.3399963378906</v>
+        <v>123.4599990844727</v>
       </c>
       <c r="D139" t="n">
-        <v>115.4199981689453</v>
+        <v>117.4199981689453</v>
       </c>
       <c r="E139" t="n">
-        <v>116.129997253418</v>
+        <v>122.7799987792969</v>
       </c>
       <c r="F139" t="n">
-        <v>7540500</v>
+        <v>7837700</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B140" t="n">
-        <v>118.620002746582</v>
+        <v>126.0599975585938</v>
       </c>
       <c r="C140" t="n">
-        <v>123.4599990844727</v>
+        <v>127.25</v>
       </c>
       <c r="D140" t="n">
-        <v>117.4199981689453</v>
+        <v>124.6600036621094</v>
       </c>
       <c r="E140" t="n">
-        <v>122.7799987792969</v>
+        <v>124.8499984741211</v>
       </c>
       <c r="F140" t="n">
-        <v>7837700</v>
+        <v>5037700</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B141" t="n">
-        <v>126.0599975585938</v>
+        <v>121.0999984741211</v>
       </c>
       <c r="C141" t="n">
-        <v>127.25</v>
+        <v>127.1999969482422</v>
       </c>
       <c r="D141" t="n">
-        <v>124.6600036621094</v>
+        <v>119.7910003662109</v>
       </c>
       <c r="E141" t="n">
-        <v>124.8499984741211</v>
+        <v>126.6800003051758</v>
       </c>
       <c r="F141" t="n">
-        <v>5037700</v>
+        <v>5125100</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B142" t="n">
-        <v>121.0999984741211</v>
+        <v>127.3199996948242</v>
       </c>
       <c r="C142" t="n">
-        <v>127.1999969482422</v>
+        <v>128.1649932861328</v>
       </c>
       <c r="D142" t="n">
-        <v>119.7910003662109</v>
+        <v>125.1650009155273</v>
       </c>
       <c r="E142" t="n">
-        <v>126.6800003051758</v>
+        <v>126.25</v>
       </c>
       <c r="F142" t="n">
-        <v>5125100</v>
+        <v>3033100</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B143" t="n">
-        <v>127.3199996948242</v>
+        <v>127.8499984741211</v>
       </c>
       <c r="C143" t="n">
-        <v>128.1649932861328</v>
+        <v>133.6999969482422</v>
       </c>
       <c r="D143" t="n">
-        <v>125.1650009155273</v>
+        <v>127.5500030517578</v>
       </c>
       <c r="E143" t="n">
-        <v>126.25</v>
+        <v>133.6399993896484</v>
       </c>
       <c r="F143" t="n">
-        <v>3033100</v>
+        <v>5758000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B144" t="n">
-        <v>127.8499984741211</v>
+        <v>143</v>
       </c>
       <c r="C144" t="n">
-        <v>133.6999969482422</v>
+        <v>146.1600036621094</v>
       </c>
       <c r="D144" t="n">
-        <v>127.5500030517578</v>
+        <v>141.1199951171875</v>
       </c>
       <c r="E144" t="n">
-        <v>133.6399993896484</v>
+        <v>145.0700073242188</v>
       </c>
       <c r="F144" t="n">
-        <v>5758000</v>
+        <v>12136800</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B145" t="n">
-        <v>143</v>
+        <v>145.1100006103516</v>
       </c>
       <c r="C145" t="n">
-        <v>146.1600036621094</v>
+        <v>146.1900024414062</v>
       </c>
       <c r="D145" t="n">
-        <v>141.1199951171875</v>
+        <v>141.1100006103516</v>
       </c>
       <c r="E145" t="n">
-        <v>145.0700073242188</v>
+        <v>146.0500030517578</v>
       </c>
       <c r="F145" t="n">
-        <v>12136800</v>
+        <v>7266100</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B146" t="n">
-        <v>145.1100006103516</v>
+        <v>147.5399932861328</v>
       </c>
       <c r="C146" t="n">
-        <v>146.1900024414062</v>
+        <v>149.3399963378906</v>
       </c>
       <c r="D146" t="n">
-        <v>141.1100006103516</v>
+        <v>145.3999938964844</v>
       </c>
       <c r="E146" t="n">
-        <v>146.0500030517578</v>
+        <v>147.3500061035156</v>
       </c>
       <c r="F146" t="n">
-        <v>7266100</v>
+        <v>7054100</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B147" t="n">
-        <v>147.5399932861328</v>
+        <v>146.7299957275391</v>
       </c>
       <c r="C147" t="n">
-        <v>149.3399963378906</v>
+        <v>152.1399993896484</v>
       </c>
       <c r="D147" t="n">
-        <v>145.3999938964844</v>
+        <v>144.7960052490234</v>
       </c>
       <c r="E147" t="n">
-        <v>147.3500061035156</v>
+        <v>152.0200042724609</v>
       </c>
       <c r="F147" t="n">
-        <v>7054100</v>
+        <v>7217900</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B148" t="n">
-        <v>146.7299957275391</v>
+        <v>153.9900054931641</v>
       </c>
       <c r="C148" t="n">
-        <v>152.1399993896484</v>
+        <v>155.4100036621094</v>
       </c>
       <c r="D148" t="n">
-        <v>144.7960052490234</v>
+        <v>150.9859924316406</v>
       </c>
       <c r="E148" t="n">
-        <v>152.0200042724609</v>
+        <v>154.3699951171875</v>
       </c>
       <c r="F148" t="n">
-        <v>7217900</v>
+        <v>7114000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B149" t="n">
-        <v>153.9900054931641</v>
+        <v>154.8200073242188</v>
       </c>
       <c r="C149" t="n">
-        <v>155.4100036621094</v>
+        <v>155.2250061035156</v>
       </c>
       <c r="D149" t="n">
-        <v>150.9859924316406</v>
+        <v>150.5200042724609</v>
       </c>
       <c r="E149" t="n">
-        <v>154.3699951171875</v>
+        <v>154.3300018310547</v>
       </c>
       <c r="F149" t="n">
-        <v>7114000</v>
+        <v>5835300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B150" t="n">
-        <v>154.8200073242188</v>
+        <v>155.9199981689453</v>
       </c>
       <c r="C150" t="n">
-        <v>155.2250061035156</v>
+        <v>161.0099945068359</v>
       </c>
       <c r="D150" t="n">
-        <v>150.5200042724609</v>
+        <v>153.3600006103516</v>
       </c>
       <c r="E150" t="n">
-        <v>154.3300018310547</v>
+        <v>161.0099945068359</v>
       </c>
       <c r="F150" t="n">
-        <v>5835300</v>
+        <v>7205600</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B151" t="n">
-        <v>155.9199981689453</v>
+        <v>162.2350006103516</v>
       </c>
       <c r="C151" t="n">
-        <v>161.0099945068359</v>
+        <v>165.2799987792969</v>
       </c>
       <c r="D151" t="n">
-        <v>153.3600006103516</v>
+        <v>160.4700012207031</v>
       </c>
       <c r="E151" t="n">
-        <v>161.0099945068359</v>
+        <v>164.2299957275391</v>
       </c>
       <c r="F151" t="n">
-        <v>7205600</v>
+        <v>8216400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B152" t="n">
-        <v>162.2350006103516</v>
+        <v>165</v>
       </c>
       <c r="C152" t="n">
-        <v>165.2799987792969</v>
+        <v>167.8999938964844</v>
       </c>
       <c r="D152" t="n">
-        <v>160.4700012207031</v>
+        <v>164.4900054931641</v>
       </c>
       <c r="E152" t="n">
-        <v>164.2299957275391</v>
+        <v>166.8500061035156</v>
       </c>
       <c r="F152" t="n">
-        <v>8216400</v>
+        <v>6113300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B153" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C153" t="n">
-        <v>167.8999938964844</v>
+        <v>173.8500061035156</v>
       </c>
       <c r="D153" t="n">
-        <v>164.4900054931641</v>
+        <v>167.2200012207031</v>
       </c>
       <c r="E153" t="n">
-        <v>166.8500061035156</v>
+        <v>172.8600006103516</v>
       </c>
       <c r="F153" t="n">
-        <v>6113300</v>
+        <v>8918900</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B154" t="n">
-        <v>170</v>
+        <v>174.3999938964844</v>
       </c>
       <c r="C154" t="n">
-        <v>173.8500061035156</v>
+        <v>178.4799957275391</v>
       </c>
       <c r="D154" t="n">
-        <v>167.2200012207031</v>
+        <v>171.1399993896484</v>
       </c>
       <c r="E154" t="n">
-        <v>172.8600006103516</v>
+        <v>177.7299957275391</v>
       </c>
       <c r="F154" t="n">
-        <v>8918900</v>
+        <v>8699400</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B155" t="n">
-        <v>174.3999938964844</v>
+        <v>177.5</v>
       </c>
       <c r="C155" t="n">
-        <v>178.4799957275391</v>
+        <v>177.75</v>
       </c>
       <c r="D155" t="n">
-        <v>171.1399993896484</v>
+        <v>169.3800048828125</v>
       </c>
       <c r="E155" t="n">
-        <v>177.7299957275391</v>
+        <v>172.5500030517578</v>
       </c>
       <c r="F155" t="n">
-        <v>8699400</v>
+        <v>7428000</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B156" t="n">
-        <v>177.5</v>
+        <v>174.5299987792969</v>
       </c>
       <c r="C156" t="n">
-        <v>177.75</v>
+        <v>179.8000030517578</v>
       </c>
       <c r="D156" t="n">
-        <v>169.3800048828125</v>
+        <v>173.5200042724609</v>
       </c>
       <c r="E156" t="n">
-        <v>172.5500030517578</v>
+        <v>176.9100036621094</v>
       </c>
       <c r="F156" t="n">
-        <v>7428000</v>
+        <v>7508000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B157" t="n">
-        <v>174.5299987792969</v>
+        <v>176.7200012207031</v>
       </c>
       <c r="C157" t="n">
-        <v>179.8000030517578</v>
+        <v>176.7599945068359</v>
       </c>
       <c r="D157" t="n">
-        <v>173.5200042724609</v>
+        <v>168.5099945068359</v>
       </c>
       <c r="E157" t="n">
-        <v>176.9100036621094</v>
+        <v>172.4700012207031</v>
       </c>
       <c r="F157" t="n">
-        <v>7508000</v>
+        <v>6782500</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B158" t="n">
-        <v>176.7200012207031</v>
+        <v>166.4799957275391</v>
       </c>
       <c r="C158" t="n">
-        <v>176.7599945068359</v>
+        <v>167.8200073242188</v>
       </c>
       <c r="D158" t="n">
-        <v>168.5099945068359</v>
+        <v>162.25</v>
       </c>
       <c r="E158" t="n">
-        <v>172.4700012207031</v>
+        <v>165.2899932861328</v>
       </c>
       <c r="F158" t="n">
-        <v>6782500</v>
+        <v>7414100</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B159" t="n">
-        <v>166.4799957275391</v>
+        <v>166.1000061035156</v>
       </c>
       <c r="C159" t="n">
-        <v>167.8200073242188</v>
+        <v>168.7299957275391</v>
       </c>
       <c r="D159" t="n">
-        <v>162.25</v>
+        <v>163.4199981689453</v>
       </c>
       <c r="E159" t="n">
-        <v>165.2899932861328</v>
+        <v>168.6799926757812</v>
       </c>
       <c r="F159" t="n">
-        <v>7414100</v>
+        <v>6270500</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B160" t="n">
-        <v>166.1000061035156</v>
+        <v>172.0099945068359</v>
       </c>
       <c r="C160" t="n">
-        <v>168.7299957275391</v>
+        <v>173.5800018310547</v>
       </c>
       <c r="D160" t="n">
-        <v>163.4199981689453</v>
+        <v>167.7599945068359</v>
       </c>
       <c r="E160" t="n">
-        <v>168.6799926757812</v>
+        <v>172.7100067138672</v>
       </c>
       <c r="F160" t="n">
-        <v>6270500</v>
+        <v>6141700</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B161" t="n">
-        <v>172.0099945068359</v>
+        <v>172.9900054931641</v>
       </c>
       <c r="C161" t="n">
-        <v>173.5800018310547</v>
+        <v>177.1799926757812</v>
       </c>
       <c r="D161" t="n">
-        <v>167.7599945068359</v>
+        <v>172</v>
       </c>
       <c r="E161" t="n">
-        <v>172.7100067138672</v>
+        <v>172.6999969482422</v>
       </c>
       <c r="F161" t="n">
-        <v>6141700</v>
+        <v>7652400</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B162" t="n">
-        <v>172.9900054931641</v>
+        <v>175.6799926757812</v>
       </c>
       <c r="C162" t="n">
-        <v>177.1799926757812</v>
+        <v>179.1000061035156</v>
       </c>
       <c r="D162" t="n">
-        <v>172</v>
+        <v>172.2850036621094</v>
       </c>
       <c r="E162" t="n">
-        <v>172.6999969482422</v>
+        <v>172.6199951171875</v>
       </c>
       <c r="F162" t="n">
-        <v>7652400</v>
+        <v>7167900</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B163" t="n">
-        <v>175.6799926757812</v>
+        <v>177</v>
       </c>
       <c r="C163" t="n">
-        <v>179.1000061035156</v>
+        <v>177.2200012207031</v>
       </c>
       <c r="D163" t="n">
-        <v>172.2850036621094</v>
+        <v>169.8899993896484</v>
       </c>
       <c r="E163" t="n">
-        <v>172.6199951171875</v>
+        <v>170.2200012207031</v>
       </c>
       <c r="F163" t="n">
-        <v>7167900</v>
+        <v>15684800</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B164" t="n">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="C164" t="n">
-        <v>177.2200012207031</v>
+        <v>154.8300018310547</v>
       </c>
       <c r="D164" t="n">
-        <v>169.8899993896484</v>
+        <v>140.5800018310547</v>
       </c>
       <c r="E164" t="n">
-        <v>170.2200012207031</v>
+        <v>147.0599975585938</v>
       </c>
       <c r="F164" t="n">
-        <v>15684800</v>
+        <v>35627200</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B165" t="n">
-        <v>153</v>
+        <v>149.2200012207031</v>
       </c>
       <c r="C165" t="n">
-        <v>154.8300018310547</v>
+        <v>149.4400024414062</v>
       </c>
       <c r="D165" t="n">
-        <v>140.5800018310547</v>
+        <v>139.6799926757812</v>
       </c>
       <c r="E165" t="n">
-        <v>147.0599975585938</v>
+        <v>141.75</v>
       </c>
       <c r="F165" t="n">
-        <v>35627200</v>
+        <v>18255700</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B166" t="n">
-        <v>149.2200012207031</v>
+        <v>142.6499938964844</v>
       </c>
       <c r="C166" t="n">
-        <v>149.4400024414062</v>
+        <v>143.9900054931641</v>
       </c>
       <c r="D166" t="n">
-        <v>139.6799926757812</v>
+        <v>138.6000061035156</v>
       </c>
       <c r="E166" t="n">
-        <v>141.75</v>
+        <v>141.7700042724609</v>
       </c>
       <c r="F166" t="n">
-        <v>18255700</v>
+        <v>20371600</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B167" t="n">
-        <v>142.6499938964844</v>
+        <v>141.3999938964844</v>
       </c>
       <c r="C167" t="n">
-        <v>143.9900054931641</v>
+        <v>142.6199951171875</v>
       </c>
       <c r="D167" t="n">
-        <v>138.6000061035156</v>
+        <v>135.1300048828125</v>
       </c>
       <c r="E167" t="n">
-        <v>141.7700042724609</v>
+        <v>136.4299926757812</v>
       </c>
       <c r="F167" t="n">
-        <v>20371600</v>
+        <v>18520900</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B168" t="n">
-        <v>141.3999938964844</v>
+        <v>136.7799987792969</v>
       </c>
       <c r="C168" t="n">
-        <v>142.6199951171875</v>
+        <v>142.9400024414062</v>
       </c>
       <c r="D168" t="n">
-        <v>135.1300048828125</v>
+        <v>135.3699951171875</v>
       </c>
       <c r="E168" t="n">
-        <v>136.4299926757812</v>
+        <v>142.5399932861328</v>
       </c>
       <c r="F168" t="n">
-        <v>18520900</v>
+        <v>12796100</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B169" t="n">
-        <v>136.7799987792969</v>
+        <v>144.8000030517578</v>
       </c>
       <c r="C169" t="n">
-        <v>142.9400024414062</v>
+        <v>147.3099975585938</v>
       </c>
       <c r="D169" t="n">
-        <v>135.3699951171875</v>
+        <v>140.3000030517578</v>
       </c>
       <c r="E169" t="n">
-        <v>142.5399932861328</v>
+        <v>140.6900024414062</v>
       </c>
       <c r="F169" t="n">
-        <v>12796100</v>
+        <v>14164600</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B170" t="n">
-        <v>144.8000030517578</v>
+        <v>142.5</v>
       </c>
       <c r="C170" t="n">
-        <v>147.3099975585938</v>
+        <v>147.8899993896484</v>
       </c>
       <c r="D170" t="n">
-        <v>140.3000030517578</v>
+        <v>141</v>
       </c>
       <c r="E170" t="n">
-        <v>140.6900024414062</v>
+        <v>147.8099975585938</v>
       </c>
       <c r="F170" t="n">
-        <v>14164600</v>
+        <v>15728200</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B171" t="n">
-        <v>142.5</v>
+        <v>144.9900054931641</v>
       </c>
       <c r="C171" t="n">
-        <v>147.8899993896484</v>
+        <v>145.8999938964844</v>
       </c>
       <c r="D171" t="n">
-        <v>141</v>
+        <v>141.7799987792969</v>
       </c>
       <c r="E171" t="n">
-        <v>147.8099975585938</v>
+        <v>141.9700012207031</v>
       </c>
       <c r="F171" t="n">
-        <v>15728200</v>
+        <v>10833000</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B172" t="n">
-        <v>144.9900054931641</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="C172" t="n">
-        <v>145.8999938964844</v>
+        <v>143.6699981689453</v>
       </c>
       <c r="D172" t="n">
-        <v>141.7799987792969</v>
+        <v>138.6399993896484</v>
       </c>
       <c r="E172" t="n">
-        <v>141.9700012207031</v>
+        <v>141.7100067138672</v>
       </c>
       <c r="F172" t="n">
-        <v>10833000</v>
+        <v>8634500</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B173" t="n">
-        <v>143.0200042724609</v>
+        <v>139.5800018310547</v>
       </c>
       <c r="C173" t="n">
-        <v>143.6699981689453</v>
+        <v>142.5</v>
       </c>
       <c r="D173" t="n">
-        <v>138.6399993896484</v>
+        <v>137</v>
       </c>
       <c r="E173" t="n">
-        <v>141.7100067138672</v>
+        <v>141.5800018310547</v>
       </c>
       <c r="F173" t="n">
-        <v>8634500</v>
+        <v>8800800</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B174" t="n">
-        <v>139.5800018310547</v>
+        <v>142</v>
       </c>
       <c r="C174" t="n">
-        <v>142.5</v>
+        <v>143.2599945068359</v>
       </c>
       <c r="D174" t="n">
-        <v>137</v>
+        <v>137.5</v>
       </c>
       <c r="E174" t="n">
-        <v>141.5800018310547</v>
+        <v>140.4900054931641</v>
       </c>
       <c r="F174" t="n">
-        <v>8800800</v>
+        <v>9617000</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B175" t="n">
-        <v>142</v>
+        <v>139.3000030517578</v>
       </c>
       <c r="C175" t="n">
-        <v>143.2599945068359</v>
+        <v>148.9900054931641</v>
       </c>
       <c r="D175" t="n">
-        <v>137.5</v>
+        <v>139.125</v>
       </c>
       <c r="E175" t="n">
-        <v>140.4900054931641</v>
+        <v>148.5899963378906</v>
       </c>
       <c r="F175" t="n">
-        <v>9617000</v>
+        <v>11620600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B176" t="n">
-        <v>139.3000030517578</v>
+        <v>152.2599945068359</v>
       </c>
       <c r="C176" t="n">
-        <v>148.9900054931641</v>
+        <v>154.3899993896484</v>
       </c>
       <c r="D176" t="n">
-        <v>139.125</v>
+        <v>149</v>
       </c>
       <c r="E176" t="n">
-        <v>148.5899963378906</v>
+        <v>154.0299987792969</v>
       </c>
       <c r="F176" t="n">
-        <v>11620600</v>
+        <v>10554600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B177" t="n">
-        <v>152.2599945068359</v>
+        <v>157.5050048828125</v>
       </c>
       <c r="C177" t="n">
-        <v>154.3899993896484</v>
+        <v>160.1399993896484</v>
       </c>
       <c r="D177" t="n">
-        <v>149</v>
+        <v>153.8899993896484</v>
       </c>
       <c r="E177" t="n">
-        <v>154.0299987792969</v>
+        <v>158.0099945068359</v>
       </c>
       <c r="F177" t="n">
-        <v>10554600</v>
+        <v>11835300</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B178" t="n">
-        <v>157.5050048828125</v>
+        <v>157.8500061035156</v>
       </c>
       <c r="C178" t="n">
-        <v>160.1399993896484</v>
+        <v>158.1100006103516</v>
       </c>
       <c r="D178" t="n">
-        <v>153.8899993896484</v>
+        <v>153.5700073242188</v>
       </c>
       <c r="E178" t="n">
-        <v>158.0099945068359</v>
+        <v>154.3099975585938</v>
       </c>
       <c r="F178" t="n">
-        <v>11835300</v>
+        <v>6982200</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B179" t="n">
-        <v>157.8500061035156</v>
+        <v>154</v>
       </c>
       <c r="C179" t="n">
-        <v>158.1100006103516</v>
+        <v>156.3800048828125</v>
       </c>
       <c r="D179" t="n">
-        <v>153.5700073242188</v>
+        <v>150.6600036621094</v>
       </c>
       <c r="E179" t="n">
-        <v>154.3099975585938</v>
+        <v>155.2700042724609</v>
       </c>
       <c r="F179" t="n">
-        <v>6982200</v>
+        <v>7194300</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B180" t="n">
-        <v>154</v>
+        <v>157.3999938964844</v>
       </c>
       <c r="C180" t="n">
-        <v>156.3800048828125</v>
+        <v>161.5</v>
       </c>
       <c r="D180" t="n">
-        <v>150.6600036621094</v>
+        <v>155.8000030517578</v>
       </c>
       <c r="E180" t="n">
-        <v>155.2700042724609</v>
+        <v>159.4700012207031</v>
       </c>
       <c r="F180" t="n">
-        <v>7194300</v>
+        <v>15385900</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B181" t="n">
-        <v>157.3999938964844</v>
+        <v>162.1399993896484</v>
       </c>
       <c r="C181" t="n">
-        <v>161.5</v>
+        <v>172.3300018310547</v>
       </c>
       <c r="D181" t="n">
-        <v>155.8000030517578</v>
+        <v>161.2799987792969</v>
       </c>
       <c r="E181" t="n">
-        <v>159.4700012207031</v>
+        <v>170.6799926757812</v>
       </c>
       <c r="F181" t="n">
-        <v>15385900</v>
+        <v>9991500</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B182" t="n">
-        <v>162.1399993896484</v>
+        <v>170.6999969482422</v>
       </c>
       <c r="C182" t="n">
-        <v>172.3300018310547</v>
+        <v>177.4799957275391</v>
       </c>
       <c r="D182" t="n">
-        <v>161.2799987792969</v>
+        <v>170.6900024414062</v>
       </c>
       <c r="E182" t="n">
-        <v>170.6799926757812</v>
+        <v>175.3300018310547</v>
       </c>
       <c r="F182" t="n">
-        <v>9991500</v>
+        <v>9144300</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B183" t="n">
-        <v>170.6999969482422</v>
+        <v>175.4900054931641</v>
       </c>
       <c r="C183" t="n">
         <v>177.4799957275391</v>
       </c>
       <c r="D183" t="n">
-        <v>170.6900024414062</v>
+        <v>168.7100067138672</v>
       </c>
       <c r="E183" t="n">
-        <v>175.3300018310547</v>
+        <v>174.3699951171875</v>
       </c>
       <c r="F183" t="n">
-        <v>9144300</v>
+        <v>8069700</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B184" t="n">
-        <v>175.4900054931641</v>
+        <v>163.0800018310547</v>
       </c>
       <c r="C184" t="n">
-        <v>177.4799957275391</v>
+        <v>167.7899932861328</v>
       </c>
       <c r="D184" t="n">
-        <v>168.7100067138672</v>
+        <v>157.3999938964844</v>
       </c>
       <c r="E184" t="n">
-        <v>174.3699951171875</v>
+        <v>166.0099945068359</v>
       </c>
       <c r="F184" t="n">
-        <v>8069700</v>
+        <v>10214000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B185" t="n">
-        <v>163.0800018310547</v>
+        <v>159.4600067138672</v>
       </c>
       <c r="C185" t="n">
-        <v>167.7899932861328</v>
+        <v>161.1929931640625</v>
       </c>
       <c r="D185" t="n">
-        <v>157.3999938964844</v>
+        <v>152.1900024414062</v>
       </c>
       <c r="E185" t="n">
-        <v>166.0099945068359</v>
+        <v>154.2700042724609</v>
       </c>
       <c r="F185" t="n">
-        <v>10214000</v>
+        <v>9094700</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B186" t="n">
-        <v>159.4600067138672</v>
+        <v>157.9499969482422</v>
       </c>
       <c r="C186" t="n">
-        <v>161.1929931640625</v>
+        <v>159.2299957275391</v>
       </c>
       <c r="D186" t="n">
-        <v>152.1900024414062</v>
+        <v>153.2530059814453</v>
       </c>
       <c r="E186" t="n">
-        <v>154.2700042724609</v>
+        <v>156.3999938964844</v>
       </c>
       <c r="F186" t="n">
-        <v>9094700</v>
+        <v>6043100</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B187" t="n">
-        <v>157.9499969482422</v>
+        <v>157.75</v>
       </c>
       <c r="C187" t="n">
-        <v>159.2299957275391</v>
+        <v>158.9900054931641</v>
       </c>
       <c r="D187" t="n">
-        <v>153.2530059814453</v>
+        <v>145.3200073242188</v>
       </c>
       <c r="E187" t="n">
-        <v>156.3999938964844</v>
+        <v>152.1600036621094</v>
       </c>
       <c r="F187" t="n">
-        <v>6043100</v>
+        <v>7334100</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B188" t="n">
-        <v>157.75</v>
+        <v>151</v>
       </c>
       <c r="C188" t="n">
-        <v>158.9900054931641</v>
+        <v>154.9700012207031</v>
       </c>
       <c r="D188" t="n">
-        <v>145.3200073242188</v>
+        <v>149</v>
       </c>
       <c r="E188" t="n">
-        <v>152.1600036621094</v>
+        <v>151.7599945068359</v>
       </c>
       <c r="F188" t="n">
-        <v>7334100</v>
+        <v>6867400</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B189" t="n">
-        <v>151</v>
+        <v>153.5800018310547</v>
       </c>
       <c r="C189" t="n">
-        <v>154.9700012207031</v>
+        <v>157.0700073242188</v>
       </c>
       <c r="D189" t="n">
-        <v>149</v>
+        <v>150.2799987792969</v>
       </c>
       <c r="E189" t="n">
-        <v>151.7599945068359</v>
+        <v>156.3999938964844</v>
       </c>
       <c r="F189" t="n">
-        <v>6867400</v>
+        <v>5326700</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B190" t="n">
-        <v>153.5800018310547</v>
+        <v>160.1100006103516</v>
       </c>
       <c r="C190" t="n">
-        <v>157.0700073242188</v>
+        <v>165.25</v>
       </c>
       <c r="D190" t="n">
-        <v>150.2799987792969</v>
+        <v>159.1349945068359</v>
       </c>
       <c r="E190" t="n">
-        <v>156.3999938964844</v>
+        <v>163.2400054931641</v>
       </c>
       <c r="F190" t="n">
-        <v>5326700</v>
+        <v>6052500</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B191" t="n">
-        <v>160.1100006103516</v>
+        <v>165.9600067138672</v>
       </c>
       <c r="C191" t="n">
-        <v>165.25</v>
+        <v>169.2799987792969</v>
       </c>
       <c r="D191" t="n">
-        <v>159.1349945068359</v>
+        <v>163.5099945068359</v>
       </c>
       <c r="E191" t="n">
-        <v>163.2400054931641</v>
+        <v>169.0899963378906</v>
       </c>
       <c r="F191" t="n">
-        <v>6052500</v>
+        <v>7240800</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B192" t="n">
-        <v>165.9600067138672</v>
+        <v>169.3000030517578</v>
       </c>
       <c r="C192" t="n">
-        <v>169.2799987792969</v>
+        <v>171.2100067138672</v>
       </c>
       <c r="D192" t="n">
-        <v>163.5099945068359</v>
+        <v>166.7799987792969</v>
       </c>
       <c r="E192" t="n">
-        <v>169.0899963378906</v>
+        <v>168.0099945068359</v>
       </c>
       <c r="F192" t="n">
-        <v>7240800</v>
+        <v>8090900</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B193" t="n">
-        <v>169.3000030517578</v>
+        <v>169.8899993896484</v>
       </c>
       <c r="C193" t="n">
-        <v>171.2100067138672</v>
+        <v>171.2899932861328</v>
       </c>
       <c r="D193" t="n">
-        <v>166.7799987792969</v>
+        <v>163.9299926757812</v>
       </c>
       <c r="E193" t="n">
-        <v>168.0099945068359</v>
+        <v>164.9299926757812</v>
       </c>
       <c r="F193" t="n">
-        <v>8090900</v>
+        <v>6229500</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B194" t="n">
-        <v>169.8899993896484</v>
+        <v>171.1999969482422</v>
       </c>
       <c r="C194" t="n">
-        <v>171.2899932861328</v>
+        <v>172</v>
       </c>
       <c r="D194" t="n">
-        <v>163.9299926757812</v>
+        <v>167.5850067138672</v>
       </c>
       <c r="E194" t="n">
-        <v>164.9299926757812</v>
+        <v>169.6699981689453</v>
       </c>
       <c r="F194" t="n">
-        <v>6229500</v>
+        <v>11130400</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B195" t="n">
-        <v>171.1999969482422</v>
+        <v>170.1100006103516</v>
       </c>
       <c r="C195" t="n">
-        <v>172</v>
+        <v>175.1999969482422</v>
       </c>
       <c r="D195" t="n">
-        <v>167.5850067138672</v>
+        <v>166.6600036621094</v>
       </c>
       <c r="E195" t="n">
-        <v>169.6699981689453</v>
+        <v>174.5599975585938</v>
       </c>
       <c r="F195" t="n">
-        <v>11130400</v>
+        <v>9494400</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B196" t="n">
-        <v>170.1100006103516</v>
+        <v>165.4299926757812</v>
       </c>
       <c r="C196" t="n">
-        <v>175.1999969482422</v>
+        <v>165.4299926757812</v>
       </c>
       <c r="D196" t="n">
-        <v>166.6600036621094</v>
+        <v>159.3600006103516</v>
       </c>
       <c r="E196" t="n">
-        <v>174.5599975585938</v>
+        <v>162.1999969482422</v>
       </c>
       <c r="F196" t="n">
-        <v>9494400</v>
+        <v>7770100</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B197" t="n">
-        <v>165.4299926757812</v>
+        <v>162.3249969482422</v>
       </c>
       <c r="C197" t="n">
-        <v>165.4299926757812</v>
+        <v>165.6799926757812</v>
       </c>
       <c r="D197" t="n">
-        <v>159.3600006103516</v>
+        <v>160.5700073242188</v>
       </c>
       <c r="E197" t="n">
-        <v>162.1999969482422</v>
+        <v>161.7400054931641</v>
       </c>
       <c r="F197" t="n">
-        <v>7770100</v>
+        <v>6350600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B198" t="n">
-        <v>162.3249969482422</v>
+        <v>167.7599945068359</v>
       </c>
       <c r="C198" t="n">
-        <v>165.6799926757812</v>
+        <v>170.1600036621094</v>
       </c>
       <c r="D198" t="n">
-        <v>160.5700073242188</v>
+        <v>159.4600067138672</v>
       </c>
       <c r="E198" t="n">
-        <v>161.7400054931641</v>
+        <v>165.4499969482422</v>
       </c>
       <c r="F198" t="n">
-        <v>6350600</v>
+        <v>8231200</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B199" t="n">
-        <v>167.7599945068359</v>
+        <v>159.9400024414062</v>
       </c>
       <c r="C199" t="n">
-        <v>170.1600036621094</v>
+        <v>161.2299957275391</v>
       </c>
       <c r="D199" t="n">
-        <v>159.4600067138672</v>
+        <v>154.7400054931641</v>
       </c>
       <c r="E199" t="n">
-        <v>165.4499969482422</v>
+        <v>157.6000061035156</v>
       </c>
       <c r="F199" t="n">
-        <v>8231200</v>
+        <v>11865200</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B200" t="n">
-        <v>159.9400024414062</v>
+        <v>158.8600006103516</v>
       </c>
       <c r="C200" t="n">
-        <v>161.2299957275391</v>
+        <v>165.6600036621094</v>
       </c>
       <c r="D200" t="n">
-        <v>154.7400054931641</v>
+        <v>155.2200012207031</v>
       </c>
       <c r="E200" t="n">
-        <v>157.6000061035156</v>
+        <v>164.1000061035156</v>
       </c>
       <c r="F200" t="n">
-        <v>11865200</v>
+        <v>8535700</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B201" t="n">
-        <v>158.8600006103516</v>
+        <v>164.1100006103516</v>
       </c>
       <c r="C201" t="n">
-        <v>165.6600036621094</v>
+        <v>172.5489959716797</v>
       </c>
       <c r="D201" t="n">
-        <v>155.2200012207031</v>
+        <v>162.6999969482422</v>
       </c>
       <c r="E201" t="n">
-        <v>164.1000061035156</v>
+        <v>169.8800048828125</v>
       </c>
       <c r="F201" t="n">
-        <v>8535700</v>
+        <v>10281800</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B202" t="n">
-        <v>164.1100006103516</v>
+        <v>165.5549926757812</v>
       </c>
       <c r="C202" t="n">
-        <v>172.5489959716797</v>
+        <v>170.5</v>
       </c>
       <c r="D202" t="n">
-        <v>162.6999969482422</v>
+        <v>159.1999969482422</v>
       </c>
       <c r="E202" t="n">
-        <v>169.8800048828125</v>
+        <v>166.6199951171875</v>
       </c>
       <c r="F202" t="n">
-        <v>10281800</v>
+        <v>9098200</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B203" t="n">
-        <v>165.5549926757812</v>
+        <v>166.3600006103516</v>
       </c>
       <c r="C203" t="n">
-        <v>170.5</v>
+        <v>167.7350006103516</v>
       </c>
       <c r="D203" t="n">
-        <v>159.1999969482422</v>
+        <v>156.6499938964844</v>
       </c>
       <c r="E203" t="n">
-        <v>166.6199951171875</v>
+        <v>159.9900054931641</v>
       </c>
       <c r="F203" t="n">
-        <v>9098200</v>
+        <v>9764500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B204" t="n">
-        <v>166.3600006103516</v>
+        <v>162.8650054931641</v>
       </c>
       <c r="C204" t="n">
-        <v>167.7350006103516</v>
+        <v>177.1999969482422</v>
       </c>
       <c r="D204" t="n">
-        <v>156.6499938964844</v>
+        <v>161.3600006103516</v>
       </c>
       <c r="E204" t="n">
-        <v>159.9900054931641</v>
+        <v>173.2799987792969</v>
       </c>
       <c r="F204" t="n">
-        <v>9764500</v>
+        <v>8509300</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B205" t="n">
-        <v>162.8650054931641</v>
+        <v>169.1000061035156</v>
       </c>
       <c r="C205" t="n">
-        <v>177.1999969482422</v>
+        <v>169.2299957275391</v>
       </c>
       <c r="D205" t="n">
-        <v>161.3600006103516</v>
+        <v>162.5899963378906</v>
       </c>
       <c r="E205" t="n">
-        <v>173.2799987792969</v>
+        <v>166.4600067138672</v>
       </c>
       <c r="F205" t="n">
-        <v>8509300</v>
+        <v>8969200</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B206" t="n">
-        <v>169.1000061035156</v>
+        <v>166.1799926757812</v>
       </c>
       <c r="C206" t="n">
-        <v>169.2299957275391</v>
+        <v>181.2700042724609</v>
       </c>
       <c r="D206" t="n">
-        <v>162.5899963378906</v>
+        <v>165.9900054931641</v>
       </c>
       <c r="E206" t="n">
-        <v>166.4600067138672</v>
+        <v>181.0500030517578</v>
       </c>
       <c r="F206" t="n">
-        <v>8969200</v>
+        <v>11912800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B207" t="n">
-        <v>166.1799926757812</v>
+        <v>187</v>
       </c>
       <c r="C207" t="n">
-        <v>181.2700042724609</v>
+        <v>189.8170013427734</v>
       </c>
       <c r="D207" t="n">
-        <v>165.9900054931641</v>
+        <v>179.8000030517578</v>
       </c>
       <c r="E207" t="n">
-        <v>181.0500030517578</v>
+        <v>184.6900024414062</v>
       </c>
       <c r="F207" t="n">
-        <v>11912800</v>
+        <v>9932000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B208" t="n">
-        <v>187</v>
+        <v>185.2969970703125</v>
       </c>
       <c r="C208" t="n">
-        <v>189.8170013427734</v>
+        <v>187.6199951171875</v>
       </c>
       <c r="D208" t="n">
-        <v>179.8000030517578</v>
+        <v>182.5</v>
       </c>
       <c r="E208" t="n">
-        <v>184.6900024414062</v>
+        <v>186.9600067138672</v>
       </c>
       <c r="F208" t="n">
-        <v>9932000</v>
+        <v>5592500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B209" t="n">
-        <v>185.2969970703125</v>
+        <v>186.2649993896484</v>
       </c>
       <c r="C209" t="n">
-        <v>187.6199951171875</v>
+        <v>189.5599975585938</v>
       </c>
       <c r="D209" t="n">
-        <v>182.5</v>
+        <v>180.5</v>
       </c>
       <c r="E209" t="n">
-        <v>186.9600067138672</v>
+        <v>181.1499938964844</v>
       </c>
       <c r="F209" t="n">
-        <v>5592500</v>
+        <v>9149500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B210" t="n">
-        <v>186.2649993896484</v>
+        <v>183.8999938964844</v>
       </c>
       <c r="C210" t="n">
-        <v>189.5599975585938</v>
+        <v>185.6000061035156</v>
       </c>
       <c r="D210" t="n">
-        <v>180.5</v>
+        <v>175.6900024414062</v>
       </c>
       <c r="E210" t="n">
-        <v>181.1499938964844</v>
+        <v>182.5700073242188</v>
       </c>
       <c r="F210" t="n">
-        <v>9149500</v>
+        <v>7566300</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B211" t="n">
-        <v>183.8999938964844</v>
+        <v>184</v>
       </c>
       <c r="C211" t="n">
-        <v>185.6000061035156</v>
+        <v>186.2100067138672</v>
       </c>
       <c r="D211" t="n">
-        <v>175.6900024414062</v>
+        <v>166.5</v>
       </c>
       <c r="E211" t="n">
-        <v>182.5700073242188</v>
+        <v>171.9199981689453</v>
       </c>
       <c r="F211" t="n">
-        <v>7566300</v>
+        <v>8095900</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B212" t="n">
-        <v>184</v>
+        <v>169.2100067138672</v>
       </c>
       <c r="C212" t="n">
-        <v>186.2100067138672</v>
+        <v>170.281005859375</v>
       </c>
       <c r="D212" t="n">
-        <v>166.5</v>
+        <v>163.6799926757812</v>
       </c>
       <c r="E212" t="n">
-        <v>171.9199981689453</v>
+        <v>168.5599975585938</v>
       </c>
       <c r="F212" t="n">
-        <v>8095900</v>
+        <v>8412300</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B213" t="n">
-        <v>169.2100067138672</v>
+        <v>163.1049957275391</v>
       </c>
       <c r="C213" t="n">
-        <v>170.281005859375</v>
+        <v>171.4299926757812</v>
       </c>
       <c r="D213" t="n">
-        <v>163.6799926757812</v>
+        <v>157.1300048828125</v>
       </c>
       <c r="E213" t="n">
-        <v>168.5599975585938</v>
+        <v>168.6100006103516</v>
       </c>
       <c r="F213" t="n">
-        <v>8412300</v>
+        <v>7560400</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B214" t="n">
-        <v>163.1049957275391</v>
+        <v>168.9400024414062</v>
       </c>
       <c r="C214" t="n">
-        <v>171.4299926757812</v>
+        <v>172.6000061035156</v>
       </c>
       <c r="D214" t="n">
-        <v>157.1300048828125</v>
+        <v>168.3200073242188</v>
       </c>
       <c r="E214" t="n">
-        <v>168.6100006103516</v>
+        <v>169.3500061035156</v>
       </c>
       <c r="F214" t="n">
-        <v>7560400</v>
+        <v>6025900</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B215" t="n">
-        <v>168.9400024414062</v>
+        <v>174.4400024414062</v>
       </c>
       <c r="C215" t="n">
-        <v>172.6000061035156</v>
+        <v>177.8800048828125</v>
       </c>
       <c r="D215" t="n">
-        <v>168.3200073242188</v>
+        <v>172.1000061035156</v>
       </c>
       <c r="E215" t="n">
-        <v>169.3500061035156</v>
+        <v>174.5800018310547</v>
       </c>
       <c r="F215" t="n">
-        <v>6025900</v>
+        <v>6357800</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B216" t="n">
-        <v>174.4400024414062</v>
+        <v>171.1349945068359</v>
       </c>
       <c r="C216" t="n">
-        <v>177.8800048828125</v>
+        <v>176.4100036621094</v>
       </c>
       <c r="D216" t="n">
-        <v>172.1000061035156</v>
+        <v>170</v>
       </c>
       <c r="E216" t="n">
-        <v>174.5800018310547</v>
+        <v>174.8699951171875</v>
       </c>
       <c r="F216" t="n">
-        <v>6357800</v>
+        <v>3342900</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B217" t="n">
-        <v>171.1349945068359</v>
+        <v>172.7700042724609</v>
       </c>
       <c r="C217" t="n">
-        <v>176.4100036621094</v>
+        <v>179.4799957275391</v>
       </c>
       <c r="D217" t="n">
-        <v>170</v>
+        <v>172.7700042724609</v>
       </c>
       <c r="E217" t="n">
-        <v>174.8699951171875</v>
+        <v>176.6100006103516</v>
       </c>
       <c r="F217" t="n">
-        <v>3342900</v>
+        <v>4338800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B218" t="n">
-        <v>172.7700042724609</v>
+        <v>174</v>
       </c>
       <c r="C218" t="n">
-        <v>179.4799957275391</v>
+        <v>177.5130004882812</v>
       </c>
       <c r="D218" t="n">
-        <v>172.7700042724609</v>
+        <v>170.9089965820312</v>
       </c>
       <c r="E218" t="n">
-        <v>176.6100006103516</v>
+        <v>173.9900054931641</v>
       </c>
       <c r="F218" t="n">
-        <v>4338800</v>
+        <v>4721500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B219" t="n">
-        <v>174</v>
+        <v>175.2100067138672</v>
       </c>
       <c r="C219" t="n">
-        <v>177.5130004882812</v>
+        <v>176.7299957275391</v>
       </c>
       <c r="D219" t="n">
-        <v>170.9089965820312</v>
+        <v>165.8999938964844</v>
       </c>
       <c r="E219" t="n">
-        <v>173.9900054931641</v>
+        <v>170.7599945068359</v>
       </c>
       <c r="F219" t="n">
-        <v>4721500</v>
+        <v>6023000</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B220" t="n">
-        <v>175.2100067138672</v>
+        <v>165.5700073242188</v>
       </c>
       <c r="C220" t="n">
-        <v>176.7299957275391</v>
+        <v>169.9700012207031</v>
       </c>
       <c r="D220" t="n">
-        <v>165.8999938964844</v>
+        <v>159.2700042724609</v>
       </c>
       <c r="E220" t="n">
-        <v>170.7599945068359</v>
+        <v>169.7100067138672</v>
       </c>
       <c r="F220" t="n">
-        <v>6023000</v>
+        <v>8561600</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B221" t="n">
-        <v>165.5700073242188</v>
+        <v>168.4499969482422</v>
       </c>
       <c r="C221" t="n">
-        <v>169.9700012207031</v>
+        <v>169.3300018310547</v>
       </c>
       <c r="D221" t="n">
-        <v>159.2700042724609</v>
+        <v>156.8399963378906</v>
       </c>
       <c r="E221" t="n">
-        <v>169.7100067138672</v>
+        <v>157.9700012207031</v>
       </c>
       <c r="F221" t="n">
-        <v>8561600</v>
+        <v>8189500</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B222" t="n">
-        <v>168.4499969482422</v>
+        <v>164.5599975585938</v>
       </c>
       <c r="C222" t="n">
-        <v>169.3300018310547</v>
+        <v>171.5099945068359</v>
       </c>
       <c r="D222" t="n">
-        <v>156.8399963378906</v>
+        <v>164.4850006103516</v>
       </c>
       <c r="E222" t="n">
-        <v>157.9700012207031</v>
+        <v>171.0200042724609</v>
       </c>
       <c r="F222" t="n">
-        <v>8189500</v>
+        <v>7284700</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B223" t="n">
-        <v>164.5599975585938</v>
+        <v>177.6000061035156</v>
       </c>
       <c r="C223" t="n">
-        <v>171.5099945068359</v>
+        <v>183.5200042724609</v>
       </c>
       <c r="D223" t="n">
-        <v>164.4850006103516</v>
+        <v>175.6999969482422</v>
       </c>
       <c r="E223" t="n">
-        <v>171.0200042724609</v>
+        <v>180.3500061035156</v>
       </c>
       <c r="F223" t="n">
-        <v>7284700</v>
+        <v>8472300</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B224" t="n">
-        <v>177.6000061035156</v>
+        <v>174.4199981689453</v>
       </c>
       <c r="C224" t="n">
-        <v>183.5200042724609</v>
+        <v>186.5700073242188</v>
       </c>
       <c r="D224" t="n">
-        <v>175.6999969482422</v>
+        <v>173.4499969482422</v>
       </c>
       <c r="E224" t="n">
-        <v>180.3500061035156</v>
+        <v>184.8899993896484</v>
       </c>
       <c r="F224" t="n">
-        <v>8472300</v>
+        <v>8335700</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B225" t="n">
-        <v>174.4199981689453</v>
+        <v>187.6999969482422</v>
       </c>
       <c r="C225" t="n">
-        <v>186.5700073242188</v>
+        <v>194.3500061035156</v>
       </c>
       <c r="D225" t="n">
-        <v>173.4499969482422</v>
+        <v>187.0110015869141</v>
       </c>
       <c r="E225" t="n">
-        <v>184.8899993896484</v>
+        <v>190.5099945068359</v>
       </c>
       <c r="F225" t="n">
-        <v>8335700</v>
+        <v>14097400</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B226" t="n">
-        <v>187.6999969482422</v>
+        <v>210.1900024414062</v>
       </c>
       <c r="C226" t="n">
-        <v>194.3500061035156</v>
+        <v>214.8899993896484</v>
       </c>
       <c r="D226" t="n">
-        <v>187.0110015869141</v>
+        <v>191.0099945068359</v>
       </c>
       <c r="E226" t="n">
-        <v>190.5099945068359</v>
+        <v>197.3099975585938</v>
       </c>
       <c r="F226" t="n">
-        <v>14097400</v>
+        <v>20227000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B227" t="n">
-        <v>210.1900024414062</v>
+        <v>192.4100036621094</v>
       </c>
       <c r="C227" t="n">
-        <v>214.8899993896484</v>
+        <v>197.1100006103516</v>
       </c>
       <c r="D227" t="n">
-        <v>191.0099945068359</v>
+        <v>189.4299926757812</v>
       </c>
       <c r="E227" t="n">
-        <v>197.3099975585938</v>
+        <v>192.3200073242188</v>
       </c>
       <c r="F227" t="n">
-        <v>20227000</v>
+        <v>7774600</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B228" t="n">
-        <v>192.4100036621094</v>
+        <v>198</v>
       </c>
       <c r="C228" t="n">
-        <v>197.1100006103516</v>
+        <v>198</v>
       </c>
       <c r="D228" t="n">
-        <v>189.4299926757812</v>
+        <v>187.5</v>
       </c>
       <c r="E228" t="n">
-        <v>192.3200073242188</v>
+        <v>188.6699981689453</v>
       </c>
       <c r="F228" t="n">
-        <v>7774600</v>
+        <v>7208500</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B229" t="n">
-        <v>198</v>
+        <v>192.4900054931641</v>
       </c>
       <c r="C229" t="n">
-        <v>198</v>
+        <v>195.6999969482422</v>
       </c>
       <c r="D229" t="n">
-        <v>187.5</v>
+        <v>187.0299987792969</v>
       </c>
       <c r="E229" t="n">
-        <v>188.6699981689453</v>
+        <v>191.5200042724609</v>
       </c>
       <c r="F229" t="n">
-        <v>7208500</v>
+        <v>5434100</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B230" t="n">
-        <v>192.4900054931641</v>
+        <v>194.5650024414062</v>
       </c>
       <c r="C230" t="n">
-        <v>195.6999969482422</v>
+        <v>198.9199981689453</v>
       </c>
       <c r="D230" t="n">
-        <v>187.0299987792969</v>
+        <v>190.4799957275391</v>
       </c>
       <c r="E230" t="n">
-        <v>191.5200042724609</v>
+        <v>197.8500061035156</v>
       </c>
       <c r="F230" t="n">
-        <v>5434100</v>
+        <v>6277300</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B231" t="n">
-        <v>194.5650024414062</v>
+        <v>205.4700012207031</v>
       </c>
       <c r="C231" t="n">
-        <v>198.9199981689453</v>
+        <v>211.4499969482422</v>
       </c>
       <c r="D231" t="n">
-        <v>190.4799957275391</v>
+        <v>203.7599945068359</v>
       </c>
       <c r="E231" t="n">
-        <v>197.8500061035156</v>
+        <v>210.5</v>
       </c>
       <c r="F231" t="n">
-        <v>6277300</v>
+        <v>10008600</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B232" t="n">
-        <v>205.4700012207031</v>
+        <v>209.7899932861328</v>
       </c>
       <c r="C232" t="n">
-        <v>211.4499969482422</v>
+        <v>210.1100006103516</v>
       </c>
       <c r="D232" t="n">
-        <v>203.7599945068359</v>
+        <v>203.5500030517578</v>
       </c>
       <c r="E232" t="n">
-        <v>210.5</v>
+        <v>203.6199951171875</v>
       </c>
       <c r="F232" t="n">
-        <v>10008600</v>
+        <v>7907800</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B233" t="n">
-        <v>209.7899932861328</v>
+        <v>205.2700042724609</v>
       </c>
       <c r="C233" t="n">
-        <v>210.1100006103516</v>
+        <v>205.2700042724609</v>
       </c>
       <c r="D233" t="n">
-        <v>203.5500030517578</v>
+        <v>198.2449951171875</v>
       </c>
       <c r="E233" t="n">
-        <v>203.6199951171875</v>
+        <v>198.8200073242188</v>
       </c>
       <c r="F233" t="n">
-        <v>7907800</v>
+        <v>4707400</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B234" t="n">
-        <v>205.2700042724609</v>
+        <v>201.1600036621094</v>
       </c>
       <c r="C234" t="n">
-        <v>205.2700042724609</v>
+        <v>202.2649993896484</v>
       </c>
       <c r="D234" t="n">
-        <v>198.2449951171875</v>
+        <v>198.3399963378906</v>
       </c>
       <c r="E234" t="n">
-        <v>198.8200073242188</v>
+        <v>201.8000030517578</v>
       </c>
       <c r="F234" t="n">
-        <v>4707400</v>
+        <v>5683900</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B235" t="n">
-        <v>201.1600036621094</v>
+        <v>196</v>
       </c>
       <c r="C235" t="n">
-        <v>202.2649993896484</v>
+        <v>197.9900054931641</v>
       </c>
       <c r="D235" t="n">
-        <v>198.3399963378906</v>
+        <v>189.6699981689453</v>
       </c>
       <c r="E235" t="n">
-        <v>201.8000030517578</v>
+        <v>193.1799926757812</v>
       </c>
       <c r="F235" t="n">
-        <v>5683900</v>
+        <v>8886900</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B236" t="n">
-        <v>196</v>
+        <v>195.0399932861328</v>
       </c>
       <c r="C236" t="n">
-        <v>197.9900054931641</v>
+        <v>195.5</v>
       </c>
       <c r="D236" t="n">
-        <v>189.6699981689453</v>
+        <v>184.5099945068359</v>
       </c>
       <c r="E236" t="n">
-        <v>193.1799926757812</v>
+        <v>186.4499969482422</v>
       </c>
       <c r="F236" t="n">
-        <v>8886900</v>
+        <v>5740500</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B237" t="n">
-        <v>195.0399932861328</v>
+        <v>185.3099975585938</v>
       </c>
       <c r="C237" t="n">
-        <v>195.5</v>
+        <v>187.2799987792969</v>
       </c>
       <c r="D237" t="n">
-        <v>184.5099945068359</v>
+        <v>182.8300018310547</v>
       </c>
       <c r="E237" t="n">
-        <v>186.4499969482422</v>
+        <v>183.75</v>
       </c>
       <c r="F237" t="n">
-        <v>5740500</v>
+        <v>4207300</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B238" t="n">
-        <v>185.3099975585938</v>
+        <v>183.7700042724609</v>
       </c>
       <c r="C238" t="n">
-        <v>187.2799987792969</v>
+        <v>190.4400024414062</v>
       </c>
       <c r="D238" t="n">
-        <v>182.8300018310547</v>
+        <v>183.5899963378906</v>
       </c>
       <c r="E238" t="n">
-        <v>183.75</v>
+        <v>188.6499938964844</v>
       </c>
       <c r="F238" t="n">
-        <v>4207300</v>
+        <v>8123600</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B239" t="n">
-        <v>183.7700042724609</v>
+        <v>186</v>
       </c>
       <c r="C239" t="n">
-        <v>190.4400024414062</v>
+        <v>190.25</v>
       </c>
       <c r="D239" t="n">
-        <v>183.5899963378906</v>
+        <v>186</v>
       </c>
       <c r="E239" t="n">
-        <v>188.6499938964844</v>
+        <v>188.1499938964844</v>
       </c>
       <c r="F239" t="n">
-        <v>8123600</v>
+        <v>5306400</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B240" t="n">
-        <v>186</v>
+        <v>192.3399963378906</v>
       </c>
       <c r="C240" t="n">
-        <v>190.25</v>
+        <v>193.1499938964844</v>
       </c>
       <c r="D240" t="n">
-        <v>186</v>
+        <v>188.0599975585938</v>
       </c>
       <c r="E240" t="n">
-        <v>188.1499938964844</v>
+        <v>190.9400024414062</v>
       </c>
       <c r="F240" t="n">
-        <v>5306400</v>
+        <v>4385100</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B241" t="n">
-        <v>192.3399963378906</v>
+        <v>190.9049987792969</v>
       </c>
       <c r="C241" t="n">
-        <v>193.1499938964844</v>
+        <v>203.3600006103516</v>
       </c>
       <c r="D241" t="n">
-        <v>188.0599975585938</v>
+        <v>190.9049987792969</v>
       </c>
       <c r="E241" t="n">
-        <v>190.9400024414062</v>
+        <v>202.25</v>
       </c>
       <c r="F241" t="n">
-        <v>4385100</v>
+        <v>7664600</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B242" t="n">
-        <v>190.9049987792969</v>
+        <v>205.8999938964844</v>
       </c>
       <c r="C242" t="n">
-        <v>203.3600006103516</v>
+        <v>206.1300048828125</v>
       </c>
       <c r="D242" t="n">
-        <v>190.9049987792969</v>
+        <v>199.2149963378906</v>
       </c>
       <c r="E242" t="n">
-        <v>202.25</v>
+        <v>201.0899963378906</v>
       </c>
       <c r="F242" t="n">
-        <v>7664600</v>
+        <v>4692700</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B243" t="n">
-        <v>205.8999938964844</v>
+        <v>200</v>
       </c>
       <c r="C243" t="n">
-        <v>206.1300048828125</v>
+        <v>200.1000061035156</v>
       </c>
       <c r="D243" t="n">
-        <v>199.2149963378906</v>
+        <v>194.6100006103516</v>
       </c>
       <c r="E243" t="n">
-        <v>201.0899963378906</v>
+        <v>195.3800048828125</v>
       </c>
       <c r="F243" t="n">
-        <v>4692700</v>
+        <v>3063000</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B244" t="n">
-        <v>200</v>
+        <v>195.5</v>
       </c>
       <c r="C244" t="n">
-        <v>200.1000061035156</v>
+        <v>197.9900054931641</v>
       </c>
       <c r="D244" t="n">
-        <v>194.6100006103516</v>
+        <v>193.9100036621094</v>
       </c>
       <c r="E244" t="n">
-        <v>195.3800048828125</v>
+        <v>195.6900024414062</v>
       </c>
       <c r="F244" t="n">
-        <v>3063000</v>
+        <v>5021700</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B245" t="n">
-        <v>195.5</v>
+        <v>195.7700042724609</v>
       </c>
       <c r="C245" t="n">
-        <v>197.9900054931641</v>
+        <v>196.5</v>
       </c>
       <c r="D245" t="n">
-        <v>193.9100036621094</v>
+        <v>188.5599975585938</v>
       </c>
       <c r="E245" t="n">
-        <v>195.6900024414062</v>
+        <v>189.2599945068359</v>
       </c>
       <c r="F245" t="n">
-        <v>5021700</v>
+        <v>4369200</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B246" t="n">
-        <v>195.7700042724609</v>
+        <v>188</v>
       </c>
       <c r="C246" t="n">
-        <v>196.5</v>
+        <v>189.8899993896484</v>
       </c>
       <c r="D246" t="n">
-        <v>188.5599975585938</v>
+        <v>184.0800018310547</v>
       </c>
       <c r="E246" t="n">
-        <v>189.2599945068359</v>
+        <v>186.1000061035156</v>
       </c>
       <c r="F246" t="n">
-        <v>4369200</v>
+        <v>4363800</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B247" t="n">
-        <v>188</v>
+        <v>185.25</v>
       </c>
       <c r="C247" t="n">
-        <v>189.8899993896484</v>
+        <v>192</v>
       </c>
       <c r="D247" t="n">
-        <v>184.0800018310547</v>
+        <v>181.2700042724609</v>
       </c>
       <c r="E247" t="n">
-        <v>186.1000061035156</v>
+        <v>191.4400024414062</v>
       </c>
       <c r="F247" t="n">
-        <v>4363800</v>
+        <v>4108500</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B248" t="n">
-        <v>185.25</v>
+        <v>192.8200073242188</v>
       </c>
       <c r="C248" t="n">
-        <v>192</v>
+        <v>197.1000061035156</v>
       </c>
       <c r="D248" t="n">
-        <v>181.2700042724609</v>
+        <v>190.5599975585938</v>
       </c>
       <c r="E248" t="n">
-        <v>191.4400024414062</v>
+        <v>193.7799987792969</v>
       </c>
       <c r="F248" t="n">
-        <v>4108500</v>
+        <v>4204100</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B249" t="n">
-        <v>192.8200073242188</v>
+        <v>196.8200073242188</v>
       </c>
       <c r="C249" t="n">
-        <v>197.1000061035156</v>
+        <v>200.6750030517578</v>
       </c>
       <c r="D249" t="n">
-        <v>190.5599975585938</v>
+        <v>194.7200012207031</v>
       </c>
       <c r="E249" t="n">
-        <v>193.7799987792969</v>
+        <v>194.9600067138672</v>
       </c>
       <c r="F249" t="n">
-        <v>4204100</v>
+        <v>4741600</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B250" t="n">
-        <v>196.8200073242188</v>
+        <v>194.8549957275391</v>
       </c>
       <c r="C250" t="n">
-        <v>200.6750030517578</v>
+        <v>196.9600067138672</v>
       </c>
       <c r="D250" t="n">
-        <v>194.7200012207031</v>
+        <v>192.0500030517578</v>
       </c>
       <c r="E250" t="n">
-        <v>194.9600067138672</v>
+        <v>192.9299926757812</v>
       </c>
       <c r="F250" t="n">
-        <v>4741600</v>
+        <v>3673900</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B251" t="n">
-        <v>194.8549957275391</v>
+        <v>189.3500061035156</v>
       </c>
       <c r="C251" t="n">
-        <v>196.9600067138672</v>
+        <v>193.0399932861328</v>
       </c>
       <c r="D251" t="n">
-        <v>192.0500030517578</v>
+        <v>187.8930053710938</v>
       </c>
       <c r="E251" t="n">
-        <v>192.9299926757812</v>
+        <v>188.9900054931641</v>
       </c>
       <c r="F251" t="n">
-        <v>3673900</v>
+        <v>2810900</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B252" t="n">
-        <v>189.3500061035156</v>
+        <v>192.2299957275391</v>
       </c>
       <c r="C252" t="n">
-        <v>193.0399932861328</v>
+        <v>200.25</v>
       </c>
       <c r="D252" t="n">
-        <v>187.8930053710938</v>
+        <v>192.1049957275391</v>
       </c>
       <c r="E252" t="n">
-        <v>188.9900054931641</v>
+        <v>199.5899963378906</v>
       </c>
       <c r="F252" t="n">
-        <v>2810900</v>
+        <v>4638000</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10518,37 +10518,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>199.59</v>
+      </c>
+      <c r="D2" t="n">
         <v>188.99</v>
       </c>
-      <c r="D2" t="n">
-        <v>192.93</v>
-      </c>
       <c r="E2" t="n">
-        <v>189.35</v>
+        <v>192.23</v>
       </c>
       <c r="F2" t="n">
-        <v>193.04</v>
+        <v>200.2192</v>
       </c>
       <c r="G2" t="n">
-        <v>187.8926</v>
+        <v>192.105</v>
       </c>
       <c r="H2" t="n">
-        <v>2808298</v>
+        <v>4636420</v>
       </c>
       <c r="I2" t="n">
-        <v>7366708</v>
+        <v>7270412</v>
       </c>
       <c r="J2" t="n">
-        <v>238358855680</v>
+        <v>251727839232</v>
       </c>
       <c r="K2" t="n">
-        <v>60.96452</v>
+        <v>63.3619</v>
       </c>
       <c r="L2" t="n">
-        <v>36.62398</v>
+        <v>38.67813</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="N2" t="n">
         <v>214.89</v>
@@ -10588,7 +10588,7 @@
         <v>11.733</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.107561</v>
+        <v>17.010994</v>
       </c>
       <c r="Z2" t="n">
         <v>0.357</v>
@@ -10600,7 +10600,7 @@
         <v>10540800000</v>
       </c>
       <c r="AC2" t="n">
-        <v>225015545856</v>
+        <v>238384529408</v>
       </c>
       <c r="AD2" t="n">
         <v>4639600128</v>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:03:59</t>
+          <t>2026-09-12 21:48:00</t>
         </is>
       </c>
     </row>
